--- a/results_(stress_test)_summary/summary.xlsx
+++ b/results_(stress_test)_summary/summary.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\RnD_Repo\Research_Engineeirng\feature_fusion_PCCxSigmoid-PLV-\results_cnn_subnetwork_evaluation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\RnD_Repo\Research_Engineeirng\feature_fusion_PCCxSigmoid-PLV-\results_(stress_test)_summary\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AFB12DF-A583-4AEC-AD58-C902FC721171}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -366,7 +366,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -536,59 +536,10 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -597,16 +548,57 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -964,10 +956,10 @@
       <c r="V1" s="12"/>
     </row>
     <row r="2" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="59" t="s">
+      <c r="A2" s="83" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="60"/>
+      <c r="B2" s="84"/>
       <c r="C2" s="20">
         <v>93.101364775358491</v>
       </c>
@@ -1001,10 +993,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C2:I2)&amp;","</f>
         <v xml:space="preserve">    93.1013647753585, 91.3266637254648, 89.7225610371485, 83.857204647099, 76.2429490451186, 60.4027774173364, 47.7409002961387,</v>
       </c>
-      <c r="M2" s="59" t="s">
+      <c r="M2" s="83" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="60"/>
+      <c r="N2" s="84"/>
       <c r="O2" s="37">
         <v>3.4649270444699574</v>
       </c>
@@ -1032,10 +1024,10 @@
       </c>
     </row>
     <row r="3" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="59" t="s">
+      <c r="A3" s="83" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="60"/>
+      <c r="B3" s="84"/>
       <c r="C3" s="37">
         <v>93.273358766079312</v>
       </c>
@@ -1069,10 +1061,10 @@
         <f t="shared" ref="L3:L4" si="0">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C3:I3)&amp;","</f>
         <v xml:space="preserve">    93.2733587660793, 91.6155877934354, 90.6205330495939, 86.5975138193237, 78.2243502683126, 60.8549929786013, 48.7439337710534,</v>
       </c>
-      <c r="M3" s="59" t="s">
+      <c r="M3" s="83" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="60"/>
+      <c r="N3" s="84"/>
       <c r="O3" s="37">
         <v>3.4672469457762647</v>
       </c>
@@ -1100,10 +1092,10 @@
       </c>
     </row>
     <row r="4" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="59" t="s">
+      <c r="A4" s="83" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="60"/>
+      <c r="B4" s="84"/>
       <c r="C4" s="24">
         <v>87.593900000000005</v>
       </c>
@@ -1137,10 +1129,10 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    87.5939, 87.6637168141593, 88.1120943952802, 87.9700256922638, 87.4617081462642, 75.2513631894163, 47.7206838582802,</v>
       </c>
-      <c r="M4" s="59" t="s">
+      <c r="M4" s="83" t="s">
         <v>10</v>
       </c>
-      <c r="N4" s="60"/>
+      <c r="N4" s="84"/>
       <c r="O4" s="55">
         <v>2.4529187882918819</v>
       </c>
@@ -1168,31 +1160,31 @@
       </c>
     </row>
     <row r="5" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="59" t="s">
+      <c r="A5" s="83" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="61"/>
-      <c r="C5" s="61"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="61"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="61"/>
-      <c r="H5" s="61"/>
-      <c r="I5" s="60"/>
+      <c r="B5" s="85"/>
+      <c r="C5" s="85"/>
+      <c r="D5" s="85"/>
+      <c r="E5" s="85"/>
+      <c r="F5" s="85"/>
+      <c r="G5" s="85"/>
+      <c r="H5" s="85"/>
+      <c r="I5" s="84"/>
       <c r="J5" s="41"/>
       <c r="K5" s="41"/>
       <c r="L5" s="12"/>
-      <c r="M5" s="59" t="s">
+      <c r="M5" s="83" t="s">
         <v>14</v>
       </c>
-      <c r="N5" s="61"/>
-      <c r="O5" s="61"/>
-      <c r="P5" s="61"/>
-      <c r="Q5" s="61"/>
-      <c r="R5" s="61"/>
-      <c r="S5" s="61"/>
-      <c r="T5" s="61"/>
-      <c r="U5" s="60"/>
+      <c r="N5" s="85"/>
+      <c r="O5" s="85"/>
+      <c r="P5" s="85"/>
+      <c r="Q5" s="85"/>
+      <c r="R5" s="85"/>
+      <c r="S5" s="85"/>
+      <c r="T5" s="85"/>
+      <c r="U5" s="84"/>
       <c r="V5" s="12"/>
     </row>
     <row r="6" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -1340,38 +1332,38 @@
       </c>
     </row>
     <row r="8" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="59" t="s">
+      <c r="A8" s="83" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="61"/>
-      <c r="C8" s="64"/>
-      <c r="D8" s="64"/>
-      <c r="E8" s="64"/>
-      <c r="F8" s="64"/>
-      <c r="G8" s="64"/>
-      <c r="H8" s="64"/>
-      <c r="I8" s="63"/>
+      <c r="B8" s="85"/>
+      <c r="C8" s="90"/>
+      <c r="D8" s="90"/>
+      <c r="E8" s="90"/>
+      <c r="F8" s="90"/>
+      <c r="G8" s="90"/>
+      <c r="H8" s="90"/>
+      <c r="I8" s="89"/>
       <c r="J8" s="41"/>
       <c r="K8" s="41"/>
       <c r="L8" s="12"/>
-      <c r="M8" s="59" t="s">
+      <c r="M8" s="83" t="s">
         <v>22</v>
       </c>
-      <c r="N8" s="61"/>
-      <c r="O8" s="64"/>
-      <c r="P8" s="64"/>
-      <c r="Q8" s="64"/>
-      <c r="R8" s="64"/>
-      <c r="S8" s="64"/>
-      <c r="T8" s="64"/>
-      <c r="U8" s="63"/>
+      <c r="N8" s="85"/>
+      <c r="O8" s="90"/>
+      <c r="P8" s="90"/>
+      <c r="Q8" s="90"/>
+      <c r="R8" s="90"/>
+      <c r="S8" s="90"/>
+      <c r="T8" s="90"/>
+      <c r="U8" s="89"/>
       <c r="V8" s="12"/>
     </row>
     <row r="9" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="59" t="s">
+      <c r="A9" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="60"/>
+      <c r="B9" s="84"/>
       <c r="C9" s="37">
         <v>93.782740335124032</v>
       </c>
@@ -1405,10 +1397,10 @@
         <f t="shared" ref="L9:L12" si="4">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C9:I9)&amp;","</f>
         <v xml:space="preserve">    93.782740335124, 91.9482088945406, 90.212980504445, 84.6303889595354, 75.3710931755465, 59.6272113080563, 47.8441855033348,</v>
       </c>
-      <c r="M9" s="59" t="s">
+      <c r="M9" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="N9" s="60"/>
+      <c r="N9" s="84"/>
       <c r="O9" s="37">
         <v>3.5391983918820551</v>
       </c>
@@ -1436,26 +1428,26 @@
       </c>
     </row>
     <row r="10" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="62" t="s">
+      <c r="A10" s="88" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="63"/>
+      <c r="B10" s="89"/>
       <c r="C10" s="40">
         <v>93.226230330712227</v>
       </c>
-      <c r="D10" s="93">
+      <c r="D10" s="41">
         <v>91.83329152212967</v>
       </c>
-      <c r="E10" s="93">
+      <c r="E10" s="41">
         <v>90.325291164571794</v>
       </c>
-      <c r="F10" s="93">
+      <c r="F10" s="41">
         <v>85.383492360083878</v>
       </c>
-      <c r="G10" s="93">
+      <c r="G10" s="41">
         <v>76.567000291236639</v>
       </c>
-      <c r="H10" s="93">
+      <c r="H10" s="41">
         <v>59.41454222499042</v>
       </c>
       <c r="I10" s="42">
@@ -1473,26 +1465,26 @@
         <f t="shared" si="4"/>
         <v xml:space="preserve">    93.2262303307122, 91.8332915221297, 90.3252911645718, 85.3834923600839, 76.5670002912366, 59.4145422249904, 50.5634074112521,</v>
       </c>
-      <c r="M10" s="59" t="s">
+      <c r="M10" s="83" t="s">
         <v>8</v>
       </c>
-      <c r="N10" s="60"/>
+      <c r="N10" s="84"/>
       <c r="O10" s="40">
         <v>3.945711842949601</v>
       </c>
-      <c r="P10" s="93">
+      <c r="P10" s="41">
         <v>4.8525950161134093</v>
       </c>
-      <c r="Q10" s="93">
+      <c r="Q10" s="41">
         <v>4.4346894499148144</v>
       </c>
-      <c r="R10" s="93">
+      <c r="R10" s="41">
         <v>5.4810029574676529</v>
       </c>
-      <c r="S10" s="93">
+      <c r="S10" s="41">
         <v>8.4636725644600066</v>
       </c>
-      <c r="T10" s="93">
+      <c r="T10" s="41">
         <v>10.788297692871961</v>
       </c>
       <c r="U10" s="42">
@@ -1504,26 +1496,26 @@
       </c>
     </row>
     <row r="11" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="59" t="s">
+      <c r="A11" s="83" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="60"/>
+      <c r="B11" s="84"/>
       <c r="C11" s="40">
         <v>93.004922187908207</v>
       </c>
-      <c r="D11" s="93">
+      <c r="D11" s="41">
         <v>91.518502178507859</v>
       </c>
-      <c r="E11" s="93">
+      <c r="E11" s="41">
         <v>89.729420958082102</v>
       </c>
-      <c r="F11" s="93">
+      <c r="F11" s="41">
         <v>83.348607398564567</v>
       </c>
-      <c r="G11" s="93">
+      <c r="G11" s="41">
         <v>74.087719905304837</v>
       </c>
-      <c r="H11" s="93">
+      <c r="H11" s="41">
         <v>57.917332041511322</v>
       </c>
       <c r="I11" s="42">
@@ -1541,26 +1533,26 @@
         <f t="shared" si="4"/>
         <v xml:space="preserve">    93.0049221879082, 91.5185021785079, 89.7294209580821, 83.3486073985646, 74.0877199053048, 57.9173320415113, 48.0077941850708,</v>
       </c>
-      <c r="M11" s="59" t="s">
+      <c r="M11" s="83" t="s">
         <v>23</v>
       </c>
-      <c r="N11" s="60"/>
+      <c r="N11" s="84"/>
       <c r="O11" s="40">
         <v>3.690401528555848</v>
       </c>
-      <c r="P11" s="93">
+      <c r="P11" s="41">
         <v>4.2469367469027457</v>
       </c>
-      <c r="Q11" s="93">
+      <c r="Q11" s="41">
         <v>4.4611096369834957</v>
       </c>
-      <c r="R11" s="93">
+      <c r="R11" s="41">
         <v>5.4089286426803449</v>
       </c>
-      <c r="S11" s="93">
+      <c r="S11" s="41">
         <v>9.092124974067179</v>
       </c>
-      <c r="T11" s="93">
+      <c r="T11" s="41">
         <v>10.83557708581068</v>
       </c>
       <c r="U11" s="42">
@@ -1572,10 +1564,10 @@
       </c>
     </row>
     <row r="12" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="59" t="s">
+      <c r="A12" s="83" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="60"/>
+      <c r="B12" s="84"/>
       <c r="C12" s="43">
         <v>93.123279613145442</v>
       </c>
@@ -1609,10 +1601,10 @@
         <f t="shared" si="4"/>
         <v xml:space="preserve">    93.1232796131454, 91.674385879924, 89.6986882816172, 84.9570671026566, 75.9390825180149, 59.9950922297482, 48.4403036935152,</v>
       </c>
-      <c r="M12" s="59" t="s">
+      <c r="M12" s="83" t="s">
         <v>24</v>
       </c>
-      <c r="N12" s="60"/>
+      <c r="N12" s="84"/>
       <c r="O12" s="43">
         <v>3.8088682011350912</v>
       </c>
@@ -1640,38 +1632,38 @@
       </c>
     </row>
     <row r="13" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="59" t="s">
+      <c r="A13" s="83" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="61"/>
-      <c r="C13" s="73"/>
-      <c r="D13" s="73"/>
-      <c r="E13" s="73"/>
-      <c r="F13" s="73"/>
-      <c r="G13" s="73"/>
-      <c r="H13" s="73"/>
-      <c r="I13" s="74"/>
+      <c r="B13" s="85"/>
+      <c r="C13" s="86"/>
+      <c r="D13" s="86"/>
+      <c r="E13" s="86"/>
+      <c r="F13" s="86"/>
+      <c r="G13" s="86"/>
+      <c r="H13" s="86"/>
+      <c r="I13" s="87"/>
       <c r="J13" s="41"/>
       <c r="K13" s="41"/>
       <c r="L13" s="12"/>
-      <c r="M13" s="59" t="s">
+      <c r="M13" s="83" t="s">
         <v>25</v>
       </c>
-      <c r="N13" s="61"/>
-      <c r="O13" s="73"/>
-      <c r="P13" s="73"/>
-      <c r="Q13" s="73"/>
-      <c r="R13" s="73"/>
-      <c r="S13" s="73"/>
-      <c r="T13" s="73"/>
-      <c r="U13" s="74"/>
+      <c r="N13" s="85"/>
+      <c r="O13" s="86"/>
+      <c r="P13" s="86"/>
+      <c r="Q13" s="86"/>
+      <c r="R13" s="86"/>
+      <c r="S13" s="86"/>
+      <c r="T13" s="86"/>
+      <c r="U13" s="87"/>
       <c r="V13" s="12"/>
     </row>
     <row r="14" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="59" t="s">
+      <c r="A14" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="60"/>
+      <c r="B14" s="84"/>
       <c r="C14" s="37">
         <v>92.969518190757128</v>
       </c>
@@ -1705,10 +1697,10 @@
         <f t="shared" ref="L14:L17" si="6">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C14:I14)&amp;","</f>
         <v xml:space="preserve">    92.9695181907571, 91.8515240904621, 90.756145526057, 87.2531365611583, 81.1789721364371, 57.3869295293788, 44.8554428094822,</v>
       </c>
-      <c r="M14" s="59" t="s">
+      <c r="M14" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="N14" s="60"/>
+      <c r="N14" s="84"/>
       <c r="O14" s="37">
         <v>3.3991921823554931</v>
       </c>
@@ -1736,26 +1728,26 @@
       </c>
     </row>
     <row r="15" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="62" t="s">
+      <c r="A15" s="88" t="s">
         <v>8</v>
       </c>
-      <c r="B15" s="63"/>
+      <c r="B15" s="89"/>
       <c r="C15" s="40">
         <v>91.898721730580135</v>
       </c>
-      <c r="D15" s="93">
+      <c r="D15" s="41">
         <v>90.765995668936</v>
       </c>
-      <c r="E15" s="93">
+      <c r="E15" s="41">
         <v>89.705268500015848</v>
       </c>
-      <c r="F15" s="93">
+      <c r="F15" s="41">
         <v>87.959685349065893</v>
       </c>
-      <c r="G15" s="93">
+      <c r="G15" s="41">
         <v>85.750000720882824</v>
       </c>
-      <c r="H15" s="93">
+      <c r="H15" s="41">
         <v>71.387388010853613</v>
       </c>
       <c r="I15" s="42">
@@ -1773,26 +1765,26 @@
         <f t="shared" si="6"/>
         <v xml:space="preserve">    91.8987217305801, 90.765995668936, 89.7052685000158, 87.9596853490659, 85.7500007208828, 71.3873880108536, 45.5963431056209,</v>
       </c>
-      <c r="M15" s="59" t="s">
+      <c r="M15" s="83" t="s">
         <v>8</v>
       </c>
-      <c r="N15" s="60"/>
+      <c r="N15" s="84"/>
       <c r="O15" s="40">
         <v>3.190312271555559</v>
       </c>
-      <c r="P15" s="93">
+      <c r="P15" s="41">
         <v>2.8828036064622768</v>
       </c>
-      <c r="Q15" s="93">
+      <c r="Q15" s="41">
         <v>2.5884740771146331</v>
       </c>
-      <c r="R15" s="93">
+      <c r="R15" s="41">
         <v>2.6213450470877251</v>
       </c>
-      <c r="S15" s="93">
+      <c r="S15" s="41">
         <v>3.203569989687661</v>
       </c>
-      <c r="T15" s="93">
+      <c r="T15" s="41">
         <v>4.756712112750666</v>
       </c>
       <c r="U15" s="42">
@@ -1804,26 +1796,26 @@
       </c>
     </row>
     <row r="16" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="59" t="s">
+      <c r="A16" s="83" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="60"/>
+      <c r="B16" s="84"/>
       <c r="C16" s="40">
         <v>93.044276622923505</v>
       </c>
-      <c r="D16" s="93">
+      <c r="D16" s="41">
         <v>91.935155148400938</v>
       </c>
-      <c r="E16" s="93">
+      <c r="E16" s="41">
         <v>90.94889229145582</v>
       </c>
-      <c r="F16" s="93">
+      <c r="F16" s="41">
         <v>85.952505356159378</v>
       </c>
-      <c r="G16" s="93">
+      <c r="G16" s="41">
         <v>78.915183810701947</v>
       </c>
-      <c r="H16" s="93">
+      <c r="H16" s="41">
         <v>59.442100133507502</v>
       </c>
       <c r="I16" s="42">
@@ -1841,26 +1833,26 @@
         <f t="shared" si="6"/>
         <v xml:space="preserve">    93.0442766229235, 91.9351551484009, 90.9488922914558, 85.9525053561594, 78.9151838107019, 59.4421001335075, 49.5338281473023,</v>
       </c>
-      <c r="M16" s="59" t="s">
+      <c r="M16" s="83" t="s">
         <v>23</v>
       </c>
-      <c r="N16" s="60"/>
+      <c r="N16" s="84"/>
       <c r="O16" s="40">
         <v>3.72078192123604</v>
       </c>
-      <c r="P16" s="93">
+      <c r="P16" s="41">
         <v>4.0467152776216686</v>
       </c>
-      <c r="Q16" s="93">
+      <c r="Q16" s="41">
         <v>4.0235763627769954</v>
       </c>
-      <c r="R16" s="93">
+      <c r="R16" s="41">
         <v>4.4767633212331157</v>
       </c>
-      <c r="S16" s="93">
+      <c r="S16" s="41">
         <v>7.2019016527503927</v>
       </c>
-      <c r="T16" s="93">
+      <c r="T16" s="41">
         <v>10.04668436860082</v>
       </c>
       <c r="U16" s="42">
@@ -1872,10 +1864,10 @@
       </c>
     </row>
     <row r="17" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="59" t="s">
+      <c r="A17" s="83" t="s">
         <v>24</v>
       </c>
-      <c r="B17" s="60"/>
+      <c r="B17" s="84"/>
       <c r="C17" s="43">
         <v>93.174110502686005</v>
       </c>
@@ -1909,10 +1901,10 @@
         <f t="shared" si="6"/>
         <v xml:space="preserve">    93.174110502686, 91.3917248419104, 89.5915391424955, 84.6905970928238, 76.4013471858177, 59.9636675057743, 47.7255772108755,</v>
       </c>
-      <c r="M17" s="59" t="s">
+      <c r="M17" s="83" t="s">
         <v>24</v>
       </c>
-      <c r="N17" s="60"/>
+      <c r="N17" s="84"/>
       <c r="O17" s="43">
         <v>3.8766021792735019</v>
       </c>
@@ -2022,10 +2014,10 @@
       <c r="V19" s="1"/>
     </row>
     <row r="20" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="65" t="s">
+      <c r="A20" s="75" t="s">
         <v>5</v>
       </c>
-      <c r="B20" s="66"/>
+      <c r="B20" s="76"/>
       <c r="C20" s="47">
         <v>92.567111769713335</v>
       </c>
@@ -2053,10 +2045,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C20:I20)&amp;","</f>
         <v xml:space="preserve">    92.5671117697133, 90.8358586083436, 89.2175053395332, 83.2372459642881, 75.380430844191, 58.9943671875974, 43.6225356413822,</v>
       </c>
-      <c r="M20" s="65" t="s">
+      <c r="M20" s="75" t="s">
         <v>5</v>
       </c>
-      <c r="N20" s="66"/>
+      <c r="N20" s="76"/>
       <c r="O20" s="46">
         <v>3.88093621561358</v>
       </c>
@@ -2084,10 +2076,10 @@
       </c>
     </row>
     <row r="21" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="65" t="s">
+      <c r="A21" s="75" t="s">
         <v>6</v>
       </c>
-      <c r="B21" s="66"/>
+      <c r="B21" s="76"/>
       <c r="C21" s="47">
         <v>92.866950218042462</v>
       </c>
@@ -2115,10 +2107,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C21:I21)&amp;","</f>
         <v xml:space="preserve">    92.8669502180425, 91.2426907647456, 90.1370532276984, 86.0801529266134, 77.4102172551968, 59.6761947649801, 46.3954904194042,</v>
       </c>
-      <c r="M21" s="65" t="s">
+      <c r="M21" s="75" t="s">
         <v>6</v>
       </c>
-      <c r="N21" s="66"/>
+      <c r="N21" s="76"/>
       <c r="O21" s="47">
         <v>3.8319643020864191</v>
       </c>
@@ -2146,10 +2138,10 @@
       </c>
     </row>
     <row r="22" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="65" t="s">
+      <c r="A22" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="B22" s="66"/>
+      <c r="B22" s="76"/>
       <c r="C22" s="34">
         <v>87.268396410214976</v>
       </c>
@@ -2177,10 +2169,10 @@
         <f t="shared" ref="L22:L25" si="9">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C22:I22)&amp;","</f>
         <v xml:space="preserve">    87.268396410215, 87.2564283986868, 87.8221063041704, 87.6807264423516, 87.1448793671852, 74.9765678865158, 46.4175473948824,</v>
       </c>
-      <c r="M22" s="65" t="s">
+      <c r="M22" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="N22" s="66"/>
+      <c r="N22" s="76"/>
       <c r="O22" s="34">
         <v>2.610595868561878</v>
       </c>
@@ -2208,31 +2200,31 @@
       </c>
     </row>
     <row r="23" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="65" t="s">
+      <c r="A23" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="B23" s="67"/>
-      <c r="C23" s="67"/>
-      <c r="D23" s="67"/>
-      <c r="E23" s="67"/>
-      <c r="F23" s="67"/>
-      <c r="G23" s="67"/>
-      <c r="H23" s="67"/>
-      <c r="I23" s="66"/>
+      <c r="B23" s="79"/>
+      <c r="C23" s="79"/>
+      <c r="D23" s="79"/>
+      <c r="E23" s="79"/>
+      <c r="F23" s="79"/>
+      <c r="G23" s="79"/>
+      <c r="H23" s="79"/>
+      <c r="I23" s="76"/>
       <c r="J23" s="50"/>
       <c r="K23" s="50"/>
       <c r="L23" s="1"/>
-      <c r="M23" s="65" t="s">
+      <c r="M23" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="N23" s="67"/>
-      <c r="O23" s="67"/>
-      <c r="P23" s="67"/>
-      <c r="Q23" s="67"/>
-      <c r="R23" s="67"/>
-      <c r="S23" s="67"/>
-      <c r="T23" s="67"/>
-      <c r="U23" s="66"/>
+      <c r="N23" s="79"/>
+      <c r="O23" s="79"/>
+      <c r="P23" s="79"/>
+      <c r="Q23" s="79"/>
+      <c r="R23" s="79"/>
+      <c r="S23" s="79"/>
+      <c r="T23" s="79"/>
+      <c r="U23" s="76"/>
       <c r="V23" s="1"/>
     </row>
     <row r="24" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
@@ -2368,38 +2360,38 @@
       </c>
     </row>
     <row r="26" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="65" t="s">
+      <c r="A26" s="75" t="s">
         <v>22</v>
       </c>
-      <c r="B26" s="67"/>
-      <c r="C26" s="68"/>
-      <c r="D26" s="68"/>
-      <c r="E26" s="68"/>
-      <c r="F26" s="68"/>
-      <c r="G26" s="68"/>
-      <c r="H26" s="68"/>
-      <c r="I26" s="69"/>
+      <c r="B26" s="79"/>
+      <c r="C26" s="82"/>
+      <c r="D26" s="82"/>
+      <c r="E26" s="82"/>
+      <c r="F26" s="82"/>
+      <c r="G26" s="82"/>
+      <c r="H26" s="82"/>
+      <c r="I26" s="78"/>
       <c r="J26" s="50"/>
       <c r="K26" s="50"/>
       <c r="L26" s="1"/>
-      <c r="M26" s="65" t="s">
+      <c r="M26" s="75" t="s">
         <v>22</v>
       </c>
-      <c r="N26" s="67"/>
-      <c r="O26" s="68"/>
-      <c r="P26" s="68"/>
-      <c r="Q26" s="68"/>
-      <c r="R26" s="68"/>
-      <c r="S26" s="68"/>
-      <c r="T26" s="68"/>
-      <c r="U26" s="69"/>
+      <c r="N26" s="79"/>
+      <c r="O26" s="82"/>
+      <c r="P26" s="82"/>
+      <c r="Q26" s="82"/>
+      <c r="R26" s="82"/>
+      <c r="S26" s="82"/>
+      <c r="T26" s="82"/>
+      <c r="U26" s="78"/>
       <c r="V26" s="1"/>
     </row>
     <row r="27" spans="1:22" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="65" t="s">
+      <c r="A27" s="75" t="s">
         <v>7</v>
       </c>
-      <c r="B27" s="66"/>
+      <c r="B27" s="76"/>
       <c r="C27" s="46">
         <v>93.403798109785029</v>
       </c>
@@ -2427,10 +2419,10 @@
         <f t="shared" ref="L27:L30" si="10">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C27:I27)&amp;","</f>
         <v xml:space="preserve">    93.403798109785, 91.5170070049374, 89.7498804626893, 83.9973095811923, 74.3949629659869, 58.0955824704985, 44.4348127062073,</v>
       </c>
-      <c r="M27" s="65" t="s">
+      <c r="M27" s="75" t="s">
         <v>7</v>
       </c>
-      <c r="N27" s="66"/>
+      <c r="N27" s="76"/>
       <c r="O27" s="46">
         <v>3.9553866501853321</v>
       </c>
@@ -2458,26 +2450,26 @@
       </c>
     </row>
     <row r="28" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="65" t="s">
+      <c r="A28" s="75" t="s">
         <v>8</v>
       </c>
-      <c r="B28" s="66"/>
+      <c r="B28" s="76"/>
       <c r="C28" s="49">
         <v>92.778947400409621</v>
       </c>
-      <c r="D28" s="94">
+      <c r="D28" s="50">
         <v>91.450368996373655</v>
       </c>
-      <c r="E28" s="94">
+      <c r="E28" s="50">
         <v>89.879480954542075</v>
       </c>
-      <c r="F28" s="94">
+      <c r="F28" s="50">
         <v>84.748756470336986</v>
       </c>
-      <c r="G28" s="94">
+      <c r="G28" s="50">
         <v>75.627608782580538</v>
       </c>
-      <c r="H28" s="94">
+      <c r="H28" s="50">
         <v>58.300265665116903</v>
       </c>
       <c r="I28" s="51">
@@ -2489,26 +2481,26 @@
         <f t="shared" si="10"/>
         <v xml:space="preserve">    92.7789474004096, 91.4503689963737, 89.8794809545421, 84.748756470337, 75.6276087825805, 58.3002656651169, 48.5841064376263,</v>
       </c>
-      <c r="M28" s="65" t="s">
+      <c r="M28" s="75" t="s">
         <v>8</v>
       </c>
-      <c r="N28" s="66"/>
+      <c r="N28" s="76"/>
       <c r="O28" s="49">
         <v>4.3743918396131134</v>
       </c>
-      <c r="P28" s="94">
+      <c r="P28" s="50">
         <v>5.1779143655465321</v>
       </c>
-      <c r="Q28" s="94">
+      <c r="Q28" s="50">
         <v>4.8362705721377752</v>
       </c>
-      <c r="R28" s="94">
+      <c r="R28" s="50">
         <v>5.6797782301447892</v>
       </c>
-      <c r="S28" s="94">
+      <c r="S28" s="50">
         <v>9.0190902977959446</v>
       </c>
-      <c r="T28" s="94">
+      <c r="T28" s="50">
         <v>11.000258135261941</v>
       </c>
       <c r="U28" s="51">
@@ -2520,26 +2512,26 @@
       </c>
     </row>
     <row r="29" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="65" t="s">
+      <c r="A29" s="75" t="s">
         <v>23</v>
       </c>
-      <c r="B29" s="66"/>
+      <c r="B29" s="76"/>
       <c r="C29" s="49">
         <v>92.492055194421354</v>
       </c>
-      <c r="D29" s="94">
+      <c r="D29" s="50">
         <v>91.055738083245984</v>
       </c>
-      <c r="E29" s="94">
+      <c r="E29" s="50">
         <v>89.241264887762341</v>
       </c>
-      <c r="F29" s="94">
+      <c r="F29" s="50">
         <v>82.713601809643421</v>
       </c>
-      <c r="G29" s="94">
+      <c r="G29" s="50">
         <v>73.133677048774885</v>
       </c>
-      <c r="H29" s="94">
+      <c r="H29" s="50">
         <v>56.229205901331248</v>
       </c>
       <c r="I29" s="51">
@@ -2551,26 +2543,26 @@
         <f t="shared" si="10"/>
         <v xml:space="preserve">    92.4920551944214, 91.055738083246, 89.2412648877623, 82.7136018096434, 73.1336770487749, 56.2292059013312, 43.695396708103,</v>
       </c>
-      <c r="M29" s="65" t="s">
+      <c r="M29" s="75" t="s">
         <v>23</v>
       </c>
-      <c r="N29" s="66"/>
+      <c r="N29" s="76"/>
       <c r="O29" s="49">
         <v>4.0986250609792014</v>
       </c>
-      <c r="P29" s="94">
+      <c r="P29" s="50">
         <v>4.5926443490712341</v>
       </c>
-      <c r="Q29" s="94">
+      <c r="Q29" s="50">
         <v>4.8521598807380544</v>
       </c>
-      <c r="R29" s="94">
+      <c r="R29" s="50">
         <v>5.8188919126166327</v>
       </c>
-      <c r="S29" s="94">
+      <c r="S29" s="50">
         <v>9.5088987825376563</v>
       </c>
-      <c r="T29" s="94">
+      <c r="T29" s="50">
         <v>11.32839542788332</v>
       </c>
       <c r="U29" s="51">
@@ -2582,10 +2574,10 @@
       </c>
     </row>
     <row r="30" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="65" t="s">
+      <c r="A30" s="75" t="s">
         <v>24</v>
       </c>
-      <c r="B30" s="66"/>
+      <c r="B30" s="76"/>
       <c r="C30" s="52">
         <v>92.657174075741665</v>
       </c>
@@ -2613,10 +2605,10 @@
         <f t="shared" si="10"/>
         <v xml:space="preserve">    92.6571740757417, 91.2080508143722, 89.1704556780914, 84.47461606277, 75.0666685936403, 58.5203409933682, 44.7861415920494,</v>
       </c>
-      <c r="M30" s="65" t="s">
+      <c r="M30" s="75" t="s">
         <v>24</v>
       </c>
-      <c r="N30" s="66"/>
+      <c r="N30" s="76"/>
       <c r="O30" s="52">
         <v>4.2589004392769629</v>
       </c>
@@ -2644,38 +2636,38 @@
       </c>
     </row>
     <row r="31" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="65" t="s">
+      <c r="A31" s="75" t="s">
         <v>25</v>
       </c>
-      <c r="B31" s="67"/>
-      <c r="C31" s="71"/>
-      <c r="D31" s="71"/>
-      <c r="E31" s="71"/>
-      <c r="F31" s="71"/>
-      <c r="G31" s="71"/>
-      <c r="H31" s="71"/>
-      <c r="I31" s="72"/>
+      <c r="B31" s="79"/>
+      <c r="C31" s="80"/>
+      <c r="D31" s="80"/>
+      <c r="E31" s="80"/>
+      <c r="F31" s="80"/>
+      <c r="G31" s="80"/>
+      <c r="H31" s="80"/>
+      <c r="I31" s="81"/>
       <c r="J31" s="50"/>
       <c r="K31" s="50"/>
       <c r="L31" s="1"/>
-      <c r="M31" s="65" t="s">
+      <c r="M31" s="75" t="s">
         <v>25</v>
       </c>
-      <c r="N31" s="67"/>
-      <c r="O31" s="71"/>
-      <c r="P31" s="71"/>
-      <c r="Q31" s="71"/>
-      <c r="R31" s="71"/>
-      <c r="S31" s="71"/>
-      <c r="T31" s="71"/>
-      <c r="U31" s="72"/>
+      <c r="N31" s="79"/>
+      <c r="O31" s="80"/>
+      <c r="P31" s="80"/>
+      <c r="Q31" s="80"/>
+      <c r="R31" s="80"/>
+      <c r="S31" s="80"/>
+      <c r="T31" s="80"/>
+      <c r="U31" s="81"/>
       <c r="V31" s="1"/>
     </row>
     <row r="32" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="65" t="s">
+      <c r="A32" s="75" t="s">
         <v>7</v>
       </c>
-      <c r="B32" s="66"/>
+      <c r="B32" s="76"/>
       <c r="C32" s="46">
         <v>92.603769819293618</v>
       </c>
@@ -2703,10 +2695,10 @@
         <f t="shared" ref="L32:L35" si="11">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C32:I32)&amp;","</f>
         <v xml:space="preserve">    92.6037698192936, 91.4319470683528, 90.3907950429996, 86.7895628282223, 80.6155540330522, 56.6095785531339, 41.2792806229243,</v>
       </c>
-      <c r="M32" s="65" t="s">
+      <c r="M32" s="75" t="s">
         <v>7</v>
       </c>
-      <c r="N32" s="66"/>
+      <c r="N32" s="76"/>
       <c r="O32" s="46">
         <v>3.708759274801273</v>
       </c>
@@ -2734,26 +2726,26 @@
       </c>
     </row>
     <row r="33" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="70" t="s">
+      <c r="A33" s="77" t="s">
         <v>8</v>
       </c>
-      <c r="B33" s="69"/>
+      <c r="B33" s="78"/>
       <c r="C33" s="49">
         <v>91.377634404932721</v>
       </c>
-      <c r="D33" s="94">
+      <c r="D33" s="50">
         <v>90.405373333245066</v>
       </c>
-      <c r="E33" s="94">
+      <c r="E33" s="50">
         <v>89.371480308332721</v>
       </c>
-      <c r="F33" s="94">
+      <c r="F33" s="50">
         <v>87.60989862639515</v>
       </c>
-      <c r="G33" s="94">
+      <c r="G33" s="50">
         <v>85.537230701510694</v>
       </c>
-      <c r="H33" s="94">
+      <c r="H33" s="50">
         <v>70.930708745421484</v>
       </c>
       <c r="I33" s="51">
@@ -2765,26 +2757,26 @@
         <f t="shared" si="11"/>
         <v xml:space="preserve">    91.3776344049327, 90.4053733332451, 89.3714803083327, 87.6098986263952, 85.5372307015107, 70.9307087454215, 44.0973262328065,</v>
       </c>
-      <c r="M33" s="65" t="s">
+      <c r="M33" s="75" t="s">
         <v>8</v>
       </c>
-      <c r="N33" s="66"/>
+      <c r="N33" s="76"/>
       <c r="O33" s="49">
         <v>3.5684194304484111</v>
       </c>
-      <c r="P33" s="94">
+      <c r="P33" s="50">
         <v>3.0347581440341318</v>
       </c>
-      <c r="Q33" s="94">
+      <c r="Q33" s="50">
         <v>2.754130276526872</v>
       </c>
-      <c r="R33" s="94">
+      <c r="R33" s="50">
         <v>2.7768782002466339</v>
       </c>
-      <c r="S33" s="94">
+      <c r="S33" s="50">
         <v>3.3184641894178428</v>
       </c>
-      <c r="T33" s="94">
+      <c r="T33" s="50">
         <v>4.9795199020249923</v>
       </c>
       <c r="U33" s="51">
@@ -2796,26 +2788,26 @@
       </c>
     </row>
     <row r="34" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="65" t="s">
+      <c r="A34" s="75" t="s">
         <v>23</v>
       </c>
-      <c r="B34" s="66"/>
+      <c r="B34" s="76"/>
       <c r="C34" s="49">
         <v>92.603715202692385</v>
       </c>
-      <c r="D34" s="94">
+      <c r="D34" s="50">
         <v>91.484997502720319</v>
       </c>
-      <c r="E34" s="94">
+      <c r="E34" s="50">
         <v>90.630171299324857</v>
       </c>
-      <c r="F34" s="94">
+      <c r="F34" s="50">
         <v>85.342034697064548</v>
       </c>
-      <c r="G34" s="94">
+      <c r="G34" s="50">
         <v>78.208607944308184</v>
       </c>
-      <c r="H34" s="94">
+      <c r="H34" s="50">
         <v>58.188767254712552</v>
       </c>
       <c r="I34" s="51">
@@ -2827,26 +2819,26 @@
         <f t="shared" si="11"/>
         <v xml:space="preserve">    92.6037152026924, 91.4849975027203, 90.6301712993249, 85.3420346970645, 78.2086079443082, 58.1887672547126, 45.4689195625762,</v>
       </c>
-      <c r="M34" s="65" t="s">
+      <c r="M34" s="75" t="s">
         <v>23</v>
       </c>
-      <c r="N34" s="66"/>
+      <c r="N34" s="76"/>
       <c r="O34" s="49">
         <v>4.0727132923350373</v>
       </c>
-      <c r="P34" s="94">
+      <c r="P34" s="50">
         <v>4.4231285957629458</v>
       </c>
-      <c r="Q34" s="94">
+      <c r="Q34" s="50">
         <v>4.3011534303531356</v>
       </c>
-      <c r="R34" s="94">
+      <c r="R34" s="50">
         <v>4.8453894583465429</v>
       </c>
-      <c r="S34" s="94">
+      <c r="S34" s="50">
         <v>7.5589700135942426</v>
       </c>
-      <c r="T34" s="94">
+      <c r="T34" s="50">
         <v>10.3740336621021</v>
       </c>
       <c r="U34" s="51">
@@ -2858,10 +2850,10 @@
       </c>
     </row>
     <row r="35" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="65" t="s">
+      <c r="A35" s="75" t="s">
         <v>24</v>
       </c>
-      <c r="B35" s="66"/>
+      <c r="B35" s="76"/>
       <c r="C35" s="52">
         <v>92.692685851985146</v>
       </c>
@@ -2889,10 +2881,10 @@
         <f t="shared" si="11"/>
         <v xml:space="preserve">    92.6926858519851, 91.0280089290633, 89.1011768502887, 84.1216953111353, 75.5145363599464, 58.5518515483004, 43.5286444786034,</v>
       </c>
-      <c r="M35" s="65" t="s">
+      <c r="M35" s="75" t="s">
         <v>24</v>
       </c>
-      <c r="N35" s="66"/>
+      <c r="N35" s="76"/>
       <c r="O35" s="52">
         <v>4.3508377678439567</v>
       </c>
@@ -3001,6 +2993,54 @@
     </row>
   </sheetData>
   <mergeCells count="56">
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="M5:U5"/>
+    <mergeCell ref="A8:I8"/>
+    <mergeCell ref="M8:U8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="M9:N9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="A13:I13"/>
+    <mergeCell ref="M13:U13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="A23:I23"/>
+    <mergeCell ref="M23:U23"/>
+    <mergeCell ref="A26:I26"/>
+    <mergeCell ref="M26:U26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="M27:N27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="M29:N29"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="M30:N30"/>
+    <mergeCell ref="A31:I31"/>
+    <mergeCell ref="M31:U31"/>
     <mergeCell ref="A35:B35"/>
     <mergeCell ref="M35:N35"/>
     <mergeCell ref="A32:B32"/>
@@ -3009,54 +3049,6 @@
     <mergeCell ref="M33:N33"/>
     <mergeCell ref="A34:B34"/>
     <mergeCell ref="M34:N34"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="M29:N29"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="M30:N30"/>
-    <mergeCell ref="A31:I31"/>
-    <mergeCell ref="M31:U31"/>
-    <mergeCell ref="A26:I26"/>
-    <mergeCell ref="M26:U26"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="M27:N27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="M22:N22"/>
-    <mergeCell ref="A23:I23"/>
-    <mergeCell ref="M23:U23"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="A13:I13"/>
-    <mergeCell ref="M13:U13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="A5:I5"/>
-    <mergeCell ref="M5:U5"/>
-    <mergeCell ref="A8:I8"/>
-    <mergeCell ref="M8:U8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="M9:N9"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="M4:N4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C6:I7 C2:I4">
@@ -3080,9 +3072,107 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="30">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C6:I7 C2:I4">
-    <cfRule type="colorScale" priority="30">
+  <conditionalFormatting sqref="C9:I11 C14:I16">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C9:I11">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C9:I12 C14:I17">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C14:I16">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:K4 C6:K7 J5:K5 J8:K17">
+    <cfRule type="colorScale" priority="26">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3191,18 +3281,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:K4 C6:K7 J5:K5 J8:K17">
-    <cfRule type="colorScale" priority="26">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="J31:K35">
     <cfRule type="colorScale" priority="13">
       <colorScale>
@@ -3249,98 +3327,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C9:I11">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C9:I11">
-    <cfRule type="colorScale" priority="9">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C9:I11">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C9:I12 C14:I17">
-    <cfRule type="colorScale" priority="10">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C14:I16">
-    <cfRule type="colorScale" priority="3">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="5">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C9:I11 C14:I16">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -3424,10 +3410,10 @@
       <c r="V1" s="12"/>
     </row>
     <row r="2" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="59" t="s">
+      <c r="A2" s="83" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="60"/>
+      <c r="B2" s="84"/>
       <c r="C2" s="20">
         <v>93.101364775358491</v>
       </c>
@@ -3461,10 +3447,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C2:I2)&amp;","</f>
         <v xml:space="preserve">    93.1013647753585, 91.3266637254648, 89.7225610371485, 83.857204647099, 76.2429490451186, 60.4027774173364, 47.7409002961387,</v>
       </c>
-      <c r="M2" s="59" t="s">
+      <c r="M2" s="83" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="60"/>
+      <c r="N2" s="84"/>
       <c r="O2" s="37">
         <v>3.4649270444699574</v>
       </c>
@@ -3492,10 +3478,10 @@
       </c>
     </row>
     <row r="3" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="59" t="s">
+      <c r="A3" s="83" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="60"/>
+      <c r="B3" s="84"/>
       <c r="C3" s="37">
         <v>93.273358766079312</v>
       </c>
@@ -3529,10 +3515,10 @@
         <f t="shared" ref="L3:L16" si="0">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C3:I3)&amp;","</f>
         <v xml:space="preserve">    93.2733587660793, 91.6155877934354, 90.6205330495939, 86.5975138193237, 78.2243502683126, 60.8549929786013, 48.7439337710534,</v>
       </c>
-      <c r="M3" s="59" t="s">
+      <c r="M3" s="83" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="60"/>
+      <c r="N3" s="84"/>
       <c r="O3" s="37">
         <v>3.4672469457762647</v>
       </c>
@@ -3560,10 +3546,10 @@
       </c>
     </row>
     <row r="4" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="59" t="s">
+      <c r="A4" s="83" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="60"/>
+      <c r="B4" s="84"/>
       <c r="C4" s="24">
         <v>87.593900000000005</v>
       </c>
@@ -3597,10 +3583,10 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    87.5939, 87.6637168141593, 88.1120943952802, 87.9700256922638, 87.4617081462642, 75.2513631894163, 47.7206838582802,</v>
       </c>
-      <c r="M4" s="59" t="s">
+      <c r="M4" s="83" t="s">
         <v>10</v>
       </c>
-      <c r="N4" s="60"/>
+      <c r="N4" s="84"/>
       <c r="O4" s="55">
         <v>2.4529187882918819</v>
       </c>
@@ -3628,31 +3614,31 @@
       </c>
     </row>
     <row r="5" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="59" t="s">
+      <c r="A5" s="83" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="61"/>
-      <c r="C5" s="61"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="61"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="61"/>
-      <c r="H5" s="61"/>
-      <c r="I5" s="60"/>
+      <c r="B5" s="85"/>
+      <c r="C5" s="85"/>
+      <c r="D5" s="85"/>
+      <c r="E5" s="85"/>
+      <c r="F5" s="85"/>
+      <c r="G5" s="85"/>
+      <c r="H5" s="85"/>
+      <c r="I5" s="84"/>
       <c r="J5" s="41"/>
       <c r="K5" s="41"/>
       <c r="L5" s="12"/>
-      <c r="M5" s="59" t="s">
+      <c r="M5" s="83" t="s">
         <v>14</v>
       </c>
-      <c r="N5" s="61"/>
-      <c r="O5" s="61"/>
-      <c r="P5" s="61"/>
-      <c r="Q5" s="61"/>
-      <c r="R5" s="61"/>
-      <c r="S5" s="61"/>
-      <c r="T5" s="61"/>
-      <c r="U5" s="60"/>
+      <c r="N5" s="85"/>
+      <c r="O5" s="85"/>
+      <c r="P5" s="85"/>
+      <c r="Q5" s="85"/>
+      <c r="R5" s="85"/>
+      <c r="S5" s="85"/>
+      <c r="T5" s="85"/>
+      <c r="U5" s="84"/>
       <c r="V5" s="12"/>
     </row>
     <row r="6" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -4068,57 +4054,57 @@
       <c r="V12" s="12"/>
     </row>
     <row r="13" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="59" t="s">
+      <c r="A13" s="83" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="61"/>
-      <c r="C13" s="64"/>
-      <c r="D13" s="64"/>
-      <c r="E13" s="64"/>
-      <c r="F13" s="64"/>
-      <c r="G13" s="64"/>
-      <c r="H13" s="64"/>
-      <c r="I13" s="63"/>
+      <c r="B13" s="85"/>
+      <c r="C13" s="90"/>
+      <c r="D13" s="90"/>
+      <c r="E13" s="90"/>
+      <c r="F13" s="90"/>
+      <c r="G13" s="90"/>
+      <c r="H13" s="90"/>
+      <c r="I13" s="89"/>
       <c r="J13" s="41"/>
       <c r="K13" s="41"/>
       <c r="L13" s="12"/>
-      <c r="M13" s="59" t="s">
+      <c r="M13" s="83" t="s">
         <v>22</v>
       </c>
-      <c r="N13" s="61"/>
-      <c r="O13" s="64"/>
-      <c r="P13" s="64"/>
-      <c r="Q13" s="64"/>
-      <c r="R13" s="64"/>
-      <c r="S13" s="64"/>
-      <c r="T13" s="64"/>
-      <c r="U13" s="63"/>
+      <c r="N13" s="85"/>
+      <c r="O13" s="90"/>
+      <c r="P13" s="90"/>
+      <c r="Q13" s="90"/>
+      <c r="R13" s="90"/>
+      <c r="S13" s="90"/>
+      <c r="T13" s="90"/>
+      <c r="U13" s="89"/>
       <c r="V13" s="12"/>
     </row>
     <row r="14" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="59" t="s">
+      <c r="A14" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="60"/>
-      <c r="C14" s="75">
+      <c r="B14" s="84"/>
+      <c r="C14" s="59">
         <v>93.782740335124032</v>
       </c>
-      <c r="D14" s="76">
+      <c r="D14" s="60">
         <v>91.948208894540599</v>
       </c>
-      <c r="E14" s="76">
+      <c r="E14" s="60">
         <v>90.212980504444957</v>
       </c>
-      <c r="F14" s="76">
+      <c r="F14" s="60">
         <v>84.630388959535409</v>
       </c>
-      <c r="G14" s="76">
+      <c r="G14" s="60">
         <v>75.371093175546491</v>
       </c>
-      <c r="H14" s="76">
+      <c r="H14" s="60">
         <v>59.627211308056303</v>
       </c>
-      <c r="I14" s="77">
+      <c r="I14" s="61">
         <v>47.844185503334799</v>
       </c>
       <c r="J14" s="41" cm="1">
@@ -4133,29 +4119,29 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    93.782740335124, 91.9482088945406, 90.212980504445, 84.6303889595354, 75.3710931755465, 59.6272113080563, 47.8441855033348,</v>
       </c>
-      <c r="M14" s="59" t="s">
+      <c r="M14" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="N14" s="60"/>
-      <c r="O14" s="75">
+      <c r="N14" s="84"/>
+      <c r="O14" s="59">
         <v>3.5391983918820551</v>
       </c>
-      <c r="P14" s="76">
+      <c r="P14" s="60">
         <v>4.1060038651541966</v>
       </c>
-      <c r="Q14" s="76">
+      <c r="Q14" s="60">
         <v>4.774795806468676</v>
       </c>
-      <c r="R14" s="76">
+      <c r="R14" s="60">
         <v>5.3483339064680431</v>
       </c>
-      <c r="S14" s="76">
+      <c r="S14" s="60">
         <v>8.0994903921197494</v>
       </c>
-      <c r="T14" s="76">
+      <c r="T14" s="60">
         <v>10.59987402205407</v>
       </c>
-      <c r="U14" s="77">
+      <c r="U14" s="61">
         <v>8.7604668874903737</v>
       </c>
       <c r="V14" s="12" t="str">
@@ -4164,29 +4150,29 @@
       </c>
     </row>
     <row r="15" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="62" t="s">
+      <c r="A15" s="88" t="s">
         <v>8</v>
       </c>
-      <c r="B15" s="63"/>
-      <c r="C15" s="78">
+      <c r="B15" s="89"/>
+      <c r="C15" s="62">
         <v>93.226230330712227</v>
       </c>
-      <c r="D15" s="79">
+      <c r="D15" s="12">
         <v>91.83329152212967</v>
       </c>
-      <c r="E15" s="79">
+      <c r="E15" s="12">
         <v>90.325291164571794</v>
       </c>
-      <c r="F15" s="79">
+      <c r="F15" s="12">
         <v>85.383492360083878</v>
       </c>
-      <c r="G15" s="79">
+      <c r="G15" s="12">
         <v>76.567000291236639</v>
       </c>
-      <c r="H15" s="79">
+      <c r="H15" s="12">
         <v>59.41454222499042</v>
       </c>
-      <c r="I15" s="80">
+      <c r="I15" s="63">
         <v>50.563407411252108</v>
       </c>
       <c r="J15" s="41" cm="1">
@@ -4201,29 +4187,29 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    93.2262303307122, 91.8332915221297, 90.3252911645718, 85.3834923600839, 76.5670002912366, 59.4145422249904, 50.5634074112521,</v>
       </c>
-      <c r="M15" s="59" t="s">
+      <c r="M15" s="83" t="s">
         <v>8</v>
       </c>
-      <c r="N15" s="60"/>
-      <c r="O15" s="78">
+      <c r="N15" s="84"/>
+      <c r="O15" s="62">
         <v>3.945711842949601</v>
       </c>
-      <c r="P15" s="79">
+      <c r="P15" s="12">
         <v>4.8525950161134093</v>
       </c>
-      <c r="Q15" s="79">
+      <c r="Q15" s="12">
         <v>4.4346894499148144</v>
       </c>
-      <c r="R15" s="79">
+      <c r="R15" s="12">
         <v>5.4810029574676529</v>
       </c>
-      <c r="S15" s="79">
+      <c r="S15" s="12">
         <v>8.4636725644600066</v>
       </c>
-      <c r="T15" s="79">
+      <c r="T15" s="12">
         <v>10.788297692871961</v>
       </c>
-      <c r="U15" s="80">
+      <c r="U15" s="63">
         <v>8.7433484877826491</v>
       </c>
       <c r="V15" s="12" t="str">
@@ -4232,29 +4218,29 @@
       </c>
     </row>
     <row r="16" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="59" t="s">
+      <c r="A16" s="83" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="60"/>
-      <c r="C16" s="78">
+      <c r="B16" s="84"/>
+      <c r="C16" s="62">
         <v>93.004922187908207</v>
       </c>
-      <c r="D16" s="79">
+      <c r="D16" s="12">
         <v>91.518502178507859</v>
       </c>
-      <c r="E16" s="79">
+      <c r="E16" s="12">
         <v>89.729420958082102</v>
       </c>
-      <c r="F16" s="79">
+      <c r="F16" s="12">
         <v>83.348607398564567</v>
       </c>
-      <c r="G16" s="79">
+      <c r="G16" s="12">
         <v>74.087719905304837</v>
       </c>
-      <c r="H16" s="79">
+      <c r="H16" s="12">
         <v>57.917332041511322</v>
       </c>
-      <c r="I16" s="80">
+      <c r="I16" s="63">
         <v>48.007794185070807</v>
       </c>
       <c r="J16" s="41" cm="1">
@@ -4269,29 +4255,29 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    93.0049221879082, 91.5185021785079, 89.7294209580821, 83.3486073985646, 74.0877199053048, 57.9173320415113, 48.0077941850708,</v>
       </c>
-      <c r="M16" s="59" t="s">
+      <c r="M16" s="83" t="s">
         <v>23</v>
       </c>
-      <c r="N16" s="60"/>
-      <c r="O16" s="78">
+      <c r="N16" s="84"/>
+      <c r="O16" s="62">
         <v>3.690401528555848</v>
       </c>
-      <c r="P16" s="79">
+      <c r="P16" s="12">
         <v>4.2469367469027457</v>
       </c>
-      <c r="Q16" s="79">
+      <c r="Q16" s="12">
         <v>4.4611096369834957</v>
       </c>
-      <c r="R16" s="79">
+      <c r="R16" s="12">
         <v>5.4089286426803449</v>
       </c>
-      <c r="S16" s="79">
+      <c r="S16" s="12">
         <v>9.092124974067179</v>
       </c>
-      <c r="T16" s="79">
+      <c r="T16" s="12">
         <v>10.83557708581068</v>
       </c>
-      <c r="U16" s="80">
+      <c r="U16" s="63">
         <v>9.2904800440053528</v>
       </c>
       <c r="V16" s="12" t="str">
@@ -4300,29 +4286,29 @@
       </c>
     </row>
     <row r="17" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="59" t="s">
+      <c r="A17" s="83" t="s">
         <v>24</v>
       </c>
-      <c r="B17" s="60"/>
-      <c r="C17" s="81">
+      <c r="B17" s="84"/>
+      <c r="C17" s="64">
         <v>93.123279613145442</v>
       </c>
-      <c r="D17" s="82">
+      <c r="D17" s="65">
         <v>91.674385879923975</v>
       </c>
-      <c r="E17" s="82">
+      <c r="E17" s="65">
         <v>89.698688281617194</v>
       </c>
-      <c r="F17" s="82">
+      <c r="F17" s="65">
         <v>84.957067102656595</v>
       </c>
-      <c r="G17" s="82">
+      <c r="G17" s="65">
         <v>75.939082518014857</v>
       </c>
-      <c r="H17" s="82">
+      <c r="H17" s="65">
         <v>59.995092229748238</v>
       </c>
-      <c r="I17" s="83">
+      <c r="I17" s="66">
         <v>48.440303693515233</v>
       </c>
       <c r="J17" s="41" cm="1">
@@ -4334,85 +4320,85 @@
         <v>80.789319111757024</v>
       </c>
       <c r="L17" s="12"/>
-      <c r="M17" s="59" t="s">
+      <c r="M17" s="83" t="s">
         <v>24</v>
       </c>
-      <c r="N17" s="60"/>
-      <c r="O17" s="81">
+      <c r="N17" s="84"/>
+      <c r="O17" s="64">
         <v>3.8088682011350912</v>
       </c>
-      <c r="P17" s="82">
+      <c r="P17" s="65">
         <v>4.4783864386850611</v>
       </c>
-      <c r="Q17" s="82">
+      <c r="Q17" s="65">
         <v>5.0849840192173117</v>
       </c>
-      <c r="R17" s="82">
+      <c r="R17" s="65">
         <v>5.0366327026230584</v>
       </c>
-      <c r="S17" s="82">
+      <c r="S17" s="65">
         <v>7.6643798786674449</v>
       </c>
-      <c r="T17" s="82">
+      <c r="T17" s="65">
         <v>10.05146904627655</v>
       </c>
-      <c r="U17" s="83">
+      <c r="U17" s="66">
         <v>9.821397671709315</v>
       </c>
       <c r="V17" s="12"/>
     </row>
     <row r="18" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="59" t="s">
+      <c r="A18" s="83" t="s">
         <v>25</v>
       </c>
-      <c r="B18" s="61"/>
-      <c r="C18" s="73"/>
-      <c r="D18" s="73"/>
-      <c r="E18" s="73"/>
-      <c r="F18" s="73"/>
-      <c r="G18" s="73"/>
-      <c r="H18" s="73"/>
-      <c r="I18" s="74"/>
+      <c r="B18" s="85"/>
+      <c r="C18" s="86"/>
+      <c r="D18" s="86"/>
+      <c r="E18" s="86"/>
+      <c r="F18" s="86"/>
+      <c r="G18" s="86"/>
+      <c r="H18" s="86"/>
+      <c r="I18" s="87"/>
       <c r="J18" s="41"/>
       <c r="K18" s="41"/>
       <c r="L18" s="12"/>
-      <c r="M18" s="59" t="s">
+      <c r="M18" s="83" t="s">
         <v>25</v>
       </c>
-      <c r="N18" s="61"/>
-      <c r="O18" s="73"/>
-      <c r="P18" s="73"/>
-      <c r="Q18" s="73"/>
-      <c r="R18" s="73"/>
-      <c r="S18" s="73"/>
-      <c r="T18" s="73"/>
-      <c r="U18" s="74"/>
+      <c r="N18" s="85"/>
+      <c r="O18" s="86"/>
+      <c r="P18" s="86"/>
+      <c r="Q18" s="86"/>
+      <c r="R18" s="86"/>
+      <c r="S18" s="86"/>
+      <c r="T18" s="86"/>
+      <c r="U18" s="87"/>
       <c r="V18" s="12"/>
     </row>
     <row r="19" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="59" t="s">
+      <c r="A19" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="B19" s="60"/>
-      <c r="C19" s="75">
+      <c r="B19" s="84"/>
+      <c r="C19" s="59">
         <v>92.969518190757128</v>
       </c>
-      <c r="D19" s="76">
+      <c r="D19" s="60">
         <v>91.851524090462149</v>
       </c>
-      <c r="E19" s="76">
+      <c r="E19" s="60">
         <v>90.756145526057011</v>
       </c>
-      <c r="F19" s="76">
+      <c r="F19" s="60">
         <v>87.253136561158271</v>
       </c>
-      <c r="G19" s="76">
+      <c r="G19" s="60">
         <v>81.178972136437139</v>
       </c>
-      <c r="H19" s="76">
+      <c r="H19" s="60">
         <v>57.386929529378847</v>
       </c>
-      <c r="I19" s="77">
+      <c r="I19" s="61">
         <v>44.855442809482213</v>
       </c>
       <c r="J19" s="41" cm="1">
@@ -4427,29 +4413,29 @@
         <f t="shared" ref="L19:L21" si="2">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C19:I19)&amp;","</f>
         <v xml:space="preserve">    92.9695181907571, 91.8515240904621, 90.756145526057, 87.2531365611583, 81.1789721364371, 57.3869295293788, 44.8554428094822,</v>
       </c>
-      <c r="M19" s="59" t="s">
+      <c r="M19" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="N19" s="60"/>
-      <c r="O19" s="75">
+      <c r="N19" s="84"/>
+      <c r="O19" s="59">
         <v>3.3991921823554931</v>
       </c>
-      <c r="P19" s="76">
+      <c r="P19" s="60">
         <v>3.6561489783789969</v>
       </c>
-      <c r="Q19" s="76">
+      <c r="Q19" s="60">
         <v>3.4316179388806831</v>
       </c>
-      <c r="R19" s="76">
+      <c r="R19" s="60">
         <v>3.3610781227617821</v>
       </c>
-      <c r="S19" s="76">
+      <c r="S19" s="60">
         <v>5.2773835873092807</v>
       </c>
-      <c r="T19" s="76">
+      <c r="T19" s="60">
         <v>8.2027130196510409</v>
       </c>
-      <c r="U19" s="77">
+      <c r="U19" s="61">
         <v>5.203571843512913</v>
       </c>
       <c r="V19" s="12" t="str">
@@ -4458,29 +4444,29 @@
       </c>
     </row>
     <row r="20" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="62" t="s">
+      <c r="A20" s="88" t="s">
         <v>8</v>
       </c>
-      <c r="B20" s="63"/>
-      <c r="C20" s="78">
+      <c r="B20" s="89"/>
+      <c r="C20" s="62">
         <v>91.898721730580135</v>
       </c>
-      <c r="D20" s="79">
+      <c r="D20" s="12">
         <v>90.765995668936</v>
       </c>
-      <c r="E20" s="79">
+      <c r="E20" s="12">
         <v>89.705268500015848</v>
       </c>
-      <c r="F20" s="79">
+      <c r="F20" s="12">
         <v>87.959685349065893</v>
       </c>
-      <c r="G20" s="79">
+      <c r="G20" s="12">
         <v>85.750000720882824</v>
       </c>
-      <c r="H20" s="79">
+      <c r="H20" s="12">
         <v>71.387388010853613</v>
       </c>
-      <c r="I20" s="80">
+      <c r="I20" s="63">
         <v>45.596343105620853</v>
       </c>
       <c r="J20" s="41" cm="1">
@@ -4495,29 +4481,29 @@
         <f t="shared" si="2"/>
         <v xml:space="preserve">    91.8987217305801, 90.765995668936, 89.7052685000158, 87.9596853490659, 85.7500007208828, 71.3873880108536, 45.5963431056209,</v>
       </c>
-      <c r="M20" s="59" t="s">
+      <c r="M20" s="83" t="s">
         <v>8</v>
       </c>
-      <c r="N20" s="60"/>
-      <c r="O20" s="78">
+      <c r="N20" s="84"/>
+      <c r="O20" s="62">
         <v>3.190312271555559</v>
       </c>
-      <c r="P20" s="79">
+      <c r="P20" s="12">
         <v>2.8828036064622768</v>
       </c>
-      <c r="Q20" s="79">
+      <c r="Q20" s="12">
         <v>2.5884740771146331</v>
       </c>
-      <c r="R20" s="79">
+      <c r="R20" s="12">
         <v>2.6213450470877251</v>
       </c>
-      <c r="S20" s="79">
+      <c r="S20" s="12">
         <v>3.203569989687661</v>
       </c>
-      <c r="T20" s="79">
+      <c r="T20" s="12">
         <v>4.756712112750666</v>
       </c>
-      <c r="U20" s="80">
+      <c r="U20" s="63">
         <v>2.488810891584841</v>
       </c>
       <c r="V20" s="12" t="str">
@@ -4526,29 +4512,29 @@
       </c>
     </row>
     <row r="21" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="59" t="s">
+      <c r="A21" s="83" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="60"/>
-      <c r="C21" s="78">
+      <c r="B21" s="84"/>
+      <c r="C21" s="62">
         <v>93.044276622923505</v>
       </c>
-      <c r="D21" s="79">
+      <c r="D21" s="12">
         <v>91.935155148400938</v>
       </c>
-      <c r="E21" s="79">
+      <c r="E21" s="12">
         <v>90.94889229145582</v>
       </c>
-      <c r="F21" s="79">
+      <c r="F21" s="12">
         <v>85.952505356159378</v>
       </c>
-      <c r="G21" s="79">
+      <c r="G21" s="12">
         <v>78.915183810701947</v>
       </c>
-      <c r="H21" s="79">
+      <c r="H21" s="12">
         <v>59.442100133507502</v>
       </c>
-      <c r="I21" s="80">
+      <c r="I21" s="63">
         <v>49.533828147302302</v>
       </c>
       <c r="J21" s="41" cm="1">
@@ -4563,29 +4549,29 @@
         <f t="shared" si="2"/>
         <v xml:space="preserve">    93.0442766229235, 91.9351551484009, 90.9488922914558, 85.9525053561594, 78.9151838107019, 59.4421001335075, 49.5338281473023,</v>
       </c>
-      <c r="M21" s="59" t="s">
+      <c r="M21" s="83" t="s">
         <v>23</v>
       </c>
-      <c r="N21" s="60"/>
-      <c r="O21" s="78">
+      <c r="N21" s="84"/>
+      <c r="O21" s="62">
         <v>3.72078192123604</v>
       </c>
-      <c r="P21" s="79">
+      <c r="P21" s="12">
         <v>4.0467152776216686</v>
       </c>
-      <c r="Q21" s="79">
+      <c r="Q21" s="12">
         <v>4.0235763627769954</v>
       </c>
-      <c r="R21" s="79">
+      <c r="R21" s="12">
         <v>4.4767633212331157</v>
       </c>
-      <c r="S21" s="79">
+      <c r="S21" s="12">
         <v>7.2019016527503927</v>
       </c>
-      <c r="T21" s="79">
+      <c r="T21" s="12">
         <v>10.04668436860082</v>
       </c>
-      <c r="U21" s="80">
+      <c r="U21" s="63">
         <v>9.2355901481835172</v>
       </c>
       <c r="V21" s="12" t="str">
@@ -4594,29 +4580,29 @@
       </c>
     </row>
     <row r="22" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="59" t="s">
+      <c r="A22" s="83" t="s">
         <v>24</v>
       </c>
-      <c r="B22" s="60"/>
-      <c r="C22" s="81">
+      <c r="B22" s="84"/>
+      <c r="C22" s="64">
         <v>93.174110502686005</v>
       </c>
-      <c r="D22" s="82">
+      <c r="D22" s="65">
         <v>91.391724841910417</v>
       </c>
-      <c r="E22" s="82">
+      <c r="E22" s="65">
         <v>89.591539142495463</v>
       </c>
-      <c r="F22" s="82">
+      <c r="F22" s="65">
         <v>84.690597092823751</v>
       </c>
-      <c r="G22" s="82">
+      <c r="G22" s="65">
         <v>76.401347185817656</v>
       </c>
-      <c r="H22" s="82">
+      <c r="H22" s="65">
         <v>59.963667505774268</v>
       </c>
-      <c r="I22" s="83">
+      <c r="I22" s="66">
         <v>47.725577210875521</v>
       </c>
       <c r="J22" s="41" cm="1">
@@ -4628,29 +4614,29 @@
         <v>80.686930106085114</v>
       </c>
       <c r="L22" s="12"/>
-      <c r="M22" s="59" t="s">
+      <c r="M22" s="83" t="s">
         <v>24</v>
       </c>
-      <c r="N22" s="60"/>
-      <c r="O22" s="81">
+      <c r="N22" s="84"/>
+      <c r="O22" s="64">
         <v>3.8766021792735019</v>
       </c>
-      <c r="P22" s="82">
+      <c r="P22" s="65">
         <v>4.8126411406228078</v>
       </c>
-      <c r="Q22" s="82">
+      <c r="Q22" s="65">
         <v>4.6512210016047986</v>
       </c>
-      <c r="R22" s="82">
+      <c r="R22" s="65">
         <v>5.2416066355763284</v>
       </c>
-      <c r="S22" s="82">
+      <c r="S22" s="65">
         <v>8.0769588602235256</v>
       </c>
-      <c r="T22" s="82">
+      <c r="T22" s="65">
         <v>10.657363307561541</v>
       </c>
-      <c r="U22" s="83">
+      <c r="U22" s="66">
         <v>9.200486032966916</v>
       </c>
       <c r="V22" s="12"/>
@@ -4738,10 +4724,10 @@
       <c r="V24" s="1"/>
     </row>
     <row r="25" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="65" t="s">
+      <c r="A25" s="75" t="s">
         <v>5</v>
       </c>
-      <c r="B25" s="66"/>
+      <c r="B25" s="76"/>
       <c r="C25" s="47">
         <v>92.567111769713335</v>
       </c>
@@ -4769,10 +4755,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C25:I25)&amp;","</f>
         <v xml:space="preserve">    92.5671117697133, 90.8358586083436, 89.2175053395332, 83.2372459642881, 75.380430844191, 58.9943671875974, 43.6225356413822,</v>
       </c>
-      <c r="M25" s="65" t="s">
+      <c r="M25" s="75" t="s">
         <v>5</v>
       </c>
-      <c r="N25" s="66"/>
+      <c r="N25" s="76"/>
       <c r="O25" s="46">
         <v>3.88093621561358</v>
       </c>
@@ -4800,10 +4786,10 @@
       </c>
     </row>
     <row r="26" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="65" t="s">
+      <c r="A26" s="75" t="s">
         <v>6</v>
       </c>
-      <c r="B26" s="66"/>
+      <c r="B26" s="76"/>
       <c r="C26" s="47">
         <v>92.866950218042462</v>
       </c>
@@ -4831,10 +4817,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C26:I26)&amp;","</f>
         <v xml:space="preserve">    92.8669502180425, 91.2426907647456, 90.1370532276984, 86.0801529266134, 77.4102172551968, 59.6761947649801, 46.3954904194042,</v>
       </c>
-      <c r="M26" s="65" t="s">
+      <c r="M26" s="75" t="s">
         <v>6</v>
       </c>
-      <c r="N26" s="66"/>
+      <c r="N26" s="76"/>
       <c r="O26" s="47">
         <v>3.8319643020864191</v>
       </c>
@@ -4862,10 +4848,10 @@
       </c>
     </row>
     <row r="27" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="65" t="s">
+      <c r="A27" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="B27" s="66"/>
+      <c r="B27" s="76"/>
       <c r="C27" s="34">
         <v>87.268396410214976</v>
       </c>
@@ -4893,10 +4879,10 @@
         <f t="shared" ref="L27:L35" si="5">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C27:I27)&amp;","</f>
         <v xml:space="preserve">    87.268396410215, 87.2564283986868, 87.8221063041704, 87.6807264423516, 87.1448793671852, 74.9765678865158, 46.4175473948824,</v>
       </c>
-      <c r="M27" s="65" t="s">
+      <c r="M27" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="N27" s="66"/>
+      <c r="N27" s="76"/>
       <c r="O27" s="34">
         <v>2.610595868561878</v>
       </c>
@@ -4924,31 +4910,31 @@
       </c>
     </row>
     <row r="28" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="65" t="s">
+      <c r="A28" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="B28" s="67"/>
-      <c r="C28" s="67"/>
-      <c r="D28" s="67"/>
-      <c r="E28" s="67"/>
-      <c r="F28" s="67"/>
-      <c r="G28" s="67"/>
-      <c r="H28" s="67"/>
-      <c r="I28" s="66"/>
+      <c r="B28" s="79"/>
+      <c r="C28" s="79"/>
+      <c r="D28" s="79"/>
+      <c r="E28" s="79"/>
+      <c r="F28" s="79"/>
+      <c r="G28" s="79"/>
+      <c r="H28" s="79"/>
+      <c r="I28" s="76"/>
       <c r="J28" s="50"/>
       <c r="K28" s="50"/>
       <c r="L28" s="1"/>
-      <c r="M28" s="65" t="s">
+      <c r="M28" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="N28" s="67"/>
-      <c r="O28" s="67"/>
-      <c r="P28" s="67"/>
-      <c r="Q28" s="67"/>
-      <c r="R28" s="67"/>
-      <c r="S28" s="67"/>
-      <c r="T28" s="67"/>
-      <c r="U28" s="66"/>
+      <c r="N28" s="79"/>
+      <c r="O28" s="79"/>
+      <c r="P28" s="79"/>
+      <c r="Q28" s="79"/>
+      <c r="R28" s="79"/>
+      <c r="S28" s="79"/>
+      <c r="T28" s="79"/>
+      <c r="U28" s="76"/>
       <c r="V28" s="1"/>
     </row>
     <row r="29" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
@@ -5334,57 +5320,57 @@
       <c r="V35" s="1"/>
     </row>
     <row r="36" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="65" t="s">
+      <c r="A36" s="75" t="s">
         <v>22</v>
       </c>
-      <c r="B36" s="67"/>
-      <c r="C36" s="68"/>
-      <c r="D36" s="68"/>
-      <c r="E36" s="68"/>
-      <c r="F36" s="68"/>
-      <c r="G36" s="68"/>
-      <c r="H36" s="68"/>
-      <c r="I36" s="69"/>
+      <c r="B36" s="79"/>
+      <c r="C36" s="82"/>
+      <c r="D36" s="82"/>
+      <c r="E36" s="82"/>
+      <c r="F36" s="82"/>
+      <c r="G36" s="82"/>
+      <c r="H36" s="82"/>
+      <c r="I36" s="78"/>
       <c r="J36" s="50"/>
       <c r="K36" s="50"/>
       <c r="L36" s="1"/>
-      <c r="M36" s="65" t="s">
+      <c r="M36" s="75" t="s">
         <v>22</v>
       </c>
-      <c r="N36" s="67"/>
-      <c r="O36" s="68"/>
-      <c r="P36" s="68"/>
-      <c r="Q36" s="68"/>
-      <c r="R36" s="68"/>
-      <c r="S36" s="68"/>
-      <c r="T36" s="68"/>
-      <c r="U36" s="69"/>
+      <c r="N36" s="79"/>
+      <c r="O36" s="82"/>
+      <c r="P36" s="82"/>
+      <c r="Q36" s="82"/>
+      <c r="R36" s="82"/>
+      <c r="S36" s="82"/>
+      <c r="T36" s="82"/>
+      <c r="U36" s="78"/>
       <c r="V36" s="1"/>
     </row>
     <row r="37" spans="1:22" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="65" t="s">
+      <c r="A37" s="75" t="s">
         <v>7</v>
       </c>
-      <c r="B37" s="66"/>
-      <c r="C37" s="84">
+      <c r="B37" s="76"/>
+      <c r="C37" s="67">
         <v>93.403798109785029</v>
       </c>
-      <c r="D37" s="85">
+      <c r="D37" s="68">
         <v>91.51700700493744</v>
       </c>
-      <c r="E37" s="85">
+      <c r="E37" s="68">
         <v>89.749880462689262</v>
       </c>
-      <c r="F37" s="85">
+      <c r="F37" s="68">
         <v>83.99730958119234</v>
       </c>
-      <c r="G37" s="85">
+      <c r="G37" s="68">
         <v>74.394962965986878</v>
       </c>
-      <c r="H37" s="85">
+      <c r="H37" s="68">
         <v>58.095582470498513</v>
       </c>
-      <c r="I37" s="86">
+      <c r="I37" s="69">
         <v>44.434812706207254</v>
       </c>
       <c r="J37" s="50"/>
@@ -5393,29 +5379,29 @@
         <f t="shared" ref="L37:L39" si="6">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C37:I37)&amp;","</f>
         <v xml:space="preserve">    93.403798109785, 91.5170070049374, 89.7498804626893, 83.9973095811923, 74.3949629659869, 58.0955824704985, 44.4348127062073,</v>
       </c>
-      <c r="M37" s="65" t="s">
+      <c r="M37" s="75" t="s">
         <v>7</v>
       </c>
-      <c r="N37" s="66"/>
-      <c r="O37" s="84">
+      <c r="N37" s="76"/>
+      <c r="O37" s="67">
         <v>3.9553866501853321</v>
       </c>
-      <c r="P37" s="85">
+      <c r="P37" s="68">
         <v>4.517630835861226</v>
       </c>
-      <c r="Q37" s="85">
+      <c r="Q37" s="68">
         <v>5.2125425794506972</v>
       </c>
-      <c r="R37" s="85">
+      <c r="R37" s="68">
         <v>5.6477461387684551</v>
       </c>
-      <c r="S37" s="85">
+      <c r="S37" s="68">
         <v>8.6090564713117175</v>
       </c>
-      <c r="T37" s="85">
+      <c r="T37" s="68">
         <v>11.357157347254571</v>
       </c>
-      <c r="U37" s="86">
+      <c r="U37" s="69">
         <v>9.3757621724255777</v>
       </c>
       <c r="V37" s="1" t="str">
@@ -5424,29 +5410,29 @@
       </c>
     </row>
     <row r="38" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="65" t="s">
+      <c r="A38" s="75" t="s">
         <v>8</v>
       </c>
-      <c r="B38" s="66"/>
-      <c r="C38" s="87">
+      <c r="B38" s="76"/>
+      <c r="C38" s="70">
         <v>92.778947400409621</v>
       </c>
-      <c r="D38" s="88">
+      <c r="D38" s="1">
         <v>91.450368996373655</v>
       </c>
-      <c r="E38" s="88">
+      <c r="E38" s="1">
         <v>89.879480954542075</v>
       </c>
-      <c r="F38" s="88">
+      <c r="F38" s="1">
         <v>84.748756470336986</v>
       </c>
-      <c r="G38" s="88">
+      <c r="G38" s="1">
         <v>75.627608782580538</v>
       </c>
-      <c r="H38" s="88">
+      <c r="H38" s="1">
         <v>58.300265665116903</v>
       </c>
-      <c r="I38" s="89">
+      <c r="I38" s="71">
         <v>48.584106437626268</v>
       </c>
       <c r="J38" s="50"/>
@@ -5455,29 +5441,29 @@
         <f t="shared" si="6"/>
         <v xml:space="preserve">    92.7789474004096, 91.4503689963737, 89.8794809545421, 84.748756470337, 75.6276087825805, 58.3002656651169, 48.5841064376263,</v>
       </c>
-      <c r="M38" s="65" t="s">
+      <c r="M38" s="75" t="s">
         <v>8</v>
       </c>
-      <c r="N38" s="66"/>
-      <c r="O38" s="87">
+      <c r="N38" s="76"/>
+      <c r="O38" s="70">
         <v>4.3743918396131134</v>
       </c>
-      <c r="P38" s="88">
+      <c r="P38" s="1">
         <v>5.1779143655465321</v>
       </c>
-      <c r="Q38" s="88">
+      <c r="Q38" s="1">
         <v>4.8362705721377752</v>
       </c>
-      <c r="R38" s="88">
+      <c r="R38" s="1">
         <v>5.6797782301447892</v>
       </c>
-      <c r="S38" s="88">
+      <c r="S38" s="1">
         <v>9.0190902977959446</v>
       </c>
-      <c r="T38" s="88">
+      <c r="T38" s="1">
         <v>11.000258135261941</v>
       </c>
-      <c r="U38" s="89">
+      <c r="U38" s="71">
         <v>9.2918474149187738</v>
       </c>
       <c r="V38" s="1" t="str">
@@ -5486,29 +5472,29 @@
       </c>
     </row>
     <row r="39" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="65" t="s">
+      <c r="A39" s="75" t="s">
         <v>23</v>
       </c>
-      <c r="B39" s="66"/>
-      <c r="C39" s="87">
+      <c r="B39" s="76"/>
+      <c r="C39" s="70">
         <v>92.492055194421354</v>
       </c>
-      <c r="D39" s="88">
+      <c r="D39" s="1">
         <v>91.055738083245984</v>
       </c>
-      <c r="E39" s="88">
+      <c r="E39" s="1">
         <v>89.241264887762341</v>
       </c>
-      <c r="F39" s="88">
+      <c r="F39" s="1">
         <v>82.713601809643421</v>
       </c>
-      <c r="G39" s="88">
+      <c r="G39" s="1">
         <v>73.133677048774885</v>
       </c>
-      <c r="H39" s="88">
+      <c r="H39" s="1">
         <v>56.229205901331248</v>
       </c>
-      <c r="I39" s="89">
+      <c r="I39" s="71">
         <v>43.695396708102962</v>
       </c>
       <c r="J39" s="50"/>
@@ -5517,29 +5503,29 @@
         <f t="shared" si="6"/>
         <v xml:space="preserve">    92.4920551944214, 91.055738083246, 89.2412648877623, 82.7136018096434, 73.1336770487749, 56.2292059013312, 43.695396708103,</v>
       </c>
-      <c r="M39" s="65" t="s">
+      <c r="M39" s="75" t="s">
         <v>23</v>
       </c>
-      <c r="N39" s="66"/>
-      <c r="O39" s="87">
+      <c r="N39" s="76"/>
+      <c r="O39" s="70">
         <v>4.0986250609792014</v>
       </c>
-      <c r="P39" s="88">
+      <c r="P39" s="1">
         <v>4.5926443490712341</v>
       </c>
-      <c r="Q39" s="88">
+      <c r="Q39" s="1">
         <v>4.8521598807380544</v>
       </c>
-      <c r="R39" s="88">
+      <c r="R39" s="1">
         <v>5.8188919126166327</v>
       </c>
-      <c r="S39" s="88">
+      <c r="S39" s="1">
         <v>9.5088987825376563</v>
       </c>
-      <c r="T39" s="88">
+      <c r="T39" s="1">
         <v>11.32839542788332</v>
       </c>
-      <c r="U39" s="89">
+      <c r="U39" s="71">
         <v>10.62887090695313</v>
       </c>
       <c r="V39" s="1" t="str">
@@ -5548,113 +5534,113 @@
       </c>
     </row>
     <row r="40" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="65" t="s">
+      <c r="A40" s="75" t="s">
         <v>24</v>
       </c>
-      <c r="B40" s="66"/>
-      <c r="C40" s="90">
+      <c r="B40" s="76"/>
+      <c r="C40" s="72">
         <v>92.657174075741665</v>
       </c>
-      <c r="D40" s="91">
+      <c r="D40" s="73">
         <v>91.208050814372243</v>
       </c>
-      <c r="E40" s="91">
+      <c r="E40" s="73">
         <v>89.170455678091372</v>
       </c>
-      <c r="F40" s="91">
+      <c r="F40" s="73">
         <v>84.474616062770011</v>
       </c>
-      <c r="G40" s="91">
+      <c r="G40" s="73">
         <v>75.066668593640316</v>
       </c>
-      <c r="H40" s="91">
+      <c r="H40" s="73">
         <v>58.520340993368222</v>
       </c>
-      <c r="I40" s="92">
+      <c r="I40" s="74">
         <v>44.786141592049418</v>
       </c>
       <c r="J40" s="58"/>
       <c r="K40" s="58"/>
       <c r="L40" s="57"/>
-      <c r="M40" s="65" t="s">
+      <c r="M40" s="75" t="s">
         <v>24</v>
       </c>
-      <c r="N40" s="66"/>
-      <c r="O40" s="90">
+      <c r="N40" s="76"/>
+      <c r="O40" s="72">
         <v>4.2589004392769629</v>
       </c>
-      <c r="P40" s="91">
+      <c r="P40" s="73">
         <v>4.8517186601265534</v>
       </c>
-      <c r="Q40" s="91">
+      <c r="Q40" s="73">
         <v>5.6717673083496472</v>
       </c>
-      <c r="R40" s="91">
+      <c r="R40" s="73">
         <v>5.3079507961921779</v>
       </c>
-      <c r="S40" s="91">
+      <c r="S40" s="73">
         <v>7.7884705615072454</v>
       </c>
-      <c r="T40" s="91">
+      <c r="T40" s="73">
         <v>10.595563377926201</v>
       </c>
-      <c r="U40" s="92">
+      <c r="U40" s="74">
         <v>10.945843294214329</v>
       </c>
       <c r="V40" s="1"/>
     </row>
     <row r="41" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="65" t="s">
+      <c r="A41" s="75" t="s">
         <v>25</v>
       </c>
-      <c r="B41" s="67"/>
-      <c r="C41" s="71"/>
-      <c r="D41" s="71"/>
-      <c r="E41" s="71"/>
-      <c r="F41" s="71"/>
-      <c r="G41" s="71"/>
-      <c r="H41" s="71"/>
-      <c r="I41" s="72"/>
+      <c r="B41" s="79"/>
+      <c r="C41" s="80"/>
+      <c r="D41" s="80"/>
+      <c r="E41" s="80"/>
+      <c r="F41" s="80"/>
+      <c r="G41" s="80"/>
+      <c r="H41" s="80"/>
+      <c r="I41" s="81"/>
       <c r="J41" s="50"/>
       <c r="K41" s="50"/>
       <c r="L41" s="1"/>
-      <c r="M41" s="65" t="s">
+      <c r="M41" s="75" t="s">
         <v>25</v>
       </c>
-      <c r="N41" s="67"/>
-      <c r="O41" s="71"/>
-      <c r="P41" s="71"/>
-      <c r="Q41" s="71"/>
-      <c r="R41" s="71"/>
-      <c r="S41" s="71"/>
-      <c r="T41" s="71"/>
-      <c r="U41" s="72"/>
+      <c r="N41" s="79"/>
+      <c r="O41" s="80"/>
+      <c r="P41" s="80"/>
+      <c r="Q41" s="80"/>
+      <c r="R41" s="80"/>
+      <c r="S41" s="80"/>
+      <c r="T41" s="80"/>
+      <c r="U41" s="81"/>
       <c r="V41" s="1"/>
     </row>
     <row r="42" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="65" t="s">
+      <c r="A42" s="75" t="s">
         <v>7</v>
       </c>
-      <c r="B42" s="66"/>
-      <c r="C42" s="84">
+      <c r="B42" s="76"/>
+      <c r="C42" s="67">
         <v>92.603769819293618</v>
       </c>
-      <c r="D42" s="85">
+      <c r="D42" s="68">
         <v>91.431947068352812</v>
       </c>
-      <c r="E42" s="85">
+      <c r="E42" s="68">
         <v>90.390795042999585</v>
       </c>
-      <c r="F42" s="85">
+      <c r="F42" s="68">
         <v>86.789562828222273</v>
       </c>
-      <c r="G42" s="85">
+      <c r="G42" s="68">
         <v>80.615554033052248</v>
       </c>
-      <c r="H42" s="85">
+      <c r="H42" s="68">
         <v>56.609578553133908</v>
       </c>
-      <c r="I42" s="86">
+      <c r="I42" s="69">
         <v>41.27928062292434</v>
       </c>
       <c r="J42" s="50"/>
@@ -5663,29 +5649,29 @@
         <f t="shared" ref="L42:L44" si="7">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C42:I42)&amp;","</f>
         <v xml:space="preserve">    92.6037698192936, 91.4319470683528, 90.3907950429996, 86.7895628282223, 80.6155540330522, 56.6095785531339, 41.2792806229243,</v>
       </c>
-      <c r="M42" s="65" t="s">
+      <c r="M42" s="75" t="s">
         <v>7</v>
       </c>
-      <c r="N42" s="66"/>
-      <c r="O42" s="84">
+      <c r="N42" s="76"/>
+      <c r="O42" s="67">
         <v>3.708759274801273</v>
       </c>
-      <c r="P42" s="85">
+      <c r="P42" s="68">
         <v>3.9640390541215931</v>
       </c>
-      <c r="Q42" s="85">
+      <c r="Q42" s="68">
         <v>3.7067998106756881</v>
       </c>
-      <c r="R42" s="85">
+      <c r="R42" s="68">
         <v>3.667452632531309</v>
       </c>
-      <c r="S42" s="85">
+      <c r="S42" s="68">
         <v>5.7548227051500218</v>
       </c>
-      <c r="T42" s="85">
+      <c r="T42" s="68">
         <v>8.5366536877555248</v>
       </c>
-      <c r="U42" s="86">
+      <c r="U42" s="69">
         <v>6.3187793027043018</v>
       </c>
       <c r="V42" s="1" t="str">
@@ -5694,29 +5680,29 @@
       </c>
     </row>
     <row r="43" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="70" t="s">
+      <c r="A43" s="77" t="s">
         <v>8</v>
       </c>
-      <c r="B43" s="69"/>
-      <c r="C43" s="87">
+      <c r="B43" s="78"/>
+      <c r="C43" s="70">
         <v>91.377634404932721</v>
       </c>
-      <c r="D43" s="88">
+      <c r="D43" s="1">
         <v>90.405373333245066</v>
       </c>
-      <c r="E43" s="88">
+      <c r="E43" s="1">
         <v>89.371480308332721</v>
       </c>
-      <c r="F43" s="88">
+      <c r="F43" s="1">
         <v>87.60989862639515</v>
       </c>
-      <c r="G43" s="88">
+      <c r="G43" s="1">
         <v>85.537230701510694</v>
       </c>
-      <c r="H43" s="88">
+      <c r="H43" s="1">
         <v>70.930708745421484</v>
       </c>
-      <c r="I43" s="89">
+      <c r="I43" s="71">
         <v>44.097326232806537</v>
       </c>
       <c r="J43" s="50"/>
@@ -5725,29 +5711,29 @@
         <f t="shared" si="7"/>
         <v xml:space="preserve">    91.3776344049327, 90.4053733332451, 89.3714803083327, 87.6098986263952, 85.5372307015107, 70.9307087454215, 44.0973262328065,</v>
       </c>
-      <c r="M43" s="65" t="s">
+      <c r="M43" s="75" t="s">
         <v>8</v>
       </c>
-      <c r="N43" s="66"/>
-      <c r="O43" s="87">
+      <c r="N43" s="76"/>
+      <c r="O43" s="70">
         <v>3.5684194304484111</v>
       </c>
-      <c r="P43" s="88">
+      <c r="P43" s="1">
         <v>3.0347581440341318</v>
       </c>
-      <c r="Q43" s="88">
+      <c r="Q43" s="1">
         <v>2.754130276526872</v>
       </c>
-      <c r="R43" s="88">
+      <c r="R43" s="1">
         <v>2.7768782002466339</v>
       </c>
-      <c r="S43" s="88">
+      <c r="S43" s="1">
         <v>3.3184641894178428</v>
       </c>
-      <c r="T43" s="88">
+      <c r="T43" s="1">
         <v>4.9795199020249923</v>
       </c>
-      <c r="U43" s="89">
+      <c r="U43" s="71">
         <v>2.9223071611371929</v>
       </c>
       <c r="V43" s="1" t="str">
@@ -5756,29 +5742,29 @@
       </c>
     </row>
     <row r="44" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="65" t="s">
+      <c r="A44" s="75" t="s">
         <v>23</v>
       </c>
-      <c r="B44" s="66"/>
-      <c r="C44" s="87">
+      <c r="B44" s="76"/>
+      <c r="C44" s="70">
         <v>92.603715202692385</v>
       </c>
-      <c r="D44" s="88">
+      <c r="D44" s="1">
         <v>91.484997502720319</v>
       </c>
-      <c r="E44" s="88">
+      <c r="E44" s="1">
         <v>90.630171299324857</v>
       </c>
-      <c r="F44" s="88">
+      <c r="F44" s="1">
         <v>85.342034697064548</v>
       </c>
-      <c r="G44" s="88">
+      <c r="G44" s="1">
         <v>78.208607944308184</v>
       </c>
-      <c r="H44" s="88">
+      <c r="H44" s="1">
         <v>58.188767254712552</v>
       </c>
-      <c r="I44" s="89">
+      <c r="I44" s="71">
         <v>45.468919562576168</v>
       </c>
       <c r="J44" s="50"/>
@@ -5787,29 +5773,29 @@
         <f t="shared" si="7"/>
         <v xml:space="preserve">    92.6037152026924, 91.4849975027203, 90.6301712993249, 85.3420346970645, 78.2086079443082, 58.1887672547126, 45.4689195625762,</v>
       </c>
-      <c r="M44" s="65" t="s">
+      <c r="M44" s="75" t="s">
         <v>23</v>
       </c>
-      <c r="N44" s="66"/>
-      <c r="O44" s="87">
+      <c r="N44" s="76"/>
+      <c r="O44" s="70">
         <v>4.0727132923350373</v>
       </c>
-      <c r="P44" s="88">
+      <c r="P44" s="1">
         <v>4.4231285957629458</v>
       </c>
-      <c r="Q44" s="88">
+      <c r="Q44" s="1">
         <v>4.3011534303531356</v>
       </c>
-      <c r="R44" s="88">
+      <c r="R44" s="1">
         <v>4.8453894583465429</v>
       </c>
-      <c r="S44" s="88">
+      <c r="S44" s="1">
         <v>7.5589700135942426</v>
       </c>
-      <c r="T44" s="88">
+      <c r="T44" s="1">
         <v>10.3740336621021</v>
       </c>
-      <c r="U44" s="89">
+      <c r="U44" s="71">
         <v>10.707618741543239</v>
       </c>
       <c r="V44" s="1" t="str">
@@ -5818,57 +5804,57 @@
       </c>
     </row>
     <row r="45" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="65" t="s">
+      <c r="A45" s="75" t="s">
         <v>24</v>
       </c>
-      <c r="B45" s="66"/>
-      <c r="C45" s="90">
+      <c r="B45" s="76"/>
+      <c r="C45" s="72">
         <v>92.692685851985146</v>
       </c>
-      <c r="D45" s="91">
+      <c r="D45" s="73">
         <v>91.028008929063319</v>
       </c>
-      <c r="E45" s="91">
+      <c r="E45" s="73">
         <v>89.101176850288709</v>
       </c>
-      <c r="F45" s="91">
+      <c r="F45" s="73">
         <v>84.121695311135312</v>
       </c>
-      <c r="G45" s="91">
+      <c r="G45" s="73">
         <v>75.514536359946376</v>
       </c>
-      <c r="H45" s="91">
+      <c r="H45" s="73">
         <v>58.551851548300363</v>
       </c>
-      <c r="I45" s="92">
+      <c r="I45" s="74">
         <v>43.528644478603361</v>
       </c>
       <c r="J45" s="50"/>
       <c r="K45" s="50"/>
       <c r="L45" s="1"/>
-      <c r="M45" s="65" t="s">
+      <c r="M45" s="75" t="s">
         <v>24</v>
       </c>
-      <c r="N45" s="66"/>
-      <c r="O45" s="90">
+      <c r="N45" s="76"/>
+      <c r="O45" s="72">
         <v>4.3508377678439567</v>
       </c>
-      <c r="P45" s="91">
+      <c r="P45" s="73">
         <v>5.1455197984597092</v>
       </c>
-      <c r="Q45" s="91">
+      <c r="Q45" s="73">
         <v>5.0319449257944937</v>
       </c>
-      <c r="R45" s="91">
+      <c r="R45" s="73">
         <v>5.4881092234662896</v>
       </c>
-      <c r="S45" s="91">
+      <c r="S45" s="73">
         <v>8.3963724907401343</v>
       </c>
-      <c r="T45" s="91">
+      <c r="T45" s="73">
         <v>11.26477476806841</v>
       </c>
-      <c r="U45" s="92">
+      <c r="U45" s="74">
         <v>10.478269846537319</v>
       </c>
       <c r="V45" s="1"/>
@@ -5955,16 +5941,36 @@
     </row>
   </sheetData>
   <mergeCells count="56">
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="M44:N44"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="M45:N45"/>
-    <mergeCell ref="A41:I41"/>
-    <mergeCell ref="M41:U41"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="M42:N42"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="M43:N43"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="M25:N25"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="M5:U5"/>
+    <mergeCell ref="M18:U18"/>
+    <mergeCell ref="A13:I13"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="M39:N39"/>
+    <mergeCell ref="M40:N40"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="M37:N37"/>
+    <mergeCell ref="M38:N38"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="M26:N26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="M27:N27"/>
+    <mergeCell ref="A28:I28"/>
+    <mergeCell ref="A16:B16"/>
     <mergeCell ref="A36:I36"/>
     <mergeCell ref="M13:U13"/>
     <mergeCell ref="M36:U36"/>
@@ -5981,36 +5987,16 @@
     <mergeCell ref="M20:N20"/>
     <mergeCell ref="M21:N21"/>
     <mergeCell ref="M22:N22"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="M39:N39"/>
-    <mergeCell ref="M40:N40"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="M37:N37"/>
-    <mergeCell ref="M38:N38"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="M26:N26"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="M27:N27"/>
-    <mergeCell ref="A28:I28"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="M25:N25"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="A5:I5"/>
-    <mergeCell ref="M5:U5"/>
-    <mergeCell ref="M18:U18"/>
-    <mergeCell ref="A13:I13"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="M44:N44"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="M45:N45"/>
+    <mergeCell ref="A41:I41"/>
+    <mergeCell ref="M41:U41"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="M42:N42"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="M43:N43"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C14:I16 C6:I7 C2:I4 C10:I12">

--- a/results_(stress_test)_summary/summary.xlsx
+++ b/results_(stress_test)_summary/summary.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\RnD_Repo\Research_Engineeirng\feature_fusion_PCCxSigmoid-PLV-\results_(stress_test)_summary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AFB12DF-A583-4AEC-AD58-C902FC721171}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1BAF393-681B-457F-874F-5B0B7EE563C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="639" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="partialdata_20260407" sheetId="6" r:id="rId1"/>
-    <sheet name="fullldata_20260407" sheetId="5" r:id="rId2"/>
+    <sheet name="partialdata_20260429" sheetId="6" r:id="rId1"/>
+    <sheet name="fullldata_20260429" sheetId="5" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -434,24 +434,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -552,54 +534,60 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -956,10 +944,10 @@
       <c r="V1" s="12"/>
     </row>
     <row r="2" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="83" t="s">
+      <c r="A2" s="69" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="84"/>
+      <c r="B2" s="70"/>
       <c r="C2" s="20">
         <v>93.101364775358491</v>
       </c>
@@ -993,29 +981,29 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C2:I2)&amp;","</f>
         <v xml:space="preserve">    93.1013647753585, 91.3266637254648, 89.7225610371485, 83.857204647099, 76.2429490451186, 60.4027774173364, 47.7409002961387,</v>
       </c>
-      <c r="M2" s="83" t="s">
+      <c r="M2" s="69" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="84"/>
-      <c r="O2" s="37">
+      <c r="N2" s="70"/>
+      <c r="O2" s="31">
         <v>3.4649270444699574</v>
       </c>
-      <c r="P2" s="38">
+      <c r="P2" s="32">
         <v>4.4611797621615326</v>
       </c>
-      <c r="Q2" s="38">
+      <c r="Q2" s="32">
         <v>4.7712065248821434</v>
       </c>
-      <c r="R2" s="38">
+      <c r="R2" s="32">
         <v>5.3965689103010375</v>
       </c>
-      <c r="S2" s="38">
+      <c r="S2" s="32">
         <v>7.9323757260741923</v>
       </c>
-      <c r="T2" s="38">
+      <c r="T2" s="32">
         <v>9.9900413492801565</v>
       </c>
-      <c r="U2" s="39">
+      <c r="U2" s="33">
         <v>9.7565309936118432</v>
       </c>
       <c r="V2" s="12" t="str">
@@ -1024,36 +1012,36 @@
       </c>
     </row>
     <row r="3" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="83" t="s">
+      <c r="A3" s="69" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="84"/>
-      <c r="C3" s="37">
+      <c r="B3" s="70"/>
+      <c r="C3" s="31">
         <v>93.273358766079312</v>
       </c>
-      <c r="D3" s="38">
+      <c r="D3" s="32">
         <v>91.615587793435367</v>
       </c>
-      <c r="E3" s="38">
+      <c r="E3" s="32">
         <v>90.62053304959386</v>
       </c>
-      <c r="F3" s="38">
+      <c r="F3" s="32">
         <v>86.59751381932368</v>
       </c>
-      <c r="G3" s="38">
+      <c r="G3" s="32">
         <v>78.22435026831262</v>
       </c>
-      <c r="H3" s="38">
+      <c r="H3" s="32">
         <v>60.854992978601317</v>
       </c>
-      <c r="I3" s="39">
+      <c r="I3" s="33">
         <v>48.743933771053378</v>
       </c>
-      <c r="J3" s="41" cm="1">
+      <c r="J3" s="35" cm="1">
         <f t="array" ref="J3">-SUMPRODUCT((D1:H1-C1:G1)*(C3:G3+D3:H3)/2)</f>
         <v>78.807498478937248</v>
       </c>
-      <c r="K3" s="41" cm="1">
+      <c r="K3" s="35" cm="1">
         <f t="array" ref="K3">-SUMPRODUCT((D1:I1-C1:H1)*(C3:H3+D3:I3)/2)</f>
         <v>81.54747164767862</v>
       </c>
@@ -1061,29 +1049,29 @@
         <f t="shared" ref="L3:L4" si="0">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C3:I3)&amp;","</f>
         <v xml:space="preserve">    93.2733587660793, 91.6155877934354, 90.6205330495939, 86.5975138193237, 78.2243502683126, 60.8549929786013, 48.7439337710534,</v>
       </c>
-      <c r="M3" s="83" t="s">
+      <c r="M3" s="69" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="84"/>
-      <c r="O3" s="37">
+      <c r="N3" s="70"/>
+      <c r="O3" s="31">
         <v>3.4672469457762647</v>
       </c>
-      <c r="P3" s="38">
+      <c r="P3" s="32">
         <v>4.1066373858138912</v>
       </c>
-      <c r="Q3" s="38">
+      <c r="Q3" s="32">
         <v>4.4433442831389707</v>
       </c>
-      <c r="R3" s="38">
+      <c r="R3" s="32">
         <v>4.8572661690244194</v>
       </c>
-      <c r="S3" s="38">
+      <c r="S3" s="32">
         <v>6.7334065011993722</v>
       </c>
-      <c r="T3" s="38">
+      <c r="T3" s="32">
         <v>9.3055912140758643</v>
       </c>
-      <c r="U3" s="39">
+      <c r="U3" s="33">
         <v>9.1853207799272329</v>
       </c>
       <c r="V3" s="12" t="str">
@@ -1092,36 +1080,36 @@
       </c>
     </row>
     <row r="4" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="83" t="s">
+      <c r="A4" s="69" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="84"/>
+      <c r="B4" s="70"/>
       <c r="C4" s="24">
         <v>87.593900000000005</v>
       </c>
-      <c r="D4" s="32">
+      <c r="D4" s="26">
         <v>87.663716814159287</v>
       </c>
-      <c r="E4" s="32">
+      <c r="E4" s="26">
         <v>88.112094395280209</v>
       </c>
-      <c r="F4" s="32">
+      <c r="F4" s="26">
         <v>87.970025692263789</v>
       </c>
-      <c r="G4" s="32">
+      <c r="G4" s="26">
         <v>87.461708146264243</v>
       </c>
-      <c r="H4" s="32">
+      <c r="H4" s="26">
         <v>75.251363189416281</v>
       </c>
-      <c r="I4" s="33">
+      <c r="I4" s="27">
         <v>47.720683858280204</v>
       </c>
-      <c r="J4" s="41" cm="1">
+      <c r="J4" s="35" cm="1">
         <f t="array" ref="J4">-SUMPRODUCT((D1:H1-C1:G1)*(C4:G4+D4:H4)/2)</f>
         <v>78.394630770414679</v>
       </c>
-      <c r="K4" s="41" cm="1">
+      <c r="K4" s="35" cm="1">
         <f t="array" ref="K4">-SUMPRODUCT((D1:I1-C1:H1)*(C4:H4+D4:I4)/2)</f>
         <v>81.468931946607086</v>
       </c>
@@ -1129,29 +1117,29 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    87.5939, 87.6637168141593, 88.1120943952802, 87.9700256922638, 87.4617081462642, 75.2513631894163, 47.7206838582802,</v>
       </c>
-      <c r="M4" s="83" t="s">
+      <c r="M4" s="69" t="s">
         <v>10</v>
       </c>
-      <c r="N4" s="84"/>
-      <c r="O4" s="55">
+      <c r="N4" s="70"/>
+      <c r="O4" s="49">
         <v>2.4529187882918819</v>
       </c>
-      <c r="P4" s="32">
+      <c r="P4" s="26">
         <v>2.16276566139488</v>
       </c>
-      <c r="Q4" s="32">
+      <c r="Q4" s="26">
         <v>2.2973398804747198</v>
       </c>
-      <c r="R4" s="32">
+      <c r="R4" s="26">
         <v>2.134165319654592</v>
       </c>
-      <c r="S4" s="32">
+      <c r="S4" s="26">
         <v>2.3834878752826651</v>
       </c>
-      <c r="T4" s="32">
+      <c r="T4" s="26">
         <v>3.787986046410059</v>
       </c>
-      <c r="U4" s="33">
+      <c r="U4" s="27">
         <v>3.7419646549723868</v>
       </c>
       <c r="V4" s="12" t="str">
@@ -1160,31 +1148,31 @@
       </c>
     </row>
     <row r="5" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="83" t="s">
+      <c r="A5" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="85"/>
-      <c r="C5" s="85"/>
-      <c r="D5" s="85"/>
-      <c r="E5" s="85"/>
-      <c r="F5" s="85"/>
-      <c r="G5" s="85"/>
-      <c r="H5" s="85"/>
-      <c r="I5" s="84"/>
-      <c r="J5" s="41"/>
-      <c r="K5" s="41"/>
+      <c r="B5" s="71"/>
+      <c r="C5" s="71"/>
+      <c r="D5" s="71"/>
+      <c r="E5" s="71"/>
+      <c r="F5" s="71"/>
+      <c r="G5" s="71"/>
+      <c r="H5" s="71"/>
+      <c r="I5" s="70"/>
+      <c r="J5" s="35"/>
+      <c r="K5" s="35"/>
       <c r="L5" s="12"/>
-      <c r="M5" s="83" t="s">
+      <c r="M5" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="N5" s="85"/>
-      <c r="O5" s="85"/>
-      <c r="P5" s="85"/>
-      <c r="Q5" s="85"/>
-      <c r="R5" s="85"/>
-      <c r="S5" s="85"/>
-      <c r="T5" s="85"/>
-      <c r="U5" s="84"/>
+      <c r="N5" s="71"/>
+      <c r="O5" s="71"/>
+      <c r="P5" s="71"/>
+      <c r="Q5" s="71"/>
+      <c r="R5" s="71"/>
+      <c r="S5" s="71"/>
+      <c r="T5" s="71"/>
+      <c r="U5" s="70"/>
       <c r="V5" s="12"/>
     </row>
     <row r="6" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -1194,38 +1182,38 @@
       <c r="B6" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="25">
-        <v>93.176991150442475</v>
-      </c>
-      <c r="D6" s="26">
-        <v>92.551622418879049</v>
-      </c>
-      <c r="E6" s="26">
-        <v>91.770912089781632</v>
-      </c>
-      <c r="F6" s="26">
-        <v>88.774349259076644</v>
-      </c>
-      <c r="G6" s="26">
-        <v>85.119574275440684</v>
-      </c>
-      <c r="H6" s="26">
-        <v>65.55219912513661</v>
-      </c>
-      <c r="I6" s="27">
-        <v>55.581651513709751</v>
-      </c>
-      <c r="J6" s="41" cm="1">
+      <c r="C6" s="85">
+        <v>93.40216322517206</v>
+      </c>
+      <c r="D6" s="86">
+        <v>91.827126532236434</v>
+      </c>
+      <c r="E6" s="86">
+        <v>90.558689954065343</v>
+      </c>
+      <c r="F6" s="86">
+        <v>86.023376788149832</v>
+      </c>
+      <c r="G6" s="86">
+        <v>80.076301121405308</v>
+      </c>
+      <c r="H6" s="86">
+        <v>61.71287813908426</v>
+      </c>
+      <c r="I6" s="87">
+        <v>46.423510007295327</v>
+      </c>
+      <c r="J6" s="35" cm="1">
         <f t="array" ref="J6">-SUMPRODUCT((D1:H1-C1:G1)*(C6:G6+D6:H6)/2)</f>
-        <v>80.539204491388332</v>
-      </c>
-      <c r="K6" s="41" cm="1">
+        <v>79.00453781318754</v>
+      </c>
+      <c r="K6" s="35" cm="1">
         <f t="array" ref="K6">-SUMPRODUCT((D1:I1-C1:H1)*(C6:H6+D6:I6)/2)</f>
-        <v>83.567550757359498</v>
+        <v>81.707947516847028</v>
       </c>
       <c r="L6" s="12" t="str">
         <f t="shared" ref="L6:L7" si="2">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C6:I6)&amp;","</f>
-        <v xml:space="preserve">    93.1769911504425, 92.551622418879, 91.7709120897816, 88.7743492590766, 85.1195742754407, 65.5521991251366, 55.5816515137098,</v>
+        <v xml:space="preserve">    93.4021632251721, 91.8271265322364, 90.5586899540653, 86.0233767881498, 80.0763011214053, 61.7128781390843, 46.4235100072953,</v>
       </c>
       <c r="M6" s="7" t="s">
         <v>12</v>
@@ -1233,163 +1221,163 @@
       <c r="N6" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="O6" s="25">
-        <v>3.3980555340015428</v>
-      </c>
-      <c r="P6" s="26">
-        <v>3.2526209506201238</v>
-      </c>
-      <c r="Q6" s="26">
-        <v>3.463276500799247</v>
-      </c>
-      <c r="R6" s="26">
-        <v>4.4197147654757591</v>
-      </c>
-      <c r="S6" s="26">
-        <v>4.9008511372208474</v>
-      </c>
-      <c r="T6" s="26">
-        <v>8.1544027156793923</v>
-      </c>
-      <c r="U6" s="27">
-        <v>8.3944532618135348</v>
+      <c r="O6" s="85">
+        <v>3.395734543818977</v>
+      </c>
+      <c r="P6" s="86">
+        <v>4.0701241715569392</v>
+      </c>
+      <c r="Q6" s="86">
+        <v>4.2545139093922257</v>
+      </c>
+      <c r="R6" s="86">
+        <v>5.0550386107492153</v>
+      </c>
+      <c r="S6" s="86">
+        <v>5.5998181447012403</v>
+      </c>
+      <c r="T6" s="86">
+        <v>8.7815136499154747</v>
+      </c>
+      <c r="U6" s="87">
+        <v>8.6649338950065129</v>
       </c>
       <c r="V6" s="12" t="str">
         <f t="shared" ref="V6:V7" si="3">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,O6:U6)&amp;","</f>
-        <v xml:space="preserve">    3.39805553400154, 3.25262095062012, 3.46327650079925, 4.41971476547576, 4.90085113722085, 8.15440271567939, 8.39445326181353,</v>
+        <v xml:space="preserve">    3.39573454381898, 4.07012417155694, 4.25451390939223, 5.05503861074922, 5.59981814470124, 8.78151364991547, 8.66493389500651,</v>
       </c>
     </row>
     <row r="7" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B7" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="40">
-        <v>92.538862792930757</v>
-      </c>
-      <c r="D7" s="41">
-        <v>92.596859257721377</v>
-      </c>
-      <c r="E7" s="41">
-        <v>92.131765845725312</v>
-      </c>
-      <c r="F7" s="41">
-        <v>91.399484424605745</v>
-      </c>
-      <c r="G7" s="41">
-        <v>88.38645086318509</v>
-      </c>
-      <c r="H7" s="41">
-        <v>71.063506893081538</v>
-      </c>
-      <c r="I7" s="42">
-        <v>52.957470797036883</v>
-      </c>
-      <c r="J7" s="41" cm="1">
+      <c r="C7" s="85">
+        <v>92.691248770894788</v>
+      </c>
+      <c r="D7" s="86">
+        <v>92.706981317600793</v>
+      </c>
+      <c r="E7" s="86">
+        <v>91.734513274336265</v>
+      </c>
+      <c r="F7" s="86">
+        <v>88.867553640890762</v>
+      </c>
+      <c r="G7" s="86">
+        <v>87.5647050003316</v>
+      </c>
+      <c r="H7" s="86">
+        <v>75.623785672886441</v>
+      </c>
+      <c r="I7" s="87">
+        <v>48.831339371447839</v>
+      </c>
+      <c r="J7" s="35" cm="1">
         <f t="array" ref="J7">-SUMPRODUCT((D1:H1-C1:G1)*(C7:G7+D7:H7)/2)</f>
-        <v>81.547963073498323</v>
-      </c>
-      <c r="K7" s="41" cm="1">
+        <v>81.271209742298794</v>
+      </c>
+      <c r="K7" s="35" cm="1">
         <f t="array" ref="K7">-SUMPRODUCT((D1:I1-C1:H1)*(C7:H7+D7:I7)/2)</f>
-        <v>84.648487515751285</v>
+        <v>84.382587868407157</v>
       </c>
       <c r="L7" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">    92.5388627929308, 92.5968592577214, 92.1317658457253, 91.3994844246057, 88.3864508631851, 71.0635068930815, 52.9574707970369,</v>
+        <v xml:space="preserve">    92.6912487708948, 92.7069813176008, 91.7345132743363, 88.8675536408908, 87.5647050003316, 75.6237856728864, 48.8313393714478,</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N7" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="O7" s="40">
-        <v>3.278810540442274</v>
-      </c>
-      <c r="P7" s="41">
-        <v>3.2750469252400021</v>
-      </c>
-      <c r="Q7" s="41">
-        <v>3.0872319165878661</v>
-      </c>
-      <c r="R7" s="41">
-        <v>3.116510241534836</v>
-      </c>
-      <c r="S7" s="41">
-        <v>3.6330124165638931</v>
-      </c>
-      <c r="T7" s="41">
-        <v>5.8392378785926198</v>
-      </c>
-      <c r="U7" s="42">
-        <v>5.8333958789788376</v>
+      <c r="O7" s="58">
+        <v>3.1492092951527728</v>
+      </c>
+      <c r="P7" s="59">
+        <v>3.3182076336991431</v>
+      </c>
+      <c r="Q7" s="59">
+        <v>3.198166186176159</v>
+      </c>
+      <c r="R7" s="59">
+        <v>3.1321269598885868</v>
+      </c>
+      <c r="S7" s="59">
+        <v>3.0750631997727318</v>
+      </c>
+      <c r="T7" s="59">
+        <v>5.166114204995413</v>
+      </c>
+      <c r="U7" s="60">
+        <v>5.9316401890770027</v>
       </c>
       <c r="V7" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">    3.27881054044227, 3.27504692524, 3.08723191658787, 3.11651024153484, 3.63301241656389, 5.83923787859262, 5.83339587897884,</v>
+        <v xml:space="preserve">    3.14920929515277, 3.31820763369914, 3.19816618617616, 3.13212695988859, 3.07506319977273, 5.16611420499541, 5.931640189077,</v>
       </c>
     </row>
     <row r="8" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="83" t="s">
+      <c r="A8" s="69" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="85"/>
-      <c r="C8" s="90"/>
-      <c r="D8" s="90"/>
-      <c r="E8" s="90"/>
-      <c r="F8" s="90"/>
-      <c r="G8" s="90"/>
-      <c r="H8" s="90"/>
-      <c r="I8" s="89"/>
-      <c r="J8" s="41"/>
-      <c r="K8" s="41"/>
+      <c r="B8" s="71"/>
+      <c r="C8" s="72"/>
+      <c r="D8" s="72"/>
+      <c r="E8" s="72"/>
+      <c r="F8" s="72"/>
+      <c r="G8" s="72"/>
+      <c r="H8" s="72"/>
+      <c r="I8" s="73"/>
+      <c r="J8" s="35"/>
+      <c r="K8" s="35"/>
       <c r="L8" s="12"/>
-      <c r="M8" s="83" t="s">
+      <c r="M8" s="69" t="s">
         <v>22</v>
       </c>
-      <c r="N8" s="85"/>
-      <c r="O8" s="90"/>
-      <c r="P8" s="90"/>
-      <c r="Q8" s="90"/>
-      <c r="R8" s="90"/>
-      <c r="S8" s="90"/>
-      <c r="T8" s="90"/>
-      <c r="U8" s="89"/>
+      <c r="N8" s="71"/>
+      <c r="O8" s="72"/>
+      <c r="P8" s="72"/>
+      <c r="Q8" s="72"/>
+      <c r="R8" s="72"/>
+      <c r="S8" s="72"/>
+      <c r="T8" s="72"/>
+      <c r="U8" s="73"/>
       <c r="V8" s="12"/>
     </row>
     <row r="9" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="83" t="s">
+      <c r="A9" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="84"/>
-      <c r="C9" s="37">
+      <c r="B9" s="70"/>
+      <c r="C9" s="31">
         <v>93.782740335124032</v>
       </c>
-      <c r="D9" s="38">
+      <c r="D9" s="32">
         <v>91.948208894540599</v>
       </c>
-      <c r="E9" s="38">
+      <c r="E9" s="32">
         <v>90.212980504444957</v>
       </c>
-      <c r="F9" s="38">
+      <c r="F9" s="32">
         <v>84.630388959535409</v>
       </c>
-      <c r="G9" s="38">
+      <c r="G9" s="32">
         <v>75.371093175546491</v>
       </c>
-      <c r="H9" s="38">
+      <c r="H9" s="32">
         <v>59.627211308056303</v>
       </c>
-      <c r="I9" s="39">
+      <c r="I9" s="33">
         <v>47.844185503334799</v>
       </c>
-      <c r="J9" s="41" cm="1">
+      <c r="J9" s="35" cm="1">
         <f t="array" ref="J9">-SUMPRODUCT((D1:H1-C1:G1)*(C9:G9+D9:H9)/2)</f>
         <v>78.220843605913544</v>
       </c>
-      <c r="K9" s="41" cm="1">
+      <c r="K9" s="35" cm="1">
         <f t="array" ref="K9">-SUMPRODUCT((D1:I1-C1:H1)*(C9:H9+D9:I9)/2)</f>
         <v>80.907628526198323</v>
       </c>
@@ -1397,29 +1385,29 @@
         <f t="shared" ref="L9:L12" si="4">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C9:I9)&amp;","</f>
         <v xml:space="preserve">    93.782740335124, 91.9482088945406, 90.212980504445, 84.6303889595354, 75.3710931755465, 59.6272113080563, 47.8441855033348,</v>
       </c>
-      <c r="M9" s="83" t="s">
+      <c r="M9" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="N9" s="84"/>
-      <c r="O9" s="37">
+      <c r="N9" s="70"/>
+      <c r="O9" s="31">
         <v>3.5391983918820551</v>
       </c>
-      <c r="P9" s="38">
+      <c r="P9" s="32">
         <v>4.1060038651541966</v>
       </c>
-      <c r="Q9" s="38">
+      <c r="Q9" s="32">
         <v>4.774795806468676</v>
       </c>
-      <c r="R9" s="38">
+      <c r="R9" s="32">
         <v>5.3483339064680431</v>
       </c>
-      <c r="S9" s="38">
+      <c r="S9" s="32">
         <v>8.0994903921197494</v>
       </c>
-      <c r="T9" s="38">
+      <c r="T9" s="32">
         <v>10.59987402205407</v>
       </c>
-      <c r="U9" s="39">
+      <c r="U9" s="33">
         <v>8.7604668874903737</v>
       </c>
       <c r="V9" s="12" t="str">
@@ -1428,36 +1416,36 @@
       </c>
     </row>
     <row r="10" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="88" t="s">
+      <c r="A10" s="74" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="89"/>
-      <c r="C10" s="40">
+      <c r="B10" s="73"/>
+      <c r="C10" s="34">
         <v>93.226230330712227</v>
       </c>
-      <c r="D10" s="41">
+      <c r="D10" s="35">
         <v>91.83329152212967</v>
       </c>
-      <c r="E10" s="41">
+      <c r="E10" s="35">
         <v>90.325291164571794</v>
       </c>
-      <c r="F10" s="41">
+      <c r="F10" s="35">
         <v>85.383492360083878</v>
       </c>
-      <c r="G10" s="41">
+      <c r="G10" s="35">
         <v>76.567000291236639</v>
       </c>
-      <c r="H10" s="41">
+      <c r="H10" s="35">
         <v>59.41454222499042</v>
       </c>
-      <c r="I10" s="42">
+      <c r="I10" s="36">
         <v>50.563407411252108</v>
       </c>
-      <c r="J10" s="41" cm="1">
+      <c r="J10" s="35" cm="1">
         <f t="array" ref="J10">-SUMPRODUCT((D1:H1-C1:G1)*(C10:G10+D10:H10)/2)</f>
         <v>78.369743178285859</v>
       </c>
-      <c r="K10" s="41" cm="1">
+      <c r="K10" s="35" cm="1">
         <f t="array" ref="K10">-SUMPRODUCT((D1:I1-C1:H1)*(C10:H10+D10:I10)/2)</f>
         <v>81.11919191919192</v>
       </c>
@@ -1465,29 +1453,29 @@
         <f t="shared" si="4"/>
         <v xml:space="preserve">    93.2262303307122, 91.8332915221297, 90.3252911645718, 85.3834923600839, 76.5670002912366, 59.4145422249904, 50.5634074112521,</v>
       </c>
-      <c r="M10" s="83" t="s">
+      <c r="M10" s="69" t="s">
         <v>8</v>
       </c>
-      <c r="N10" s="84"/>
-      <c r="O10" s="40">
+      <c r="N10" s="70"/>
+      <c r="O10" s="34">
         <v>3.945711842949601</v>
       </c>
-      <c r="P10" s="41">
+      <c r="P10" s="35">
         <v>4.8525950161134093</v>
       </c>
-      <c r="Q10" s="41">
+      <c r="Q10" s="35">
         <v>4.4346894499148144</v>
       </c>
-      <c r="R10" s="41">
+      <c r="R10" s="35">
         <v>5.4810029574676529</v>
       </c>
-      <c r="S10" s="41">
+      <c r="S10" s="35">
         <v>8.4636725644600066</v>
       </c>
-      <c r="T10" s="41">
+      <c r="T10" s="35">
         <v>10.788297692871961</v>
       </c>
-      <c r="U10" s="42">
+      <c r="U10" s="36">
         <v>8.7433484877826491</v>
       </c>
       <c r="V10" s="12" t="str">
@@ -1496,36 +1484,36 @@
       </c>
     </row>
     <row r="11" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="83" t="s">
+      <c r="A11" s="69" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="84"/>
-      <c r="C11" s="40">
+      <c r="B11" s="70"/>
+      <c r="C11" s="34">
         <v>93.004922187908207</v>
       </c>
-      <c r="D11" s="41">
+      <c r="D11" s="35">
         <v>91.518502178507859</v>
       </c>
-      <c r="E11" s="41">
+      <c r="E11" s="35">
         <v>89.729420958082102</v>
       </c>
-      <c r="F11" s="41">
+      <c r="F11" s="35">
         <v>83.348607398564567</v>
       </c>
-      <c r="G11" s="41">
+      <c r="G11" s="35">
         <v>74.087719905304837</v>
       </c>
-      <c r="H11" s="41">
+      <c r="H11" s="35">
         <v>57.917332041511322</v>
       </c>
-      <c r="I11" s="42">
+      <c r="I11" s="36">
         <v>48.007794185070807</v>
       </c>
-      <c r="J11" s="41" cm="1">
+      <c r="J11" s="35" cm="1">
         <f t="array" ref="J11">-SUMPRODUCT((D1:H1-C1:G1)*(C11:G11+D11:H11)/2)</f>
         <v>77.501290236074709</v>
       </c>
-      <c r="K11" s="41" cm="1">
+      <c r="K11" s="35" cm="1">
         <f t="array" ref="K11">-SUMPRODUCT((D1:I1-C1:H1)*(C11:H11+D11:I11)/2)</f>
         <v>80.14941839173926</v>
       </c>
@@ -1533,29 +1521,29 @@
         <f t="shared" si="4"/>
         <v xml:space="preserve">    93.0049221879082, 91.5185021785079, 89.7294209580821, 83.3486073985646, 74.0877199053048, 57.9173320415113, 48.0077941850708,</v>
       </c>
-      <c r="M11" s="83" t="s">
+      <c r="M11" s="69" t="s">
         <v>23</v>
       </c>
-      <c r="N11" s="84"/>
-      <c r="O11" s="40">
+      <c r="N11" s="70"/>
+      <c r="O11" s="34">
         <v>3.690401528555848</v>
       </c>
-      <c r="P11" s="41">
+      <c r="P11" s="35">
         <v>4.2469367469027457</v>
       </c>
-      <c r="Q11" s="41">
+      <c r="Q11" s="35">
         <v>4.4611096369834957</v>
       </c>
-      <c r="R11" s="41">
+      <c r="R11" s="35">
         <v>5.4089286426803449</v>
       </c>
-      <c r="S11" s="41">
+      <c r="S11" s="35">
         <v>9.092124974067179</v>
       </c>
-      <c r="T11" s="41">
+      <c r="T11" s="35">
         <v>10.83557708581068</v>
       </c>
-      <c r="U11" s="42">
+      <c r="U11" s="36">
         <v>9.2904800440053528</v>
       </c>
       <c r="V11" s="12" t="str">
@@ -1564,36 +1552,36 @@
       </c>
     </row>
     <row r="12" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="83" t="s">
+      <c r="A12" s="69" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="84"/>
-      <c r="C12" s="43">
+      <c r="B12" s="70"/>
+      <c r="C12" s="37">
         <v>93.123279613145442</v>
       </c>
-      <c r="D12" s="44">
+      <c r="D12" s="38">
         <v>91.674385879923975</v>
       </c>
-      <c r="E12" s="44">
+      <c r="E12" s="38">
         <v>89.698688281617194</v>
       </c>
-      <c r="F12" s="44">
+      <c r="F12" s="38">
         <v>84.957067102656595</v>
       </c>
-      <c r="G12" s="44">
+      <c r="G12" s="38">
         <v>75.939082518014857</v>
       </c>
-      <c r="H12" s="44">
+      <c r="H12" s="38">
         <v>59.995092229748238</v>
       </c>
-      <c r="I12" s="45">
+      <c r="I12" s="39">
         <v>48.440303693515233</v>
       </c>
-      <c r="J12" s="41" cm="1">
+      <c r="J12" s="35" cm="1">
         <f t="array" ref="J12">-SUMPRODUCT((D1:H1-C1:G1)*(C12:G12+D12:H12)/2)</f>
         <v>78.078434213675436</v>
       </c>
-      <c r="K12" s="41" cm="1">
+      <c r="K12" s="35" cm="1">
         <f t="array" ref="K12">-SUMPRODUCT((D1:I1-C1:H1)*(C12:H12+D12:I12)/2)</f>
         <v>80.789319111757024</v>
       </c>
@@ -1601,29 +1589,29 @@
         <f t="shared" si="4"/>
         <v xml:space="preserve">    93.1232796131454, 91.674385879924, 89.6986882816172, 84.9570671026566, 75.9390825180149, 59.9950922297482, 48.4403036935152,</v>
       </c>
-      <c r="M12" s="83" t="s">
+      <c r="M12" s="69" t="s">
         <v>24</v>
       </c>
-      <c r="N12" s="84"/>
-      <c r="O12" s="43">
+      <c r="N12" s="70"/>
+      <c r="O12" s="37">
         <v>3.8088682011350912</v>
       </c>
-      <c r="P12" s="44">
+      <c r="P12" s="38">
         <v>4.4783864386850611</v>
       </c>
-      <c r="Q12" s="44">
+      <c r="Q12" s="38">
         <v>5.0849840192173117</v>
       </c>
-      <c r="R12" s="44">
+      <c r="R12" s="38">
         <v>5.0366327026230584</v>
       </c>
-      <c r="S12" s="44">
+      <c r="S12" s="38">
         <v>7.6643798786674449</v>
       </c>
-      <c r="T12" s="44">
+      <c r="T12" s="38">
         <v>10.05146904627655</v>
       </c>
-      <c r="U12" s="45">
+      <c r="U12" s="39">
         <v>9.821397671709315</v>
       </c>
       <c r="V12" s="12" t="str">
@@ -1632,64 +1620,64 @@
       </c>
     </row>
     <row r="13" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="83" t="s">
+      <c r="A13" s="69" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="85"/>
-      <c r="C13" s="86"/>
-      <c r="D13" s="86"/>
-      <c r="E13" s="86"/>
-      <c r="F13" s="86"/>
-      <c r="G13" s="86"/>
-      <c r="H13" s="86"/>
-      <c r="I13" s="87"/>
-      <c r="J13" s="41"/>
-      <c r="K13" s="41"/>
+      <c r="B13" s="71"/>
+      <c r="C13" s="75"/>
+      <c r="D13" s="75"/>
+      <c r="E13" s="75"/>
+      <c r="F13" s="75"/>
+      <c r="G13" s="75"/>
+      <c r="H13" s="75"/>
+      <c r="I13" s="76"/>
+      <c r="J13" s="35"/>
+      <c r="K13" s="35"/>
       <c r="L13" s="12"/>
-      <c r="M13" s="83" t="s">
+      <c r="M13" s="69" t="s">
         <v>25</v>
       </c>
-      <c r="N13" s="85"/>
-      <c r="O13" s="86"/>
-      <c r="P13" s="86"/>
-      <c r="Q13" s="86"/>
-      <c r="R13" s="86"/>
-      <c r="S13" s="86"/>
-      <c r="T13" s="86"/>
-      <c r="U13" s="87"/>
+      <c r="N13" s="71"/>
+      <c r="O13" s="75"/>
+      <c r="P13" s="75"/>
+      <c r="Q13" s="75"/>
+      <c r="R13" s="75"/>
+      <c r="S13" s="75"/>
+      <c r="T13" s="75"/>
+      <c r="U13" s="76"/>
       <c r="V13" s="12"/>
     </row>
     <row r="14" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="83" t="s">
+      <c r="A14" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="84"/>
-      <c r="C14" s="37">
+      <c r="B14" s="70"/>
+      <c r="C14" s="31">
         <v>92.969518190757128</v>
       </c>
-      <c r="D14" s="38">
+      <c r="D14" s="32">
         <v>91.851524090462149</v>
       </c>
-      <c r="E14" s="38">
+      <c r="E14" s="32">
         <v>90.756145526057011</v>
       </c>
-      <c r="F14" s="38">
+      <c r="F14" s="32">
         <v>87.253136561158271</v>
       </c>
-      <c r="G14" s="38">
+      <c r="G14" s="32">
         <v>81.178972136437139</v>
       </c>
-      <c r="H14" s="38">
+      <c r="H14" s="32">
         <v>57.386929529378847</v>
       </c>
-      <c r="I14" s="39">
+      <c r="I14" s="33">
         <v>44.855442809482213</v>
       </c>
-      <c r="J14" s="41" cm="1">
+      <c r="J14" s="35" cm="1">
         <f t="array" ref="J14">-SUMPRODUCT((D1:H1-C1:G1)*(C14:G14+D14:H14)/2)</f>
         <v>79.079417714109411</v>
       </c>
-      <c r="K14" s="41" cm="1">
+      <c r="K14" s="35" cm="1">
         <f t="array" ref="K14">-SUMPRODUCT((D1:I1-C1:H1)*(C14:H14+D14:I14)/2)</f>
         <v>81.635477022580943</v>
       </c>
@@ -1697,29 +1685,29 @@
         <f t="shared" ref="L14:L17" si="6">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C14:I14)&amp;","</f>
         <v xml:space="preserve">    92.9695181907571, 91.8515240904621, 90.756145526057, 87.2531365611583, 81.1789721364371, 57.3869295293788, 44.8554428094822,</v>
       </c>
-      <c r="M14" s="83" t="s">
+      <c r="M14" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="N14" s="84"/>
-      <c r="O14" s="37">
+      <c r="N14" s="70"/>
+      <c r="O14" s="31">
         <v>3.3991921823554931</v>
       </c>
-      <c r="P14" s="38">
+      <c r="P14" s="32">
         <v>3.6561489783789969</v>
       </c>
-      <c r="Q14" s="38">
+      <c r="Q14" s="32">
         <v>3.4316179388806831</v>
       </c>
-      <c r="R14" s="38">
+      <c r="R14" s="32">
         <v>3.3610781227617821</v>
       </c>
-      <c r="S14" s="38">
+      <c r="S14" s="32">
         <v>5.2773835873092807</v>
       </c>
-      <c r="T14" s="38">
+      <c r="T14" s="32">
         <v>8.2027130196510409</v>
       </c>
-      <c r="U14" s="39">
+      <c r="U14" s="33">
         <v>5.203571843512913</v>
       </c>
       <c r="V14" s="12" t="str">
@@ -1728,36 +1716,36 @@
       </c>
     </row>
     <row r="15" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="88" t="s">
+      <c r="A15" s="74" t="s">
         <v>8</v>
       </c>
-      <c r="B15" s="89"/>
-      <c r="C15" s="40">
+      <c r="B15" s="73"/>
+      <c r="C15" s="34">
         <v>91.898721730580135</v>
       </c>
-      <c r="D15" s="41">
+      <c r="D15" s="35">
         <v>90.765995668936</v>
       </c>
-      <c r="E15" s="41">
+      <c r="E15" s="35">
         <v>89.705268500015848</v>
       </c>
-      <c r="F15" s="41">
+      <c r="F15" s="35">
         <v>87.959685349065893</v>
       </c>
-      <c r="G15" s="41">
+      <c r="G15" s="35">
         <v>85.750000720882824</v>
       </c>
-      <c r="H15" s="41">
+      <c r="H15" s="35">
         <v>71.387388010853613</v>
       </c>
-      <c r="I15" s="42">
+      <c r="I15" s="36">
         <v>45.596343105620853</v>
       </c>
-      <c r="J15" s="41" cm="1">
+      <c r="J15" s="35" cm="1">
         <f t="array" ref="J15">-SUMPRODUCT((D1:H1-C1:G1)*(C15:G15+D15:H15)/2)</f>
         <v>79.700846821050931</v>
       </c>
-      <c r="K15" s="41" cm="1">
+      <c r="K15" s="35" cm="1">
         <f t="array" ref="K15">-SUMPRODUCT((D1:I1-C1:H1)*(C15:H15+D15:I15)/2)</f>
         <v>82.625440098962798</v>
       </c>
@@ -1765,29 +1753,29 @@
         <f t="shared" si="6"/>
         <v xml:space="preserve">    91.8987217305801, 90.765995668936, 89.7052685000158, 87.9596853490659, 85.7500007208828, 71.3873880108536, 45.5963431056209,</v>
       </c>
-      <c r="M15" s="83" t="s">
+      <c r="M15" s="69" t="s">
         <v>8</v>
       </c>
-      <c r="N15" s="84"/>
-      <c r="O15" s="40">
+      <c r="N15" s="70"/>
+      <c r="O15" s="34">
         <v>3.190312271555559</v>
       </c>
-      <c r="P15" s="41">
+      <c r="P15" s="35">
         <v>2.8828036064622768</v>
       </c>
-      <c r="Q15" s="41">
+      <c r="Q15" s="35">
         <v>2.5884740771146331</v>
       </c>
-      <c r="R15" s="41">
+      <c r="R15" s="35">
         <v>2.6213450470877251</v>
       </c>
-      <c r="S15" s="41">
+      <c r="S15" s="35">
         <v>3.203569989687661</v>
       </c>
-      <c r="T15" s="41">
+      <c r="T15" s="35">
         <v>4.756712112750666</v>
       </c>
-      <c r="U15" s="42">
+      <c r="U15" s="36">
         <v>2.488810891584841</v>
       </c>
       <c r="V15" s="12" t="str">
@@ -1796,36 +1784,36 @@
       </c>
     </row>
     <row r="16" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="83" t="s">
+      <c r="A16" s="69" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="84"/>
-      <c r="C16" s="40">
+      <c r="B16" s="70"/>
+      <c r="C16" s="34">
         <v>93.044276622923505</v>
       </c>
-      <c r="D16" s="41">
+      <c r="D16" s="35">
         <v>91.935155148400938</v>
       </c>
-      <c r="E16" s="41">
+      <c r="E16" s="35">
         <v>90.94889229145582</v>
       </c>
-      <c r="F16" s="41">
+      <c r="F16" s="35">
         <v>85.952505356159378</v>
       </c>
-      <c r="G16" s="41">
+      <c r="G16" s="35">
         <v>78.915183810701947</v>
       </c>
-      <c r="H16" s="41">
+      <c r="H16" s="35">
         <v>59.442100133507502</v>
       </c>
-      <c r="I16" s="42">
+      <c r="I16" s="36">
         <v>49.533828147302302</v>
       </c>
-      <c r="J16" s="41" cm="1">
+      <c r="J16" s="35" cm="1">
         <f t="array" ref="J16">-SUMPRODUCT((D1:H1-C1:G1)*(C16:G16+D16:H16)/2)</f>
         <v>78.834323321712716</v>
       </c>
-      <c r="K16" s="41" cm="1">
+      <c r="K16" s="35" cm="1">
         <f t="array" ref="K16">-SUMPRODUCT((D1:I1-C1:H1)*(C16:H16+D16:I16)/2)</f>
         <v>81.55872152873296</v>
       </c>
@@ -1833,29 +1821,29 @@
         <f t="shared" si="6"/>
         <v xml:space="preserve">    93.0442766229235, 91.9351551484009, 90.9488922914558, 85.9525053561594, 78.9151838107019, 59.4421001335075, 49.5338281473023,</v>
       </c>
-      <c r="M16" s="83" t="s">
+      <c r="M16" s="69" t="s">
         <v>23</v>
       </c>
-      <c r="N16" s="84"/>
-      <c r="O16" s="40">
+      <c r="N16" s="70"/>
+      <c r="O16" s="34">
         <v>3.72078192123604</v>
       </c>
-      <c r="P16" s="41">
+      <c r="P16" s="35">
         <v>4.0467152776216686</v>
       </c>
-      <c r="Q16" s="41">
+      <c r="Q16" s="35">
         <v>4.0235763627769954</v>
       </c>
-      <c r="R16" s="41">
+      <c r="R16" s="35">
         <v>4.4767633212331157</v>
       </c>
-      <c r="S16" s="41">
+      <c r="S16" s="35">
         <v>7.2019016527503927</v>
       </c>
-      <c r="T16" s="41">
+      <c r="T16" s="35">
         <v>10.04668436860082</v>
       </c>
-      <c r="U16" s="42">
+      <c r="U16" s="36">
         <v>9.2355901481835172</v>
       </c>
       <c r="V16" s="12" t="str">
@@ -1864,36 +1852,36 @@
       </c>
     </row>
     <row r="17" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="83" t="s">
+      <c r="A17" s="69" t="s">
         <v>24</v>
       </c>
-      <c r="B17" s="84"/>
-      <c r="C17" s="43">
+      <c r="B17" s="70"/>
+      <c r="C17" s="37">
         <v>93.174110502686005</v>
       </c>
-      <c r="D17" s="44">
+      <c r="D17" s="38">
         <v>91.391724841910417</v>
       </c>
-      <c r="E17" s="44">
+      <c r="E17" s="38">
         <v>89.591539142495463</v>
       </c>
-      <c r="F17" s="44">
+      <c r="F17" s="38">
         <v>84.690597092823751</v>
       </c>
-      <c r="G17" s="44">
+      <c r="G17" s="38">
         <v>76.401347185817656</v>
       </c>
-      <c r="H17" s="44">
+      <c r="H17" s="38">
         <v>59.963667505774268</v>
       </c>
-      <c r="I17" s="45">
+      <c r="I17" s="39">
         <v>47.725577210875521</v>
       </c>
-      <c r="J17" s="41" cm="1">
+      <c r="J17" s="35" cm="1">
         <f t="array" ref="J17">-SUMPRODUCT((D1:H1-C1:G1)*(C17:G17+D17:H17)/2)</f>
         <v>77.994698988168864</v>
       </c>
-      <c r="K17" s="41" cm="1">
+      <c r="K17" s="35" cm="1">
         <f t="array" ref="K17">-SUMPRODUCT((D1:I1-C1:H1)*(C17:H17+D17:I17)/2)</f>
         <v>80.686930106085114</v>
       </c>
@@ -1901,29 +1889,29 @@
         <f t="shared" si="6"/>
         <v xml:space="preserve">    93.174110502686, 91.3917248419104, 89.5915391424955, 84.6905970928238, 76.4013471858177, 59.9636675057743, 47.7255772108755,</v>
       </c>
-      <c r="M17" s="83" t="s">
+      <c r="M17" s="69" t="s">
         <v>24</v>
       </c>
-      <c r="N17" s="84"/>
-      <c r="O17" s="43">
+      <c r="N17" s="70"/>
+      <c r="O17" s="37">
         <v>3.8766021792735019</v>
       </c>
-      <c r="P17" s="44">
+      <c r="P17" s="38">
         <v>4.8126411406228078</v>
       </c>
-      <c r="Q17" s="44">
+      <c r="Q17" s="38">
         <v>4.6512210016047986</v>
       </c>
-      <c r="R17" s="44">
+      <c r="R17" s="38">
         <v>5.2416066355763284</v>
       </c>
-      <c r="S17" s="44">
+      <c r="S17" s="38">
         <v>8.0769588602235256</v>
       </c>
-      <c r="T17" s="44">
+      <c r="T17" s="38">
         <v>10.657363307561541</v>
       </c>
-      <c r="U17" s="45">
+      <c r="U17" s="39">
         <v>9.200486032966916</v>
       </c>
       <c r="V17" s="12" t="str">
@@ -1932,26 +1920,26 @@
       </c>
     </row>
     <row r="18" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="31"/>
-      <c r="B18" s="31"/>
-      <c r="C18" s="31"/>
-      <c r="D18" s="31"/>
-      <c r="E18" s="31"/>
-      <c r="F18" s="31"/>
-      <c r="G18" s="31"/>
-      <c r="H18" s="31"/>
-      <c r="I18" s="31"/>
-      <c r="J18" s="31"/>
-      <c r="K18" s="31"/>
-      <c r="M18" s="31"/>
-      <c r="N18" s="31"/>
-      <c r="O18" s="31"/>
-      <c r="P18" s="31"/>
-      <c r="Q18" s="31"/>
-      <c r="R18" s="31"/>
-      <c r="S18" s="31"/>
-      <c r="T18" s="31"/>
-      <c r="U18" s="31"/>
+      <c r="A18" s="25"/>
+      <c r="B18" s="25"/>
+      <c r="C18" s="25"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="25"/>
+      <c r="G18" s="25"/>
+      <c r="H18" s="25"/>
+      <c r="I18" s="25"/>
+      <c r="J18" s="25"/>
+      <c r="K18" s="25"/>
+      <c r="M18" s="25"/>
+      <c r="N18" s="25"/>
+      <c r="O18" s="25"/>
+      <c r="P18" s="25"/>
+      <c r="Q18" s="25"/>
+      <c r="R18" s="25"/>
+      <c r="S18" s="25"/>
+      <c r="T18" s="25"/>
+      <c r="U18" s="25"/>
     </row>
     <row r="19" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
@@ -2014,60 +2002,60 @@
       <c r="V19" s="1"/>
     </row>
     <row r="20" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="75" t="s">
+      <c r="A20" s="77" t="s">
         <v>5</v>
       </c>
-      <c r="B20" s="76"/>
-      <c r="C20" s="47">
+      <c r="B20" s="78"/>
+      <c r="C20" s="41">
         <v>92.567111769713335</v>
       </c>
-      <c r="D20" s="47">
+      <c r="D20" s="41">
         <v>90.835858608343599</v>
       </c>
-      <c r="E20" s="47">
+      <c r="E20" s="41">
         <v>89.217505339533233</v>
       </c>
-      <c r="F20" s="47">
+      <c r="F20" s="41">
         <v>83.237245964288078</v>
       </c>
-      <c r="G20" s="47">
+      <c r="G20" s="41">
         <v>75.380430844191011</v>
       </c>
-      <c r="H20" s="47">
+      <c r="H20" s="41">
         <v>58.994367187597383</v>
       </c>
-      <c r="I20" s="48">
+      <c r="I20" s="42">
         <v>43.622535641382179</v>
       </c>
-      <c r="J20" s="50"/>
-      <c r="K20" s="50"/>
+      <c r="J20" s="44"/>
+      <c r="K20" s="44"/>
       <c r="L20" s="1" t="str">
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C20:I20)&amp;","</f>
         <v xml:space="preserve">    92.5671117697133, 90.8358586083436, 89.2175053395332, 83.2372459642881, 75.380430844191, 58.9943671875974, 43.6225356413822,</v>
       </c>
-      <c r="M20" s="75" t="s">
+      <c r="M20" s="77" t="s">
         <v>5</v>
       </c>
-      <c r="N20" s="76"/>
-      <c r="O20" s="46">
+      <c r="N20" s="78"/>
+      <c r="O20" s="40">
         <v>3.88093621561358</v>
       </c>
-      <c r="P20" s="47">
+      <c r="P20" s="41">
         <v>4.8164746829677396</v>
       </c>
-      <c r="Q20" s="47">
+      <c r="Q20" s="41">
         <v>5.2250608386616522</v>
       </c>
-      <c r="R20" s="47">
+      <c r="R20" s="41">
         <v>5.6675721086724113</v>
       </c>
-      <c r="S20" s="47">
+      <c r="S20" s="41">
         <v>8.3263283482936075</v>
       </c>
-      <c r="T20" s="47">
+      <c r="T20" s="41">
         <v>10.49020927094638</v>
       </c>
-      <c r="U20" s="48">
+      <c r="U20" s="42">
         <v>11.060437347759546</v>
       </c>
       <c r="V20" s="1" t="str">
@@ -2076,60 +2064,60 @@
       </c>
     </row>
     <row r="21" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="75" t="s">
+      <c r="A21" s="77" t="s">
         <v>6</v>
       </c>
-      <c r="B21" s="76"/>
-      <c r="C21" s="47">
+      <c r="B21" s="78"/>
+      <c r="C21" s="41">
         <v>92.866950218042462</v>
       </c>
-      <c r="D21" s="47">
+      <c r="D21" s="41">
         <v>91.242690764745561</v>
       </c>
-      <c r="E21" s="47">
+      <c r="E21" s="41">
         <v>90.137053227698445</v>
       </c>
-      <c r="F21" s="47">
+      <c r="F21" s="41">
         <v>86.080152926613408</v>
       </c>
-      <c r="G21" s="47">
+      <c r="G21" s="41">
         <v>77.410217255196784</v>
       </c>
-      <c r="H21" s="47">
+      <c r="H21" s="41">
         <v>59.676194764980139</v>
       </c>
-      <c r="I21" s="48">
+      <c r="I21" s="42">
         <v>46.395490419404197</v>
       </c>
-      <c r="J21" s="50"/>
-      <c r="K21" s="50"/>
+      <c r="J21" s="44"/>
+      <c r="K21" s="44"/>
       <c r="L21" s="1" t="str">
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C21:I21)&amp;","</f>
         <v xml:space="preserve">    92.8669502180425, 91.2426907647456, 90.1370532276984, 86.0801529266134, 77.4102172551968, 59.6761947649801, 46.3954904194042,</v>
       </c>
-      <c r="M21" s="75" t="s">
+      <c r="M21" s="77" t="s">
         <v>6</v>
       </c>
-      <c r="N21" s="76"/>
-      <c r="O21" s="47">
+      <c r="N21" s="78"/>
+      <c r="O21" s="41">
         <v>3.8319643020864191</v>
       </c>
-      <c r="P21" s="47">
+      <c r="P21" s="41">
         <v>4.3603246705255447</v>
       </c>
-      <c r="Q21" s="47">
+      <c r="Q21" s="41">
         <v>4.7987735191879262</v>
       </c>
-      <c r="R21" s="47">
+      <c r="R21" s="41">
         <v>5.1262965367330251</v>
       </c>
-      <c r="S21" s="47">
+      <c r="S21" s="41">
         <v>7.087258799823358</v>
       </c>
-      <c r="T21" s="47">
+      <c r="T21" s="41">
         <v>9.7457736576346736</v>
       </c>
-      <c r="U21" s="48">
+      <c r="U21" s="42">
         <v>10.021578856839133</v>
       </c>
       <c r="V21" s="1" t="str">
@@ -2138,60 +2126,60 @@
       </c>
     </row>
     <row r="22" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="75" t="s">
+      <c r="A22" s="77" t="s">
         <v>10</v>
       </c>
-      <c r="B22" s="76"/>
-      <c r="C22" s="34">
+      <c r="B22" s="78"/>
+      <c r="C22" s="28">
         <v>87.268396410214976</v>
       </c>
-      <c r="D22" s="35">
+      <c r="D22" s="29">
         <v>87.256428398686779</v>
       </c>
-      <c r="E22" s="35">
+      <c r="E22" s="29">
         <v>87.822106304170404</v>
       </c>
-      <c r="F22" s="35">
+      <c r="F22" s="29">
         <v>87.68072644235157</v>
       </c>
-      <c r="G22" s="35">
+      <c r="G22" s="29">
         <v>87.144879367185226</v>
       </c>
-      <c r="H22" s="35">
+      <c r="H22" s="29">
         <v>74.976567886515753</v>
       </c>
-      <c r="I22" s="36">
+      <c r="I22" s="30">
         <v>46.41754739488244</v>
       </c>
-      <c r="J22" s="50"/>
-      <c r="K22" s="50"/>
+      <c r="J22" s="44"/>
+      <c r="K22" s="44"/>
       <c r="L22" s="1" t="str">
         <f t="shared" ref="L22:L25" si="9">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C22:I22)&amp;","</f>
         <v xml:space="preserve">    87.268396410215, 87.2564283986868, 87.8221063041704, 87.6807264423516, 87.1448793671852, 74.9765678865158, 46.4175473948824,</v>
       </c>
-      <c r="M22" s="75" t="s">
+      <c r="M22" s="77" t="s">
         <v>10</v>
       </c>
-      <c r="N22" s="76"/>
-      <c r="O22" s="34">
+      <c r="N22" s="78"/>
+      <c r="O22" s="28">
         <v>2.610595868561878</v>
       </c>
-      <c r="P22" s="35">
+      <c r="P22" s="29">
         <v>2.3209805270224559</v>
       </c>
-      <c r="Q22" s="35">
+      <c r="Q22" s="29">
         <v>2.4426244152699921</v>
       </c>
-      <c r="R22" s="35">
+      <c r="R22" s="29">
         <v>2.2821255442986761</v>
       </c>
-      <c r="S22" s="35">
+      <c r="S22" s="29">
         <v>2.523131741400912</v>
       </c>
-      <c r="T22" s="35">
+      <c r="T22" s="29">
         <v>3.7626100419371111</v>
       </c>
-      <c r="U22" s="36">
+      <c r="U22" s="30">
         <v>4.1161081119796732</v>
       </c>
       <c r="V22" s="1" t="str">
@@ -2200,7 +2188,7 @@
       </c>
     </row>
     <row r="23" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="75" t="s">
+      <c r="A23" s="77" t="s">
         <v>14</v>
       </c>
       <c r="B23" s="79"/>
@@ -2210,11 +2198,11 @@
       <c r="F23" s="79"/>
       <c r="G23" s="79"/>
       <c r="H23" s="79"/>
-      <c r="I23" s="76"/>
-      <c r="J23" s="50"/>
-      <c r="K23" s="50"/>
+      <c r="I23" s="78"/>
+      <c r="J23" s="44"/>
+      <c r="K23" s="44"/>
       <c r="L23" s="1"/>
-      <c r="M23" s="75" t="s">
+      <c r="M23" s="77" t="s">
         <v>14</v>
       </c>
       <c r="N23" s="79"/>
@@ -2224,7 +2212,7 @@
       <c r="R23" s="79"/>
       <c r="S23" s="79"/>
       <c r="T23" s="79"/>
-      <c r="U23" s="76"/>
+      <c r="U23" s="78"/>
       <c r="V23" s="1"/>
     </row>
     <row r="24" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
@@ -2234,32 +2222,32 @@
       <c r="B24" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C24" s="28">
-        <v>92.718331539365238</v>
-      </c>
-      <c r="D24" s="29">
-        <v>92.140084144598461</v>
-      </c>
-      <c r="E24" s="29">
-        <v>91.379904797106931</v>
-      </c>
-      <c r="F24" s="29">
-        <v>88.378075938007726</v>
-      </c>
-      <c r="G24" s="29">
-        <v>84.574966803458963</v>
-      </c>
-      <c r="H24" s="29">
-        <v>64.524084468318208</v>
-      </c>
-      <c r="I24" s="30">
-        <v>53.783251685995403</v>
-      </c>
-      <c r="J24" s="50"/>
-      <c r="K24" s="50"/>
+      <c r="C24" s="88">
+        <v>92.975694513442221</v>
+      </c>
+      <c r="D24" s="89">
+        <v>91.363613749154311</v>
+      </c>
+      <c r="E24" s="89">
+        <v>90.094017961161143</v>
+      </c>
+      <c r="F24" s="89">
+        <v>85.37773791839254</v>
+      </c>
+      <c r="G24" s="89">
+        <v>79.268159049010507</v>
+      </c>
+      <c r="H24" s="89">
+        <v>60.52121651399365</v>
+      </c>
+      <c r="I24" s="90">
+        <v>42.05444880665619</v>
+      </c>
+      <c r="J24" s="44"/>
+      <c r="K24" s="44"/>
       <c r="L24" s="1" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">    92.7183315393652, 92.1400841445985, 91.3799047971069, 88.3780759380077, 84.574966803459, 64.5240844683182, 53.7832516859954,</v>
+        <v xml:space="preserve">    92.9756945134422, 91.3636137491543, 90.0940179611611, 85.3777379183925, 79.2681590490105, 60.5212165139937, 42.0544488066562,</v>
       </c>
       <c r="M24" s="14" t="s">
         <v>12</v>
@@ -2267,181 +2255,181 @@
       <c r="N24" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="O24" s="28">
-        <v>3.7093306081953399</v>
-      </c>
-      <c r="P24" s="29">
-        <v>3.557353374868756</v>
-      </c>
-      <c r="Q24" s="29">
-        <v>3.8505126265401719</v>
-      </c>
-      <c r="R24" s="29">
-        <v>4.6860631563763482</v>
-      </c>
-      <c r="S24" s="29">
-        <v>5.2335990268297223</v>
-      </c>
-      <c r="T24" s="29">
-        <v>8.5303914956588702</v>
-      </c>
-      <c r="U24" s="30">
-        <v>9.1099237449071975</v>
+      <c r="O24" s="88">
+        <v>3.782557259829499</v>
+      </c>
+      <c r="P24" s="89">
+        <v>4.4459073754732694</v>
+      </c>
+      <c r="Q24" s="89">
+        <v>4.6323081197737448</v>
+      </c>
+      <c r="R24" s="89">
+        <v>5.3746795640933653</v>
+      </c>
+      <c r="S24" s="89">
+        <v>5.9912912250355319</v>
+      </c>
+      <c r="T24" s="89">
+        <v>9.0901817740237139</v>
+      </c>
+      <c r="U24" s="90">
+        <v>9.5108664952359483</v>
       </c>
       <c r="V24" s="1" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">    3.70933060819534, 3.55735337486876, 3.85051262654017, 4.68606315637635, 5.23359902682972, 8.53039149565887, 9.1099237449072,</v>
+        <v xml:space="preserve">    3.7825572598295, 4.44590737547327, 4.63230811977374, 5.37467956409337, 5.99129122503553, 9.09018177402371, 9.51086649523595,</v>
       </c>
     </row>
     <row r="25" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B25" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C25" s="49">
-        <v>92.111918497964766</v>
-      </c>
-      <c r="D25" s="50">
-        <v>92.236437130021557</v>
-      </c>
-      <c r="E25" s="50">
-        <v>91.847628837606763</v>
-      </c>
-      <c r="F25" s="50">
-        <v>91.031961472589515</v>
-      </c>
-      <c r="G25" s="50">
-        <v>87.968996103656281</v>
-      </c>
-      <c r="H25" s="50">
-        <v>70.680435455032196</v>
-      </c>
-      <c r="I25" s="51">
-        <v>51.144510191286152</v>
-      </c>
-      <c r="J25" s="50"/>
-      <c r="K25" s="50"/>
+      <c r="C25" s="66">
+        <v>92.311293413260969</v>
+      </c>
+      <c r="D25" s="67">
+        <v>92.333521756806476</v>
+      </c>
+      <c r="E25" s="67">
+        <v>91.381357522919643</v>
+      </c>
+      <c r="F25" s="67">
+        <v>88.560101371956989</v>
+      </c>
+      <c r="G25" s="67">
+        <v>87.278991705998607</v>
+      </c>
+      <c r="H25" s="67">
+        <v>75.38789705567028</v>
+      </c>
+      <c r="I25" s="68">
+        <v>47.478737907175287</v>
+      </c>
+      <c r="J25" s="44"/>
+      <c r="K25" s="44"/>
       <c r="L25" s="1" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">    92.1119184979648, 92.2364371300216, 91.8476288376068, 91.0319614725895, 87.9689961036563, 70.6804354550322, 51.1445101912862,</v>
+        <v xml:space="preserve">    92.311293413261, 92.3335217568065, 91.3813575229196, 88.560101371957, 87.2789917059986, 75.3878970556703, 47.4787379071753,</v>
       </c>
       <c r="M25" s="14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N25" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="O25" s="49">
-        <v>3.5860589390986259</v>
-      </c>
-      <c r="P25" s="50">
-        <v>3.5458492835339008</v>
-      </c>
-      <c r="Q25" s="50">
-        <v>3.3222516092178069</v>
-      </c>
-      <c r="R25" s="50">
-        <v>3.385168684859547</v>
-      </c>
-      <c r="S25" s="50">
-        <v>3.8142946105661402</v>
-      </c>
-      <c r="T25" s="50">
-        <v>5.9054798361883787</v>
-      </c>
-      <c r="U25" s="51">
-        <v>6.303799515839513</v>
+      <c r="O25" s="66">
+        <v>3.45837660705662</v>
+      </c>
+      <c r="P25" s="67">
+        <v>3.6213315124355141</v>
+      </c>
+      <c r="Q25" s="67">
+        <v>3.418827656161032</v>
+      </c>
+      <c r="R25" s="67">
+        <v>3.2543979140806938</v>
+      </c>
+      <c r="S25" s="67">
+        <v>3.202126822778443</v>
+      </c>
+      <c r="T25" s="67">
+        <v>5.2358921781492196</v>
+      </c>
+      <c r="U25" s="68">
+        <v>6.1375770825509051</v>
       </c>
       <c r="V25" s="1" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">    3.58605893909863, 3.5458492835339, 3.32225160921781, 3.38516868485955, 3.81429461056614, 5.90547983618838, 6.30379951583951,</v>
+        <v xml:space="preserve">    3.45837660705662, 3.62133151243551, 3.41882765616103, 3.25439791408069, 3.20212682277844, 5.23589217814922, 6.13757708255091,</v>
       </c>
     </row>
     <row r="26" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="75" t="s">
+      <c r="A26" s="77" t="s">
         <v>22</v>
       </c>
       <c r="B26" s="79"/>
-      <c r="C26" s="82"/>
-      <c r="D26" s="82"/>
-      <c r="E26" s="82"/>
-      <c r="F26" s="82"/>
-      <c r="G26" s="82"/>
-      <c r="H26" s="82"/>
-      <c r="I26" s="78"/>
-      <c r="J26" s="50"/>
-      <c r="K26" s="50"/>
+      <c r="C26" s="80"/>
+      <c r="D26" s="80"/>
+      <c r="E26" s="80"/>
+      <c r="F26" s="80"/>
+      <c r="G26" s="80"/>
+      <c r="H26" s="80"/>
+      <c r="I26" s="81"/>
+      <c r="J26" s="44"/>
+      <c r="K26" s="44"/>
       <c r="L26" s="1"/>
-      <c r="M26" s="75" t="s">
+      <c r="M26" s="77" t="s">
         <v>22</v>
       </c>
       <c r="N26" s="79"/>
-      <c r="O26" s="82"/>
-      <c r="P26" s="82"/>
-      <c r="Q26" s="82"/>
-      <c r="R26" s="82"/>
-      <c r="S26" s="82"/>
-      <c r="T26" s="82"/>
-      <c r="U26" s="78"/>
+      <c r="O26" s="80"/>
+      <c r="P26" s="80"/>
+      <c r="Q26" s="80"/>
+      <c r="R26" s="80"/>
+      <c r="S26" s="80"/>
+      <c r="T26" s="80"/>
+      <c r="U26" s="81"/>
       <c r="V26" s="1"/>
     </row>
     <row r="27" spans="1:22" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="75" t="s">
+      <c r="A27" s="77" t="s">
         <v>7</v>
       </c>
-      <c r="B27" s="76"/>
-      <c r="C27" s="46">
+      <c r="B27" s="78"/>
+      <c r="C27" s="40">
         <v>93.403798109785029</v>
       </c>
-      <c r="D27" s="47">
+      <c r="D27" s="41">
         <v>91.51700700493744</v>
       </c>
-      <c r="E27" s="47">
+      <c r="E27" s="41">
         <v>89.749880462689262</v>
       </c>
-      <c r="F27" s="47">
+      <c r="F27" s="41">
         <v>83.99730958119234</v>
       </c>
-      <c r="G27" s="47">
+      <c r="G27" s="41">
         <v>74.394962965986878</v>
       </c>
-      <c r="H27" s="47">
+      <c r="H27" s="41">
         <v>58.095582470498513</v>
       </c>
-      <c r="I27" s="48">
+      <c r="I27" s="42">
         <v>44.434812706207254</v>
       </c>
-      <c r="J27" s="50"/>
-      <c r="K27" s="50"/>
+      <c r="J27" s="44"/>
+      <c r="K27" s="44"/>
       <c r="L27" s="1" t="str">
         <f t="shared" ref="L27:L30" si="10">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C27:I27)&amp;","</f>
         <v xml:space="preserve">    93.403798109785, 91.5170070049374, 89.7498804626893, 83.9973095811923, 74.3949629659869, 58.0955824704985, 44.4348127062073,</v>
       </c>
-      <c r="M27" s="75" t="s">
+      <c r="M27" s="77" t="s">
         <v>7</v>
       </c>
-      <c r="N27" s="76"/>
-      <c r="O27" s="46">
+      <c r="N27" s="78"/>
+      <c r="O27" s="40">
         <v>3.9553866501853321</v>
       </c>
-      <c r="P27" s="47">
+      <c r="P27" s="41">
         <v>4.517630835861226</v>
       </c>
-      <c r="Q27" s="47">
+      <c r="Q27" s="41">
         <v>5.2125425794506972</v>
       </c>
-      <c r="R27" s="47">
+      <c r="R27" s="41">
         <v>5.6477461387684551</v>
       </c>
-      <c r="S27" s="47">
+      <c r="S27" s="41">
         <v>8.6090564713117175</v>
       </c>
-      <c r="T27" s="47">
+      <c r="T27" s="41">
         <v>11.357157347254571</v>
       </c>
-      <c r="U27" s="48">
+      <c r="U27" s="42">
         <v>9.3757621724255777</v>
       </c>
       <c r="V27" s="1" t="str">
@@ -2450,60 +2438,60 @@
       </c>
     </row>
     <row r="28" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="75" t="s">
+      <c r="A28" s="77" t="s">
         <v>8</v>
       </c>
-      <c r="B28" s="76"/>
-      <c r="C28" s="49">
+      <c r="B28" s="78"/>
+      <c r="C28" s="43">
         <v>92.778947400409621</v>
       </c>
-      <c r="D28" s="50">
+      <c r="D28" s="44">
         <v>91.450368996373655</v>
       </c>
-      <c r="E28" s="50">
+      <c r="E28" s="44">
         <v>89.879480954542075</v>
       </c>
-      <c r="F28" s="50">
+      <c r="F28" s="44">
         <v>84.748756470336986</v>
       </c>
-      <c r="G28" s="50">
+      <c r="G28" s="44">
         <v>75.627608782580538</v>
       </c>
-      <c r="H28" s="50">
+      <c r="H28" s="44">
         <v>58.300265665116903</v>
       </c>
-      <c r="I28" s="51">
+      <c r="I28" s="45">
         <v>48.584106437626268</v>
       </c>
-      <c r="J28" s="50"/>
-      <c r="K28" s="50"/>
+      <c r="J28" s="44"/>
+      <c r="K28" s="44"/>
       <c r="L28" s="1" t="str">
         <f t="shared" si="10"/>
         <v xml:space="preserve">    92.7789474004096, 91.4503689963737, 89.8794809545421, 84.748756470337, 75.6276087825805, 58.3002656651169, 48.5841064376263,</v>
       </c>
-      <c r="M28" s="75" t="s">
+      <c r="M28" s="77" t="s">
         <v>8</v>
       </c>
-      <c r="N28" s="76"/>
-      <c r="O28" s="49">
+      <c r="N28" s="78"/>
+      <c r="O28" s="43">
         <v>4.3743918396131134</v>
       </c>
-      <c r="P28" s="50">
+      <c r="P28" s="44">
         <v>5.1779143655465321</v>
       </c>
-      <c r="Q28" s="50">
+      <c r="Q28" s="44">
         <v>4.8362705721377752</v>
       </c>
-      <c r="R28" s="50">
+      <c r="R28" s="44">
         <v>5.6797782301447892</v>
       </c>
-      <c r="S28" s="50">
+      <c r="S28" s="44">
         <v>9.0190902977959446</v>
       </c>
-      <c r="T28" s="50">
+      <c r="T28" s="44">
         <v>11.000258135261941</v>
       </c>
-      <c r="U28" s="51">
+      <c r="U28" s="45">
         <v>9.2918474149187738</v>
       </c>
       <c r="V28" s="1" t="str">
@@ -2512,60 +2500,60 @@
       </c>
     </row>
     <row r="29" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="75" t="s">
+      <c r="A29" s="77" t="s">
         <v>23</v>
       </c>
-      <c r="B29" s="76"/>
-      <c r="C29" s="49">
+      <c r="B29" s="78"/>
+      <c r="C29" s="43">
         <v>92.492055194421354</v>
       </c>
-      <c r="D29" s="50">
+      <c r="D29" s="44">
         <v>91.055738083245984</v>
       </c>
-      <c r="E29" s="50">
+      <c r="E29" s="44">
         <v>89.241264887762341</v>
       </c>
-      <c r="F29" s="50">
+      <c r="F29" s="44">
         <v>82.713601809643421</v>
       </c>
-      <c r="G29" s="50">
+      <c r="G29" s="44">
         <v>73.133677048774885</v>
       </c>
-      <c r="H29" s="50">
+      <c r="H29" s="44">
         <v>56.229205901331248</v>
       </c>
-      <c r="I29" s="51">
+      <c r="I29" s="45">
         <v>43.695396708102962</v>
       </c>
-      <c r="J29" s="50"/>
-      <c r="K29" s="50"/>
+      <c r="J29" s="44"/>
+      <c r="K29" s="44"/>
       <c r="L29" s="1" t="str">
         <f t="shared" si="10"/>
         <v xml:space="preserve">    92.4920551944214, 91.055738083246, 89.2412648877623, 82.7136018096434, 73.1336770487749, 56.2292059013312, 43.695396708103,</v>
       </c>
-      <c r="M29" s="75" t="s">
+      <c r="M29" s="77" t="s">
         <v>23</v>
       </c>
-      <c r="N29" s="76"/>
-      <c r="O29" s="49">
+      <c r="N29" s="78"/>
+      <c r="O29" s="43">
         <v>4.0986250609792014</v>
       </c>
-      <c r="P29" s="50">
+      <c r="P29" s="44">
         <v>4.5926443490712341</v>
       </c>
-      <c r="Q29" s="50">
+      <c r="Q29" s="44">
         <v>4.8521598807380544</v>
       </c>
-      <c r="R29" s="50">
+      <c r="R29" s="44">
         <v>5.8188919126166327</v>
       </c>
-      <c r="S29" s="50">
+      <c r="S29" s="44">
         <v>9.5088987825376563</v>
       </c>
-      <c r="T29" s="50">
+      <c r="T29" s="44">
         <v>11.32839542788332</v>
       </c>
-      <c r="U29" s="51">
+      <c r="U29" s="45">
         <v>10.62887090695313</v>
       </c>
       <c r="V29" s="1" t="str">
@@ -2574,60 +2562,60 @@
       </c>
     </row>
     <row r="30" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="75" t="s">
+      <c r="A30" s="77" t="s">
         <v>24</v>
       </c>
-      <c r="B30" s="76"/>
-      <c r="C30" s="52">
+      <c r="B30" s="78"/>
+      <c r="C30" s="46">
         <v>92.657174075741665</v>
       </c>
-      <c r="D30" s="53">
+      <c r="D30" s="47">
         <v>91.208050814372243</v>
       </c>
-      <c r="E30" s="53">
+      <c r="E30" s="47">
         <v>89.170455678091372</v>
       </c>
-      <c r="F30" s="53">
+      <c r="F30" s="47">
         <v>84.474616062770011</v>
       </c>
-      <c r="G30" s="53">
+      <c r="G30" s="47">
         <v>75.066668593640316</v>
       </c>
-      <c r="H30" s="53">
+      <c r="H30" s="47">
         <v>58.520340993368222</v>
       </c>
-      <c r="I30" s="54">
+      <c r="I30" s="48">
         <v>44.786141592049418</v>
       </c>
-      <c r="J30" s="58"/>
-      <c r="K30" s="58"/>
+      <c r="J30" s="52"/>
+      <c r="K30" s="52"/>
       <c r="L30" s="1" t="str">
         <f t="shared" si="10"/>
         <v xml:space="preserve">    92.6571740757417, 91.2080508143722, 89.1704556780914, 84.47461606277, 75.0666685936403, 58.5203409933682, 44.7861415920494,</v>
       </c>
-      <c r="M30" s="75" t="s">
+      <c r="M30" s="77" t="s">
         <v>24</v>
       </c>
-      <c r="N30" s="76"/>
-      <c r="O30" s="52">
+      <c r="N30" s="78"/>
+      <c r="O30" s="46">
         <v>4.2589004392769629</v>
       </c>
-      <c r="P30" s="53">
+      <c r="P30" s="47">
         <v>4.8517186601265534</v>
       </c>
-      <c r="Q30" s="53">
+      <c r="Q30" s="47">
         <v>5.6717673083496472</v>
       </c>
-      <c r="R30" s="53">
+      <c r="R30" s="47">
         <v>5.3079507961921779</v>
       </c>
-      <c r="S30" s="53">
+      <c r="S30" s="47">
         <v>7.7884705615072454</v>
       </c>
-      <c r="T30" s="53">
+      <c r="T30" s="47">
         <v>10.595563377926201</v>
       </c>
-      <c r="U30" s="54">
+      <c r="U30" s="48">
         <v>10.945843294214329</v>
       </c>
       <c r="V30" s="1" t="str">
@@ -2636,88 +2624,88 @@
       </c>
     </row>
     <row r="31" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="75" t="s">
+      <c r="A31" s="77" t="s">
         <v>25</v>
       </c>
       <c r="B31" s="79"/>
-      <c r="C31" s="80"/>
-      <c r="D31" s="80"/>
-      <c r="E31" s="80"/>
-      <c r="F31" s="80"/>
-      <c r="G31" s="80"/>
-      <c r="H31" s="80"/>
-      <c r="I31" s="81"/>
-      <c r="J31" s="50"/>
-      <c r="K31" s="50"/>
+      <c r="C31" s="82"/>
+      <c r="D31" s="82"/>
+      <c r="E31" s="82"/>
+      <c r="F31" s="82"/>
+      <c r="G31" s="82"/>
+      <c r="H31" s="82"/>
+      <c r="I31" s="83"/>
+      <c r="J31" s="44"/>
+      <c r="K31" s="44"/>
       <c r="L31" s="1"/>
-      <c r="M31" s="75" t="s">
+      <c r="M31" s="77" t="s">
         <v>25</v>
       </c>
       <c r="N31" s="79"/>
-      <c r="O31" s="80"/>
-      <c r="P31" s="80"/>
-      <c r="Q31" s="80"/>
-      <c r="R31" s="80"/>
-      <c r="S31" s="80"/>
-      <c r="T31" s="80"/>
-      <c r="U31" s="81"/>
+      <c r="O31" s="82"/>
+      <c r="P31" s="82"/>
+      <c r="Q31" s="82"/>
+      <c r="R31" s="82"/>
+      <c r="S31" s="82"/>
+      <c r="T31" s="82"/>
+      <c r="U31" s="83"/>
       <c r="V31" s="1"/>
     </row>
     <row r="32" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="75" t="s">
+      <c r="A32" s="77" t="s">
         <v>7</v>
       </c>
-      <c r="B32" s="76"/>
-      <c r="C32" s="46">
+      <c r="B32" s="78"/>
+      <c r="C32" s="40">
         <v>92.603769819293618</v>
       </c>
-      <c r="D32" s="47">
+      <c r="D32" s="41">
         <v>91.431947068352812</v>
       </c>
-      <c r="E32" s="47">
+      <c r="E32" s="41">
         <v>90.390795042999585</v>
       </c>
-      <c r="F32" s="47">
+      <c r="F32" s="41">
         <v>86.789562828222273</v>
       </c>
-      <c r="G32" s="47">
+      <c r="G32" s="41">
         <v>80.615554033052248</v>
       </c>
-      <c r="H32" s="47">
+      <c r="H32" s="41">
         <v>56.609578553133908</v>
       </c>
-      <c r="I32" s="48">
+      <c r="I32" s="42">
         <v>41.27928062292434</v>
       </c>
-      <c r="J32" s="50"/>
-      <c r="K32" s="50"/>
+      <c r="J32" s="44"/>
+      <c r="K32" s="44"/>
       <c r="L32" s="1" t="str">
         <f t="shared" ref="L32:L35" si="11">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C32:I32)&amp;","</f>
         <v xml:space="preserve">    92.6037698192936, 91.4319470683528, 90.3907950429996, 86.7895628282223, 80.6155540330522, 56.6095785531339, 41.2792806229243,</v>
       </c>
-      <c r="M32" s="75" t="s">
+      <c r="M32" s="77" t="s">
         <v>7</v>
       </c>
-      <c r="N32" s="76"/>
-      <c r="O32" s="46">
+      <c r="N32" s="78"/>
+      <c r="O32" s="40">
         <v>3.708759274801273</v>
       </c>
-      <c r="P32" s="47">
+      <c r="P32" s="41">
         <v>3.9640390541215931</v>
       </c>
-      <c r="Q32" s="47">
+      <c r="Q32" s="41">
         <v>3.7067998106756881</v>
       </c>
-      <c r="R32" s="47">
+      <c r="R32" s="41">
         <v>3.667452632531309</v>
       </c>
-      <c r="S32" s="47">
+      <c r="S32" s="41">
         <v>5.7548227051500218</v>
       </c>
-      <c r="T32" s="47">
+      <c r="T32" s="41">
         <v>8.5366536877555248</v>
       </c>
-      <c r="U32" s="48">
+      <c r="U32" s="42">
         <v>6.3187793027043018</v>
       </c>
       <c r="V32" s="1" t="str">
@@ -2726,60 +2714,60 @@
       </c>
     </row>
     <row r="33" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="77" t="s">
+      <c r="A33" s="84" t="s">
         <v>8</v>
       </c>
-      <c r="B33" s="78"/>
-      <c r="C33" s="49">
+      <c r="B33" s="81"/>
+      <c r="C33" s="43">
         <v>91.377634404932721</v>
       </c>
-      <c r="D33" s="50">
+      <c r="D33" s="44">
         <v>90.405373333245066</v>
       </c>
-      <c r="E33" s="50">
+      <c r="E33" s="44">
         <v>89.371480308332721</v>
       </c>
-      <c r="F33" s="50">
+      <c r="F33" s="44">
         <v>87.60989862639515</v>
       </c>
-      <c r="G33" s="50">
+      <c r="G33" s="44">
         <v>85.537230701510694</v>
       </c>
-      <c r="H33" s="50">
+      <c r="H33" s="44">
         <v>70.930708745421484</v>
       </c>
-      <c r="I33" s="51">
+      <c r="I33" s="45">
         <v>44.097326232806537</v>
       </c>
-      <c r="J33" s="50"/>
-      <c r="K33" s="50"/>
+      <c r="J33" s="44"/>
+      <c r="K33" s="44"/>
       <c r="L33" s="1" t="str">
         <f t="shared" si="11"/>
         <v xml:space="preserve">    91.3776344049327, 90.4053733332451, 89.3714803083327, 87.6098986263952, 85.5372307015107, 70.9307087454215, 44.0973262328065,</v>
       </c>
-      <c r="M33" s="75" t="s">
+      <c r="M33" s="77" t="s">
         <v>8</v>
       </c>
-      <c r="N33" s="76"/>
-      <c r="O33" s="49">
+      <c r="N33" s="78"/>
+      <c r="O33" s="43">
         <v>3.5684194304484111</v>
       </c>
-      <c r="P33" s="50">
+      <c r="P33" s="44">
         <v>3.0347581440341318</v>
       </c>
-      <c r="Q33" s="50">
+      <c r="Q33" s="44">
         <v>2.754130276526872</v>
       </c>
-      <c r="R33" s="50">
+      <c r="R33" s="44">
         <v>2.7768782002466339</v>
       </c>
-      <c r="S33" s="50">
+      <c r="S33" s="44">
         <v>3.3184641894178428</v>
       </c>
-      <c r="T33" s="50">
+      <c r="T33" s="44">
         <v>4.9795199020249923</v>
       </c>
-      <c r="U33" s="51">
+      <c r="U33" s="45">
         <v>2.9223071611371929</v>
       </c>
       <c r="V33" s="1" t="str">
@@ -2788,60 +2776,60 @@
       </c>
     </row>
     <row r="34" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="75" t="s">
+      <c r="A34" s="77" t="s">
         <v>23</v>
       </c>
-      <c r="B34" s="76"/>
-      <c r="C34" s="49">
+      <c r="B34" s="78"/>
+      <c r="C34" s="43">
         <v>92.603715202692385</v>
       </c>
-      <c r="D34" s="50">
+      <c r="D34" s="44">
         <v>91.484997502720319</v>
       </c>
-      <c r="E34" s="50">
+      <c r="E34" s="44">
         <v>90.630171299324857</v>
       </c>
-      <c r="F34" s="50">
+      <c r="F34" s="44">
         <v>85.342034697064548</v>
       </c>
-      <c r="G34" s="50">
+      <c r="G34" s="44">
         <v>78.208607944308184</v>
       </c>
-      <c r="H34" s="50">
+      <c r="H34" s="44">
         <v>58.188767254712552</v>
       </c>
-      <c r="I34" s="51">
+      <c r="I34" s="45">
         <v>45.468919562576168</v>
       </c>
-      <c r="J34" s="50"/>
-      <c r="K34" s="50"/>
+      <c r="J34" s="44"/>
+      <c r="K34" s="44"/>
       <c r="L34" s="1" t="str">
         <f t="shared" si="11"/>
         <v xml:space="preserve">    92.6037152026924, 91.4849975027203, 90.6301712993249, 85.3420346970645, 78.2086079443082, 58.1887672547126, 45.4689195625762,</v>
       </c>
-      <c r="M34" s="75" t="s">
+      <c r="M34" s="77" t="s">
         <v>23</v>
       </c>
-      <c r="N34" s="76"/>
-      <c r="O34" s="49">
+      <c r="N34" s="78"/>
+      <c r="O34" s="43">
         <v>4.0727132923350373</v>
       </c>
-      <c r="P34" s="50">
+      <c r="P34" s="44">
         <v>4.4231285957629458</v>
       </c>
-      <c r="Q34" s="50">
+      <c r="Q34" s="44">
         <v>4.3011534303531356</v>
       </c>
-      <c r="R34" s="50">
+      <c r="R34" s="44">
         <v>4.8453894583465429</v>
       </c>
-      <c r="S34" s="50">
+      <c r="S34" s="44">
         <v>7.5589700135942426</v>
       </c>
-      <c r="T34" s="50">
+      <c r="T34" s="44">
         <v>10.3740336621021</v>
       </c>
-      <c r="U34" s="51">
+      <c r="U34" s="45">
         <v>10.707618741543239</v>
       </c>
       <c r="V34" s="1" t="str">
@@ -2850,60 +2838,60 @@
       </c>
     </row>
     <row r="35" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="75" t="s">
+      <c r="A35" s="77" t="s">
         <v>24</v>
       </c>
-      <c r="B35" s="76"/>
-      <c r="C35" s="52">
+      <c r="B35" s="78"/>
+      <c r="C35" s="46">
         <v>92.692685851985146</v>
       </c>
-      <c r="D35" s="53">
+      <c r="D35" s="47">
         <v>91.028008929063319</v>
       </c>
-      <c r="E35" s="53">
+      <c r="E35" s="47">
         <v>89.101176850288709</v>
       </c>
-      <c r="F35" s="53">
+      <c r="F35" s="47">
         <v>84.121695311135312</v>
       </c>
-      <c r="G35" s="53">
+      <c r="G35" s="47">
         <v>75.514536359946376</v>
       </c>
-      <c r="H35" s="53">
+      <c r="H35" s="47">
         <v>58.551851548300363</v>
       </c>
-      <c r="I35" s="54">
+      <c r="I35" s="48">
         <v>43.528644478603361</v>
       </c>
-      <c r="J35" s="50"/>
-      <c r="K35" s="50"/>
+      <c r="J35" s="44"/>
+      <c r="K35" s="44"/>
       <c r="L35" s="1" t="str">
         <f t="shared" si="11"/>
         <v xml:space="preserve">    92.6926858519851, 91.0280089290633, 89.1011768502887, 84.1216953111353, 75.5145363599464, 58.5518515483004, 43.5286444786034,</v>
       </c>
-      <c r="M35" s="75" t="s">
+      <c r="M35" s="77" t="s">
         <v>24</v>
       </c>
-      <c r="N35" s="76"/>
-      <c r="O35" s="52">
+      <c r="N35" s="78"/>
+      <c r="O35" s="46">
         <v>4.3508377678439567</v>
       </c>
-      <c r="P35" s="53">
+      <c r="P35" s="47">
         <v>5.1455197984597092</v>
       </c>
-      <c r="Q35" s="53">
+      <c r="Q35" s="47">
         <v>5.0319449257944937</v>
       </c>
-      <c r="R35" s="53">
+      <c r="R35" s="47">
         <v>5.4881092234662896</v>
       </c>
-      <c r="S35" s="53">
+      <c r="S35" s="47">
         <v>8.3963724907401343</v>
       </c>
-      <c r="T35" s="53">
+      <c r="T35" s="47">
         <v>11.26477476806841</v>
       </c>
-      <c r="U35" s="54">
+      <c r="U35" s="48">
         <v>10.478269846537319</v>
       </c>
       <c r="V35" s="1" t="str">
@@ -2993,54 +2981,6 @@
     </row>
   </sheetData>
   <mergeCells count="56">
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="A5:I5"/>
-    <mergeCell ref="M5:U5"/>
-    <mergeCell ref="A8:I8"/>
-    <mergeCell ref="M8:U8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="M9:N9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="A13:I13"/>
-    <mergeCell ref="M13:U13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="M22:N22"/>
-    <mergeCell ref="A23:I23"/>
-    <mergeCell ref="M23:U23"/>
-    <mergeCell ref="A26:I26"/>
-    <mergeCell ref="M26:U26"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="M27:N27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="M29:N29"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="M30:N30"/>
-    <mergeCell ref="A31:I31"/>
-    <mergeCell ref="M31:U31"/>
     <mergeCell ref="A35:B35"/>
     <mergeCell ref="M35:N35"/>
     <mergeCell ref="A32:B32"/>
@@ -3049,10 +2989,58 @@
     <mergeCell ref="M33:N33"/>
     <mergeCell ref="A34:B34"/>
     <mergeCell ref="M34:N34"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="M29:N29"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="M30:N30"/>
+    <mergeCell ref="A31:I31"/>
+    <mergeCell ref="M31:U31"/>
+    <mergeCell ref="A26:I26"/>
+    <mergeCell ref="M26:U26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="M27:N27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="A23:I23"/>
+    <mergeCell ref="M23:U23"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="A13:I13"/>
+    <mergeCell ref="M13:U13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="M5:U5"/>
+    <mergeCell ref="A8:I8"/>
+    <mergeCell ref="M8:U8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="M9:N9"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="M4:N4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="C6:I7 C2:I4">
-    <cfRule type="colorScale" priority="27">
+  <conditionalFormatting sqref="C2:I4">
+    <cfRule type="colorScale" priority="43">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3062,7 +3050,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="28">
+    <cfRule type="colorScale" priority="44">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3072,7 +3060,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="30">
+    <cfRule type="colorScale" priority="46">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3084,7 +3072,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C9:I11 C14:I16">
-    <cfRule type="colorScale" priority="6">
+    <cfRule type="colorScale" priority="22">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3096,160 +3084,6 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C9:I11">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="9">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C9:I12 C14:I17">
-    <cfRule type="colorScale" priority="10">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C14:I16">
-    <cfRule type="colorScale" priority="3">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="5">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C2:K4 C6:K7 J5:K5 J8:K17">
-    <cfRule type="colorScale" priority="26">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J17">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J31:J35">
-    <cfRule type="colorScale" priority="14">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:K17">
-    <cfRule type="colorScale" priority="249">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J5:K5 C3:K4">
-    <cfRule type="colorScale" priority="20">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="21">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="22">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
     <cfRule type="colorScale" priority="23">
       <colorScale>
         <cfvo type="min"/>
@@ -3281,8 +3115,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J31:K35">
-    <cfRule type="colorScale" priority="13">
+  <conditionalFormatting sqref="C9:I12 C14:I17">
+    <cfRule type="colorScale" priority="26">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3292,7 +3126,161 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="15">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C14:I16">
+    <cfRule type="colorScale" priority="19">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="21">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:K4 J5:K17">
+    <cfRule type="colorScale" priority="42">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J17">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J31:J35">
+    <cfRule type="colorScale" priority="30">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:K17">
+    <cfRule type="colorScale" priority="265">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J5:K5 C3:K4">
+    <cfRule type="colorScale" priority="36">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="37">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="38">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="39">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="40">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="41">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J31:K35">
+    <cfRule type="colorScale" priority="29">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="31">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3304,6 +3292,54 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K17">
+    <cfRule type="colorScale" priority="17">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K31:K35">
+    <cfRule type="colorScale" priority="32">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C7:I7">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C7:I7">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C6:I6">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -3315,8 +3351,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K31:K35">
-    <cfRule type="colorScale" priority="16">
+  <conditionalFormatting sqref="C6:I6">
+    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3410,10 +3446,10 @@
       <c r="V1" s="12"/>
     </row>
     <row r="2" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="83" t="s">
+      <c r="A2" s="69" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="84"/>
+      <c r="B2" s="70"/>
       <c r="C2" s="20">
         <v>93.101364775358491</v>
       </c>
@@ -3447,29 +3483,29 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C2:I2)&amp;","</f>
         <v xml:space="preserve">    93.1013647753585, 91.3266637254648, 89.7225610371485, 83.857204647099, 76.2429490451186, 60.4027774173364, 47.7409002961387,</v>
       </c>
-      <c r="M2" s="83" t="s">
+      <c r="M2" s="69" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="84"/>
-      <c r="O2" s="37">
+      <c r="N2" s="70"/>
+      <c r="O2" s="31">
         <v>3.4649270444699574</v>
       </c>
-      <c r="P2" s="38">
+      <c r="P2" s="32">
         <v>4.4611797621615326</v>
       </c>
-      <c r="Q2" s="38">
+      <c r="Q2" s="32">
         <v>4.7712065248821434</v>
       </c>
-      <c r="R2" s="38">
+      <c r="R2" s="32">
         <v>5.3965689103010375</v>
       </c>
-      <c r="S2" s="38">
+      <c r="S2" s="32">
         <v>7.9323757260741923</v>
       </c>
-      <c r="T2" s="38">
+      <c r="T2" s="32">
         <v>9.9900413492801565</v>
       </c>
-      <c r="U2" s="39">
+      <c r="U2" s="33">
         <v>9.7565309936118432</v>
       </c>
       <c r="V2" s="12" t="str">
@@ -3478,36 +3514,36 @@
       </c>
     </row>
     <row r="3" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="83" t="s">
+      <c r="A3" s="69" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="84"/>
-      <c r="C3" s="37">
+      <c r="B3" s="70"/>
+      <c r="C3" s="31">
         <v>93.273358766079312</v>
       </c>
-      <c r="D3" s="38">
+      <c r="D3" s="32">
         <v>91.615587793435367</v>
       </c>
-      <c r="E3" s="38">
+      <c r="E3" s="32">
         <v>90.62053304959386</v>
       </c>
-      <c r="F3" s="38">
+      <c r="F3" s="32">
         <v>86.59751381932368</v>
       </c>
-      <c r="G3" s="38">
+      <c r="G3" s="32">
         <v>78.22435026831262</v>
       </c>
-      <c r="H3" s="38">
+      <c r="H3" s="32">
         <v>60.854992978601317</v>
       </c>
-      <c r="I3" s="39">
+      <c r="I3" s="33">
         <v>48.743933771053378</v>
       </c>
-      <c r="J3" s="41" cm="1">
+      <c r="J3" s="35" cm="1">
         <f t="array" ref="J3">-SUMPRODUCT((D1:H1-C1:G1)*(C3:G3+D3:H3)/2)</f>
         <v>78.807498478937248</v>
       </c>
-      <c r="K3" s="41" cm="1">
+      <c r="K3" s="35" cm="1">
         <f t="array" ref="K3">-SUMPRODUCT((D1:I1-C1:H1)*(C3:H3+D3:I3)/2)</f>
         <v>81.54747164767862</v>
       </c>
@@ -3515,29 +3551,29 @@
         <f t="shared" ref="L3:L16" si="0">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C3:I3)&amp;","</f>
         <v xml:space="preserve">    93.2733587660793, 91.6155877934354, 90.6205330495939, 86.5975138193237, 78.2243502683126, 60.8549929786013, 48.7439337710534,</v>
       </c>
-      <c r="M3" s="83" t="s">
+      <c r="M3" s="69" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="84"/>
-      <c r="O3" s="37">
+      <c r="N3" s="70"/>
+      <c r="O3" s="31">
         <v>3.4672469457762647</v>
       </c>
-      <c r="P3" s="38">
+      <c r="P3" s="32">
         <v>4.1066373858138912</v>
       </c>
-      <c r="Q3" s="38">
+      <c r="Q3" s="32">
         <v>4.4433442831389707</v>
       </c>
-      <c r="R3" s="38">
+      <c r="R3" s="32">
         <v>4.8572661690244194</v>
       </c>
-      <c r="S3" s="38">
+      <c r="S3" s="32">
         <v>6.7334065011993722</v>
       </c>
-      <c r="T3" s="38">
+      <c r="T3" s="32">
         <v>9.3055912140758643</v>
       </c>
-      <c r="U3" s="39">
+      <c r="U3" s="33">
         <v>9.1853207799272329</v>
       </c>
       <c r="V3" s="12" t="str">
@@ -3546,36 +3582,36 @@
       </c>
     </row>
     <row r="4" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="83" t="s">
+      <c r="A4" s="69" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="84"/>
+      <c r="B4" s="70"/>
       <c r="C4" s="24">
         <v>87.593900000000005</v>
       </c>
-      <c r="D4" s="32">
+      <c r="D4" s="26">
         <v>87.663716814159287</v>
       </c>
-      <c r="E4" s="32">
+      <c r="E4" s="26">
         <v>88.112094395280209</v>
       </c>
-      <c r="F4" s="32">
+      <c r="F4" s="26">
         <v>87.970025692263789</v>
       </c>
-      <c r="G4" s="32">
+      <c r="G4" s="26">
         <v>87.461708146264243</v>
       </c>
-      <c r="H4" s="32">
+      <c r="H4" s="26">
         <v>75.251363189416281</v>
       </c>
-      <c r="I4" s="33">
+      <c r="I4" s="27">
         <v>47.720683858280204</v>
       </c>
-      <c r="J4" s="41" cm="1">
+      <c r="J4" s="35" cm="1">
         <f t="array" ref="J4">-SUMPRODUCT((D1:H1-C1:G1)*(C4:G4+D4:H4)/2)</f>
         <v>78.394630770414679</v>
       </c>
-      <c r="K4" s="41" cm="1">
+      <c r="K4" s="35" cm="1">
         <f t="array" ref="K4">-SUMPRODUCT((D1:I1-C1:H1)*(C4:H4+D4:I4)/2)</f>
         <v>81.468931946607086</v>
       </c>
@@ -3583,29 +3619,29 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    87.5939, 87.6637168141593, 88.1120943952802, 87.9700256922638, 87.4617081462642, 75.2513631894163, 47.7206838582802,</v>
       </c>
-      <c r="M4" s="83" t="s">
+      <c r="M4" s="69" t="s">
         <v>10</v>
       </c>
-      <c r="N4" s="84"/>
-      <c r="O4" s="55">
+      <c r="N4" s="70"/>
+      <c r="O4" s="49">
         <v>2.4529187882918819</v>
       </c>
-      <c r="P4" s="32">
+      <c r="P4" s="26">
         <v>2.16276566139488</v>
       </c>
-      <c r="Q4" s="32">
+      <c r="Q4" s="26">
         <v>2.2973398804747198</v>
       </c>
-      <c r="R4" s="32">
+      <c r="R4" s="26">
         <v>2.134165319654592</v>
       </c>
-      <c r="S4" s="32">
+      <c r="S4" s="26">
         <v>2.3834878752826651</v>
       </c>
-      <c r="T4" s="32">
+      <c r="T4" s="26">
         <v>3.787986046410059</v>
       </c>
-      <c r="U4" s="33">
+      <c r="U4" s="27">
         <v>3.7419646549723868</v>
       </c>
       <c r="V4" s="12" t="str">
@@ -3614,31 +3650,31 @@
       </c>
     </row>
     <row r="5" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="83" t="s">
+      <c r="A5" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="85"/>
-      <c r="C5" s="85"/>
-      <c r="D5" s="85"/>
-      <c r="E5" s="85"/>
-      <c r="F5" s="85"/>
-      <c r="G5" s="85"/>
-      <c r="H5" s="85"/>
-      <c r="I5" s="84"/>
-      <c r="J5" s="41"/>
-      <c r="K5" s="41"/>
+      <c r="B5" s="71"/>
+      <c r="C5" s="71"/>
+      <c r="D5" s="71"/>
+      <c r="E5" s="71"/>
+      <c r="F5" s="71"/>
+      <c r="G5" s="71"/>
+      <c r="H5" s="71"/>
+      <c r="I5" s="70"/>
+      <c r="J5" s="35"/>
+      <c r="K5" s="35"/>
       <c r="L5" s="12"/>
-      <c r="M5" s="83" t="s">
+      <c r="M5" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="N5" s="85"/>
-      <c r="O5" s="85"/>
-      <c r="P5" s="85"/>
-      <c r="Q5" s="85"/>
-      <c r="R5" s="85"/>
-      <c r="S5" s="85"/>
-      <c r="T5" s="85"/>
-      <c r="U5" s="84"/>
+      <c r="N5" s="71"/>
+      <c r="O5" s="71"/>
+      <c r="P5" s="71"/>
+      <c r="Q5" s="71"/>
+      <c r="R5" s="71"/>
+      <c r="S5" s="71"/>
+      <c r="T5" s="71"/>
+      <c r="U5" s="70"/>
       <c r="V5" s="12"/>
     </row>
     <row r="6" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -3648,38 +3684,38 @@
       <c r="B6" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="25">
-        <v>93.176991150442475</v>
-      </c>
-      <c r="D6" s="26">
-        <v>92.551622418879049</v>
-      </c>
-      <c r="E6" s="26">
-        <v>91.770912089781632</v>
-      </c>
-      <c r="F6" s="26">
-        <v>88.774349259076644</v>
-      </c>
-      <c r="G6" s="26">
-        <v>85.119574275440684</v>
-      </c>
-      <c r="H6" s="26">
-        <v>65.55219912513661</v>
-      </c>
-      <c r="I6" s="27">
-        <v>55.581651513709751</v>
-      </c>
-      <c r="J6" s="41" cm="1">
+      <c r="C6" s="85">
+        <v>93.40216322517206</v>
+      </c>
+      <c r="D6" s="86">
+        <v>91.827126532236434</v>
+      </c>
+      <c r="E6" s="86">
+        <v>90.558689954065343</v>
+      </c>
+      <c r="F6" s="86">
+        <v>86.023376788149832</v>
+      </c>
+      <c r="G6" s="86">
+        <v>80.076301121405308</v>
+      </c>
+      <c r="H6" s="86">
+        <v>61.71287813908426</v>
+      </c>
+      <c r="I6" s="87">
+        <v>46.423510007295327</v>
+      </c>
+      <c r="J6" s="35" cm="1">
         <f t="array" ref="J6">-SUMPRODUCT((D1:H1-C1:G1)*(C6:G6+D6:H6)/2)</f>
-        <v>80.539204491388332</v>
-      </c>
-      <c r="K6" s="41" cm="1">
+        <v>79.00453781318754</v>
+      </c>
+      <c r="K6" s="35" cm="1">
         <f t="array" ref="K6">-SUMPRODUCT((D1:I1-C1:H1)*(C6:H6+D6:I6)/2)</f>
-        <v>83.567550757359498</v>
+        <v>81.707947516847028</v>
       </c>
       <c r="L6" s="12" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">    93.1769911504425, 92.551622418879, 91.7709120897816, 88.7743492590766, 85.1195742754407, 65.5521991251366, 55.5816515137098,</v>
+        <v xml:space="preserve">    93.4021632251721, 91.8271265322364, 90.5586899540653, 86.0233767881498, 80.0763011214053, 61.7128781390843, 46.4235100072953,</v>
       </c>
       <c r="M6" s="7" t="s">
         <v>12</v>
@@ -3687,71 +3723,71 @@
       <c r="N6" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="O6" s="25">
-        <v>3.3980555340015428</v>
-      </c>
-      <c r="P6" s="26">
-        <v>3.2526209506201238</v>
-      </c>
-      <c r="Q6" s="26">
-        <v>3.463276500799247</v>
-      </c>
-      <c r="R6" s="26">
-        <v>4.4197147654757591</v>
-      </c>
-      <c r="S6" s="26">
-        <v>4.9008511372208474</v>
-      </c>
-      <c r="T6" s="26">
-        <v>8.1544027156793923</v>
-      </c>
-      <c r="U6" s="27">
-        <v>8.3944532618135348</v>
+      <c r="O6" s="85">
+        <v>3.395734543818977</v>
+      </c>
+      <c r="P6" s="86">
+        <v>4.0701241715569392</v>
+      </c>
+      <c r="Q6" s="86">
+        <v>4.2545139093922257</v>
+      </c>
+      <c r="R6" s="86">
+        <v>5.0550386107492153</v>
+      </c>
+      <c r="S6" s="86">
+        <v>5.5998181447012403</v>
+      </c>
+      <c r="T6" s="86">
+        <v>8.7815136499154747</v>
+      </c>
+      <c r="U6" s="87">
+        <v>8.6649338950065129</v>
       </c>
       <c r="V6" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">    3.39805553400154, 3.25262095062012, 3.46327650079925, 4.41971476547576, 4.90085113722085, 8.15440271567939, 8.39445326181353,</v>
+        <v xml:space="preserve">    3.39573454381898, 4.07012417155694, 4.25451390939223, 5.05503861074922, 5.59981814470124, 8.78151364991547, 8.66493389500651,</v>
       </c>
     </row>
     <row r="7" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B7" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="40">
-        <v>92.538862792930757</v>
-      </c>
-      <c r="D7" s="41">
-        <v>92.596859257721377</v>
-      </c>
-      <c r="E7" s="41">
-        <v>92.131765845725312</v>
-      </c>
-      <c r="F7" s="41">
-        <v>91.399484424605745</v>
-      </c>
-      <c r="G7" s="41">
-        <v>88.38645086318509</v>
-      </c>
-      <c r="H7" s="41">
-        <v>71.063506893081538</v>
-      </c>
-      <c r="I7" s="42">
-        <v>52.957470797036883</v>
-      </c>
-      <c r="J7" s="41" cm="1">
+      <c r="C7" s="85">
+        <v>92.691248770894788</v>
+      </c>
+      <c r="D7" s="86">
+        <v>92.706981317600793</v>
+      </c>
+      <c r="E7" s="86">
+        <v>91.734513274336265</v>
+      </c>
+      <c r="F7" s="86">
+        <v>88.867553640890762</v>
+      </c>
+      <c r="G7" s="86">
+        <v>87.5647050003316</v>
+      </c>
+      <c r="H7" s="86">
+        <v>75.623785672886441</v>
+      </c>
+      <c r="I7" s="87">
+        <v>48.831339371447839</v>
+      </c>
+      <c r="J7" s="35" cm="1">
         <f t="array" ref="J7">-SUMPRODUCT((D1:H1-C1:G1)*(C7:G7+D7:H7)/2)</f>
-        <v>81.547963073498323</v>
-      </c>
-      <c r="K7" s="41" cm="1">
+        <v>81.271209742298794</v>
+      </c>
+      <c r="K7" s="35" cm="1">
         <f t="array" ref="K7">-SUMPRODUCT((D1:I1-C1:H1)*(C7:H7+D7:I7)/2)</f>
-        <v>84.648487515751285</v>
+        <v>84.382587868407157</v>
       </c>
       <c r="L7" s="12" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">    92.5388627929308, 92.5968592577214, 92.1317658457253, 91.3994844246057, 88.3864508631851, 71.0635068930815, 52.9574707970369,</v>
+        <v xml:space="preserve">    92.6912487708948, 92.7069813176008, 91.7345132743363, 88.8675536408908, 87.5647050003316, 75.6237856728864, 48.8313393714478,</v>
       </c>
       <c r="M7" s="7" t="s">
         <v>13</v>
@@ -3759,30 +3795,30 @@
       <c r="N7" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="O7" s="40">
-        <v>3.278810540442274</v>
-      </c>
-      <c r="P7" s="41">
-        <v>3.2750469252400021</v>
-      </c>
-      <c r="Q7" s="41">
-        <v>3.0872319165878661</v>
-      </c>
-      <c r="R7" s="41">
-        <v>3.116510241534836</v>
-      </c>
-      <c r="S7" s="41">
-        <v>3.6330124165638931</v>
-      </c>
-      <c r="T7" s="41">
-        <v>5.8392378785926198</v>
-      </c>
-      <c r="U7" s="42">
-        <v>5.8333958789788376</v>
+      <c r="O7" s="58">
+        <v>3.1492092951527728</v>
+      </c>
+      <c r="P7" s="59">
+        <v>3.3182076336991431</v>
+      </c>
+      <c r="Q7" s="59">
+        <v>3.198166186176159</v>
+      </c>
+      <c r="R7" s="59">
+        <v>3.1321269598885868</v>
+      </c>
+      <c r="S7" s="59">
+        <v>3.0750631997727318</v>
+      </c>
+      <c r="T7" s="59">
+        <v>5.166114204995413</v>
+      </c>
+      <c r="U7" s="60">
+        <v>5.9316401890770027</v>
       </c>
       <c r="V7" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">    3.27881054044227, 3.27504692524, 3.08723191658787, 3.11651024153484, 3.63301241656389, 5.83923787859262, 5.83339587897884,</v>
+        <v xml:space="preserve">    3.14920929515277, 3.31820763369914, 3.19816618617616, 3.13212695988859, 3.07506319977273, 5.16611420499541, 5.931640189077,</v>
       </c>
     </row>
     <row r="8" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -3792,34 +3828,20 @@
       <c r="B8" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="37">
-        <v>93.178957718780751</v>
-      </c>
-      <c r="D8" s="38">
-        <v>92.588021234324387</v>
-      </c>
-      <c r="E8" s="38">
-        <v>91.154392915740331</v>
-      </c>
-      <c r="F8" s="38">
-        <v>86.726182752445951</v>
-      </c>
-      <c r="G8" s="38">
-        <v>79.592533960789737</v>
-      </c>
-      <c r="H8" s="38">
-        <v>59.385398374265058</v>
-      </c>
-      <c r="I8" s="39">
-        <v>46.003956204926787</v>
-      </c>
-      <c r="J8" s="41" cm="1">
+      <c r="C8" s="31"/>
+      <c r="D8" s="32"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="32"/>
+      <c r="H8" s="32"/>
+      <c r="I8" s="33"/>
+      <c r="J8" s="35" cm="1">
         <f t="array" ref="J8">-SUMPRODUCT((D1:H1-C1:G1)*(C8:G8+D8:H8)/2)</f>
-        <v>79.241564157129375</v>
-      </c>
-      <c r="K8" s="41" cm="1">
+        <v>0</v>
+      </c>
+      <c r="K8" s="35" cm="1">
         <f t="array" ref="K8">-SUMPRODUCT((D1:I1-C1:H1)*(C8:H8+D8:I8)/2)</f>
-        <v>81.876298021609173</v>
+        <v>0</v>
       </c>
       <c r="L8" s="12"/>
       <c r="M8" s="7" t="s">
@@ -3828,27 +3850,13 @@
       <c r="N8" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="O8" s="37">
-        <v>3.4918802134136859</v>
-      </c>
-      <c r="P8" s="38">
-        <v>3.2674185777936322</v>
-      </c>
-      <c r="Q8" s="38">
-        <v>3.5657852237659609</v>
-      </c>
-      <c r="R8" s="38">
-        <v>4.788330235940748</v>
-      </c>
-      <c r="S8" s="38">
-        <v>6.7304751140555794</v>
-      </c>
-      <c r="T8" s="38">
-        <v>9.9654838580001908</v>
-      </c>
-      <c r="U8" s="39">
-        <v>8.2806755227569209</v>
-      </c>
+      <c r="O8" s="31"/>
+      <c r="P8" s="32"/>
+      <c r="Q8" s="32"/>
+      <c r="R8" s="32"/>
+      <c r="S8" s="32"/>
+      <c r="T8" s="32"/>
+      <c r="U8" s="33"/>
       <c r="V8" s="12"/>
     </row>
     <row r="9" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -3858,34 +3866,34 @@
       <c r="B9" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="55">
-        <v>93.484787930691454</v>
-      </c>
-      <c r="D9" s="32">
-        <v>92.286170295590779</v>
-      </c>
-      <c r="E9" s="32">
-        <v>90.520439911533245</v>
-      </c>
-      <c r="F9" s="32">
-        <v>86.970262141829366</v>
-      </c>
-      <c r="G9" s="32">
-        <v>76.004036943802859</v>
-      </c>
-      <c r="H9" s="32">
-        <v>57.733005187472791</v>
-      </c>
-      <c r="I9" s="33">
-        <v>47.315746676009297</v>
-      </c>
-      <c r="J9" s="41" cm="1">
+      <c r="C9" s="58">
+        <v>93.402168992234664</v>
+      </c>
+      <c r="D9" s="59">
+        <v>93.248776661851196</v>
+      </c>
+      <c r="E9" s="59">
+        <v>92.691271839145102</v>
+      </c>
+      <c r="F9" s="59">
+        <v>88.452475079080841</v>
+      </c>
+      <c r="G9" s="59">
+        <v>80.836250025230896</v>
+      </c>
+      <c r="H9" s="59">
+        <v>58.587493548098742</v>
+      </c>
+      <c r="I9" s="60">
+        <v>46.761612701378603</v>
+      </c>
+      <c r="J9" s="35" cm="1">
         <f t="array" ref="J9">-SUMPRODUCT((D1:H1-C1:G1)*(C9:G9+D9:H9)/2)</f>
-        <v>78.656833320357435</v>
-      </c>
-      <c r="K9" s="41" cm="1">
+        <v>80.123872395089933</v>
+      </c>
+      <c r="K9" s="35" cm="1">
         <f t="array" ref="K9">-SUMPRODUCT((D1:I1-C1:H1)*(C9:H9+D9:I9)/2)</f>
-        <v>81.283052116944489</v>
+        <v>82.757600051326861</v>
       </c>
       <c r="L9" s="12"/>
       <c r="M9" s="7" t="s">
@@ -3894,26 +3902,26 @@
       <c r="N9" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="O9" s="55">
-        <v>3.4442566922914959</v>
-      </c>
-      <c r="P9" s="32">
-        <v>3.9409056823187019</v>
-      </c>
-      <c r="Q9" s="32">
-        <v>4.0414392946512523</v>
-      </c>
-      <c r="R9" s="32">
-        <v>4.0313253500272799</v>
-      </c>
-      <c r="S9" s="32">
-        <v>9.4673894695851892</v>
-      </c>
-      <c r="T9" s="32">
-        <v>11.13615006293981</v>
-      </c>
-      <c r="U9" s="33">
-        <v>9.7110750490101303</v>
+      <c r="O9" s="58">
+        <v>3.54951767012634</v>
+      </c>
+      <c r="P9" s="59">
+        <v>3.9476305437492138</v>
+      </c>
+      <c r="Q9" s="59">
+        <v>3.9153520636466741</v>
+      </c>
+      <c r="R9" s="59">
+        <v>4.7440261437688536</v>
+      </c>
+      <c r="S9" s="59">
+        <v>6.9981331013815007</v>
+      </c>
+      <c r="T9" s="59">
+        <v>10.73836101002882</v>
+      </c>
+      <c r="U9" s="60">
+        <v>8.4598560379029468</v>
       </c>
       <c r="V9" s="12"/>
     </row>
@@ -3924,38 +3932,24 @@
       <c r="B10" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="55">
-        <v>93.108161258603744</v>
-      </c>
-      <c r="D10" s="32">
-        <v>92.06688062468821</v>
-      </c>
-      <c r="E10" s="32">
-        <v>91.050153259687931</v>
-      </c>
-      <c r="F10" s="32">
-        <v>88.14252141742864</v>
-      </c>
-      <c r="G10" s="32">
-        <v>81.805525999359858</v>
-      </c>
-      <c r="H10" s="32">
-        <v>61.262652214407851</v>
-      </c>
-      <c r="I10" s="33">
-        <v>50.605371442082827</v>
-      </c>
-      <c r="J10" s="41" cm="1">
+      <c r="C10" s="49"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="26"/>
+      <c r="I10" s="27"/>
+      <c r="J10" s="35" cm="1">
         <f t="array" ref="J10">-SUMPRODUCT((D1:H1-C1:G1)*(C10:G10+D10:H10)/2)</f>
-        <v>79.606588220197978</v>
-      </c>
-      <c r="K10" s="41" cm="1">
+        <v>0</v>
+      </c>
+      <c r="K10" s="35" cm="1">
         <f t="array" ref="K10">-SUMPRODUCT((D1:I1-C1:H1)*(C10:H10+D10:I10)/2)</f>
-        <v>82.403288811610238</v>
+        <v>0</v>
       </c>
       <c r="L10" s="12" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">    93.1081612586037, 92.0668806246882, 91.0501532596879, 88.1425214174286, 81.8055259993599, 61.2626522144079, 50.6053714420828,</v>
+        <v xml:space="preserve">    ,</v>
       </c>
       <c r="M10" s="7" t="s">
         <v>12</v>
@@ -3963,27 +3957,13 @@
       <c r="N10" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="O10" s="55">
-        <v>3.8601198040536779</v>
-      </c>
-      <c r="P10" s="32">
-        <v>3.8002863673418821</v>
-      </c>
-      <c r="Q10" s="32">
-        <v>3.9464349866089141</v>
-      </c>
-      <c r="R10" s="32">
-        <v>3.955874479625876</v>
-      </c>
-      <c r="S10" s="32">
-        <v>5.3194143005645147</v>
-      </c>
-      <c r="T10" s="32">
-        <v>9.6259787509159409</v>
-      </c>
-      <c r="U10" s="33">
-        <v>8.0386616165015887</v>
-      </c>
+      <c r="O10" s="49"/>
+      <c r="P10" s="26"/>
+      <c r="Q10" s="26"/>
+      <c r="R10" s="26"/>
+      <c r="S10" s="26"/>
+      <c r="T10" s="26"/>
+      <c r="U10" s="27"/>
       <c r="V10" s="12"/>
     </row>
     <row r="11" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -3993,15 +3973,35 @@
       <c r="B11" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="43"/>
-      <c r="D11" s="44"/>
-      <c r="E11" s="44"/>
-      <c r="F11" s="44"/>
-      <c r="G11" s="44"/>
-      <c r="H11" s="44"/>
-      <c r="I11" s="45"/>
-      <c r="J11" s="41"/>
-      <c r="K11" s="41"/>
+      <c r="C11" s="58">
+        <v>90.295968534906564</v>
+      </c>
+      <c r="D11" s="59">
+        <v>90.405113077679459</v>
+      </c>
+      <c r="E11" s="59">
+        <v>90.529243332554771</v>
+      </c>
+      <c r="F11" s="59">
+        <v>90.464208167890718</v>
+      </c>
+      <c r="G11" s="59">
+        <v>89.370346340942973</v>
+      </c>
+      <c r="H11" s="59">
+        <v>80.495811670804514</v>
+      </c>
+      <c r="I11" s="60">
+        <v>54.200509231625418</v>
+      </c>
+      <c r="J11" s="35" cm="1">
+        <f t="array" ref="J11">-SUMPRODUCT((D1:H1-C1:G1)*(C11:G11+D11:H11)/2)</f>
+        <v>80.788810528926135</v>
+      </c>
+      <c r="K11" s="35" cm="1">
+        <f t="array" ref="K11">-SUMPRODUCT((D1:I1-C1:H1)*(C11:H11+D11:I11)/2)</f>
+        <v>84.156218551486887</v>
+      </c>
       <c r="L11" s="12"/>
       <c r="M11" s="7" t="s">
         <v>11</v>
@@ -4009,13 +4009,27 @@
       <c r="N11" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="O11" s="43"/>
-      <c r="P11" s="44"/>
-      <c r="Q11" s="44"/>
-      <c r="R11" s="44"/>
-      <c r="S11" s="44"/>
-      <c r="T11" s="44"/>
-      <c r="U11" s="45"/>
+      <c r="O11" s="58">
+        <v>2.645635465917767</v>
+      </c>
+      <c r="P11" s="59">
+        <v>2.349990742414489</v>
+      </c>
+      <c r="Q11" s="59">
+        <v>2.284121152514234</v>
+      </c>
+      <c r="R11" s="59">
+        <v>2.4722451039664972</v>
+      </c>
+      <c r="S11" s="59">
+        <v>2.569604191233966</v>
+      </c>
+      <c r="T11" s="59">
+        <v>3.931910154117956</v>
+      </c>
+      <c r="U11" s="60">
+        <v>6.3131910290344502</v>
+      </c>
       <c r="V11" s="12"/>
     </row>
     <row r="12" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -4025,15 +4039,15 @@
       <c r="B12" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="43"/>
-      <c r="D12" s="44"/>
-      <c r="E12" s="44"/>
-      <c r="F12" s="44"/>
-      <c r="G12" s="44"/>
-      <c r="H12" s="44"/>
-      <c r="I12" s="45"/>
-      <c r="J12" s="41"/>
-      <c r="K12" s="41"/>
+      <c r="C12" s="37"/>
+      <c r="D12" s="38"/>
+      <c r="E12" s="38"/>
+      <c r="F12" s="38"/>
+      <c r="G12" s="38"/>
+      <c r="H12" s="38"/>
+      <c r="I12" s="39"/>
+      <c r="J12" s="35"/>
+      <c r="K12" s="35"/>
       <c r="L12" s="12" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
@@ -4044,74 +4058,74 @@
       <c r="N12" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="O12" s="43"/>
-      <c r="P12" s="44"/>
-      <c r="Q12" s="44"/>
-      <c r="R12" s="44"/>
-      <c r="S12" s="44"/>
-      <c r="T12" s="44"/>
-      <c r="U12" s="45"/>
+      <c r="O12" s="37"/>
+      <c r="P12" s="38"/>
+      <c r="Q12" s="38"/>
+      <c r="R12" s="38"/>
+      <c r="S12" s="38"/>
+      <c r="T12" s="38"/>
+      <c r="U12" s="39"/>
       <c r="V12" s="12"/>
     </row>
     <row r="13" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="83" t="s">
+      <c r="A13" s="69" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="85"/>
-      <c r="C13" s="90"/>
-      <c r="D13" s="90"/>
-      <c r="E13" s="90"/>
-      <c r="F13" s="90"/>
-      <c r="G13" s="90"/>
-      <c r="H13" s="90"/>
-      <c r="I13" s="89"/>
-      <c r="J13" s="41"/>
-      <c r="K13" s="41"/>
+      <c r="B13" s="71"/>
+      <c r="C13" s="72"/>
+      <c r="D13" s="72"/>
+      <c r="E13" s="72"/>
+      <c r="F13" s="72"/>
+      <c r="G13" s="72"/>
+      <c r="H13" s="72"/>
+      <c r="I13" s="73"/>
+      <c r="J13" s="35"/>
+      <c r="K13" s="35"/>
       <c r="L13" s="12"/>
-      <c r="M13" s="83" t="s">
+      <c r="M13" s="69" t="s">
         <v>22</v>
       </c>
-      <c r="N13" s="85"/>
-      <c r="O13" s="90"/>
-      <c r="P13" s="90"/>
-      <c r="Q13" s="90"/>
-      <c r="R13" s="90"/>
-      <c r="S13" s="90"/>
-      <c r="T13" s="90"/>
-      <c r="U13" s="89"/>
+      <c r="N13" s="71"/>
+      <c r="O13" s="72"/>
+      <c r="P13" s="72"/>
+      <c r="Q13" s="72"/>
+      <c r="R13" s="72"/>
+      <c r="S13" s="72"/>
+      <c r="T13" s="72"/>
+      <c r="U13" s="73"/>
       <c r="V13" s="12"/>
     </row>
     <row r="14" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="83" t="s">
+      <c r="A14" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="84"/>
-      <c r="C14" s="59">
+      <c r="B14" s="70"/>
+      <c r="C14" s="53">
         <v>93.782740335124032</v>
       </c>
-      <c r="D14" s="60">
+      <c r="D14" s="54">
         <v>91.948208894540599</v>
       </c>
-      <c r="E14" s="60">
+      <c r="E14" s="54">
         <v>90.212980504444957</v>
       </c>
-      <c r="F14" s="60">
+      <c r="F14" s="54">
         <v>84.630388959535409</v>
       </c>
-      <c r="G14" s="60">
+      <c r="G14" s="54">
         <v>75.371093175546491</v>
       </c>
-      <c r="H14" s="60">
+      <c r="H14" s="54">
         <v>59.627211308056303</v>
       </c>
-      <c r="I14" s="61">
+      <c r="I14" s="55">
         <v>47.844185503334799</v>
       </c>
-      <c r="J14" s="41" cm="1">
+      <c r="J14" s="35" cm="1">
         <f t="array" ref="J14">-SUMPRODUCT((D1:H1-C1:G1)*(C14:G14+D14:H14)/2)</f>
         <v>78.220843605913544</v>
       </c>
-      <c r="K14" s="41" cm="1">
+      <c r="K14" s="35" cm="1">
         <f t="array" ref="K14">-SUMPRODUCT((D1:I1-C1:H1)*(C14:H14+D14:I14)/2)</f>
         <v>80.907628526198323</v>
       </c>
@@ -4119,29 +4133,29 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    93.782740335124, 91.9482088945406, 90.212980504445, 84.6303889595354, 75.3710931755465, 59.6272113080563, 47.8441855033348,</v>
       </c>
-      <c r="M14" s="83" t="s">
+      <c r="M14" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="N14" s="84"/>
-      <c r="O14" s="59">
+      <c r="N14" s="70"/>
+      <c r="O14" s="53">
         <v>3.5391983918820551</v>
       </c>
-      <c r="P14" s="60">
+      <c r="P14" s="54">
         <v>4.1060038651541966</v>
       </c>
-      <c r="Q14" s="60">
+      <c r="Q14" s="54">
         <v>4.774795806468676</v>
       </c>
-      <c r="R14" s="60">
+      <c r="R14" s="54">
         <v>5.3483339064680431</v>
       </c>
-      <c r="S14" s="60">
+      <c r="S14" s="54">
         <v>8.0994903921197494</v>
       </c>
-      <c r="T14" s="60">
+      <c r="T14" s="54">
         <v>10.59987402205407</v>
       </c>
-      <c r="U14" s="61">
+      <c r="U14" s="55">
         <v>8.7604668874903737</v>
       </c>
       <c r="V14" s="12" t="str">
@@ -4150,11 +4164,11 @@
       </c>
     </row>
     <row r="15" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="88" t="s">
+      <c r="A15" s="74" t="s">
         <v>8</v>
       </c>
-      <c r="B15" s="89"/>
-      <c r="C15" s="62">
+      <c r="B15" s="73"/>
+      <c r="C15" s="56">
         <v>93.226230330712227</v>
       </c>
       <c r="D15" s="12">
@@ -4172,14 +4186,14 @@
       <c r="H15" s="12">
         <v>59.41454222499042</v>
       </c>
-      <c r="I15" s="63">
+      <c r="I15" s="57">
         <v>50.563407411252108</v>
       </c>
-      <c r="J15" s="41" cm="1">
+      <c r="J15" s="35" cm="1">
         <f t="array" ref="J15">-SUMPRODUCT((D1:H1-C1:G1)*(C15:G15+D15:H15)/2)</f>
         <v>78.369743178285859</v>
       </c>
-      <c r="K15" s="41" cm="1">
+      <c r="K15" s="35" cm="1">
         <f t="array" ref="K15">-SUMPRODUCT((D1:I1-C1:H1)*(C15:H15+D15:I15)/2)</f>
         <v>81.11919191919192</v>
       </c>
@@ -4187,11 +4201,11 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    93.2262303307122, 91.8332915221297, 90.3252911645718, 85.3834923600839, 76.5670002912366, 59.4145422249904, 50.5634074112521,</v>
       </c>
-      <c r="M15" s="83" t="s">
+      <c r="M15" s="69" t="s">
         <v>8</v>
       </c>
-      <c r="N15" s="84"/>
-      <c r="O15" s="62">
+      <c r="N15" s="70"/>
+      <c r="O15" s="56">
         <v>3.945711842949601</v>
       </c>
       <c r="P15" s="12">
@@ -4209,7 +4223,7 @@
       <c r="T15" s="12">
         <v>10.788297692871961</v>
       </c>
-      <c r="U15" s="63">
+      <c r="U15" s="57">
         <v>8.7433484877826491</v>
       </c>
       <c r="V15" s="12" t="str">
@@ -4218,11 +4232,11 @@
       </c>
     </row>
     <row r="16" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="83" t="s">
+      <c r="A16" s="69" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="84"/>
-      <c r="C16" s="62">
+      <c r="B16" s="70"/>
+      <c r="C16" s="56">
         <v>93.004922187908207</v>
       </c>
       <c r="D16" s="12">
@@ -4240,14 +4254,14 @@
       <c r="H16" s="12">
         <v>57.917332041511322</v>
       </c>
-      <c r="I16" s="63">
+      <c r="I16" s="57">
         <v>48.007794185070807</v>
       </c>
-      <c r="J16" s="41" cm="1">
+      <c r="J16" s="35" cm="1">
         <f t="array" ref="J16">-SUMPRODUCT((D1:H1-C1:G1)*(C16:G16+D16:H16)/2)</f>
         <v>77.501290236074709</v>
       </c>
-      <c r="K16" s="41" cm="1">
+      <c r="K16" s="35" cm="1">
         <f t="array" ref="K16">-SUMPRODUCT((D1:I1-C1:H1)*(C16:H16+D16:I16)/2)</f>
         <v>80.14941839173926</v>
       </c>
@@ -4255,11 +4269,11 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    93.0049221879082, 91.5185021785079, 89.7294209580821, 83.3486073985646, 74.0877199053048, 57.9173320415113, 48.0077941850708,</v>
       </c>
-      <c r="M16" s="83" t="s">
+      <c r="M16" s="69" t="s">
         <v>23</v>
       </c>
-      <c r="N16" s="84"/>
-      <c r="O16" s="62">
+      <c r="N16" s="70"/>
+      <c r="O16" s="56">
         <v>3.690401528555848</v>
       </c>
       <c r="P16" s="12">
@@ -4277,7 +4291,7 @@
       <c r="T16" s="12">
         <v>10.83557708581068</v>
       </c>
-      <c r="U16" s="63">
+      <c r="U16" s="57">
         <v>9.2904800440053528</v>
       </c>
       <c r="V16" s="12" t="str">
@@ -4286,126 +4300,126 @@
       </c>
     </row>
     <row r="17" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="83" t="s">
+      <c r="A17" s="69" t="s">
         <v>24</v>
       </c>
-      <c r="B17" s="84"/>
-      <c r="C17" s="64">
+      <c r="B17" s="70"/>
+      <c r="C17" s="58">
         <v>93.123279613145442</v>
       </c>
-      <c r="D17" s="65">
+      <c r="D17" s="59">
         <v>91.674385879923975</v>
       </c>
-      <c r="E17" s="65">
+      <c r="E17" s="59">
         <v>89.698688281617194</v>
       </c>
-      <c r="F17" s="65">
+      <c r="F17" s="59">
         <v>84.957067102656595</v>
       </c>
-      <c r="G17" s="65">
+      <c r="G17" s="59">
         <v>75.939082518014857</v>
       </c>
-      <c r="H17" s="65">
+      <c r="H17" s="59">
         <v>59.995092229748238</v>
       </c>
-      <c r="I17" s="66">
+      <c r="I17" s="60">
         <v>48.440303693515233</v>
       </c>
-      <c r="J17" s="41" cm="1">
+      <c r="J17" s="35" cm="1">
         <f t="array" ref="J17">-SUMPRODUCT((D1:H1-C1:G1)*(C17:G17+D17:H17)/2)</f>
         <v>78.078434213675436</v>
       </c>
-      <c r="K17" s="41" cm="1">
+      <c r="K17" s="35" cm="1">
         <f t="array" ref="K17">-SUMPRODUCT((D1:I1-C1:H1)*(C17:H17+D17:I17)/2)</f>
         <v>80.789319111757024</v>
       </c>
       <c r="L17" s="12"/>
-      <c r="M17" s="83" t="s">
+      <c r="M17" s="69" t="s">
         <v>24</v>
       </c>
-      <c r="N17" s="84"/>
-      <c r="O17" s="64">
+      <c r="N17" s="70"/>
+      <c r="O17" s="58">
         <v>3.8088682011350912</v>
       </c>
-      <c r="P17" s="65">
+      <c r="P17" s="59">
         <v>4.4783864386850611</v>
       </c>
-      <c r="Q17" s="65">
+      <c r="Q17" s="59">
         <v>5.0849840192173117</v>
       </c>
-      <c r="R17" s="65">
+      <c r="R17" s="59">
         <v>5.0366327026230584</v>
       </c>
-      <c r="S17" s="65">
+      <c r="S17" s="59">
         <v>7.6643798786674449</v>
       </c>
-      <c r="T17" s="65">
+      <c r="T17" s="59">
         <v>10.05146904627655</v>
       </c>
-      <c r="U17" s="66">
+      <c r="U17" s="60">
         <v>9.821397671709315</v>
       </c>
       <c r="V17" s="12"/>
     </row>
     <row r="18" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="83" t="s">
+      <c r="A18" s="69" t="s">
         <v>25</v>
       </c>
-      <c r="B18" s="85"/>
-      <c r="C18" s="86"/>
-      <c r="D18" s="86"/>
-      <c r="E18" s="86"/>
-      <c r="F18" s="86"/>
-      <c r="G18" s="86"/>
-      <c r="H18" s="86"/>
-      <c r="I18" s="87"/>
-      <c r="J18" s="41"/>
-      <c r="K18" s="41"/>
+      <c r="B18" s="71"/>
+      <c r="C18" s="75"/>
+      <c r="D18" s="75"/>
+      <c r="E18" s="75"/>
+      <c r="F18" s="75"/>
+      <c r="G18" s="75"/>
+      <c r="H18" s="75"/>
+      <c r="I18" s="76"/>
+      <c r="J18" s="35"/>
+      <c r="K18" s="35"/>
       <c r="L18" s="12"/>
-      <c r="M18" s="83" t="s">
+      <c r="M18" s="69" t="s">
         <v>25</v>
       </c>
-      <c r="N18" s="85"/>
-      <c r="O18" s="86"/>
-      <c r="P18" s="86"/>
-      <c r="Q18" s="86"/>
-      <c r="R18" s="86"/>
-      <c r="S18" s="86"/>
-      <c r="T18" s="86"/>
-      <c r="U18" s="87"/>
+      <c r="N18" s="71"/>
+      <c r="O18" s="75"/>
+      <c r="P18" s="75"/>
+      <c r="Q18" s="75"/>
+      <c r="R18" s="75"/>
+      <c r="S18" s="75"/>
+      <c r="T18" s="75"/>
+      <c r="U18" s="76"/>
       <c r="V18" s="12"/>
     </row>
     <row r="19" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="83" t="s">
+      <c r="A19" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="B19" s="84"/>
-      <c r="C19" s="59">
+      <c r="B19" s="70"/>
+      <c r="C19" s="53">
         <v>92.969518190757128</v>
       </c>
-      <c r="D19" s="60">
+      <c r="D19" s="54">
         <v>91.851524090462149</v>
       </c>
-      <c r="E19" s="60">
+      <c r="E19" s="54">
         <v>90.756145526057011</v>
       </c>
-      <c r="F19" s="60">
+      <c r="F19" s="54">
         <v>87.253136561158271</v>
       </c>
-      <c r="G19" s="60">
+      <c r="G19" s="54">
         <v>81.178972136437139</v>
       </c>
-      <c r="H19" s="60">
+      <c r="H19" s="54">
         <v>57.386929529378847</v>
       </c>
-      <c r="I19" s="61">
+      <c r="I19" s="55">
         <v>44.855442809482213</v>
       </c>
-      <c r="J19" s="41" cm="1">
+      <c r="J19" s="35" cm="1">
         <f t="array" ref="J19">-SUMPRODUCT((D1:H1-C1:G1)*(C19:G19+D19:H19)/2)</f>
         <v>79.079417714109411</v>
       </c>
-      <c r="K19" s="41" cm="1">
+      <c r="K19" s="35" cm="1">
         <f t="array" ref="K19">-SUMPRODUCT((D1:I1-C1:H1)*(C19:H19+D19:I19)/2)</f>
         <v>81.635477022580943</v>
       </c>
@@ -4413,29 +4427,29 @@
         <f t="shared" ref="L19:L21" si="2">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C19:I19)&amp;","</f>
         <v xml:space="preserve">    92.9695181907571, 91.8515240904621, 90.756145526057, 87.2531365611583, 81.1789721364371, 57.3869295293788, 44.8554428094822,</v>
       </c>
-      <c r="M19" s="83" t="s">
+      <c r="M19" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="N19" s="84"/>
-      <c r="O19" s="59">
+      <c r="N19" s="70"/>
+      <c r="O19" s="53">
         <v>3.3991921823554931</v>
       </c>
-      <c r="P19" s="60">
+      <c r="P19" s="54">
         <v>3.6561489783789969</v>
       </c>
-      <c r="Q19" s="60">
+      <c r="Q19" s="54">
         <v>3.4316179388806831</v>
       </c>
-      <c r="R19" s="60">
+      <c r="R19" s="54">
         <v>3.3610781227617821</v>
       </c>
-      <c r="S19" s="60">
+      <c r="S19" s="54">
         <v>5.2773835873092807</v>
       </c>
-      <c r="T19" s="60">
+      <c r="T19" s="54">
         <v>8.2027130196510409</v>
       </c>
-      <c r="U19" s="61">
+      <c r="U19" s="55">
         <v>5.203571843512913</v>
       </c>
       <c r="V19" s="12" t="str">
@@ -4444,11 +4458,11 @@
       </c>
     </row>
     <row r="20" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="88" t="s">
+      <c r="A20" s="74" t="s">
         <v>8</v>
       </c>
-      <c r="B20" s="89"/>
-      <c r="C20" s="62">
+      <c r="B20" s="73"/>
+      <c r="C20" s="56">
         <v>91.898721730580135</v>
       </c>
       <c r="D20" s="12">
@@ -4466,14 +4480,14 @@
       <c r="H20" s="12">
         <v>71.387388010853613</v>
       </c>
-      <c r="I20" s="63">
+      <c r="I20" s="57">
         <v>45.596343105620853</v>
       </c>
-      <c r="J20" s="41" cm="1">
+      <c r="J20" s="35" cm="1">
         <f t="array" ref="J20">-SUMPRODUCT((D1:H1-C1:G1)*(C20:G20+D20:H20)/2)</f>
         <v>79.700846821050931</v>
       </c>
-      <c r="K20" s="41" cm="1">
+      <c r="K20" s="35" cm="1">
         <f t="array" ref="K20">-SUMPRODUCT((D1:I1-C1:H1)*(C20:H20+D20:I20)/2)</f>
         <v>82.625440098962798</v>
       </c>
@@ -4481,11 +4495,11 @@
         <f t="shared" si="2"/>
         <v xml:space="preserve">    91.8987217305801, 90.765995668936, 89.7052685000158, 87.9596853490659, 85.7500007208828, 71.3873880108536, 45.5963431056209,</v>
       </c>
-      <c r="M20" s="83" t="s">
+      <c r="M20" s="69" t="s">
         <v>8</v>
       </c>
-      <c r="N20" s="84"/>
-      <c r="O20" s="62">
+      <c r="N20" s="70"/>
+      <c r="O20" s="56">
         <v>3.190312271555559</v>
       </c>
       <c r="P20" s="12">
@@ -4503,7 +4517,7 @@
       <c r="T20" s="12">
         <v>4.756712112750666</v>
       </c>
-      <c r="U20" s="63">
+      <c r="U20" s="57">
         <v>2.488810891584841</v>
       </c>
       <c r="V20" s="12" t="str">
@@ -4512,11 +4526,11 @@
       </c>
     </row>
     <row r="21" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="83" t="s">
+      <c r="A21" s="69" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="84"/>
-      <c r="C21" s="62">
+      <c r="B21" s="70"/>
+      <c r="C21" s="56">
         <v>93.044276622923505</v>
       </c>
       <c r="D21" s="12">
@@ -4534,14 +4548,14 @@
       <c r="H21" s="12">
         <v>59.442100133507502</v>
       </c>
-      <c r="I21" s="63">
+      <c r="I21" s="57">
         <v>49.533828147302302</v>
       </c>
-      <c r="J21" s="41" cm="1">
+      <c r="J21" s="35" cm="1">
         <f t="array" ref="J21">-SUMPRODUCT((D1:H1-C1:G1)*(C21:G21+D21:H21)/2)</f>
         <v>78.834323321712716</v>
       </c>
-      <c r="K21" s="41" cm="1">
+      <c r="K21" s="35" cm="1">
         <f t="array" ref="K21">-SUMPRODUCT((D1:I1-C1:H1)*(C21:H21+D21:I21)/2)</f>
         <v>81.55872152873296</v>
       </c>
@@ -4549,11 +4563,11 @@
         <f t="shared" si="2"/>
         <v xml:space="preserve">    93.0442766229235, 91.9351551484009, 90.9488922914558, 85.9525053561594, 78.9151838107019, 59.4421001335075, 49.5338281473023,</v>
       </c>
-      <c r="M21" s="83" t="s">
+      <c r="M21" s="69" t="s">
         <v>23</v>
       </c>
-      <c r="N21" s="84"/>
-      <c r="O21" s="62">
+      <c r="N21" s="70"/>
+      <c r="O21" s="56">
         <v>3.72078192123604</v>
       </c>
       <c r="P21" s="12">
@@ -4571,7 +4585,7 @@
       <c r="T21" s="12">
         <v>10.04668436860082</v>
       </c>
-      <c r="U21" s="63">
+      <c r="U21" s="57">
         <v>9.2355901481835172</v>
       </c>
       <c r="V21" s="12" t="str">
@@ -4580,88 +4594,88 @@
       </c>
     </row>
     <row r="22" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="83" t="s">
+      <c r="A22" s="69" t="s">
         <v>24</v>
       </c>
-      <c r="B22" s="84"/>
-      <c r="C22" s="64">
+      <c r="B22" s="70"/>
+      <c r="C22" s="58">
         <v>93.174110502686005</v>
       </c>
-      <c r="D22" s="65">
+      <c r="D22" s="59">
         <v>91.391724841910417</v>
       </c>
-      <c r="E22" s="65">
+      <c r="E22" s="59">
         <v>89.591539142495463</v>
       </c>
-      <c r="F22" s="65">
+      <c r="F22" s="59">
         <v>84.690597092823751</v>
       </c>
-      <c r="G22" s="65">
+      <c r="G22" s="59">
         <v>76.401347185817656</v>
       </c>
-      <c r="H22" s="65">
+      <c r="H22" s="59">
         <v>59.963667505774268</v>
       </c>
-      <c r="I22" s="66">
+      <c r="I22" s="60">
         <v>47.725577210875521</v>
       </c>
-      <c r="J22" s="41" cm="1">
+      <c r="J22" s="35" cm="1">
         <f t="array" ref="J22">-SUMPRODUCT((D1:H1-C1:G1)*(C22:G22+D22:H22)/2)</f>
         <v>77.994698988168864</v>
       </c>
-      <c r="K22" s="41" cm="1">
+      <c r="K22" s="35" cm="1">
         <f t="array" ref="K22">-SUMPRODUCT((D1:I1-C1:H1)*(C22:H22+D22:I22)/2)</f>
         <v>80.686930106085114</v>
       </c>
       <c r="L22" s="12"/>
-      <c r="M22" s="83" t="s">
+      <c r="M22" s="69" t="s">
         <v>24</v>
       </c>
-      <c r="N22" s="84"/>
-      <c r="O22" s="64">
+      <c r="N22" s="70"/>
+      <c r="O22" s="58">
         <v>3.8766021792735019</v>
       </c>
-      <c r="P22" s="65">
+      <c r="P22" s="59">
         <v>4.8126411406228078</v>
       </c>
-      <c r="Q22" s="65">
+      <c r="Q22" s="59">
         <v>4.6512210016047986</v>
       </c>
-      <c r="R22" s="65">
+      <c r="R22" s="59">
         <v>5.2416066355763284</v>
       </c>
-      <c r="S22" s="65">
+      <c r="S22" s="59">
         <v>8.0769588602235256</v>
       </c>
-      <c r="T22" s="65">
+      <c r="T22" s="59">
         <v>10.657363307561541</v>
       </c>
-      <c r="U22" s="66">
+      <c r="U22" s="60">
         <v>9.200486032966916</v>
       </c>
       <c r="V22" s="12"/>
     </row>
     <row r="23" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="31"/>
-      <c r="B23" s="31"/>
-      <c r="C23" s="31"/>
-      <c r="D23" s="31"/>
-      <c r="E23" s="31"/>
-      <c r="F23" s="31"/>
-      <c r="G23" s="31"/>
-      <c r="H23" s="31"/>
-      <c r="I23" s="31"/>
-      <c r="J23" s="31"/>
-      <c r="K23" s="31"/>
-      <c r="M23" s="31"/>
-      <c r="N23" s="31"/>
-      <c r="O23" s="31"/>
-      <c r="P23" s="31"/>
-      <c r="Q23" s="31"/>
-      <c r="R23" s="31"/>
-      <c r="S23" s="31"/>
-      <c r="T23" s="31"/>
-      <c r="U23" s="31"/>
+      <c r="A23" s="25"/>
+      <c r="B23" s="25"/>
+      <c r="C23" s="25"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="25"/>
+      <c r="F23" s="25"/>
+      <c r="G23" s="25"/>
+      <c r="H23" s="25"/>
+      <c r="I23" s="25"/>
+      <c r="J23" s="25"/>
+      <c r="K23" s="25"/>
+      <c r="M23" s="25"/>
+      <c r="N23" s="25"/>
+      <c r="O23" s="25"/>
+      <c r="P23" s="25"/>
+      <c r="Q23" s="25"/>
+      <c r="R23" s="25"/>
+      <c r="S23" s="25"/>
+      <c r="T23" s="25"/>
+      <c r="U23" s="25"/>
     </row>
     <row r="24" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
@@ -4724,60 +4738,60 @@
       <c r="V24" s="1"/>
     </row>
     <row r="25" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="75" t="s">
+      <c r="A25" s="77" t="s">
         <v>5</v>
       </c>
-      <c r="B25" s="76"/>
-      <c r="C25" s="47">
+      <c r="B25" s="78"/>
+      <c r="C25" s="41">
         <v>92.567111769713335</v>
       </c>
-      <c r="D25" s="47">
+      <c r="D25" s="41">
         <v>90.835858608343599</v>
       </c>
-      <c r="E25" s="47">
+      <c r="E25" s="41">
         <v>89.217505339533233</v>
       </c>
-      <c r="F25" s="47">
+      <c r="F25" s="41">
         <v>83.237245964288078</v>
       </c>
-      <c r="G25" s="47">
+      <c r="G25" s="41">
         <v>75.380430844191011</v>
       </c>
-      <c r="H25" s="47">
+      <c r="H25" s="41">
         <v>58.994367187597383</v>
       </c>
-      <c r="I25" s="48">
+      <c r="I25" s="42">
         <v>43.622535641382179</v>
       </c>
-      <c r="J25" s="50"/>
-      <c r="K25" s="50"/>
+      <c r="J25" s="44"/>
+      <c r="K25" s="44"/>
       <c r="L25" s="1" t="str">
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C25:I25)&amp;","</f>
         <v xml:space="preserve">    92.5671117697133, 90.8358586083436, 89.2175053395332, 83.2372459642881, 75.380430844191, 58.9943671875974, 43.6225356413822,</v>
       </c>
-      <c r="M25" s="75" t="s">
+      <c r="M25" s="77" t="s">
         <v>5</v>
       </c>
-      <c r="N25" s="76"/>
-      <c r="O25" s="46">
+      <c r="N25" s="78"/>
+      <c r="O25" s="40">
         <v>3.88093621561358</v>
       </c>
-      <c r="P25" s="47">
+      <c r="P25" s="41">
         <v>4.8164746829677396</v>
       </c>
-      <c r="Q25" s="47">
+      <c r="Q25" s="41">
         <v>5.2250608386616522</v>
       </c>
-      <c r="R25" s="47">
+      <c r="R25" s="41">
         <v>5.6675721086724113</v>
       </c>
-      <c r="S25" s="47">
+      <c r="S25" s="41">
         <v>8.3263283482936075</v>
       </c>
-      <c r="T25" s="47">
+      <c r="T25" s="41">
         <v>10.49020927094638</v>
       </c>
-      <c r="U25" s="48">
+      <c r="U25" s="42">
         <v>11.060437347759546</v>
       </c>
       <c r="V25" s="1" t="str">
@@ -4786,60 +4800,60 @@
       </c>
     </row>
     <row r="26" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="75" t="s">
+      <c r="A26" s="77" t="s">
         <v>6</v>
       </c>
-      <c r="B26" s="76"/>
-      <c r="C26" s="47">
+      <c r="B26" s="78"/>
+      <c r="C26" s="41">
         <v>92.866950218042462</v>
       </c>
-      <c r="D26" s="47">
+      <c r="D26" s="41">
         <v>91.242690764745561</v>
       </c>
-      <c r="E26" s="47">
+      <c r="E26" s="41">
         <v>90.137053227698445</v>
       </c>
-      <c r="F26" s="47">
+      <c r="F26" s="41">
         <v>86.080152926613408</v>
       </c>
-      <c r="G26" s="47">
+      <c r="G26" s="41">
         <v>77.410217255196784</v>
       </c>
-      <c r="H26" s="47">
+      <c r="H26" s="41">
         <v>59.676194764980139</v>
       </c>
-      <c r="I26" s="48">
+      <c r="I26" s="42">
         <v>46.395490419404197</v>
       </c>
-      <c r="J26" s="50"/>
-      <c r="K26" s="50"/>
+      <c r="J26" s="44"/>
+      <c r="K26" s="44"/>
       <c r="L26" s="1" t="str">
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C26:I26)&amp;","</f>
         <v xml:space="preserve">    92.8669502180425, 91.2426907647456, 90.1370532276984, 86.0801529266134, 77.4102172551968, 59.6761947649801, 46.3954904194042,</v>
       </c>
-      <c r="M26" s="75" t="s">
+      <c r="M26" s="77" t="s">
         <v>6</v>
       </c>
-      <c r="N26" s="76"/>
-      <c r="O26" s="47">
+      <c r="N26" s="78"/>
+      <c r="O26" s="41">
         <v>3.8319643020864191</v>
       </c>
-      <c r="P26" s="47">
+      <c r="P26" s="41">
         <v>4.3603246705255447</v>
       </c>
-      <c r="Q26" s="47">
+      <c r="Q26" s="41">
         <v>4.7987735191879262</v>
       </c>
-      <c r="R26" s="47">
+      <c r="R26" s="41">
         <v>5.1262965367330251</v>
       </c>
-      <c r="S26" s="47">
+      <c r="S26" s="41">
         <v>7.087258799823358</v>
       </c>
-      <c r="T26" s="47">
+      <c r="T26" s="41">
         <v>9.7457736576346736</v>
       </c>
-      <c r="U26" s="48">
+      <c r="U26" s="42">
         <v>10.021578856839133</v>
       </c>
       <c r="V26" s="1" t="str">
@@ -4848,60 +4862,60 @@
       </c>
     </row>
     <row r="27" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="75" t="s">
+      <c r="A27" s="77" t="s">
         <v>10</v>
       </c>
-      <c r="B27" s="76"/>
-      <c r="C27" s="34">
+      <c r="B27" s="78"/>
+      <c r="C27" s="28">
         <v>87.268396410214976</v>
       </c>
-      <c r="D27" s="35">
+      <c r="D27" s="29">
         <v>87.256428398686779</v>
       </c>
-      <c r="E27" s="35">
+      <c r="E27" s="29">
         <v>87.822106304170404</v>
       </c>
-      <c r="F27" s="35">
+      <c r="F27" s="29">
         <v>87.68072644235157</v>
       </c>
-      <c r="G27" s="35">
+      <c r="G27" s="29">
         <v>87.144879367185226</v>
       </c>
-      <c r="H27" s="35">
+      <c r="H27" s="29">
         <v>74.976567886515753</v>
       </c>
-      <c r="I27" s="36">
+      <c r="I27" s="30">
         <v>46.41754739488244</v>
       </c>
-      <c r="J27" s="50"/>
-      <c r="K27" s="50"/>
+      <c r="J27" s="44"/>
+      <c r="K27" s="44"/>
       <c r="L27" s="1" t="str">
         <f t="shared" ref="L27:L35" si="5">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C27:I27)&amp;","</f>
         <v xml:space="preserve">    87.268396410215, 87.2564283986868, 87.8221063041704, 87.6807264423516, 87.1448793671852, 74.9765678865158, 46.4175473948824,</v>
       </c>
-      <c r="M27" s="75" t="s">
+      <c r="M27" s="77" t="s">
         <v>10</v>
       </c>
-      <c r="N27" s="76"/>
-      <c r="O27" s="34">
+      <c r="N27" s="78"/>
+      <c r="O27" s="28">
         <v>2.610595868561878</v>
       </c>
-      <c r="P27" s="35">
+      <c r="P27" s="29">
         <v>2.3209805270224559</v>
       </c>
-      <c r="Q27" s="35">
+      <c r="Q27" s="29">
         <v>2.4426244152699921</v>
       </c>
-      <c r="R27" s="35">
+      <c r="R27" s="29">
         <v>2.2821255442986761</v>
       </c>
-      <c r="S27" s="35">
+      <c r="S27" s="29">
         <v>2.523131741400912</v>
       </c>
-      <c r="T27" s="35">
+      <c r="T27" s="29">
         <v>3.7626100419371111</v>
       </c>
-      <c r="U27" s="36">
+      <c r="U27" s="30">
         <v>4.1161081119796732</v>
       </c>
       <c r="V27" s="1" t="str">
@@ -4910,7 +4924,7 @@
       </c>
     </row>
     <row r="28" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="75" t="s">
+      <c r="A28" s="77" t="s">
         <v>14</v>
       </c>
       <c r="B28" s="79"/>
@@ -4920,11 +4934,11 @@
       <c r="F28" s="79"/>
       <c r="G28" s="79"/>
       <c r="H28" s="79"/>
-      <c r="I28" s="76"/>
-      <c r="J28" s="50"/>
-      <c r="K28" s="50"/>
+      <c r="I28" s="78"/>
+      <c r="J28" s="44"/>
+      <c r="K28" s="44"/>
       <c r="L28" s="1"/>
-      <c r="M28" s="75" t="s">
+      <c r="M28" s="77" t="s">
         <v>14</v>
       </c>
       <c r="N28" s="79"/>
@@ -4934,7 +4948,7 @@
       <c r="R28" s="79"/>
       <c r="S28" s="79"/>
       <c r="T28" s="79"/>
-      <c r="U28" s="76"/>
+      <c r="U28" s="78"/>
       <c r="V28" s="1"/>
     </row>
     <row r="29" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
@@ -4944,32 +4958,32 @@
       <c r="B29" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C29" s="28">
-        <v>92.718331539365238</v>
-      </c>
-      <c r="D29" s="29">
-        <v>92.140084144598461</v>
-      </c>
-      <c r="E29" s="29">
-        <v>91.379904797106931</v>
-      </c>
-      <c r="F29" s="29">
-        <v>88.378075938007726</v>
-      </c>
-      <c r="G29" s="29">
-        <v>84.574966803458963</v>
-      </c>
-      <c r="H29" s="29">
-        <v>64.524084468318208</v>
-      </c>
-      <c r="I29" s="30">
-        <v>53.783251685995403</v>
-      </c>
-      <c r="J29" s="50"/>
-      <c r="K29" s="50"/>
+      <c r="C29" s="88">
+        <v>92.975694513442221</v>
+      </c>
+      <c r="D29" s="89">
+        <v>91.363613749154311</v>
+      </c>
+      <c r="E29" s="89">
+        <v>90.094017961161143</v>
+      </c>
+      <c r="F29" s="89">
+        <v>85.37773791839254</v>
+      </c>
+      <c r="G29" s="89">
+        <v>79.268159049010507</v>
+      </c>
+      <c r="H29" s="89">
+        <v>60.52121651399365</v>
+      </c>
+      <c r="I29" s="90">
+        <v>42.05444880665619</v>
+      </c>
+      <c r="J29" s="44"/>
+      <c r="K29" s="44"/>
       <c r="L29" s="1" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">    92.7183315393652, 92.1400841445985, 91.3799047971069, 88.3780759380077, 84.574966803459, 64.5240844683182, 53.7832516859954,</v>
+        <v xml:space="preserve">    92.9756945134422, 91.3636137491543, 90.0940179611611, 85.3777379183925, 79.2681590490105, 60.5212165139937, 42.0544488066562,</v>
       </c>
       <c r="M29" s="14" t="s">
         <v>12</v>
@@ -4977,30 +4991,30 @@
       <c r="N29" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="O29" s="28">
-        <v>3.7093306081953399</v>
-      </c>
-      <c r="P29" s="29">
-        <v>3.557353374868756</v>
-      </c>
-      <c r="Q29" s="29">
-        <v>3.8505126265401719</v>
-      </c>
-      <c r="R29" s="29">
-        <v>4.6860631563763482</v>
-      </c>
-      <c r="S29" s="29">
-        <v>5.2335990268297223</v>
-      </c>
-      <c r="T29" s="29">
-        <v>8.5303914956588702</v>
-      </c>
-      <c r="U29" s="30">
-        <v>9.1099237449071975</v>
+      <c r="O29" s="88">
+        <v>3.782557259829499</v>
+      </c>
+      <c r="P29" s="89">
+        <v>4.4459073754732694</v>
+      </c>
+      <c r="Q29" s="89">
+        <v>4.6323081197737448</v>
+      </c>
+      <c r="R29" s="89">
+        <v>5.3746795640933653</v>
+      </c>
+      <c r="S29" s="89">
+        <v>5.9912912250355319</v>
+      </c>
+      <c r="T29" s="89">
+        <v>9.0901817740237139</v>
+      </c>
+      <c r="U29" s="90">
+        <v>9.5108664952359483</v>
       </c>
       <c r="V29" s="1" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">    3.70933060819534, 3.55735337486876, 3.85051262654017, 4.68606315637635, 5.23359902682972, 8.53039149565887, 9.1099237449072,</v>
+        <v xml:space="preserve">    3.7825572598295, 4.44590737547327, 4.63230811977374, 5.37467956409337, 5.99129122503553, 9.09018177402371, 9.51086649523595,</v>
       </c>
     </row>
     <row r="30" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
@@ -5010,32 +5024,32 @@
       <c r="B30" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C30" s="49">
-        <v>92.111918497964766</v>
-      </c>
-      <c r="D30" s="50">
-        <v>92.236437130021557</v>
-      </c>
-      <c r="E30" s="50">
-        <v>91.847628837606763</v>
-      </c>
-      <c r="F30" s="50">
-        <v>91.031961472589515</v>
-      </c>
-      <c r="G30" s="50">
-        <v>87.968996103656281</v>
-      </c>
-      <c r="H30" s="50">
-        <v>70.680435455032196</v>
-      </c>
-      <c r="I30" s="51">
-        <v>51.144510191286152</v>
-      </c>
-      <c r="J30" s="50"/>
-      <c r="K30" s="50"/>
+      <c r="C30" s="66">
+        <v>92.311293413260969</v>
+      </c>
+      <c r="D30" s="67">
+        <v>92.333521756806476</v>
+      </c>
+      <c r="E30" s="67">
+        <v>91.381357522919643</v>
+      </c>
+      <c r="F30" s="67">
+        <v>88.560101371956989</v>
+      </c>
+      <c r="G30" s="67">
+        <v>87.278991705998607</v>
+      </c>
+      <c r="H30" s="67">
+        <v>75.38789705567028</v>
+      </c>
+      <c r="I30" s="68">
+        <v>47.478737907175287</v>
+      </c>
+      <c r="J30" s="44"/>
+      <c r="K30" s="44"/>
       <c r="L30" s="1" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">    92.1119184979648, 92.2364371300216, 91.8476288376068, 91.0319614725895, 87.9689961036563, 70.6804354550322, 51.1445101912862,</v>
+        <v xml:space="preserve">    92.311293413261, 92.3335217568065, 91.3813575229196, 88.560101371957, 87.2789917059986, 75.3878970556703, 47.4787379071753,</v>
       </c>
       <c r="M30" s="14" t="s">
         <v>13</v>
@@ -5043,30 +5057,30 @@
       <c r="N30" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="O30" s="49">
-        <v>3.5860589390986259</v>
-      </c>
-      <c r="P30" s="50">
-        <v>3.5458492835339008</v>
-      </c>
-      <c r="Q30" s="50">
-        <v>3.3222516092178069</v>
-      </c>
-      <c r="R30" s="50">
-        <v>3.385168684859547</v>
-      </c>
-      <c r="S30" s="50">
-        <v>3.8142946105661402</v>
-      </c>
-      <c r="T30" s="50">
-        <v>5.9054798361883787</v>
-      </c>
-      <c r="U30" s="51">
-        <v>6.303799515839513</v>
+      <c r="O30" s="66">
+        <v>3.45837660705662</v>
+      </c>
+      <c r="P30" s="67">
+        <v>3.6213315124355141</v>
+      </c>
+      <c r="Q30" s="67">
+        <v>3.418827656161032</v>
+      </c>
+      <c r="R30" s="67">
+        <v>3.2543979140806938</v>
+      </c>
+      <c r="S30" s="67">
+        <v>3.202126822778443</v>
+      </c>
+      <c r="T30" s="67">
+        <v>5.2358921781492196</v>
+      </c>
+      <c r="U30" s="68">
+        <v>6.1375770825509051</v>
       </c>
       <c r="V30" s="1" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">    3.58605893909863, 3.5458492835339, 3.32225160921781, 3.38516868485955, 3.81429461056614, 5.90547983618838, 6.30379951583951,</v>
+        <v xml:space="preserve">    3.45837660705662, 3.62133151243551, 3.41882765616103, 3.25439791408069, 3.20212682277844, 5.23589217814922, 6.13757708255091,</v>
       </c>
     </row>
     <row r="31" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
@@ -5076,29 +5090,15 @@
       <c r="B31" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C31" s="47">
-        <v>92.825943579912774</v>
-      </c>
-      <c r="D31" s="47">
-        <v>92.155443041619591</v>
-      </c>
-      <c r="E31" s="47">
-        <v>90.757710215515047</v>
-      </c>
-      <c r="F31" s="47">
-        <v>86.103066347316471</v>
-      </c>
-      <c r="G31" s="47">
-        <v>78.832060707290182</v>
-      </c>
-      <c r="H31" s="47">
-        <v>57.474188345490397</v>
-      </c>
-      <c r="I31" s="48">
-        <v>41.050623769761458</v>
-      </c>
-      <c r="J31" s="50"/>
-      <c r="K31" s="50"/>
+      <c r="C31" s="41"/>
+      <c r="D31" s="41"/>
+      <c r="E31" s="41"/>
+      <c r="F31" s="41"/>
+      <c r="G31" s="41"/>
+      <c r="H31" s="41"/>
+      <c r="I31" s="42"/>
+      <c r="J31" s="44"/>
+      <c r="K31" s="44"/>
       <c r="L31" s="1"/>
       <c r="M31" s="14" t="s">
         <v>12</v>
@@ -5106,27 +5106,13 @@
       <c r="N31" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="O31" s="47">
-        <v>3.8019394848570141</v>
-      </c>
-      <c r="P31" s="47">
-        <v>3.575586565560668</v>
-      </c>
-      <c r="Q31" s="47">
-        <v>3.823963538753008</v>
-      </c>
-      <c r="R31" s="47">
-        <v>5.1791780366569888</v>
-      </c>
-      <c r="S31" s="47">
-        <v>7.1631576731781328</v>
-      </c>
-      <c r="T31" s="47">
-        <v>10.59398505131753</v>
-      </c>
-      <c r="U31" s="48">
-        <v>10.09437645234315</v>
-      </c>
+      <c r="O31" s="41"/>
+      <c r="P31" s="41"/>
+      <c r="Q31" s="41"/>
+      <c r="R31" s="41"/>
+      <c r="S31" s="41"/>
+      <c r="T31" s="41"/>
+      <c r="U31" s="42"/>
       <c r="V31" s="1"/>
     </row>
     <row r="32" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
@@ -5136,29 +5122,29 @@
       <c r="B32" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C32" s="34">
-        <v>93.041122751220755</v>
-      </c>
-      <c r="D32" s="35">
-        <v>91.860409028861255</v>
-      </c>
-      <c r="E32" s="35">
-        <v>90.078455478721949</v>
-      </c>
-      <c r="F32" s="35">
-        <v>86.392751389335601</v>
-      </c>
-      <c r="G32" s="35">
-        <v>75.019539414722558</v>
-      </c>
-      <c r="H32" s="35">
-        <v>56.592631108340719</v>
-      </c>
-      <c r="I32" s="36">
-        <v>43.843975581234297</v>
-      </c>
-      <c r="J32" s="50"/>
-      <c r="K32" s="50"/>
+      <c r="C32" s="66">
+        <v>93.003107171421291</v>
+      </c>
+      <c r="D32" s="67">
+        <v>92.882665900806714</v>
+      </c>
+      <c r="E32" s="67">
+        <v>92.323250249861715</v>
+      </c>
+      <c r="F32" s="67">
+        <v>87.896361279111929</v>
+      </c>
+      <c r="G32" s="67">
+        <v>80.149965599113543</v>
+      </c>
+      <c r="H32" s="67">
+        <v>57.360910597574737</v>
+      </c>
+      <c r="I32" s="68">
+        <v>43.986149507359343</v>
+      </c>
+      <c r="J32" s="44"/>
+      <c r="K32" s="44"/>
       <c r="L32" s="1"/>
       <c r="M32" s="14" t="s">
         <v>12</v>
@@ -5166,26 +5152,26 @@
       <c r="N32" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="O32" s="34">
-        <v>3.8448027846295161</v>
-      </c>
-      <c r="P32" s="35">
-        <v>4.3320041409026686</v>
-      </c>
-      <c r="Q32" s="35">
-        <v>4.4538172465866941</v>
-      </c>
-      <c r="R32" s="35">
-        <v>4.3073898502712948</v>
-      </c>
-      <c r="S32" s="35">
-        <v>9.9239732988158718</v>
-      </c>
-      <c r="T32" s="35">
-        <v>11.463911844631459</v>
-      </c>
-      <c r="U32" s="36">
-        <v>10.663674571971409</v>
+      <c r="O32" s="66">
+        <v>3.8815673789284708</v>
+      </c>
+      <c r="P32" s="67">
+        <v>4.3723258101522813</v>
+      </c>
+      <c r="Q32" s="67">
+        <v>4.2934275551121281</v>
+      </c>
+      <c r="R32" s="67">
+        <v>5.2017150988587044</v>
+      </c>
+      <c r="S32" s="67">
+        <v>7.2625504458350916</v>
+      </c>
+      <c r="T32" s="67">
+        <v>11.40658683680142</v>
+      </c>
+      <c r="U32" s="68">
+        <v>9.5393474867950871</v>
       </c>
       <c r="V32" s="1"/>
     </row>
@@ -5196,32 +5182,18 @@
       <c r="B33" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C33" s="34">
-        <v>92.68357207739561</v>
-      </c>
-      <c r="D33" s="35">
-        <v>91.723989054076753</v>
-      </c>
-      <c r="E33" s="35">
-        <v>90.643879177716514</v>
-      </c>
-      <c r="F33" s="35">
-        <v>87.700045335658899</v>
-      </c>
-      <c r="G33" s="35">
-        <v>81.238224301247357</v>
-      </c>
-      <c r="H33" s="35">
-        <v>60.242672309064993</v>
-      </c>
-      <c r="I33" s="36">
-        <v>47.896022751757073</v>
-      </c>
-      <c r="J33" s="50"/>
-      <c r="K33" s="50"/>
+      <c r="C33" s="28"/>
+      <c r="D33" s="29"/>
+      <c r="E33" s="29"/>
+      <c r="F33" s="29"/>
+      <c r="G33" s="29"/>
+      <c r="H33" s="29"/>
+      <c r="I33" s="30"/>
+      <c r="J33" s="44"/>
+      <c r="K33" s="44"/>
       <c r="L33" s="1" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">    92.6835720773956, 91.7239890540768, 90.6438791777165, 87.7000453356589, 81.2382243012474, 60.242672309065, 47.8960227517571,</v>
+        <v xml:space="preserve">    ,</v>
       </c>
       <c r="M33" s="14" t="s">
         <v>12</v>
@@ -5229,27 +5201,13 @@
       <c r="N33" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="O33" s="34">
-        <v>4.2575085387426066</v>
-      </c>
-      <c r="P33" s="35">
-        <v>4.1044928297974694</v>
-      </c>
-      <c r="Q33" s="35">
-        <v>4.224361853279194</v>
-      </c>
-      <c r="R33" s="35">
-        <v>4.246956163355768</v>
-      </c>
-      <c r="S33" s="35">
-        <v>5.4782720237935472</v>
-      </c>
-      <c r="T33" s="35">
-        <v>9.9625588159654015</v>
-      </c>
-      <c r="U33" s="36">
-        <v>8.9073404575096671</v>
-      </c>
+      <c r="O33" s="28"/>
+      <c r="P33" s="29"/>
+      <c r="Q33" s="29"/>
+      <c r="R33" s="29"/>
+      <c r="S33" s="29"/>
+      <c r="T33" s="29"/>
+      <c r="U33" s="30"/>
       <c r="V33" s="1"/>
     </row>
     <row r="34" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
@@ -5259,15 +5217,29 @@
       <c r="B34" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C34" s="52"/>
-      <c r="D34" s="53"/>
-      <c r="E34" s="53"/>
-      <c r="F34" s="53"/>
-      <c r="G34" s="53"/>
-      <c r="H34" s="53"/>
-      <c r="I34" s="54"/>
-      <c r="J34" s="50"/>
-      <c r="K34" s="50"/>
+      <c r="C34" s="66">
+        <v>89.74449346032101</v>
+      </c>
+      <c r="D34" s="67">
+        <v>89.961854893326574</v>
+      </c>
+      <c r="E34" s="67">
+        <v>90.011537582574022</v>
+      </c>
+      <c r="F34" s="67">
+        <v>90.064770133428496</v>
+      </c>
+      <c r="G34" s="67">
+        <v>88.967446677518851</v>
+      </c>
+      <c r="H34" s="67">
+        <v>80.083589667611676</v>
+      </c>
+      <c r="I34" s="68">
+        <v>52.982008110476087</v>
+      </c>
+      <c r="J34" s="44"/>
+      <c r="K34" s="44"/>
       <c r="L34" s="1"/>
       <c r="M34" s="14" t="s">
         <v>11</v>
@@ -5275,13 +5247,27 @@
       <c r="N34" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="O34" s="52"/>
-      <c r="P34" s="53"/>
-      <c r="Q34" s="53"/>
-      <c r="R34" s="53"/>
-      <c r="S34" s="53"/>
-      <c r="T34" s="53"/>
-      <c r="U34" s="54"/>
+      <c r="O34" s="66">
+        <v>2.9793986812049931</v>
+      </c>
+      <c r="P34" s="67">
+        <v>2.5386471681353431</v>
+      </c>
+      <c r="Q34" s="67">
+        <v>2.4449126963196481</v>
+      </c>
+      <c r="R34" s="67">
+        <v>2.6222789037595908</v>
+      </c>
+      <c r="S34" s="67">
+        <v>2.7817641077346069</v>
+      </c>
+      <c r="T34" s="67">
+        <v>4.0935792052005926</v>
+      </c>
+      <c r="U34" s="68">
+        <v>6.5884863469929558</v>
+      </c>
       <c r="V34" s="1"/>
     </row>
     <row r="35" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
@@ -5291,117 +5277,117 @@
       <c r="B35" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C35" s="52"/>
-      <c r="D35" s="53"/>
-      <c r="E35" s="53"/>
-      <c r="F35" s="53"/>
-      <c r="G35" s="53"/>
-      <c r="H35" s="53"/>
-      <c r="I35" s="54"/>
-      <c r="J35" s="50"/>
-      <c r="K35" s="50"/>
+      <c r="C35" s="46"/>
+      <c r="D35" s="47"/>
+      <c r="E35" s="47"/>
+      <c r="F35" s="47"/>
+      <c r="G35" s="47"/>
+      <c r="H35" s="47"/>
+      <c r="I35" s="48"/>
+      <c r="J35" s="44"/>
+      <c r="K35" s="44"/>
       <c r="L35" s="1" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M35" s="56" t="s">
+      <c r="M35" s="50" t="s">
         <v>11</v>
       </c>
       <c r="N35" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="O35" s="52"/>
-      <c r="P35" s="53"/>
-      <c r="Q35" s="53"/>
-      <c r="R35" s="53"/>
-      <c r="S35" s="53"/>
-      <c r="T35" s="53"/>
-      <c r="U35" s="54"/>
+      <c r="O35" s="46"/>
+      <c r="P35" s="47"/>
+      <c r="Q35" s="47"/>
+      <c r="R35" s="47"/>
+      <c r="S35" s="47"/>
+      <c r="T35" s="47"/>
+      <c r="U35" s="48"/>
       <c r="V35" s="1"/>
     </row>
     <row r="36" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="75" t="s">
+      <c r="A36" s="77" t="s">
         <v>22</v>
       </c>
       <c r="B36" s="79"/>
-      <c r="C36" s="82"/>
-      <c r="D36" s="82"/>
-      <c r="E36" s="82"/>
-      <c r="F36" s="82"/>
-      <c r="G36" s="82"/>
-      <c r="H36" s="82"/>
-      <c r="I36" s="78"/>
-      <c r="J36" s="50"/>
-      <c r="K36" s="50"/>
+      <c r="C36" s="80"/>
+      <c r="D36" s="80"/>
+      <c r="E36" s="80"/>
+      <c r="F36" s="80"/>
+      <c r="G36" s="80"/>
+      <c r="H36" s="80"/>
+      <c r="I36" s="81"/>
+      <c r="J36" s="44"/>
+      <c r="K36" s="44"/>
       <c r="L36" s="1"/>
-      <c r="M36" s="75" t="s">
+      <c r="M36" s="77" t="s">
         <v>22</v>
       </c>
       <c r="N36" s="79"/>
-      <c r="O36" s="82"/>
-      <c r="P36" s="82"/>
-      <c r="Q36" s="82"/>
-      <c r="R36" s="82"/>
-      <c r="S36" s="82"/>
-      <c r="T36" s="82"/>
-      <c r="U36" s="78"/>
+      <c r="O36" s="80"/>
+      <c r="P36" s="80"/>
+      <c r="Q36" s="80"/>
+      <c r="R36" s="80"/>
+      <c r="S36" s="80"/>
+      <c r="T36" s="80"/>
+      <c r="U36" s="81"/>
       <c r="V36" s="1"/>
     </row>
     <row r="37" spans="1:22" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="75" t="s">
+      <c r="A37" s="77" t="s">
         <v>7</v>
       </c>
-      <c r="B37" s="76"/>
-      <c r="C37" s="67">
+      <c r="B37" s="78"/>
+      <c r="C37" s="61">
         <v>93.403798109785029</v>
       </c>
-      <c r="D37" s="68">
+      <c r="D37" s="62">
         <v>91.51700700493744</v>
       </c>
-      <c r="E37" s="68">
+      <c r="E37" s="62">
         <v>89.749880462689262</v>
       </c>
-      <c r="F37" s="68">
+      <c r="F37" s="62">
         <v>83.99730958119234</v>
       </c>
-      <c r="G37" s="68">
+      <c r="G37" s="62">
         <v>74.394962965986878</v>
       </c>
-      <c r="H37" s="68">
+      <c r="H37" s="62">
         <v>58.095582470498513</v>
       </c>
-      <c r="I37" s="69">
+      <c r="I37" s="63">
         <v>44.434812706207254</v>
       </c>
-      <c r="J37" s="50"/>
-      <c r="K37" s="50"/>
+      <c r="J37" s="44"/>
+      <c r="K37" s="44"/>
       <c r="L37" s="1" t="str">
         <f t="shared" ref="L37:L39" si="6">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C37:I37)&amp;","</f>
         <v xml:space="preserve">    93.403798109785, 91.5170070049374, 89.7498804626893, 83.9973095811923, 74.3949629659869, 58.0955824704985, 44.4348127062073,</v>
       </c>
-      <c r="M37" s="75" t="s">
+      <c r="M37" s="77" t="s">
         <v>7</v>
       </c>
-      <c r="N37" s="76"/>
-      <c r="O37" s="67">
+      <c r="N37" s="78"/>
+      <c r="O37" s="61">
         <v>3.9553866501853321</v>
       </c>
-      <c r="P37" s="68">
+      <c r="P37" s="62">
         <v>4.517630835861226</v>
       </c>
-      <c r="Q37" s="68">
+      <c r="Q37" s="62">
         <v>5.2125425794506972</v>
       </c>
-      <c r="R37" s="68">
+      <c r="R37" s="62">
         <v>5.6477461387684551</v>
       </c>
-      <c r="S37" s="68">
+      <c r="S37" s="62">
         <v>8.6090564713117175</v>
       </c>
-      <c r="T37" s="68">
+      <c r="T37" s="62">
         <v>11.357157347254571</v>
       </c>
-      <c r="U37" s="69">
+      <c r="U37" s="63">
         <v>9.3757621724255777</v>
       </c>
       <c r="V37" s="1" t="str">
@@ -5410,11 +5396,11 @@
       </c>
     </row>
     <row r="38" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="75" t="s">
+      <c r="A38" s="77" t="s">
         <v>8</v>
       </c>
-      <c r="B38" s="76"/>
-      <c r="C38" s="70">
+      <c r="B38" s="78"/>
+      <c r="C38" s="64">
         <v>92.778947400409621</v>
       </c>
       <c r="D38" s="1">
@@ -5432,20 +5418,20 @@
       <c r="H38" s="1">
         <v>58.300265665116903</v>
       </c>
-      <c r="I38" s="71">
+      <c r="I38" s="65">
         <v>48.584106437626268</v>
       </c>
-      <c r="J38" s="50"/>
-      <c r="K38" s="50"/>
+      <c r="J38" s="44"/>
+      <c r="K38" s="44"/>
       <c r="L38" s="1" t="str">
         <f t="shared" si="6"/>
         <v xml:space="preserve">    92.7789474004096, 91.4503689963737, 89.8794809545421, 84.748756470337, 75.6276087825805, 58.3002656651169, 48.5841064376263,</v>
       </c>
-      <c r="M38" s="75" t="s">
+      <c r="M38" s="77" t="s">
         <v>8</v>
       </c>
-      <c r="N38" s="76"/>
-      <c r="O38" s="70">
+      <c r="N38" s="78"/>
+      <c r="O38" s="64">
         <v>4.3743918396131134</v>
       </c>
       <c r="P38" s="1">
@@ -5463,7 +5449,7 @@
       <c r="T38" s="1">
         <v>11.000258135261941</v>
       </c>
-      <c r="U38" s="71">
+      <c r="U38" s="65">
         <v>9.2918474149187738</v>
       </c>
       <c r="V38" s="1" t="str">
@@ -5472,11 +5458,11 @@
       </c>
     </row>
     <row r="39" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="75" t="s">
+      <c r="A39" s="77" t="s">
         <v>23</v>
       </c>
-      <c r="B39" s="76"/>
-      <c r="C39" s="70">
+      <c r="B39" s="78"/>
+      <c r="C39" s="64">
         <v>92.492055194421354</v>
       </c>
       <c r="D39" s="1">
@@ -5494,20 +5480,20 @@
       <c r="H39" s="1">
         <v>56.229205901331248</v>
       </c>
-      <c r="I39" s="71">
+      <c r="I39" s="65">
         <v>43.695396708102962</v>
       </c>
-      <c r="J39" s="50"/>
-      <c r="K39" s="50"/>
+      <c r="J39" s="44"/>
+      <c r="K39" s="44"/>
       <c r="L39" s="1" t="str">
         <f t="shared" si="6"/>
         <v xml:space="preserve">    92.4920551944214, 91.055738083246, 89.2412648877623, 82.7136018096434, 73.1336770487749, 56.2292059013312, 43.695396708103,</v>
       </c>
-      <c r="M39" s="75" t="s">
+      <c r="M39" s="77" t="s">
         <v>23</v>
       </c>
-      <c r="N39" s="76"/>
-      <c r="O39" s="70">
+      <c r="N39" s="78"/>
+      <c r="O39" s="64">
         <v>4.0986250609792014</v>
       </c>
       <c r="P39" s="1">
@@ -5525,7 +5511,7 @@
       <c r="T39" s="1">
         <v>11.32839542788332</v>
       </c>
-      <c r="U39" s="71">
+      <c r="U39" s="65">
         <v>10.62887090695313</v>
       </c>
       <c r="V39" s="1" t="str">
@@ -5534,144 +5520,144 @@
       </c>
     </row>
     <row r="40" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="75" t="s">
+      <c r="A40" s="77" t="s">
         <v>24</v>
       </c>
-      <c r="B40" s="76"/>
-      <c r="C40" s="72">
+      <c r="B40" s="78"/>
+      <c r="C40" s="66">
         <v>92.657174075741665</v>
       </c>
-      <c r="D40" s="73">
+      <c r="D40" s="67">
         <v>91.208050814372243</v>
       </c>
-      <c r="E40" s="73">
+      <c r="E40" s="67">
         <v>89.170455678091372</v>
       </c>
-      <c r="F40" s="73">
+      <c r="F40" s="67">
         <v>84.474616062770011</v>
       </c>
-      <c r="G40" s="73">
+      <c r="G40" s="67">
         <v>75.066668593640316</v>
       </c>
-      <c r="H40" s="73">
+      <c r="H40" s="67">
         <v>58.520340993368222</v>
       </c>
-      <c r="I40" s="74">
+      <c r="I40" s="68">
         <v>44.786141592049418</v>
       </c>
-      <c r="J40" s="58"/>
-      <c r="K40" s="58"/>
-      <c r="L40" s="57"/>
-      <c r="M40" s="75" t="s">
+      <c r="J40" s="52"/>
+      <c r="K40" s="52"/>
+      <c r="L40" s="51"/>
+      <c r="M40" s="77" t="s">
         <v>24</v>
       </c>
-      <c r="N40" s="76"/>
-      <c r="O40" s="72">
+      <c r="N40" s="78"/>
+      <c r="O40" s="66">
         <v>4.2589004392769629</v>
       </c>
-      <c r="P40" s="73">
+      <c r="P40" s="67">
         <v>4.8517186601265534</v>
       </c>
-      <c r="Q40" s="73">
+      <c r="Q40" s="67">
         <v>5.6717673083496472</v>
       </c>
-      <c r="R40" s="73">
+      <c r="R40" s="67">
         <v>5.3079507961921779</v>
       </c>
-      <c r="S40" s="73">
+      <c r="S40" s="67">
         <v>7.7884705615072454</v>
       </c>
-      <c r="T40" s="73">
+      <c r="T40" s="67">
         <v>10.595563377926201</v>
       </c>
-      <c r="U40" s="74">
+      <c r="U40" s="68">
         <v>10.945843294214329</v>
       </c>
       <c r="V40" s="1"/>
     </row>
     <row r="41" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="75" t="s">
+      <c r="A41" s="77" t="s">
         <v>25</v>
       </c>
       <c r="B41" s="79"/>
-      <c r="C41" s="80"/>
-      <c r="D41" s="80"/>
-      <c r="E41" s="80"/>
-      <c r="F41" s="80"/>
-      <c r="G41" s="80"/>
-      <c r="H41" s="80"/>
-      <c r="I41" s="81"/>
-      <c r="J41" s="50"/>
-      <c r="K41" s="50"/>
+      <c r="C41" s="82"/>
+      <c r="D41" s="82"/>
+      <c r="E41" s="82"/>
+      <c r="F41" s="82"/>
+      <c r="G41" s="82"/>
+      <c r="H41" s="82"/>
+      <c r="I41" s="83"/>
+      <c r="J41" s="44"/>
+      <c r="K41" s="44"/>
       <c r="L41" s="1"/>
-      <c r="M41" s="75" t="s">
+      <c r="M41" s="77" t="s">
         <v>25</v>
       </c>
       <c r="N41" s="79"/>
-      <c r="O41" s="80"/>
-      <c r="P41" s="80"/>
-      <c r="Q41" s="80"/>
-      <c r="R41" s="80"/>
-      <c r="S41" s="80"/>
-      <c r="T41" s="80"/>
-      <c r="U41" s="81"/>
+      <c r="O41" s="82"/>
+      <c r="P41" s="82"/>
+      <c r="Q41" s="82"/>
+      <c r="R41" s="82"/>
+      <c r="S41" s="82"/>
+      <c r="T41" s="82"/>
+      <c r="U41" s="83"/>
       <c r="V41" s="1"/>
     </row>
     <row r="42" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="75" t="s">
+      <c r="A42" s="77" t="s">
         <v>7</v>
       </c>
-      <c r="B42" s="76"/>
-      <c r="C42" s="67">
+      <c r="B42" s="78"/>
+      <c r="C42" s="61">
         <v>92.603769819293618</v>
       </c>
-      <c r="D42" s="68">
+      <c r="D42" s="62">
         <v>91.431947068352812</v>
       </c>
-      <c r="E42" s="68">
+      <c r="E42" s="62">
         <v>90.390795042999585</v>
       </c>
-      <c r="F42" s="68">
+      <c r="F42" s="62">
         <v>86.789562828222273</v>
       </c>
-      <c r="G42" s="68">
+      <c r="G42" s="62">
         <v>80.615554033052248</v>
       </c>
-      <c r="H42" s="68">
+      <c r="H42" s="62">
         <v>56.609578553133908</v>
       </c>
-      <c r="I42" s="69">
+      <c r="I42" s="63">
         <v>41.27928062292434</v>
       </c>
-      <c r="J42" s="50"/>
-      <c r="K42" s="50"/>
+      <c r="J42" s="44"/>
+      <c r="K42" s="44"/>
       <c r="L42" s="1" t="str">
         <f t="shared" ref="L42:L44" si="7">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C42:I42)&amp;","</f>
         <v xml:space="preserve">    92.6037698192936, 91.4319470683528, 90.3907950429996, 86.7895628282223, 80.6155540330522, 56.6095785531339, 41.2792806229243,</v>
       </c>
-      <c r="M42" s="75" t="s">
+      <c r="M42" s="77" t="s">
         <v>7</v>
       </c>
-      <c r="N42" s="76"/>
-      <c r="O42" s="67">
+      <c r="N42" s="78"/>
+      <c r="O42" s="61">
         <v>3.708759274801273</v>
       </c>
-      <c r="P42" s="68">
+      <c r="P42" s="62">
         <v>3.9640390541215931</v>
       </c>
-      <c r="Q42" s="68">
+      <c r="Q42" s="62">
         <v>3.7067998106756881</v>
       </c>
-      <c r="R42" s="68">
+      <c r="R42" s="62">
         <v>3.667452632531309</v>
       </c>
-      <c r="S42" s="68">
+      <c r="S42" s="62">
         <v>5.7548227051500218</v>
       </c>
-      <c r="T42" s="68">
+      <c r="T42" s="62">
         <v>8.5366536877555248</v>
       </c>
-      <c r="U42" s="69">
+      <c r="U42" s="63">
         <v>6.3187793027043018</v>
       </c>
       <c r="V42" s="1" t="str">
@@ -5680,11 +5666,11 @@
       </c>
     </row>
     <row r="43" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="77" t="s">
+      <c r="A43" s="84" t="s">
         <v>8</v>
       </c>
-      <c r="B43" s="78"/>
-      <c r="C43" s="70">
+      <c r="B43" s="81"/>
+      <c r="C43" s="64">
         <v>91.377634404932721</v>
       </c>
       <c r="D43" s="1">
@@ -5702,20 +5688,20 @@
       <c r="H43" s="1">
         <v>70.930708745421484</v>
       </c>
-      <c r="I43" s="71">
+      <c r="I43" s="65">
         <v>44.097326232806537</v>
       </c>
-      <c r="J43" s="50"/>
-      <c r="K43" s="50"/>
+      <c r="J43" s="44"/>
+      <c r="K43" s="44"/>
       <c r="L43" s="1" t="str">
         <f t="shared" si="7"/>
         <v xml:space="preserve">    91.3776344049327, 90.4053733332451, 89.3714803083327, 87.6098986263952, 85.5372307015107, 70.9307087454215, 44.0973262328065,</v>
       </c>
-      <c r="M43" s="75" t="s">
+      <c r="M43" s="77" t="s">
         <v>8</v>
       </c>
-      <c r="N43" s="76"/>
-      <c r="O43" s="70">
+      <c r="N43" s="78"/>
+      <c r="O43" s="64">
         <v>3.5684194304484111</v>
       </c>
       <c r="P43" s="1">
@@ -5733,7 +5719,7 @@
       <c r="T43" s="1">
         <v>4.9795199020249923</v>
       </c>
-      <c r="U43" s="71">
+      <c r="U43" s="65">
         <v>2.9223071611371929</v>
       </c>
       <c r="V43" s="1" t="str">
@@ -5742,11 +5728,11 @@
       </c>
     </row>
     <row r="44" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="75" t="s">
+      <c r="A44" s="77" t="s">
         <v>23</v>
       </c>
-      <c r="B44" s="76"/>
-      <c r="C44" s="70">
+      <c r="B44" s="78"/>
+      <c r="C44" s="64">
         <v>92.603715202692385</v>
       </c>
       <c r="D44" s="1">
@@ -5764,20 +5750,20 @@
       <c r="H44" s="1">
         <v>58.188767254712552</v>
       </c>
-      <c r="I44" s="71">
+      <c r="I44" s="65">
         <v>45.468919562576168</v>
       </c>
-      <c r="J44" s="50"/>
-      <c r="K44" s="50"/>
+      <c r="J44" s="44"/>
+      <c r="K44" s="44"/>
       <c r="L44" s="1" t="str">
         <f t="shared" si="7"/>
         <v xml:space="preserve">    92.6037152026924, 91.4849975027203, 90.6301712993249, 85.3420346970645, 78.2086079443082, 58.1887672547126, 45.4689195625762,</v>
       </c>
-      <c r="M44" s="75" t="s">
+      <c r="M44" s="77" t="s">
         <v>23</v>
       </c>
-      <c r="N44" s="76"/>
-      <c r="O44" s="70">
+      <c r="N44" s="78"/>
+      <c r="O44" s="64">
         <v>4.0727132923350373</v>
       </c>
       <c r="P44" s="1">
@@ -5795,7 +5781,7 @@
       <c r="T44" s="1">
         <v>10.3740336621021</v>
       </c>
-      <c r="U44" s="71">
+      <c r="U44" s="65">
         <v>10.707618741543239</v>
       </c>
       <c r="V44" s="1" t="str">
@@ -5804,57 +5790,57 @@
       </c>
     </row>
     <row r="45" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="75" t="s">
+      <c r="A45" s="77" t="s">
         <v>24</v>
       </c>
-      <c r="B45" s="76"/>
-      <c r="C45" s="72">
+      <c r="B45" s="78"/>
+      <c r="C45" s="66">
         <v>92.692685851985146</v>
       </c>
-      <c r="D45" s="73">
+      <c r="D45" s="67">
         <v>91.028008929063319</v>
       </c>
-      <c r="E45" s="73">
+      <c r="E45" s="67">
         <v>89.101176850288709</v>
       </c>
-      <c r="F45" s="73">
+      <c r="F45" s="67">
         <v>84.121695311135312</v>
       </c>
-      <c r="G45" s="73">
+      <c r="G45" s="67">
         <v>75.514536359946376</v>
       </c>
-      <c r="H45" s="73">
+      <c r="H45" s="67">
         <v>58.551851548300363</v>
       </c>
-      <c r="I45" s="74">
+      <c r="I45" s="68">
         <v>43.528644478603361</v>
       </c>
-      <c r="J45" s="50"/>
-      <c r="K45" s="50"/>
+      <c r="J45" s="44"/>
+      <c r="K45" s="44"/>
       <c r="L45" s="1"/>
-      <c r="M45" s="75" t="s">
+      <c r="M45" s="77" t="s">
         <v>24</v>
       </c>
-      <c r="N45" s="76"/>
-      <c r="O45" s="72">
+      <c r="N45" s="78"/>
+      <c r="O45" s="66">
         <v>4.3508377678439567</v>
       </c>
-      <c r="P45" s="73">
+      <c r="P45" s="67">
         <v>5.1455197984597092</v>
       </c>
-      <c r="Q45" s="73">
+      <c r="Q45" s="67">
         <v>5.0319449257944937</v>
       </c>
-      <c r="R45" s="73">
+      <c r="R45" s="67">
         <v>5.4881092234662896</v>
       </c>
-      <c r="S45" s="73">
+      <c r="S45" s="67">
         <v>8.3963724907401343</v>
       </c>
-      <c r="T45" s="73">
+      <c r="T45" s="67">
         <v>11.26477476806841</v>
       </c>
-      <c r="U45" s="74">
+      <c r="U45" s="68">
         <v>10.478269846537319</v>
       </c>
       <c r="V45" s="1"/>
@@ -5941,20 +5927,32 @@
     </row>
   </sheetData>
   <mergeCells count="56">
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="M25:N25"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="A5:I5"/>
-    <mergeCell ref="M5:U5"/>
-    <mergeCell ref="M18:U18"/>
-    <mergeCell ref="A13:I13"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="M44:N44"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="M45:N45"/>
+    <mergeCell ref="A41:I41"/>
+    <mergeCell ref="M41:U41"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="M42:N42"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="M43:N43"/>
+    <mergeCell ref="A36:I36"/>
+    <mergeCell ref="M13:U13"/>
+    <mergeCell ref="M36:U36"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="M28:U28"/>
+    <mergeCell ref="A18:I18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="M19:N19"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="M22:N22"/>
     <mergeCell ref="A39:B39"/>
     <mergeCell ref="A40:B40"/>
     <mergeCell ref="M39:N39"/>
@@ -5971,35 +5969,201 @@
     <mergeCell ref="M27:N27"/>
     <mergeCell ref="A28:I28"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A36:I36"/>
-    <mergeCell ref="M13:U13"/>
-    <mergeCell ref="M36:U36"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="M28:U28"/>
-    <mergeCell ref="A18:I18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="M19:N19"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="M22:N22"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="M44:N44"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="M45:N45"/>
-    <mergeCell ref="A41:I41"/>
-    <mergeCell ref="M41:U41"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="M42:N42"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="M43:N43"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="M25:N25"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="M5:U5"/>
+    <mergeCell ref="M18:U18"/>
+    <mergeCell ref="A13:I13"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="C14:I16 C6:I7 C2:I4 C10:I12">
+  <conditionalFormatting sqref="C14:I16 C2:I4 C10:I10 C12:I12">
+    <cfRule type="colorScale" priority="154">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C14:I16 C2:I4 C12:I12">
+    <cfRule type="colorScale" priority="158">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C14:I16 C2:I4 C8:I8 C12:I12 C10:I10">
+    <cfRule type="colorScale" priority="151">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C14:I17 C2:I4 C19:I22 C8:I8 C12:I12 C10:I10">
+    <cfRule type="colorScale" priority="162">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C19:I21">
+    <cfRule type="colorScale" priority="23">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="25">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J22">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J41:J45">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:K22">
+    <cfRule type="colorScale" priority="228">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J5:K5 C3:K4">
+    <cfRule type="colorScale" priority="95">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="96">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="97">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="98">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="99">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="100">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J17:K18 C2:K4 C12:K12 C14:K16 J13:K13 J22:K22 C19:K21 J5:K11">
     <cfRule type="colorScale" priority="142">
       <colorScale>
         <cfvo type="min"/>
@@ -6011,8 +6175,18 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C14:I16 C6:I7 C2:I4 C12:I12">
-    <cfRule type="colorScale" priority="146">
+  <conditionalFormatting sqref="J41:K45">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="21">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6023,8 +6197,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C14:I16 C6:I12 C2:I4">
-    <cfRule type="colorScale" priority="139">
+  <conditionalFormatting sqref="K2:K22">
+    <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6035,8 +6209,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C14:I17 C6:I12 C2:I4 C19:I22">
-    <cfRule type="colorScale" priority="150">
+  <conditionalFormatting sqref="K41:K45">
+    <cfRule type="colorScale" priority="22">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6047,28 +6221,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C19:I21">
-    <cfRule type="colorScale" priority="11">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="12">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="13">
+  <conditionalFormatting sqref="C11:I11">
+    <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6079,19 +6233,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J22">
-    <cfRule type="colorScale" priority="214">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J41:J45">
+  <conditionalFormatting sqref="C11:I11">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -6103,8 +6245,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:K22">
-    <cfRule type="colorScale" priority="216">
+  <conditionalFormatting sqref="C9:I9">
+    <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6115,58 +6257,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J5:K5 C3:K4">
-    <cfRule type="colorScale" priority="83">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="84">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="85">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="86">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="87">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="88">
+  <conditionalFormatting sqref="C9:I9">
+    <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6177,8 +6269,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J17:K18 C2:K4 C6:K7 J5:K5 J8:K11 C12:K12 C14:K16 J13:K13 J22:K22 C19:K21">
-    <cfRule type="colorScale" priority="130">
+  <conditionalFormatting sqref="C7:I7">
+    <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6189,18 +6281,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J41:K45">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="9">
+  <conditionalFormatting sqref="C7:I7">
+    <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6211,8 +6293,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K22">
-    <cfRule type="colorScale" priority="218">
+  <conditionalFormatting sqref="C6:I6">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6223,8 +6305,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K41:K45">
-    <cfRule type="colorScale" priority="10">
+  <conditionalFormatting sqref="C6:I6">
+    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>

--- a/results_(stress_test)_summary/summary.xlsx
+++ b/results_(stress_test)_summary/summary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\RnD_Repo\Research_Engineeirng\feature_fusion_PCCxSigmoid-PLV-\results_(stress_test)_summary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1BAF393-681B-457F-874F-5B0B7EE563C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE118874-1CE2-47AC-B526-1CF529D5F8D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="639" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="639" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="partialdata_20260429" sheetId="6" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="24">
   <si>
     <t>Accuracy</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -103,15 +103,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>optimal params ()</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>optimal params (heaviside)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>optimal params (k=50)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -366,7 +358,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -509,9 +501,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -534,6 +523,30 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -543,43 +556,31 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -944,10 +945,10 @@
       <c r="V1" s="12"/>
     </row>
     <row r="2" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="69" t="s">
+      <c r="A2" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="70"/>
+      <c r="B2" s="77"/>
       <c r="C2" s="20">
         <v>93.101364775358491</v>
       </c>
@@ -981,10 +982,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C2:I2)&amp;","</f>
         <v xml:space="preserve">    93.1013647753585, 91.3266637254648, 89.7225610371485, 83.857204647099, 76.2429490451186, 60.4027774173364, 47.7409002961387,</v>
       </c>
-      <c r="M2" s="69" t="s">
+      <c r="M2" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="70"/>
+      <c r="N2" s="77"/>
       <c r="O2" s="31">
         <v>3.4649270444699574</v>
       </c>
@@ -1012,10 +1013,10 @@
       </c>
     </row>
     <row r="3" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="69" t="s">
+      <c r="A3" s="76" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="70"/>
+      <c r="B3" s="77"/>
       <c r="C3" s="31">
         <v>93.273358766079312</v>
       </c>
@@ -1049,10 +1050,10 @@
         <f t="shared" ref="L3:L4" si="0">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C3:I3)&amp;","</f>
         <v xml:space="preserve">    93.2733587660793, 91.6155877934354, 90.6205330495939, 86.5975138193237, 78.2243502683126, 60.8549929786013, 48.7439337710534,</v>
       </c>
-      <c r="M3" s="69" t="s">
+      <c r="M3" s="76" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="70"/>
+      <c r="N3" s="77"/>
       <c r="O3" s="31">
         <v>3.4672469457762647</v>
       </c>
@@ -1080,10 +1081,10 @@
       </c>
     </row>
     <row r="4" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="69" t="s">
+      <c r="A4" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="70"/>
+      <c r="B4" s="77"/>
       <c r="C4" s="24">
         <v>87.593900000000005</v>
       </c>
@@ -1117,10 +1118,10 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    87.5939, 87.6637168141593, 88.1120943952802, 87.9700256922638, 87.4617081462642, 75.2513631894163, 47.7206838582802,</v>
       </c>
-      <c r="M4" s="69" t="s">
+      <c r="M4" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="N4" s="70"/>
+      <c r="N4" s="77"/>
       <c r="O4" s="49">
         <v>2.4529187882918819</v>
       </c>
@@ -1148,59 +1149,59 @@
       </c>
     </row>
     <row r="5" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="69" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="71"/>
-      <c r="C5" s="71"/>
-      <c r="D5" s="71"/>
-      <c r="E5" s="71"/>
-      <c r="F5" s="71"/>
-      <c r="G5" s="71"/>
-      <c r="H5" s="71"/>
-      <c r="I5" s="70"/>
+      <c r="A5" s="76" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="78"/>
+      <c r="C5" s="78"/>
+      <c r="D5" s="78"/>
+      <c r="E5" s="78"/>
+      <c r="F5" s="78"/>
+      <c r="G5" s="78"/>
+      <c r="H5" s="78"/>
+      <c r="I5" s="77"/>
       <c r="J5" s="35"/>
       <c r="K5" s="35"/>
       <c r="L5" s="12"/>
-      <c r="M5" s="69" t="s">
-        <v>14</v>
-      </c>
-      <c r="N5" s="71"/>
-      <c r="O5" s="71"/>
-      <c r="P5" s="71"/>
-      <c r="Q5" s="71"/>
-      <c r="R5" s="71"/>
-      <c r="S5" s="71"/>
-      <c r="T5" s="71"/>
-      <c r="U5" s="70"/>
+      <c r="M5" s="76" t="s">
+        <v>12</v>
+      </c>
+      <c r="N5" s="78"/>
+      <c r="O5" s="78"/>
+      <c r="P5" s="78"/>
+      <c r="Q5" s="78"/>
+      <c r="R5" s="78"/>
+      <c r="S5" s="78"/>
+      <c r="T5" s="78"/>
+      <c r="U5" s="77"/>
       <c r="V5" s="12"/>
     </row>
     <row r="6" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="85">
+        <v>13</v>
+      </c>
+      <c r="C6" s="57">
         <v>93.40216322517206</v>
       </c>
-      <c r="D6" s="86">
+      <c r="D6" s="58">
         <v>91.827126532236434</v>
       </c>
-      <c r="E6" s="86">
+      <c r="E6" s="58">
         <v>90.558689954065343</v>
       </c>
-      <c r="F6" s="86">
+      <c r="F6" s="58">
         <v>86.023376788149832</v>
       </c>
-      <c r="G6" s="86">
+      <c r="G6" s="58">
         <v>80.076301121405308</v>
       </c>
-      <c r="H6" s="86">
+      <c r="H6" s="58">
         <v>61.71287813908426</v>
       </c>
-      <c r="I6" s="87">
+      <c r="I6" s="59">
         <v>46.423510007295327</v>
       </c>
       <c r="J6" s="35" cm="1">
@@ -1216,30 +1217,30 @@
         <v xml:space="preserve">    93.4021632251721, 91.8271265322364, 90.5586899540653, 86.0233767881498, 80.0763011214053, 61.7128781390843, 46.4235100072953,</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N6" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="O6" s="85">
+        <v>13</v>
+      </c>
+      <c r="O6" s="57">
         <v>3.395734543818977</v>
       </c>
-      <c r="P6" s="86">
+      <c r="P6" s="58">
         <v>4.0701241715569392</v>
       </c>
-      <c r="Q6" s="86">
+      <c r="Q6" s="58">
         <v>4.2545139093922257</v>
       </c>
-      <c r="R6" s="86">
+      <c r="R6" s="58">
         <v>5.0550386107492153</v>
       </c>
-      <c r="S6" s="86">
+      <c r="S6" s="58">
         <v>5.5998181447012403</v>
       </c>
-      <c r="T6" s="86">
+      <c r="T6" s="58">
         <v>8.7815136499154747</v>
       </c>
-      <c r="U6" s="87">
+      <c r="U6" s="59">
         <v>8.6649338950065129</v>
       </c>
       <c r="V6" s="12" t="str">
@@ -1249,30 +1250,30 @@
     </row>
     <row r="7" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="85">
+        <v>14</v>
+      </c>
+      <c r="C7" s="57">
         <v>92.691248770894788</v>
       </c>
-      <c r="D7" s="86">
+      <c r="D7" s="58">
         <v>92.706981317600793</v>
       </c>
-      <c r="E7" s="86">
+      <c r="E7" s="58">
         <v>91.734513274336265</v>
       </c>
-      <c r="F7" s="86">
+      <c r="F7" s="58">
         <v>88.867553640890762</v>
       </c>
-      <c r="G7" s="86">
+      <c r="G7" s="58">
         <v>87.5647050003316</v>
       </c>
-      <c r="H7" s="86">
+      <c r="H7" s="58">
         <v>75.623785672886441</v>
       </c>
-      <c r="I7" s="87">
+      <c r="I7" s="59">
         <v>48.831339371447839</v>
       </c>
       <c r="J7" s="35" cm="1">
@@ -1288,30 +1289,30 @@
         <v xml:space="preserve">    92.6912487708948, 92.7069813176008, 91.7345132743363, 88.8675536408908, 87.5647050003316, 75.6237856728864, 48.8313393714478,</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N7" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="O7" s="58">
+        <v>14</v>
+      </c>
+      <c r="O7" s="57">
         <v>3.1492092951527728</v>
       </c>
-      <c r="P7" s="59">
+      <c r="P7" s="58">
         <v>3.3182076336991431</v>
       </c>
-      <c r="Q7" s="59">
+      <c r="Q7" s="58">
         <v>3.198166186176159</v>
       </c>
-      <c r="R7" s="59">
+      <c r="R7" s="58">
         <v>3.1321269598885868</v>
       </c>
-      <c r="S7" s="59">
+      <c r="S7" s="58">
         <v>3.0750631997727318</v>
       </c>
-      <c r="T7" s="59">
+      <c r="T7" s="58">
         <v>5.166114204995413</v>
       </c>
-      <c r="U7" s="60">
+      <c r="U7" s="59">
         <v>5.9316401890770027</v>
       </c>
       <c r="V7" s="12" t="str">
@@ -1320,38 +1321,38 @@
       </c>
     </row>
     <row r="8" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="69" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" s="71"/>
-      <c r="C8" s="72"/>
-      <c r="D8" s="72"/>
-      <c r="E8" s="72"/>
-      <c r="F8" s="72"/>
-      <c r="G8" s="72"/>
-      <c r="H8" s="72"/>
-      <c r="I8" s="73"/>
+      <c r="A8" s="76" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="78"/>
+      <c r="C8" s="83"/>
+      <c r="D8" s="83"/>
+      <c r="E8" s="83"/>
+      <c r="F8" s="83"/>
+      <c r="G8" s="83"/>
+      <c r="H8" s="83"/>
+      <c r="I8" s="82"/>
       <c r="J8" s="35"/>
       <c r="K8" s="35"/>
       <c r="L8" s="12"/>
-      <c r="M8" s="69" t="s">
-        <v>22</v>
-      </c>
-      <c r="N8" s="71"/>
-      <c r="O8" s="72"/>
-      <c r="P8" s="72"/>
-      <c r="Q8" s="72"/>
-      <c r="R8" s="72"/>
-      <c r="S8" s="72"/>
-      <c r="T8" s="72"/>
-      <c r="U8" s="73"/>
+      <c r="M8" s="76" t="s">
+        <v>20</v>
+      </c>
+      <c r="N8" s="78"/>
+      <c r="O8" s="83"/>
+      <c r="P8" s="83"/>
+      <c r="Q8" s="83"/>
+      <c r="R8" s="83"/>
+      <c r="S8" s="83"/>
+      <c r="T8" s="83"/>
+      <c r="U8" s="82"/>
       <c r="V8" s="12"/>
     </row>
     <row r="9" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="69" t="s">
+      <c r="A9" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="70"/>
+      <c r="B9" s="77"/>
       <c r="C9" s="31">
         <v>93.782740335124032</v>
       </c>
@@ -1385,10 +1386,10 @@
         <f t="shared" ref="L9:L12" si="4">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C9:I9)&amp;","</f>
         <v xml:space="preserve">    93.782740335124, 91.9482088945406, 90.212980504445, 84.6303889595354, 75.3710931755465, 59.6272113080563, 47.8441855033348,</v>
       </c>
-      <c r="M9" s="69" t="s">
+      <c r="M9" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="N9" s="70"/>
+      <c r="N9" s="77"/>
       <c r="O9" s="31">
         <v>3.5391983918820551</v>
       </c>
@@ -1416,10 +1417,10 @@
       </c>
     </row>
     <row r="10" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="74" t="s">
+      <c r="A10" s="81" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="73"/>
+      <c r="B10" s="82"/>
       <c r="C10" s="34">
         <v>93.226230330712227</v>
       </c>
@@ -1453,10 +1454,10 @@
         <f t="shared" si="4"/>
         <v xml:space="preserve">    93.2262303307122, 91.8332915221297, 90.3252911645718, 85.3834923600839, 76.5670002912366, 59.4145422249904, 50.5634074112521,</v>
       </c>
-      <c r="M10" s="69" t="s">
+      <c r="M10" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="N10" s="70"/>
+      <c r="N10" s="77"/>
       <c r="O10" s="34">
         <v>3.945711842949601</v>
       </c>
@@ -1484,10 +1485,10 @@
       </c>
     </row>
     <row r="11" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="69" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" s="70"/>
+      <c r="A11" s="76" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="77"/>
       <c r="C11" s="34">
         <v>93.004922187908207</v>
       </c>
@@ -1521,10 +1522,10 @@
         <f t="shared" si="4"/>
         <v xml:space="preserve">    93.0049221879082, 91.5185021785079, 89.7294209580821, 83.3486073985646, 74.0877199053048, 57.9173320415113, 48.0077941850708,</v>
       </c>
-      <c r="M11" s="69" t="s">
-        <v>23</v>
-      </c>
-      <c r="N11" s="70"/>
+      <c r="M11" s="76" t="s">
+        <v>21</v>
+      </c>
+      <c r="N11" s="77"/>
       <c r="O11" s="34">
         <v>3.690401528555848</v>
       </c>
@@ -1552,10 +1553,10 @@
       </c>
     </row>
     <row r="12" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="69" t="s">
-        <v>24</v>
-      </c>
-      <c r="B12" s="70"/>
+      <c r="A12" s="76" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="77"/>
       <c r="C12" s="37">
         <v>93.123279613145442</v>
       </c>
@@ -1589,10 +1590,10 @@
         <f t="shared" si="4"/>
         <v xml:space="preserve">    93.1232796131454, 91.674385879924, 89.6986882816172, 84.9570671026566, 75.9390825180149, 59.9950922297482, 48.4403036935152,</v>
       </c>
-      <c r="M12" s="69" t="s">
-        <v>24</v>
-      </c>
-      <c r="N12" s="70"/>
+      <c r="M12" s="76" t="s">
+        <v>22</v>
+      </c>
+      <c r="N12" s="77"/>
       <c r="O12" s="37">
         <v>3.8088682011350912</v>
       </c>
@@ -1620,38 +1621,38 @@
       </c>
     </row>
     <row r="13" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="69" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" s="71"/>
-      <c r="C13" s="75"/>
-      <c r="D13" s="75"/>
-      <c r="E13" s="75"/>
-      <c r="F13" s="75"/>
-      <c r="G13" s="75"/>
-      <c r="H13" s="75"/>
-      <c r="I13" s="76"/>
+      <c r="A13" s="76" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="78"/>
+      <c r="C13" s="79"/>
+      <c r="D13" s="79"/>
+      <c r="E13" s="79"/>
+      <c r="F13" s="79"/>
+      <c r="G13" s="79"/>
+      <c r="H13" s="79"/>
+      <c r="I13" s="80"/>
       <c r="J13" s="35"/>
       <c r="K13" s="35"/>
       <c r="L13" s="12"/>
-      <c r="M13" s="69" t="s">
-        <v>25</v>
-      </c>
-      <c r="N13" s="71"/>
-      <c r="O13" s="75"/>
-      <c r="P13" s="75"/>
-      <c r="Q13" s="75"/>
-      <c r="R13" s="75"/>
-      <c r="S13" s="75"/>
-      <c r="T13" s="75"/>
-      <c r="U13" s="76"/>
+      <c r="M13" s="76" t="s">
+        <v>23</v>
+      </c>
+      <c r="N13" s="78"/>
+      <c r="O13" s="79"/>
+      <c r="P13" s="79"/>
+      <c r="Q13" s="79"/>
+      <c r="R13" s="79"/>
+      <c r="S13" s="79"/>
+      <c r="T13" s="79"/>
+      <c r="U13" s="80"/>
       <c r="V13" s="12"/>
     </row>
     <row r="14" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="69" t="s">
+      <c r="A14" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="70"/>
+      <c r="B14" s="77"/>
       <c r="C14" s="31">
         <v>92.969518190757128</v>
       </c>
@@ -1685,10 +1686,10 @@
         <f t="shared" ref="L14:L17" si="6">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C14:I14)&amp;","</f>
         <v xml:space="preserve">    92.9695181907571, 91.8515240904621, 90.756145526057, 87.2531365611583, 81.1789721364371, 57.3869295293788, 44.8554428094822,</v>
       </c>
-      <c r="M14" s="69" t="s">
+      <c r="M14" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="N14" s="70"/>
+      <c r="N14" s="77"/>
       <c r="O14" s="31">
         <v>3.3991921823554931</v>
       </c>
@@ -1716,10 +1717,10 @@
       </c>
     </row>
     <row r="15" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="74" t="s">
+      <c r="A15" s="81" t="s">
         <v>8</v>
       </c>
-      <c r="B15" s="73"/>
+      <c r="B15" s="82"/>
       <c r="C15" s="34">
         <v>91.898721730580135</v>
       </c>
@@ -1753,10 +1754,10 @@
         <f t="shared" si="6"/>
         <v xml:space="preserve">    91.8987217305801, 90.765995668936, 89.7052685000158, 87.9596853490659, 85.7500007208828, 71.3873880108536, 45.5963431056209,</v>
       </c>
-      <c r="M15" s="69" t="s">
+      <c r="M15" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="N15" s="70"/>
+      <c r="N15" s="77"/>
       <c r="O15" s="34">
         <v>3.190312271555559</v>
       </c>
@@ -1784,10 +1785,10 @@
       </c>
     </row>
     <row r="16" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="69" t="s">
-        <v>23</v>
-      </c>
-      <c r="B16" s="70"/>
+      <c r="A16" s="76" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" s="77"/>
       <c r="C16" s="34">
         <v>93.044276622923505</v>
       </c>
@@ -1821,10 +1822,10 @@
         <f t="shared" si="6"/>
         <v xml:space="preserve">    93.0442766229235, 91.9351551484009, 90.9488922914558, 85.9525053561594, 78.9151838107019, 59.4421001335075, 49.5338281473023,</v>
       </c>
-      <c r="M16" s="69" t="s">
-        <v>23</v>
-      </c>
-      <c r="N16" s="70"/>
+      <c r="M16" s="76" t="s">
+        <v>21</v>
+      </c>
+      <c r="N16" s="77"/>
       <c r="O16" s="34">
         <v>3.72078192123604</v>
       </c>
@@ -1852,10 +1853,10 @@
       </c>
     </row>
     <row r="17" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="69" t="s">
-        <v>24</v>
-      </c>
-      <c r="B17" s="70"/>
+      <c r="A17" s="76" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" s="77"/>
       <c r="C17" s="37">
         <v>93.174110502686005</v>
       </c>
@@ -1889,10 +1890,10 @@
         <f t="shared" si="6"/>
         <v xml:space="preserve">    93.174110502686, 91.3917248419104, 89.5915391424955, 84.6905970928238, 76.4013471858177, 59.9636675057743, 47.7255772108755,</v>
       </c>
-      <c r="M17" s="69" t="s">
-        <v>24</v>
-      </c>
-      <c r="N17" s="70"/>
+      <c r="M17" s="76" t="s">
+        <v>22</v>
+      </c>
+      <c r="N17" s="77"/>
       <c r="O17" s="37">
         <v>3.8766021792735019</v>
       </c>
@@ -2002,10 +2003,10 @@
       <c r="V19" s="1"/>
     </row>
     <row r="20" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="77" t="s">
+      <c r="A20" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="B20" s="78"/>
+      <c r="B20" s="69"/>
       <c r="C20" s="41">
         <v>92.567111769713335</v>
       </c>
@@ -2033,10 +2034,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C20:I20)&amp;","</f>
         <v xml:space="preserve">    92.5671117697133, 90.8358586083436, 89.2175053395332, 83.2372459642881, 75.380430844191, 58.9943671875974, 43.6225356413822,</v>
       </c>
-      <c r="M20" s="77" t="s">
+      <c r="M20" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="N20" s="78"/>
+      <c r="N20" s="69"/>
       <c r="O20" s="40">
         <v>3.88093621561358</v>
       </c>
@@ -2064,10 +2065,10 @@
       </c>
     </row>
     <row r="21" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="77" t="s">
+      <c r="A21" s="68" t="s">
         <v>6</v>
       </c>
-      <c r="B21" s="78"/>
+      <c r="B21" s="69"/>
       <c r="C21" s="41">
         <v>92.866950218042462</v>
       </c>
@@ -2095,10 +2096,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C21:I21)&amp;","</f>
         <v xml:space="preserve">    92.8669502180425, 91.2426907647456, 90.1370532276984, 86.0801529266134, 77.4102172551968, 59.6761947649801, 46.3954904194042,</v>
       </c>
-      <c r="M21" s="77" t="s">
+      <c r="M21" s="68" t="s">
         <v>6</v>
       </c>
-      <c r="N21" s="78"/>
+      <c r="N21" s="69"/>
       <c r="O21" s="41">
         <v>3.8319643020864191</v>
       </c>
@@ -2126,10 +2127,10 @@
       </c>
     </row>
     <row r="22" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="77" t="s">
+      <c r="A22" s="68" t="s">
         <v>10</v>
       </c>
-      <c r="B22" s="78"/>
+      <c r="B22" s="69"/>
       <c r="C22" s="28">
         <v>87.268396410214976</v>
       </c>
@@ -2157,10 +2158,10 @@
         <f t="shared" ref="L22:L25" si="9">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C22:I22)&amp;","</f>
         <v xml:space="preserve">    87.268396410215, 87.2564283986868, 87.8221063041704, 87.6807264423516, 87.1448793671852, 74.9765678865158, 46.4175473948824,</v>
       </c>
-      <c r="M22" s="77" t="s">
+      <c r="M22" s="68" t="s">
         <v>10</v>
       </c>
-      <c r="N22" s="78"/>
+      <c r="N22" s="69"/>
       <c r="O22" s="28">
         <v>2.610595868561878</v>
       </c>
@@ -2188,59 +2189,59 @@
       </c>
     </row>
     <row r="23" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="77" t="s">
-        <v>14</v>
-      </c>
-      <c r="B23" s="79"/>
-      <c r="C23" s="79"/>
-      <c r="D23" s="79"/>
-      <c r="E23" s="79"/>
-      <c r="F23" s="79"/>
-      <c r="G23" s="79"/>
-      <c r="H23" s="79"/>
-      <c r="I23" s="78"/>
+      <c r="A23" s="68" t="s">
+        <v>12</v>
+      </c>
+      <c r="B23" s="72"/>
+      <c r="C23" s="72"/>
+      <c r="D23" s="72"/>
+      <c r="E23" s="72"/>
+      <c r="F23" s="72"/>
+      <c r="G23" s="72"/>
+      <c r="H23" s="72"/>
+      <c r="I23" s="69"/>
       <c r="J23" s="44"/>
       <c r="K23" s="44"/>
       <c r="L23" s="1"/>
-      <c r="M23" s="77" t="s">
-        <v>14</v>
-      </c>
-      <c r="N23" s="79"/>
-      <c r="O23" s="79"/>
-      <c r="P23" s="79"/>
-      <c r="Q23" s="79"/>
-      <c r="R23" s="79"/>
-      <c r="S23" s="79"/>
-      <c r="T23" s="79"/>
-      <c r="U23" s="78"/>
+      <c r="M23" s="68" t="s">
+        <v>12</v>
+      </c>
+      <c r="N23" s="72"/>
+      <c r="O23" s="72"/>
+      <c r="P23" s="72"/>
+      <c r="Q23" s="72"/>
+      <c r="R23" s="72"/>
+      <c r="S23" s="72"/>
+      <c r="T23" s="72"/>
+      <c r="U23" s="69"/>
       <c r="V23" s="1"/>
     </row>
     <row r="24" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C24" s="88">
+        <v>13</v>
+      </c>
+      <c r="C24" s="65">
         <v>92.975694513442221</v>
       </c>
-      <c r="D24" s="89">
+      <c r="D24" s="66">
         <v>91.363613749154311</v>
       </c>
-      <c r="E24" s="89">
+      <c r="E24" s="66">
         <v>90.094017961161143</v>
       </c>
-      <c r="F24" s="89">
+      <c r="F24" s="66">
         <v>85.37773791839254</v>
       </c>
-      <c r="G24" s="89">
+      <c r="G24" s="66">
         <v>79.268159049010507</v>
       </c>
-      <c r="H24" s="89">
+      <c r="H24" s="66">
         <v>60.52121651399365</v>
       </c>
-      <c r="I24" s="90">
+      <c r="I24" s="67">
         <v>42.05444880665619</v>
       </c>
       <c r="J24" s="44"/>
@@ -2250,30 +2251,30 @@
         <v xml:space="preserve">    92.9756945134422, 91.3636137491543, 90.0940179611611, 85.3777379183925, 79.2681590490105, 60.5212165139937, 42.0544488066562,</v>
       </c>
       <c r="M24" s="14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N24" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="O24" s="88">
+        <v>13</v>
+      </c>
+      <c r="O24" s="65">
         <v>3.782557259829499</v>
       </c>
-      <c r="P24" s="89">
+      <c r="P24" s="66">
         <v>4.4459073754732694</v>
       </c>
-      <c r="Q24" s="89">
+      <c r="Q24" s="66">
         <v>4.6323081197737448</v>
       </c>
-      <c r="R24" s="89">
+      <c r="R24" s="66">
         <v>5.3746795640933653</v>
       </c>
-      <c r="S24" s="89">
+      <c r="S24" s="66">
         <v>5.9912912250355319</v>
       </c>
-      <c r="T24" s="89">
+      <c r="T24" s="66">
         <v>9.0901817740237139</v>
       </c>
-      <c r="U24" s="90">
+      <c r="U24" s="67">
         <v>9.5108664952359483</v>
       </c>
       <c r="V24" s="1" t="str">
@@ -2283,30 +2284,30 @@
     </row>
     <row r="25" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C25" s="66">
+        <v>14</v>
+      </c>
+      <c r="C25" s="65">
         <v>92.311293413260969</v>
       </c>
-      <c r="D25" s="67">
+      <c r="D25" s="66">
         <v>92.333521756806476</v>
       </c>
-      <c r="E25" s="67">
+      <c r="E25" s="66">
         <v>91.381357522919643</v>
       </c>
-      <c r="F25" s="67">
+      <c r="F25" s="66">
         <v>88.560101371956989</v>
       </c>
-      <c r="G25" s="67">
+      <c r="G25" s="66">
         <v>87.278991705998607</v>
       </c>
-      <c r="H25" s="67">
+      <c r="H25" s="66">
         <v>75.38789705567028</v>
       </c>
-      <c r="I25" s="68">
+      <c r="I25" s="67">
         <v>47.478737907175287</v>
       </c>
       <c r="J25" s="44"/>
@@ -2316,30 +2317,30 @@
         <v xml:space="preserve">    92.311293413261, 92.3335217568065, 91.3813575229196, 88.560101371957, 87.2789917059986, 75.3878970556703, 47.4787379071753,</v>
       </c>
       <c r="M25" s="14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="O25" s="66">
+        <v>14</v>
+      </c>
+      <c r="O25" s="65">
         <v>3.45837660705662</v>
       </c>
-      <c r="P25" s="67">
+      <c r="P25" s="66">
         <v>3.6213315124355141</v>
       </c>
-      <c r="Q25" s="67">
+      <c r="Q25" s="66">
         <v>3.418827656161032</v>
       </c>
-      <c r="R25" s="67">
+      <c r="R25" s="66">
         <v>3.2543979140806938</v>
       </c>
-      <c r="S25" s="67">
+      <c r="S25" s="66">
         <v>3.202126822778443</v>
       </c>
-      <c r="T25" s="67">
+      <c r="T25" s="66">
         <v>5.2358921781492196</v>
       </c>
-      <c r="U25" s="68">
+      <c r="U25" s="67">
         <v>6.1375770825509051</v>
       </c>
       <c r="V25" s="1" t="str">
@@ -2348,38 +2349,38 @@
       </c>
     </row>
     <row r="26" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="77" t="s">
-        <v>22</v>
-      </c>
-      <c r="B26" s="79"/>
-      <c r="C26" s="80"/>
-      <c r="D26" s="80"/>
-      <c r="E26" s="80"/>
-      <c r="F26" s="80"/>
-      <c r="G26" s="80"/>
-      <c r="H26" s="80"/>
-      <c r="I26" s="81"/>
+      <c r="A26" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="B26" s="72"/>
+      <c r="C26" s="75"/>
+      <c r="D26" s="75"/>
+      <c r="E26" s="75"/>
+      <c r="F26" s="75"/>
+      <c r="G26" s="75"/>
+      <c r="H26" s="75"/>
+      <c r="I26" s="71"/>
       <c r="J26" s="44"/>
       <c r="K26" s="44"/>
       <c r="L26" s="1"/>
-      <c r="M26" s="77" t="s">
-        <v>22</v>
-      </c>
-      <c r="N26" s="79"/>
-      <c r="O26" s="80"/>
-      <c r="P26" s="80"/>
-      <c r="Q26" s="80"/>
-      <c r="R26" s="80"/>
-      <c r="S26" s="80"/>
-      <c r="T26" s="80"/>
-      <c r="U26" s="81"/>
+      <c r="M26" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="N26" s="72"/>
+      <c r="O26" s="75"/>
+      <c r="P26" s="75"/>
+      <c r="Q26" s="75"/>
+      <c r="R26" s="75"/>
+      <c r="S26" s="75"/>
+      <c r="T26" s="75"/>
+      <c r="U26" s="71"/>
       <c r="V26" s="1"/>
     </row>
     <row r="27" spans="1:22" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="77" t="s">
+      <c r="A27" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="B27" s="78"/>
+      <c r="B27" s="69"/>
       <c r="C27" s="40">
         <v>93.403798109785029</v>
       </c>
@@ -2407,10 +2408,10 @@
         <f t="shared" ref="L27:L30" si="10">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C27:I27)&amp;","</f>
         <v xml:space="preserve">    93.403798109785, 91.5170070049374, 89.7498804626893, 83.9973095811923, 74.3949629659869, 58.0955824704985, 44.4348127062073,</v>
       </c>
-      <c r="M27" s="77" t="s">
+      <c r="M27" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="N27" s="78"/>
+      <c r="N27" s="69"/>
       <c r="O27" s="40">
         <v>3.9553866501853321</v>
       </c>
@@ -2438,10 +2439,10 @@
       </c>
     </row>
     <row r="28" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="77" t="s">
+      <c r="A28" s="68" t="s">
         <v>8</v>
       </c>
-      <c r="B28" s="78"/>
+      <c r="B28" s="69"/>
       <c r="C28" s="43">
         <v>92.778947400409621</v>
       </c>
@@ -2469,10 +2470,10 @@
         <f t="shared" si="10"/>
         <v xml:space="preserve">    92.7789474004096, 91.4503689963737, 89.8794809545421, 84.748756470337, 75.6276087825805, 58.3002656651169, 48.5841064376263,</v>
       </c>
-      <c r="M28" s="77" t="s">
+      <c r="M28" s="68" t="s">
         <v>8</v>
       </c>
-      <c r="N28" s="78"/>
+      <c r="N28" s="69"/>
       <c r="O28" s="43">
         <v>4.3743918396131134</v>
       </c>
@@ -2500,10 +2501,10 @@
       </c>
     </row>
     <row r="29" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="77" t="s">
-        <v>23</v>
-      </c>
-      <c r="B29" s="78"/>
+      <c r="A29" s="68" t="s">
+        <v>21</v>
+      </c>
+      <c r="B29" s="69"/>
       <c r="C29" s="43">
         <v>92.492055194421354</v>
       </c>
@@ -2531,10 +2532,10 @@
         <f t="shared" si="10"/>
         <v xml:space="preserve">    92.4920551944214, 91.055738083246, 89.2412648877623, 82.7136018096434, 73.1336770487749, 56.2292059013312, 43.695396708103,</v>
       </c>
-      <c r="M29" s="77" t="s">
-        <v>23</v>
-      </c>
-      <c r="N29" s="78"/>
+      <c r="M29" s="68" t="s">
+        <v>21</v>
+      </c>
+      <c r="N29" s="69"/>
       <c r="O29" s="43">
         <v>4.0986250609792014</v>
       </c>
@@ -2562,10 +2563,10 @@
       </c>
     </row>
     <row r="30" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="77" t="s">
-        <v>24</v>
-      </c>
-      <c r="B30" s="78"/>
+      <c r="A30" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="B30" s="69"/>
       <c r="C30" s="46">
         <v>92.657174075741665</v>
       </c>
@@ -2587,16 +2588,16 @@
       <c r="I30" s="48">
         <v>44.786141592049418</v>
       </c>
-      <c r="J30" s="52"/>
-      <c r="K30" s="52"/>
+      <c r="J30" s="51"/>
+      <c r="K30" s="51"/>
       <c r="L30" s="1" t="str">
         <f t="shared" si="10"/>
         <v xml:space="preserve">    92.6571740757417, 91.2080508143722, 89.1704556780914, 84.47461606277, 75.0666685936403, 58.5203409933682, 44.7861415920494,</v>
       </c>
-      <c r="M30" s="77" t="s">
-        <v>24</v>
-      </c>
-      <c r="N30" s="78"/>
+      <c r="M30" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="N30" s="69"/>
       <c r="O30" s="46">
         <v>4.2589004392769629</v>
       </c>
@@ -2624,38 +2625,38 @@
       </c>
     </row>
     <row r="31" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="77" t="s">
-        <v>25</v>
-      </c>
-      <c r="B31" s="79"/>
-      <c r="C31" s="82"/>
-      <c r="D31" s="82"/>
-      <c r="E31" s="82"/>
-      <c r="F31" s="82"/>
-      <c r="G31" s="82"/>
-      <c r="H31" s="82"/>
-      <c r="I31" s="83"/>
+      <c r="A31" s="68" t="s">
+        <v>23</v>
+      </c>
+      <c r="B31" s="72"/>
+      <c r="C31" s="73"/>
+      <c r="D31" s="73"/>
+      <c r="E31" s="73"/>
+      <c r="F31" s="73"/>
+      <c r="G31" s="73"/>
+      <c r="H31" s="73"/>
+      <c r="I31" s="74"/>
       <c r="J31" s="44"/>
       <c r="K31" s="44"/>
       <c r="L31" s="1"/>
-      <c r="M31" s="77" t="s">
-        <v>25</v>
-      </c>
-      <c r="N31" s="79"/>
-      <c r="O31" s="82"/>
-      <c r="P31" s="82"/>
-      <c r="Q31" s="82"/>
-      <c r="R31" s="82"/>
-      <c r="S31" s="82"/>
-      <c r="T31" s="82"/>
-      <c r="U31" s="83"/>
+      <c r="M31" s="68" t="s">
+        <v>23</v>
+      </c>
+      <c r="N31" s="72"/>
+      <c r="O31" s="73"/>
+      <c r="P31" s="73"/>
+      <c r="Q31" s="73"/>
+      <c r="R31" s="73"/>
+      <c r="S31" s="73"/>
+      <c r="T31" s="73"/>
+      <c r="U31" s="74"/>
       <c r="V31" s="1"/>
     </row>
     <row r="32" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="77" t="s">
+      <c r="A32" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="B32" s="78"/>
+      <c r="B32" s="69"/>
       <c r="C32" s="40">
         <v>92.603769819293618</v>
       </c>
@@ -2683,10 +2684,10 @@
         <f t="shared" ref="L32:L35" si="11">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C32:I32)&amp;","</f>
         <v xml:space="preserve">    92.6037698192936, 91.4319470683528, 90.3907950429996, 86.7895628282223, 80.6155540330522, 56.6095785531339, 41.2792806229243,</v>
       </c>
-      <c r="M32" s="77" t="s">
+      <c r="M32" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="N32" s="78"/>
+      <c r="N32" s="69"/>
       <c r="O32" s="40">
         <v>3.708759274801273</v>
       </c>
@@ -2714,10 +2715,10 @@
       </c>
     </row>
     <row r="33" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="84" t="s">
+      <c r="A33" s="70" t="s">
         <v>8</v>
       </c>
-      <c r="B33" s="81"/>
+      <c r="B33" s="71"/>
       <c r="C33" s="43">
         <v>91.377634404932721</v>
       </c>
@@ -2745,10 +2746,10 @@
         <f t="shared" si="11"/>
         <v xml:space="preserve">    91.3776344049327, 90.4053733332451, 89.3714803083327, 87.6098986263952, 85.5372307015107, 70.9307087454215, 44.0973262328065,</v>
       </c>
-      <c r="M33" s="77" t="s">
+      <c r="M33" s="68" t="s">
         <v>8</v>
       </c>
-      <c r="N33" s="78"/>
+      <c r="N33" s="69"/>
       <c r="O33" s="43">
         <v>3.5684194304484111</v>
       </c>
@@ -2776,10 +2777,10 @@
       </c>
     </row>
     <row r="34" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="77" t="s">
-        <v>23</v>
-      </c>
-      <c r="B34" s="78"/>
+      <c r="A34" s="68" t="s">
+        <v>21</v>
+      </c>
+      <c r="B34" s="69"/>
       <c r="C34" s="43">
         <v>92.603715202692385</v>
       </c>
@@ -2807,10 +2808,10 @@
         <f t="shared" si="11"/>
         <v xml:space="preserve">    92.6037152026924, 91.4849975027203, 90.6301712993249, 85.3420346970645, 78.2086079443082, 58.1887672547126, 45.4689195625762,</v>
       </c>
-      <c r="M34" s="77" t="s">
-        <v>23</v>
-      </c>
-      <c r="N34" s="78"/>
+      <c r="M34" s="68" t="s">
+        <v>21</v>
+      </c>
+      <c r="N34" s="69"/>
       <c r="O34" s="43">
         <v>4.0727132923350373</v>
       </c>
@@ -2838,10 +2839,10 @@
       </c>
     </row>
     <row r="35" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="77" t="s">
-        <v>24</v>
-      </c>
-      <c r="B35" s="78"/>
+      <c r="A35" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="B35" s="69"/>
       <c r="C35" s="46">
         <v>92.692685851985146</v>
       </c>
@@ -2869,10 +2870,10 @@
         <f t="shared" si="11"/>
         <v xml:space="preserve">    92.6926858519851, 91.0280089290633, 89.1011768502887, 84.1216953111353, 75.5145363599464, 58.5518515483004, 43.5286444786034,</v>
       </c>
-      <c r="M35" s="77" t="s">
-        <v>24</v>
-      </c>
-      <c r="N35" s="78"/>
+      <c r="M35" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="N35" s="69"/>
       <c r="O35" s="46">
         <v>4.3508377678439567</v>
       </c>
@@ -2981,6 +2982,54 @@
     </row>
   </sheetData>
   <mergeCells count="56">
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="M5:U5"/>
+    <mergeCell ref="A8:I8"/>
+    <mergeCell ref="M8:U8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="M9:N9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="A13:I13"/>
+    <mergeCell ref="M13:U13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="A23:I23"/>
+    <mergeCell ref="M23:U23"/>
+    <mergeCell ref="A26:I26"/>
+    <mergeCell ref="M26:U26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="M27:N27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="M29:N29"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="M30:N30"/>
+    <mergeCell ref="A31:I31"/>
+    <mergeCell ref="M31:U31"/>
     <mergeCell ref="A35:B35"/>
     <mergeCell ref="M35:N35"/>
     <mergeCell ref="A32:B32"/>
@@ -2989,54 +3038,6 @@
     <mergeCell ref="M33:N33"/>
     <mergeCell ref="A34:B34"/>
     <mergeCell ref="M34:N34"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="M29:N29"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="M30:N30"/>
-    <mergeCell ref="A31:I31"/>
-    <mergeCell ref="M31:U31"/>
-    <mergeCell ref="A26:I26"/>
-    <mergeCell ref="M26:U26"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="M27:N27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="M22:N22"/>
-    <mergeCell ref="A23:I23"/>
-    <mergeCell ref="M23:U23"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="A13:I13"/>
-    <mergeCell ref="M13:U13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="A5:I5"/>
-    <mergeCell ref="M5:U5"/>
-    <mergeCell ref="A8:I8"/>
-    <mergeCell ref="M8:U8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="M9:N9"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="M4:N4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C2:I4">
@@ -3061,6 +3062,50 @@
       </colorScale>
     </cfRule>
     <cfRule type="colorScale" priority="46">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C6:I6">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C7:I7">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3315,54 +3360,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C7:I7">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C7:I7">
-    <cfRule type="colorScale" priority="9">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C6:I6">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C6:I6">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -3446,10 +3443,10 @@
       <c r="V1" s="12"/>
     </row>
     <row r="2" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="69" t="s">
+      <c r="A2" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="70"/>
+      <c r="B2" s="77"/>
       <c r="C2" s="20">
         <v>93.101364775358491</v>
       </c>
@@ -3483,10 +3480,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C2:I2)&amp;","</f>
         <v xml:space="preserve">    93.1013647753585, 91.3266637254648, 89.7225610371485, 83.857204647099, 76.2429490451186, 60.4027774173364, 47.7409002961387,</v>
       </c>
-      <c r="M2" s="69" t="s">
+      <c r="M2" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="70"/>
+      <c r="N2" s="77"/>
       <c r="O2" s="31">
         <v>3.4649270444699574</v>
       </c>
@@ -3514,10 +3511,10 @@
       </c>
     </row>
     <row r="3" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="69" t="s">
+      <c r="A3" s="76" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="70"/>
+      <c r="B3" s="77"/>
       <c r="C3" s="31">
         <v>93.273358766079312</v>
       </c>
@@ -3551,10 +3548,10 @@
         <f t="shared" ref="L3:L16" si="0">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C3:I3)&amp;","</f>
         <v xml:space="preserve">    93.2733587660793, 91.6155877934354, 90.6205330495939, 86.5975138193237, 78.2243502683126, 60.8549929786013, 48.7439337710534,</v>
       </c>
-      <c r="M3" s="69" t="s">
+      <c r="M3" s="76" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="70"/>
+      <c r="N3" s="77"/>
       <c r="O3" s="31">
         <v>3.4672469457762647</v>
       </c>
@@ -3582,10 +3579,10 @@
       </c>
     </row>
     <row r="4" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="69" t="s">
+      <c r="A4" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="70"/>
+      <c r="B4" s="77"/>
       <c r="C4" s="24">
         <v>87.593900000000005</v>
       </c>
@@ -3619,10 +3616,10 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    87.5939, 87.6637168141593, 88.1120943952802, 87.9700256922638, 87.4617081462642, 75.2513631894163, 47.7206838582802,</v>
       </c>
-      <c r="M4" s="69" t="s">
+      <c r="M4" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="N4" s="70"/>
+      <c r="N4" s="77"/>
       <c r="O4" s="49">
         <v>2.4529187882918819</v>
       </c>
@@ -3650,59 +3647,59 @@
       </c>
     </row>
     <row r="5" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="69" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="71"/>
-      <c r="C5" s="71"/>
-      <c r="D5" s="71"/>
-      <c r="E5" s="71"/>
-      <c r="F5" s="71"/>
-      <c r="G5" s="71"/>
-      <c r="H5" s="71"/>
-      <c r="I5" s="70"/>
+      <c r="A5" s="76" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="78"/>
+      <c r="C5" s="78"/>
+      <c r="D5" s="78"/>
+      <c r="E5" s="78"/>
+      <c r="F5" s="78"/>
+      <c r="G5" s="78"/>
+      <c r="H5" s="78"/>
+      <c r="I5" s="77"/>
       <c r="J5" s="35"/>
       <c r="K5" s="35"/>
       <c r="L5" s="12"/>
-      <c r="M5" s="69" t="s">
-        <v>14</v>
-      </c>
-      <c r="N5" s="71"/>
-      <c r="O5" s="71"/>
-      <c r="P5" s="71"/>
-      <c r="Q5" s="71"/>
-      <c r="R5" s="71"/>
-      <c r="S5" s="71"/>
-      <c r="T5" s="71"/>
-      <c r="U5" s="70"/>
+      <c r="M5" s="76" t="s">
+        <v>12</v>
+      </c>
+      <c r="N5" s="78"/>
+      <c r="O5" s="78"/>
+      <c r="P5" s="78"/>
+      <c r="Q5" s="78"/>
+      <c r="R5" s="78"/>
+      <c r="S5" s="78"/>
+      <c r="T5" s="78"/>
+      <c r="U5" s="77"/>
       <c r="V5" s="12"/>
     </row>
     <row r="6" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="85">
+        <v>13</v>
+      </c>
+      <c r="C6" s="57">
         <v>93.40216322517206</v>
       </c>
-      <c r="D6" s="86">
+      <c r="D6" s="58">
         <v>91.827126532236434</v>
       </c>
-      <c r="E6" s="86">
+      <c r="E6" s="58">
         <v>90.558689954065343</v>
       </c>
-      <c r="F6" s="86">
+      <c r="F6" s="58">
         <v>86.023376788149832</v>
       </c>
-      <c r="G6" s="86">
+      <c r="G6" s="58">
         <v>80.076301121405308</v>
       </c>
-      <c r="H6" s="86">
+      <c r="H6" s="58">
         <v>61.71287813908426</v>
       </c>
-      <c r="I6" s="87">
+      <c r="I6" s="59">
         <v>46.423510007295327</v>
       </c>
       <c r="J6" s="35" cm="1">
@@ -3717,31 +3714,31 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    93.4021632251721, 91.8271265322364, 90.5586899540653, 86.0233767881498, 80.0763011214053, 61.7128781390843, 46.4235100072953,</v>
       </c>
-      <c r="M6" s="7" t="s">
-        <v>12</v>
+      <c r="M6" s="93" t="s">
+        <v>11</v>
       </c>
       <c r="N6" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="O6" s="85">
+        <v>13</v>
+      </c>
+      <c r="O6" s="57">
         <v>3.395734543818977</v>
       </c>
-      <c r="P6" s="86">
+      <c r="P6" s="58">
         <v>4.0701241715569392</v>
       </c>
-      <c r="Q6" s="86">
+      <c r="Q6" s="58">
         <v>4.2545139093922257</v>
       </c>
-      <c r="R6" s="86">
+      <c r="R6" s="58">
         <v>5.0550386107492153</v>
       </c>
-      <c r="S6" s="86">
+      <c r="S6" s="58">
         <v>5.5998181447012403</v>
       </c>
-      <c r="T6" s="86">
+      <c r="T6" s="58">
         <v>8.7815136499154747</v>
       </c>
-      <c r="U6" s="87">
+      <c r="U6" s="59">
         <v>8.6649338950065129</v>
       </c>
       <c r="V6" s="12" t="str">
@@ -3751,30 +3748,30 @@
     </row>
     <row r="7" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="85">
+        <v>14</v>
+      </c>
+      <c r="C7" s="57">
         <v>92.691248770894788</v>
       </c>
-      <c r="D7" s="86">
+      <c r="D7" s="58">
         <v>92.706981317600793</v>
       </c>
-      <c r="E7" s="86">
+      <c r="E7" s="58">
         <v>91.734513274336265</v>
       </c>
-      <c r="F7" s="86">
+      <c r="F7" s="58">
         <v>88.867553640890762</v>
       </c>
-      <c r="G7" s="86">
+      <c r="G7" s="58">
         <v>87.5647050003316</v>
       </c>
-      <c r="H7" s="86">
+      <c r="H7" s="58">
         <v>75.623785672886441</v>
       </c>
-      <c r="I7" s="87">
+      <c r="I7" s="59">
         <v>48.831339371447839</v>
       </c>
       <c r="J7" s="35" cm="1">
@@ -3789,31 +3786,31 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    92.6912487708948, 92.7069813176008, 91.7345132743363, 88.8675536408908, 87.5647050003316, 75.6237856728864, 48.8313393714478,</v>
       </c>
-      <c r="M7" s="7" t="s">
-        <v>13</v>
+      <c r="M7" s="93" t="s">
+        <v>11</v>
       </c>
       <c r="N7" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="O7" s="58">
+        <v>14</v>
+      </c>
+      <c r="O7" s="57">
         <v>3.1492092951527728</v>
       </c>
-      <c r="P7" s="59">
+      <c r="P7" s="58">
         <v>3.3182076336991431</v>
       </c>
-      <c r="Q7" s="59">
+      <c r="Q7" s="58">
         <v>3.198166186176159</v>
       </c>
-      <c r="R7" s="59">
+      <c r="R7" s="58">
         <v>3.1321269598885868</v>
       </c>
-      <c r="S7" s="59">
+      <c r="S7" s="58">
         <v>3.0750631997727318</v>
       </c>
-      <c r="T7" s="59">
+      <c r="T7" s="58">
         <v>5.166114204995413</v>
       </c>
-      <c r="U7" s="60">
+      <c r="U7" s="59">
         <v>5.9316401890770027</v>
       </c>
       <c r="V7" s="12" t="str">
@@ -3823,68 +3820,96 @@
     </row>
     <row r="8" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="31"/>
-      <c r="D8" s="32"/>
-      <c r="E8" s="32"/>
-      <c r="F8" s="32"/>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="33"/>
+        <v>17</v>
+      </c>
+      <c r="C8" s="84">
+        <v>93.359910841212596</v>
+      </c>
+      <c r="D8" s="85">
+        <v>93.004951023221068</v>
+      </c>
+      <c r="E8" s="85">
+        <v>91.679628139805132</v>
+      </c>
+      <c r="F8" s="85">
+        <v>85.408749210633317</v>
+      </c>
+      <c r="G8" s="85">
+        <v>76.226619607436049</v>
+      </c>
+      <c r="H8" s="85">
+        <v>61.249065014979941</v>
+      </c>
+      <c r="I8" s="86">
+        <v>49.631651946239451</v>
+      </c>
       <c r="J8" s="35" cm="1">
         <f t="array" ref="J8">-SUMPRODUCT((D1:H1-C1:G1)*(C8:G8+D8:H8)/2)</f>
-        <v>0</v>
+        <v>79.045570535500588</v>
       </c>
       <c r="K8" s="35" cm="1">
         <f t="array" ref="K8">-SUMPRODUCT((D1:I1-C1:H1)*(C8:H8+D8:I8)/2)</f>
-        <v>0</v>
+        <v>81.817588459531066</v>
       </c>
       <c r="L8" s="12"/>
-      <c r="M8" s="7" t="s">
-        <v>12</v>
+      <c r="M8" s="93" t="s">
+        <v>11</v>
       </c>
       <c r="N8" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="O8" s="31"/>
-      <c r="P8" s="32"/>
-      <c r="Q8" s="32"/>
-      <c r="R8" s="32"/>
-      <c r="S8" s="32"/>
-      <c r="T8" s="32"/>
-      <c r="U8" s="33"/>
+        <v>17</v>
+      </c>
+      <c r="O8" s="87">
+        <v>3.6969489802746338</v>
+      </c>
+      <c r="P8" s="88">
+        <v>3.7743162236554419</v>
+      </c>
+      <c r="Q8" s="88">
+        <v>4.0183161455895977</v>
+      </c>
+      <c r="R8" s="88">
+        <v>5.5239472036366646</v>
+      </c>
+      <c r="S8" s="88">
+        <v>8.887831326254588</v>
+      </c>
+      <c r="T8" s="88">
+        <v>10.788676865113089</v>
+      </c>
+      <c r="U8" s="89">
+        <v>8.9042998213690989</v>
+      </c>
       <c r="V8" s="12"/>
     </row>
     <row r="9" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="58">
+        <v>18</v>
+      </c>
+      <c r="C9" s="57">
         <v>93.402168992234664</v>
       </c>
-      <c r="D9" s="59">
+      <c r="D9" s="58">
         <v>93.248776661851196</v>
       </c>
-      <c r="E9" s="59">
+      <c r="E9" s="58">
         <v>92.691271839145102</v>
       </c>
-      <c r="F9" s="59">
+      <c r="F9" s="58">
         <v>88.452475079080841</v>
       </c>
-      <c r="G9" s="59">
+      <c r="G9" s="58">
         <v>80.836250025230896</v>
       </c>
-      <c r="H9" s="59">
+      <c r="H9" s="58">
         <v>58.587493548098742</v>
       </c>
-      <c r="I9" s="60">
+      <c r="I9" s="59">
         <v>46.761612701378603</v>
       </c>
       <c r="J9" s="35" cm="1">
@@ -3896,102 +3921,130 @@
         <v>82.757600051326861</v>
       </c>
       <c r="L9" s="12"/>
-      <c r="M9" s="7" t="s">
-        <v>12</v>
+      <c r="M9" s="93" t="s">
+        <v>11</v>
       </c>
       <c r="N9" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="O9" s="58">
+        <v>18</v>
+      </c>
+      <c r="O9" s="57">
         <v>3.54951767012634</v>
       </c>
-      <c r="P9" s="59">
+      <c r="P9" s="58">
         <v>3.9476305437492138</v>
       </c>
-      <c r="Q9" s="59">
+      <c r="Q9" s="58">
         <v>3.9153520636466741</v>
       </c>
-      <c r="R9" s="59">
+      <c r="R9" s="58">
         <v>4.7440261437688536</v>
       </c>
-      <c r="S9" s="59">
+      <c r="S9" s="58">
         <v>6.9981331013815007</v>
       </c>
-      <c r="T9" s="59">
+      <c r="T9" s="58">
         <v>10.73836101002882</v>
       </c>
-      <c r="U9" s="60">
+      <c r="U9" s="59">
         <v>8.4598560379029468</v>
       </c>
       <c r="V9" s="12"/>
     </row>
     <row r="10" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="49"/>
-      <c r="D10" s="26"/>
-      <c r="E10" s="26"/>
-      <c r="F10" s="26"/>
-      <c r="G10" s="26"/>
-      <c r="H10" s="26"/>
-      <c r="I10" s="27"/>
+        <v>15</v>
+      </c>
+      <c r="C10" s="94">
+        <v>93.347099311701101</v>
+      </c>
+      <c r="D10" s="95">
+        <v>92.429741318408162</v>
+      </c>
+      <c r="E10" s="95">
+        <v>91.177980201674188</v>
+      </c>
+      <c r="F10" s="95">
+        <v>88.609442988261151</v>
+      </c>
+      <c r="G10" s="95">
+        <v>83.887882536469476</v>
+      </c>
+      <c r="H10" s="95">
+        <v>65.46502997430774</v>
+      </c>
+      <c r="I10" s="96">
+        <v>53.025920062745648</v>
+      </c>
       <c r="J10" s="35" cm="1">
         <f t="array" ref="J10">-SUMPRODUCT((D1:H1-C1:G1)*(C10:G10+D10:H10)/2)</f>
-        <v>0</v>
+        <v>80.24432448954289</v>
       </c>
       <c r="K10" s="35" cm="1">
         <f t="array" ref="K10">-SUMPRODUCT((D1:I1-C1:H1)*(C10:H10+D10:I10)/2)</f>
-        <v>0</v>
+        <v>83.206598240469219</v>
       </c>
       <c r="L10" s="12" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">    ,</v>
-      </c>
-      <c r="M10" s="7" t="s">
-        <v>12</v>
+        <v xml:space="preserve">    93.3470993117011, 92.4297413184082, 91.1779802016742, 88.6094429882612, 83.8878825364695, 65.4650299743077, 53.0259200627456,</v>
+      </c>
+      <c r="M10" s="93" t="s">
+        <v>11</v>
       </c>
       <c r="N10" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="O10" s="49"/>
-      <c r="P10" s="26"/>
-      <c r="Q10" s="26"/>
-      <c r="R10" s="26"/>
-      <c r="S10" s="26"/>
-      <c r="T10" s="26"/>
-      <c r="U10" s="27"/>
+        <v>15</v>
+      </c>
+      <c r="O10" s="94">
+        <v>3.530639787063353</v>
+      </c>
+      <c r="P10" s="95">
+        <v>3.7877954805458178</v>
+      </c>
+      <c r="Q10" s="95">
+        <v>3.5724123756053681</v>
+      </c>
+      <c r="R10" s="95">
+        <v>3.9540852979376608</v>
+      </c>
+      <c r="S10" s="95">
+        <v>4.7311149340952454</v>
+      </c>
+      <c r="T10" s="95">
+        <v>6.8843348259745856</v>
+      </c>
+      <c r="U10" s="96">
+        <v>6.3274200723455936</v>
+      </c>
       <c r="V10" s="12"/>
     </row>
     <row r="11" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="93" t="s">
         <v>11</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="58">
+        <v>19</v>
+      </c>
+      <c r="C11" s="57">
         <v>90.295968534906564</v>
       </c>
-      <c r="D11" s="59">
+      <c r="D11" s="58">
         <v>90.405113077679459</v>
       </c>
-      <c r="E11" s="59">
+      <c r="E11" s="58">
         <v>90.529243332554771</v>
       </c>
-      <c r="F11" s="59">
+      <c r="F11" s="58">
         <v>90.464208167890718</v>
       </c>
-      <c r="G11" s="59">
+      <c r="G11" s="58">
         <v>89.370346340942973</v>
       </c>
-      <c r="H11" s="59">
+      <c r="H11" s="58">
         <v>80.495811670804514</v>
       </c>
-      <c r="I11" s="60">
+      <c r="I11" s="59">
         <v>54.200509231625418</v>
       </c>
       <c r="J11" s="35" cm="1">
@@ -4003,122 +4056,156 @@
         <v>84.156218551486887</v>
       </c>
       <c r="L11" s="12"/>
-      <c r="M11" s="7" t="s">
+      <c r="M11" s="93" t="s">
         <v>11</v>
       </c>
       <c r="N11" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="O11" s="58">
+        <v>19</v>
+      </c>
+      <c r="O11" s="57">
         <v>2.645635465917767</v>
       </c>
-      <c r="P11" s="59">
+      <c r="P11" s="58">
         <v>2.349990742414489</v>
       </c>
-      <c r="Q11" s="59">
+      <c r="Q11" s="58">
         <v>2.284121152514234</v>
       </c>
-      <c r="R11" s="59">
+      <c r="R11" s="58">
         <v>2.4722451039664972</v>
       </c>
-      <c r="S11" s="59">
+      <c r="S11" s="58">
         <v>2.569604191233966</v>
       </c>
-      <c r="T11" s="59">
+      <c r="T11" s="58">
         <v>3.931910154117956</v>
       </c>
-      <c r="U11" s="60">
+      <c r="U11" s="59">
         <v>6.3131910290344502</v>
       </c>
       <c r="V11" s="12"/>
     </row>
     <row r="12" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="93" t="s">
         <v>11</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" s="37"/>
-      <c r="D12" s="38"/>
-      <c r="E12" s="38"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="38"/>
-      <c r="H12" s="38"/>
-      <c r="I12" s="39"/>
-      <c r="J12" s="35"/>
-      <c r="K12" s="35"/>
+        <v>16</v>
+      </c>
+      <c r="C12" s="94">
+        <v>87.757128810226178</v>
+      </c>
+      <c r="D12" s="95">
+        <v>87.214361715931787</v>
+      </c>
+      <c r="E12" s="95">
+        <v>87.421857743867449</v>
+      </c>
+      <c r="F12" s="95">
+        <v>87.622418879056042</v>
+      </c>
+      <c r="G12" s="95">
+        <v>86.807385877040446</v>
+      </c>
+      <c r="H12" s="95">
+        <v>75.901045856798063</v>
+      </c>
+      <c r="I12" s="96">
+        <v>48.250428925279053</v>
+      </c>
+      <c r="J12" s="35" cm="1">
+        <f t="array" ref="J12">-SUMPRODUCT((D1:H1-C1:G1)*(C12:G12+D12:H12)/2)</f>
+        <v>78.062303235033738</v>
+      </c>
+      <c r="K12" s="35" cm="1">
+        <f t="array" ref="K12">-SUMPRODUCT((D1:I1-C1:H1)*(C12:H12+D12:I12)/2)</f>
+        <v>81.166090104585663</v>
+      </c>
       <c r="L12" s="12" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">    ,</v>
-      </c>
-      <c r="M12" s="3" t="s">
+        <v xml:space="preserve">    87.7571288102262, 87.2143617159318, 87.4218577438674, 87.622418879056, 86.8073858770404, 75.9010458567981, 48.2504289252791,</v>
+      </c>
+      <c r="M12" s="93" t="s">
         <v>11</v>
       </c>
       <c r="N12" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="O12" s="37"/>
-      <c r="P12" s="38"/>
-      <c r="Q12" s="38"/>
-      <c r="R12" s="38"/>
-      <c r="S12" s="38"/>
-      <c r="T12" s="38"/>
-      <c r="U12" s="39"/>
+        <v>16</v>
+      </c>
+      <c r="O12" s="94">
+        <v>2.4219047595763121</v>
+      </c>
+      <c r="P12" s="95">
+        <v>2.3217688638534999</v>
+      </c>
+      <c r="Q12" s="95">
+        <v>1.9206629777265249</v>
+      </c>
+      <c r="R12" s="95">
+        <v>2.0167242206543352</v>
+      </c>
+      <c r="S12" s="95">
+        <v>1.6755361920192899</v>
+      </c>
+      <c r="T12" s="95">
+        <v>3.611109605289736</v>
+      </c>
+      <c r="U12" s="96">
+        <v>3.8722711387036122</v>
+      </c>
       <c r="V12" s="12"/>
     </row>
     <row r="13" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="69" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" s="71"/>
-      <c r="C13" s="72"/>
-      <c r="D13" s="72"/>
-      <c r="E13" s="72"/>
-      <c r="F13" s="72"/>
-      <c r="G13" s="72"/>
-      <c r="H13" s="72"/>
-      <c r="I13" s="73"/>
+      <c r="A13" s="76" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="78"/>
+      <c r="C13" s="83"/>
+      <c r="D13" s="83"/>
+      <c r="E13" s="83"/>
+      <c r="F13" s="83"/>
+      <c r="G13" s="83"/>
+      <c r="H13" s="83"/>
+      <c r="I13" s="82"/>
       <c r="J13" s="35"/>
       <c r="K13" s="35"/>
       <c r="L13" s="12"/>
-      <c r="M13" s="69" t="s">
-        <v>22</v>
-      </c>
-      <c r="N13" s="71"/>
-      <c r="O13" s="72"/>
-      <c r="P13" s="72"/>
-      <c r="Q13" s="72"/>
-      <c r="R13" s="72"/>
-      <c r="S13" s="72"/>
-      <c r="T13" s="72"/>
-      <c r="U13" s="73"/>
+      <c r="M13" s="76" t="s">
+        <v>20</v>
+      </c>
+      <c r="N13" s="78"/>
+      <c r="O13" s="83"/>
+      <c r="P13" s="83"/>
+      <c r="Q13" s="83"/>
+      <c r="R13" s="83"/>
+      <c r="S13" s="83"/>
+      <c r="T13" s="83"/>
+      <c r="U13" s="82"/>
       <c r="V13" s="12"/>
     </row>
     <row r="14" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="69" t="s">
+      <c r="A14" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="70"/>
-      <c r="C14" s="53">
+      <c r="B14" s="77"/>
+      <c r="C14" s="52">
         <v>93.782740335124032</v>
       </c>
-      <c r="D14" s="54">
+      <c r="D14" s="53">
         <v>91.948208894540599</v>
       </c>
-      <c r="E14" s="54">
+      <c r="E14" s="53">
         <v>90.212980504444957</v>
       </c>
-      <c r="F14" s="54">
+      <c r="F14" s="53">
         <v>84.630388959535409</v>
       </c>
-      <c r="G14" s="54">
+      <c r="G14" s="53">
         <v>75.371093175546491</v>
       </c>
-      <c r="H14" s="54">
+      <c r="H14" s="53">
         <v>59.627211308056303</v>
       </c>
-      <c r="I14" s="55">
+      <c r="I14" s="54">
         <v>47.844185503334799</v>
       </c>
       <c r="J14" s="35" cm="1">
@@ -4133,29 +4220,29 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    93.782740335124, 91.9482088945406, 90.212980504445, 84.6303889595354, 75.3710931755465, 59.6272113080563, 47.8441855033348,</v>
       </c>
-      <c r="M14" s="69" t="s">
+      <c r="M14" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="N14" s="70"/>
-      <c r="O14" s="53">
+      <c r="N14" s="77"/>
+      <c r="O14" s="52">
         <v>3.5391983918820551</v>
       </c>
-      <c r="P14" s="54">
+      <c r="P14" s="53">
         <v>4.1060038651541966</v>
       </c>
-      <c r="Q14" s="54">
+      <c r="Q14" s="53">
         <v>4.774795806468676</v>
       </c>
-      <c r="R14" s="54">
+      <c r="R14" s="53">
         <v>5.3483339064680431</v>
       </c>
-      <c r="S14" s="54">
+      <c r="S14" s="53">
         <v>8.0994903921197494</v>
       </c>
-      <c r="T14" s="54">
+      <c r="T14" s="53">
         <v>10.59987402205407</v>
       </c>
-      <c r="U14" s="55">
+      <c r="U14" s="54">
         <v>8.7604668874903737</v>
       </c>
       <c r="V14" s="12" t="str">
@@ -4164,11 +4251,11 @@
       </c>
     </row>
     <row r="15" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="74" t="s">
+      <c r="A15" s="81" t="s">
         <v>8</v>
       </c>
-      <c r="B15" s="73"/>
-      <c r="C15" s="56">
+      <c r="B15" s="82"/>
+      <c r="C15" s="55">
         <v>93.226230330712227</v>
       </c>
       <c r="D15" s="12">
@@ -4186,7 +4273,7 @@
       <c r="H15" s="12">
         <v>59.41454222499042</v>
       </c>
-      <c r="I15" s="57">
+      <c r="I15" s="56">
         <v>50.563407411252108</v>
       </c>
       <c r="J15" s="35" cm="1">
@@ -4201,11 +4288,11 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    93.2262303307122, 91.8332915221297, 90.3252911645718, 85.3834923600839, 76.5670002912366, 59.4145422249904, 50.5634074112521,</v>
       </c>
-      <c r="M15" s="69" t="s">
+      <c r="M15" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="N15" s="70"/>
-      <c r="O15" s="56">
+      <c r="N15" s="77"/>
+      <c r="O15" s="55">
         <v>3.945711842949601</v>
       </c>
       <c r="P15" s="12">
@@ -4223,7 +4310,7 @@
       <c r="T15" s="12">
         <v>10.788297692871961</v>
       </c>
-      <c r="U15" s="57">
+      <c r="U15" s="56">
         <v>8.7433484877826491</v>
       </c>
       <c r="V15" s="12" t="str">
@@ -4232,11 +4319,11 @@
       </c>
     </row>
     <row r="16" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="69" t="s">
-        <v>23</v>
-      </c>
-      <c r="B16" s="70"/>
-      <c r="C16" s="56">
+      <c r="A16" s="76" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" s="77"/>
+      <c r="C16" s="55">
         <v>93.004922187908207</v>
       </c>
       <c r="D16" s="12">
@@ -4254,7 +4341,7 @@
       <c r="H16" s="12">
         <v>57.917332041511322</v>
       </c>
-      <c r="I16" s="57">
+      <c r="I16" s="56">
         <v>48.007794185070807</v>
       </c>
       <c r="J16" s="35" cm="1">
@@ -4269,11 +4356,11 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    93.0049221879082, 91.5185021785079, 89.7294209580821, 83.3486073985646, 74.0877199053048, 57.9173320415113, 48.0077941850708,</v>
       </c>
-      <c r="M16" s="69" t="s">
-        <v>23</v>
-      </c>
-      <c r="N16" s="70"/>
-      <c r="O16" s="56">
+      <c r="M16" s="76" t="s">
+        <v>21</v>
+      </c>
+      <c r="N16" s="77"/>
+      <c r="O16" s="55">
         <v>3.690401528555848</v>
       </c>
       <c r="P16" s="12">
@@ -4291,7 +4378,7 @@
       <c r="T16" s="12">
         <v>10.83557708581068</v>
       </c>
-      <c r="U16" s="57">
+      <c r="U16" s="56">
         <v>9.2904800440053528</v>
       </c>
       <c r="V16" s="12" t="str">
@@ -4300,29 +4387,29 @@
       </c>
     </row>
     <row r="17" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="69" t="s">
-        <v>24</v>
-      </c>
-      <c r="B17" s="70"/>
-      <c r="C17" s="58">
+      <c r="A17" s="76" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" s="77"/>
+      <c r="C17" s="57">
         <v>93.123279613145442</v>
       </c>
-      <c r="D17" s="59">
+      <c r="D17" s="58">
         <v>91.674385879923975</v>
       </c>
-      <c r="E17" s="59">
+      <c r="E17" s="58">
         <v>89.698688281617194</v>
       </c>
-      <c r="F17" s="59">
+      <c r="F17" s="58">
         <v>84.957067102656595</v>
       </c>
-      <c r="G17" s="59">
+      <c r="G17" s="58">
         <v>75.939082518014857</v>
       </c>
-      <c r="H17" s="59">
+      <c r="H17" s="58">
         <v>59.995092229748238</v>
       </c>
-      <c r="I17" s="60">
+      <c r="I17" s="59">
         <v>48.440303693515233</v>
       </c>
       <c r="J17" s="35" cm="1">
@@ -4334,85 +4421,85 @@
         <v>80.789319111757024</v>
       </c>
       <c r="L17" s="12"/>
-      <c r="M17" s="69" t="s">
-        <v>24</v>
-      </c>
-      <c r="N17" s="70"/>
-      <c r="O17" s="58">
+      <c r="M17" s="76" t="s">
+        <v>22</v>
+      </c>
+      <c r="N17" s="77"/>
+      <c r="O17" s="57">
         <v>3.8088682011350912</v>
       </c>
-      <c r="P17" s="59">
+      <c r="P17" s="58">
         <v>4.4783864386850611</v>
       </c>
-      <c r="Q17" s="59">
+      <c r="Q17" s="58">
         <v>5.0849840192173117</v>
       </c>
-      <c r="R17" s="59">
+      <c r="R17" s="58">
         <v>5.0366327026230584</v>
       </c>
-      <c r="S17" s="59">
+      <c r="S17" s="58">
         <v>7.6643798786674449</v>
       </c>
-      <c r="T17" s="59">
+      <c r="T17" s="58">
         <v>10.05146904627655</v>
       </c>
-      <c r="U17" s="60">
+      <c r="U17" s="59">
         <v>9.821397671709315</v>
       </c>
       <c r="V17" s="12"/>
     </row>
     <row r="18" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="69" t="s">
-        <v>25</v>
-      </c>
-      <c r="B18" s="71"/>
-      <c r="C18" s="75"/>
-      <c r="D18" s="75"/>
-      <c r="E18" s="75"/>
-      <c r="F18" s="75"/>
-      <c r="G18" s="75"/>
-      <c r="H18" s="75"/>
-      <c r="I18" s="76"/>
+      <c r="A18" s="76" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" s="78"/>
+      <c r="C18" s="79"/>
+      <c r="D18" s="79"/>
+      <c r="E18" s="79"/>
+      <c r="F18" s="79"/>
+      <c r="G18" s="79"/>
+      <c r="H18" s="79"/>
+      <c r="I18" s="80"/>
       <c r="J18" s="35"/>
       <c r="K18" s="35"/>
       <c r="L18" s="12"/>
-      <c r="M18" s="69" t="s">
-        <v>25</v>
-      </c>
-      <c r="N18" s="71"/>
-      <c r="O18" s="75"/>
-      <c r="P18" s="75"/>
-      <c r="Q18" s="75"/>
-      <c r="R18" s="75"/>
-      <c r="S18" s="75"/>
-      <c r="T18" s="75"/>
-      <c r="U18" s="76"/>
+      <c r="M18" s="76" t="s">
+        <v>23</v>
+      </c>
+      <c r="N18" s="78"/>
+      <c r="O18" s="79"/>
+      <c r="P18" s="79"/>
+      <c r="Q18" s="79"/>
+      <c r="R18" s="79"/>
+      <c r="S18" s="79"/>
+      <c r="T18" s="79"/>
+      <c r="U18" s="80"/>
       <c r="V18" s="12"/>
     </row>
     <row r="19" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="69" t="s">
+      <c r="A19" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="B19" s="70"/>
-      <c r="C19" s="53">
+      <c r="B19" s="77"/>
+      <c r="C19" s="52">
         <v>92.969518190757128</v>
       </c>
-      <c r="D19" s="54">
+      <c r="D19" s="53">
         <v>91.851524090462149</v>
       </c>
-      <c r="E19" s="54">
+      <c r="E19" s="53">
         <v>90.756145526057011</v>
       </c>
-      <c r="F19" s="54">
+      <c r="F19" s="53">
         <v>87.253136561158271</v>
       </c>
-      <c r="G19" s="54">
+      <c r="G19" s="53">
         <v>81.178972136437139</v>
       </c>
-      <c r="H19" s="54">
+      <c r="H19" s="53">
         <v>57.386929529378847</v>
       </c>
-      <c r="I19" s="55">
+      <c r="I19" s="54">
         <v>44.855442809482213</v>
       </c>
       <c r="J19" s="35" cm="1">
@@ -4427,29 +4514,29 @@
         <f t="shared" ref="L19:L21" si="2">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C19:I19)&amp;","</f>
         <v xml:space="preserve">    92.9695181907571, 91.8515240904621, 90.756145526057, 87.2531365611583, 81.1789721364371, 57.3869295293788, 44.8554428094822,</v>
       </c>
-      <c r="M19" s="69" t="s">
+      <c r="M19" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="N19" s="70"/>
-      <c r="O19" s="53">
+      <c r="N19" s="77"/>
+      <c r="O19" s="52">
         <v>3.3991921823554931</v>
       </c>
-      <c r="P19" s="54">
+      <c r="P19" s="53">
         <v>3.6561489783789969</v>
       </c>
-      <c r="Q19" s="54">
+      <c r="Q19" s="53">
         <v>3.4316179388806831</v>
       </c>
-      <c r="R19" s="54">
+      <c r="R19" s="53">
         <v>3.3610781227617821</v>
       </c>
-      <c r="S19" s="54">
+      <c r="S19" s="53">
         <v>5.2773835873092807</v>
       </c>
-      <c r="T19" s="54">
+      <c r="T19" s="53">
         <v>8.2027130196510409</v>
       </c>
-      <c r="U19" s="55">
+      <c r="U19" s="54">
         <v>5.203571843512913</v>
       </c>
       <c r="V19" s="12" t="str">
@@ -4458,11 +4545,11 @@
       </c>
     </row>
     <row r="20" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="74" t="s">
+      <c r="A20" s="81" t="s">
         <v>8</v>
       </c>
-      <c r="B20" s="73"/>
-      <c r="C20" s="56">
+      <c r="B20" s="82"/>
+      <c r="C20" s="55">
         <v>91.898721730580135</v>
       </c>
       <c r="D20" s="12">
@@ -4480,7 +4567,7 @@
       <c r="H20" s="12">
         <v>71.387388010853613</v>
       </c>
-      <c r="I20" s="57">
+      <c r="I20" s="56">
         <v>45.596343105620853</v>
       </c>
       <c r="J20" s="35" cm="1">
@@ -4495,11 +4582,11 @@
         <f t="shared" si="2"/>
         <v xml:space="preserve">    91.8987217305801, 90.765995668936, 89.7052685000158, 87.9596853490659, 85.7500007208828, 71.3873880108536, 45.5963431056209,</v>
       </c>
-      <c r="M20" s="69" t="s">
+      <c r="M20" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="N20" s="70"/>
-      <c r="O20" s="56">
+      <c r="N20" s="77"/>
+      <c r="O20" s="55">
         <v>3.190312271555559</v>
       </c>
       <c r="P20" s="12">
@@ -4517,7 +4604,7 @@
       <c r="T20" s="12">
         <v>4.756712112750666</v>
       </c>
-      <c r="U20" s="57">
+      <c r="U20" s="56">
         <v>2.488810891584841</v>
       </c>
       <c r="V20" s="12" t="str">
@@ -4526,11 +4613,11 @@
       </c>
     </row>
     <row r="21" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="69" t="s">
-        <v>23</v>
-      </c>
-      <c r="B21" s="70"/>
-      <c r="C21" s="56">
+      <c r="A21" s="76" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" s="77"/>
+      <c r="C21" s="55">
         <v>93.044276622923505</v>
       </c>
       <c r="D21" s="12">
@@ -4548,7 +4635,7 @@
       <c r="H21" s="12">
         <v>59.442100133507502</v>
       </c>
-      <c r="I21" s="57">
+      <c r="I21" s="56">
         <v>49.533828147302302</v>
       </c>
       <c r="J21" s="35" cm="1">
@@ -4563,11 +4650,11 @@
         <f t="shared" si="2"/>
         <v xml:space="preserve">    93.0442766229235, 91.9351551484009, 90.9488922914558, 85.9525053561594, 78.9151838107019, 59.4421001335075, 49.5338281473023,</v>
       </c>
-      <c r="M21" s="69" t="s">
-        <v>23</v>
-      </c>
-      <c r="N21" s="70"/>
-      <c r="O21" s="56">
+      <c r="M21" s="76" t="s">
+        <v>21</v>
+      </c>
+      <c r="N21" s="77"/>
+      <c r="O21" s="55">
         <v>3.72078192123604</v>
       </c>
       <c r="P21" s="12">
@@ -4585,7 +4672,7 @@
       <c r="T21" s="12">
         <v>10.04668436860082</v>
       </c>
-      <c r="U21" s="57">
+      <c r="U21" s="56">
         <v>9.2355901481835172</v>
       </c>
       <c r="V21" s="12" t="str">
@@ -4594,29 +4681,29 @@
       </c>
     </row>
     <row r="22" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="69" t="s">
-        <v>24</v>
-      </c>
-      <c r="B22" s="70"/>
-      <c r="C22" s="58">
+      <c r="A22" s="76" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" s="77"/>
+      <c r="C22" s="57">
         <v>93.174110502686005</v>
       </c>
-      <c r="D22" s="59">
+      <c r="D22" s="58">
         <v>91.391724841910417</v>
       </c>
-      <c r="E22" s="59">
+      <c r="E22" s="58">
         <v>89.591539142495463</v>
       </c>
-      <c r="F22" s="59">
+      <c r="F22" s="58">
         <v>84.690597092823751</v>
       </c>
-      <c r="G22" s="59">
+      <c r="G22" s="58">
         <v>76.401347185817656</v>
       </c>
-      <c r="H22" s="59">
+      <c r="H22" s="58">
         <v>59.963667505774268</v>
       </c>
-      <c r="I22" s="60">
+      <c r="I22" s="59">
         <v>47.725577210875521</v>
       </c>
       <c r="J22" s="35" cm="1">
@@ -4628,29 +4715,29 @@
         <v>80.686930106085114</v>
       </c>
       <c r="L22" s="12"/>
-      <c r="M22" s="69" t="s">
-        <v>24</v>
-      </c>
-      <c r="N22" s="70"/>
-      <c r="O22" s="58">
+      <c r="M22" s="76" t="s">
+        <v>22</v>
+      </c>
+      <c r="N22" s="77"/>
+      <c r="O22" s="57">
         <v>3.8766021792735019</v>
       </c>
-      <c r="P22" s="59">
+      <c r="P22" s="58">
         <v>4.8126411406228078</v>
       </c>
-      <c r="Q22" s="59">
+      <c r="Q22" s="58">
         <v>4.6512210016047986</v>
       </c>
-      <c r="R22" s="59">
+      <c r="R22" s="58">
         <v>5.2416066355763284</v>
       </c>
-      <c r="S22" s="59">
+      <c r="S22" s="58">
         <v>8.0769588602235256</v>
       </c>
-      <c r="T22" s="59">
+      <c r="T22" s="58">
         <v>10.657363307561541</v>
       </c>
-      <c r="U22" s="60">
+      <c r="U22" s="59">
         <v>9.200486032966916</v>
       </c>
       <c r="V22" s="12"/>
@@ -4738,10 +4825,10 @@
       <c r="V24" s="1"/>
     </row>
     <row r="25" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="77" t="s">
+      <c r="A25" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="B25" s="78"/>
+      <c r="B25" s="69"/>
       <c r="C25" s="41">
         <v>92.567111769713335</v>
       </c>
@@ -4769,10 +4856,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C25:I25)&amp;","</f>
         <v xml:space="preserve">    92.5671117697133, 90.8358586083436, 89.2175053395332, 83.2372459642881, 75.380430844191, 58.9943671875974, 43.6225356413822,</v>
       </c>
-      <c r="M25" s="77" t="s">
+      <c r="M25" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="N25" s="78"/>
+      <c r="N25" s="69"/>
       <c r="O25" s="40">
         <v>3.88093621561358</v>
       </c>
@@ -4800,10 +4887,10 @@
       </c>
     </row>
     <row r="26" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="77" t="s">
+      <c r="A26" s="68" t="s">
         <v>6</v>
       </c>
-      <c r="B26" s="78"/>
+      <c r="B26" s="69"/>
       <c r="C26" s="41">
         <v>92.866950218042462</v>
       </c>
@@ -4831,10 +4918,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C26:I26)&amp;","</f>
         <v xml:space="preserve">    92.8669502180425, 91.2426907647456, 90.1370532276984, 86.0801529266134, 77.4102172551968, 59.6761947649801, 46.3954904194042,</v>
       </c>
-      <c r="M26" s="77" t="s">
+      <c r="M26" s="68" t="s">
         <v>6</v>
       </c>
-      <c r="N26" s="78"/>
+      <c r="N26" s="69"/>
       <c r="O26" s="41">
         <v>3.8319643020864191</v>
       </c>
@@ -4862,10 +4949,10 @@
       </c>
     </row>
     <row r="27" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="77" t="s">
+      <c r="A27" s="68" t="s">
         <v>10</v>
       </c>
-      <c r="B27" s="78"/>
+      <c r="B27" s="69"/>
       <c r="C27" s="28">
         <v>87.268396410214976</v>
       </c>
@@ -4893,10 +4980,10 @@
         <f t="shared" ref="L27:L35" si="5">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C27:I27)&amp;","</f>
         <v xml:space="preserve">    87.268396410215, 87.2564283986868, 87.8221063041704, 87.6807264423516, 87.1448793671852, 74.9765678865158, 46.4175473948824,</v>
       </c>
-      <c r="M27" s="77" t="s">
+      <c r="M27" s="68" t="s">
         <v>10</v>
       </c>
-      <c r="N27" s="78"/>
+      <c r="N27" s="69"/>
       <c r="O27" s="28">
         <v>2.610595868561878</v>
       </c>
@@ -4924,59 +5011,59 @@
       </c>
     </row>
     <row r="28" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="77" t="s">
-        <v>14</v>
-      </c>
-      <c r="B28" s="79"/>
-      <c r="C28" s="79"/>
-      <c r="D28" s="79"/>
-      <c r="E28" s="79"/>
-      <c r="F28" s="79"/>
-      <c r="G28" s="79"/>
-      <c r="H28" s="79"/>
-      <c r="I28" s="78"/>
+      <c r="A28" s="68" t="s">
+        <v>12</v>
+      </c>
+      <c r="B28" s="72"/>
+      <c r="C28" s="72"/>
+      <c r="D28" s="72"/>
+      <c r="E28" s="72"/>
+      <c r="F28" s="72"/>
+      <c r="G28" s="72"/>
+      <c r="H28" s="72"/>
+      <c r="I28" s="69"/>
       <c r="J28" s="44"/>
       <c r="K28" s="44"/>
       <c r="L28" s="1"/>
-      <c r="M28" s="77" t="s">
-        <v>14</v>
-      </c>
-      <c r="N28" s="79"/>
-      <c r="O28" s="79"/>
-      <c r="P28" s="79"/>
-      <c r="Q28" s="79"/>
-      <c r="R28" s="79"/>
-      <c r="S28" s="79"/>
-      <c r="T28" s="79"/>
-      <c r="U28" s="78"/>
+      <c r="M28" s="68" t="s">
+        <v>12</v>
+      </c>
+      <c r="N28" s="72"/>
+      <c r="O28" s="72"/>
+      <c r="P28" s="72"/>
+      <c r="Q28" s="72"/>
+      <c r="R28" s="72"/>
+      <c r="S28" s="72"/>
+      <c r="T28" s="72"/>
+      <c r="U28" s="69"/>
       <c r="V28" s="1"/>
     </row>
     <row r="29" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A29" s="14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C29" s="88">
+        <v>13</v>
+      </c>
+      <c r="C29" s="65">
         <v>92.975694513442221</v>
       </c>
-      <c r="D29" s="89">
+      <c r="D29" s="66">
         <v>91.363613749154311</v>
       </c>
-      <c r="E29" s="89">
+      <c r="E29" s="66">
         <v>90.094017961161143</v>
       </c>
-      <c r="F29" s="89">
+      <c r="F29" s="66">
         <v>85.37773791839254</v>
       </c>
-      <c r="G29" s="89">
+      <c r="G29" s="66">
         <v>79.268159049010507</v>
       </c>
-      <c r="H29" s="89">
+      <c r="H29" s="66">
         <v>60.52121651399365</v>
       </c>
-      <c r="I29" s="90">
+      <c r="I29" s="67">
         <v>42.05444880665619</v>
       </c>
       <c r="J29" s="44"/>
@@ -4986,30 +5073,30 @@
         <v xml:space="preserve">    92.9756945134422, 91.3636137491543, 90.0940179611611, 85.3777379183925, 79.2681590490105, 60.5212165139937, 42.0544488066562,</v>
       </c>
       <c r="M29" s="14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="O29" s="88">
+        <v>13</v>
+      </c>
+      <c r="O29" s="65">
         <v>3.782557259829499</v>
       </c>
-      <c r="P29" s="89">
+      <c r="P29" s="66">
         <v>4.4459073754732694</v>
       </c>
-      <c r="Q29" s="89">
+      <c r="Q29" s="66">
         <v>4.6323081197737448</v>
       </c>
-      <c r="R29" s="89">
+      <c r="R29" s="66">
         <v>5.3746795640933653</v>
       </c>
-      <c r="S29" s="89">
+      <c r="S29" s="66">
         <v>5.9912912250355319</v>
       </c>
-      <c r="T29" s="89">
+      <c r="T29" s="66">
         <v>9.0901817740237139</v>
       </c>
-      <c r="U29" s="90">
+      <c r="U29" s="67">
         <v>9.5108664952359483</v>
       </c>
       <c r="V29" s="1" t="str">
@@ -5019,30 +5106,30 @@
     </row>
     <row r="30" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A30" s="14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C30" s="66">
+        <v>14</v>
+      </c>
+      <c r="C30" s="65">
         <v>92.311293413260969</v>
       </c>
-      <c r="D30" s="67">
+      <c r="D30" s="66">
         <v>92.333521756806476</v>
       </c>
-      <c r="E30" s="67">
+      <c r="E30" s="66">
         <v>91.381357522919643</v>
       </c>
-      <c r="F30" s="67">
+      <c r="F30" s="66">
         <v>88.560101371956989</v>
       </c>
-      <c r="G30" s="67">
+      <c r="G30" s="66">
         <v>87.278991705998607</v>
       </c>
-      <c r="H30" s="67">
+      <c r="H30" s="66">
         <v>75.38789705567028</v>
       </c>
-      <c r="I30" s="68">
+      <c r="I30" s="67">
         <v>47.478737907175287</v>
       </c>
       <c r="J30" s="44"/>
@@ -5052,30 +5139,30 @@
         <v xml:space="preserve">    92.311293413261, 92.3335217568065, 91.3813575229196, 88.560101371957, 87.2789917059986, 75.3878970556703, 47.4787379071753,</v>
       </c>
       <c r="M30" s="14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N30" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="O30" s="66">
+        <v>14</v>
+      </c>
+      <c r="O30" s="65">
         <v>3.45837660705662</v>
       </c>
-      <c r="P30" s="67">
+      <c r="P30" s="66">
         <v>3.6213315124355141</v>
       </c>
-      <c r="Q30" s="67">
+      <c r="Q30" s="66">
         <v>3.418827656161032</v>
       </c>
-      <c r="R30" s="67">
+      <c r="R30" s="66">
         <v>3.2543979140806938</v>
       </c>
-      <c r="S30" s="67">
+      <c r="S30" s="66">
         <v>3.202126822778443</v>
       </c>
-      <c r="T30" s="67">
+      <c r="T30" s="66">
         <v>5.2358921781492196</v>
       </c>
-      <c r="U30" s="68">
+      <c r="U30" s="67">
         <v>6.1375770825509051</v>
       </c>
       <c r="V30" s="1" t="str">
@@ -5085,129 +5172,185 @@
     </row>
     <row r="31" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A31" s="14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="C31" s="41"/>
-      <c r="D31" s="41"/>
-      <c r="E31" s="41"/>
-      <c r="F31" s="41"/>
-      <c r="G31" s="41"/>
-      <c r="H31" s="41"/>
-      <c r="I31" s="42"/>
+        <v>17</v>
+      </c>
+      <c r="C31" s="97">
+        <v>92.98334081387425</v>
+      </c>
+      <c r="D31" s="98">
+        <v>92.665002460688413</v>
+      </c>
+      <c r="E31" s="98">
+        <v>91.240968563949494</v>
+      </c>
+      <c r="F31" s="98">
+        <v>84.837780429069838</v>
+      </c>
+      <c r="G31" s="98">
+        <v>75.450480295384878</v>
+      </c>
+      <c r="H31" s="98">
+        <v>59.708500699124301</v>
+      </c>
+      <c r="I31" s="99">
+        <v>46.827950364949707</v>
+      </c>
       <c r="J31" s="44"/>
       <c r="K31" s="44"/>
       <c r="L31" s="1"/>
       <c r="M31" s="14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="O31" s="41"/>
-      <c r="P31" s="41"/>
-      <c r="Q31" s="41"/>
-      <c r="R31" s="41"/>
-      <c r="S31" s="41"/>
-      <c r="T31" s="41"/>
-      <c r="U31" s="42"/>
+        <v>17</v>
+      </c>
+      <c r="O31" s="90">
+        <v>4.047029068549703</v>
+      </c>
+      <c r="P31" s="91">
+        <v>4.0939802876249018</v>
+      </c>
+      <c r="Q31" s="91">
+        <v>4.4520389395614499</v>
+      </c>
+      <c r="R31" s="91">
+        <v>5.8725133520041934</v>
+      </c>
+      <c r="S31" s="91">
+        <v>9.1198860433459092</v>
+      </c>
+      <c r="T31" s="91">
+        <v>11.4228840807754</v>
+      </c>
+      <c r="U31" s="92">
+        <v>9.7047317426323225</v>
+      </c>
       <c r="V31" s="1"/>
     </row>
     <row r="32" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A32" s="14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C32" s="66">
+        <v>18</v>
+      </c>
+      <c r="C32" s="65">
         <v>93.003107171421291</v>
       </c>
-      <c r="D32" s="67">
+      <c r="D32" s="66">
         <v>92.882665900806714</v>
       </c>
-      <c r="E32" s="67">
+      <c r="E32" s="66">
         <v>92.323250249861715</v>
       </c>
-      <c r="F32" s="67">
+      <c r="F32" s="66">
         <v>87.896361279111929</v>
       </c>
-      <c r="G32" s="67">
+      <c r="G32" s="66">
         <v>80.149965599113543</v>
       </c>
-      <c r="H32" s="67">
+      <c r="H32" s="66">
         <v>57.360910597574737</v>
       </c>
-      <c r="I32" s="68">
+      <c r="I32" s="67">
         <v>43.986149507359343</v>
       </c>
       <c r="J32" s="44"/>
       <c r="K32" s="44"/>
       <c r="L32" s="1"/>
       <c r="M32" s="14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N32" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="O32" s="66">
+        <v>18</v>
+      </c>
+      <c r="O32" s="65">
         <v>3.8815673789284708</v>
       </c>
-      <c r="P32" s="67">
+      <c r="P32" s="66">
         <v>4.3723258101522813</v>
       </c>
-      <c r="Q32" s="67">
+      <c r="Q32" s="66">
         <v>4.2934275551121281</v>
       </c>
-      <c r="R32" s="67">
+      <c r="R32" s="66">
         <v>5.2017150988587044</v>
       </c>
-      <c r="S32" s="67">
+      <c r="S32" s="66">
         <v>7.2625504458350916</v>
       </c>
-      <c r="T32" s="67">
+      <c r="T32" s="66">
         <v>11.40658683680142</v>
       </c>
-      <c r="U32" s="68">
+      <c r="U32" s="67">
         <v>9.5393474867950871</v>
       </c>
       <c r="V32" s="1"/>
     </row>
     <row r="33" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A33" s="14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C33" s="28"/>
-      <c r="D33" s="29"/>
-      <c r="E33" s="29"/>
-      <c r="F33" s="29"/>
-      <c r="G33" s="29"/>
-      <c r="H33" s="29"/>
-      <c r="I33" s="30"/>
+        <v>15</v>
+      </c>
+      <c r="C33" s="97">
+        <v>92.988386774165761</v>
+      </c>
+      <c r="D33" s="98">
+        <v>92.050616029386802</v>
+      </c>
+      <c r="E33" s="98">
+        <v>90.719698676196401</v>
+      </c>
+      <c r="F33" s="98">
+        <v>88.185686945633506</v>
+      </c>
+      <c r="G33" s="98">
+        <v>83.275334389555965</v>
+      </c>
+      <c r="H33" s="98">
+        <v>64.685401955234482</v>
+      </c>
+      <c r="I33" s="99">
+        <v>51.069046974801182</v>
+      </c>
       <c r="J33" s="44"/>
       <c r="K33" s="44"/>
       <c r="L33" s="1" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">    ,</v>
+        <v xml:space="preserve">    92.9883867741658, 92.0506160293868, 90.7196986761964, 88.1856869456335, 83.275334389556, 64.6854019552345, 51.0690469748012,</v>
       </c>
       <c r="M33" s="14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="O33" s="28"/>
-      <c r="P33" s="29"/>
-      <c r="Q33" s="29"/>
-      <c r="R33" s="29"/>
-      <c r="S33" s="29"/>
-      <c r="T33" s="29"/>
-      <c r="U33" s="30"/>
+        <v>15</v>
+      </c>
+      <c r="O33" s="97">
+        <v>3.845990120862357</v>
+      </c>
+      <c r="P33" s="98">
+        <v>4.1197830115536282</v>
+      </c>
+      <c r="Q33" s="98">
+        <v>3.9254290526154212</v>
+      </c>
+      <c r="R33" s="98">
+        <v>4.2886830099031732</v>
+      </c>
+      <c r="S33" s="98">
+        <v>5.0859486951315533</v>
+      </c>
+      <c r="T33" s="98">
+        <v>7.2871022167686217</v>
+      </c>
+      <c r="U33" s="99">
+        <v>6.9147061894583581</v>
+      </c>
       <c r="V33" s="1"/>
     </row>
     <row r="34" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
@@ -5215,27 +5358,27 @@
         <v>11</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C34" s="66">
+        <v>19</v>
+      </c>
+      <c r="C34" s="65">
         <v>89.74449346032101</v>
       </c>
-      <c r="D34" s="67">
+      <c r="D34" s="66">
         <v>89.961854893326574</v>
       </c>
-      <c r="E34" s="67">
+      <c r="E34" s="66">
         <v>90.011537582574022</v>
       </c>
-      <c r="F34" s="67">
+      <c r="F34" s="66">
         <v>90.064770133428496</v>
       </c>
-      <c r="G34" s="67">
+      <c r="G34" s="66">
         <v>88.967446677518851</v>
       </c>
-      <c r="H34" s="67">
+      <c r="H34" s="66">
         <v>80.083589667611676</v>
       </c>
-      <c r="I34" s="68">
+      <c r="I34" s="67">
         <v>52.982008110476087</v>
       </c>
       <c r="J34" s="44"/>
@@ -5245,27 +5388,27 @@
         <v>11</v>
       </c>
       <c r="N34" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="O34" s="66">
+        <v>19</v>
+      </c>
+      <c r="O34" s="65">
         <v>2.9793986812049931</v>
       </c>
-      <c r="P34" s="67">
+      <c r="P34" s="66">
         <v>2.5386471681353431</v>
       </c>
-      <c r="Q34" s="67">
+      <c r="Q34" s="66">
         <v>2.4449126963196481</v>
       </c>
-      <c r="R34" s="67">
+      <c r="R34" s="66">
         <v>2.6222789037595908</v>
       </c>
-      <c r="S34" s="67">
+      <c r="S34" s="66">
         <v>2.7817641077346069</v>
       </c>
-      <c r="T34" s="67">
+      <c r="T34" s="66">
         <v>4.0935792052005926</v>
       </c>
-      <c r="U34" s="68">
+      <c r="U34" s="67">
         <v>6.5884863469929558</v>
       </c>
       <c r="V34" s="1"/>
@@ -5275,88 +5418,116 @@
         <v>11</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C35" s="46"/>
-      <c r="D35" s="47"/>
-      <c r="E35" s="47"/>
-      <c r="F35" s="47"/>
-      <c r="G35" s="47"/>
-      <c r="H35" s="47"/>
-      <c r="I35" s="48"/>
+        <v>16</v>
+      </c>
+      <c r="C35" s="97">
+        <v>87.287634799049286</v>
+      </c>
+      <c r="D35" s="98">
+        <v>86.878696750662726</v>
+      </c>
+      <c r="E35" s="98">
+        <v>87.083363148466532</v>
+      </c>
+      <c r="F35" s="98">
+        <v>87.300294897904948</v>
+      </c>
+      <c r="G35" s="98">
+        <v>86.527431822215689</v>
+      </c>
+      <c r="H35" s="98">
+        <v>75.689128775848914</v>
+      </c>
+      <c r="I35" s="99">
+        <v>46.886907074094779</v>
+      </c>
       <c r="J35" s="44"/>
       <c r="K35" s="44"/>
       <c r="L35" s="1" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">    ,</v>
-      </c>
-      <c r="M35" s="50" t="s">
+        <v xml:space="preserve">    87.2876347990493, 86.8786967506627, 87.0833631484665, 87.3002948979049, 86.5274318222157, 75.6891287758489, 46.8869070740948,</v>
+      </c>
+      <c r="M35" s="14" t="s">
         <v>11</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="O35" s="46"/>
-      <c r="P35" s="47"/>
-      <c r="Q35" s="47"/>
-      <c r="R35" s="47"/>
-      <c r="S35" s="47"/>
-      <c r="T35" s="47"/>
-      <c r="U35" s="48"/>
+        <v>16</v>
+      </c>
+      <c r="O35" s="97">
+        <v>2.5152339820278629</v>
+      </c>
+      <c r="P35" s="98">
+        <v>2.5980079882709322</v>
+      </c>
+      <c r="Q35" s="98">
+        <v>2.0296317104437578</v>
+      </c>
+      <c r="R35" s="98">
+        <v>2.161003670540631</v>
+      </c>
+      <c r="S35" s="98">
+        <v>1.7804591714461351</v>
+      </c>
+      <c r="T35" s="98">
+        <v>3.6175089321994709</v>
+      </c>
+      <c r="U35" s="99">
+        <v>4.0563769517378363</v>
+      </c>
       <c r="V35" s="1"/>
     </row>
     <row r="36" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="77" t="s">
-        <v>22</v>
-      </c>
-      <c r="B36" s="79"/>
-      <c r="C36" s="80"/>
-      <c r="D36" s="80"/>
-      <c r="E36" s="80"/>
-      <c r="F36" s="80"/>
-      <c r="G36" s="80"/>
-      <c r="H36" s="80"/>
-      <c r="I36" s="81"/>
+      <c r="A36" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="B36" s="72"/>
+      <c r="C36" s="75"/>
+      <c r="D36" s="75"/>
+      <c r="E36" s="75"/>
+      <c r="F36" s="75"/>
+      <c r="G36" s="75"/>
+      <c r="H36" s="75"/>
+      <c r="I36" s="71"/>
       <c r="J36" s="44"/>
       <c r="K36" s="44"/>
       <c r="L36" s="1"/>
-      <c r="M36" s="77" t="s">
-        <v>22</v>
-      </c>
-      <c r="N36" s="79"/>
-      <c r="O36" s="80"/>
-      <c r="P36" s="80"/>
-      <c r="Q36" s="80"/>
-      <c r="R36" s="80"/>
-      <c r="S36" s="80"/>
-      <c r="T36" s="80"/>
-      <c r="U36" s="81"/>
+      <c r="M36" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="N36" s="72"/>
+      <c r="O36" s="75"/>
+      <c r="P36" s="75"/>
+      <c r="Q36" s="75"/>
+      <c r="R36" s="75"/>
+      <c r="S36" s="75"/>
+      <c r="T36" s="75"/>
+      <c r="U36" s="71"/>
       <c r="V36" s="1"/>
     </row>
     <row r="37" spans="1:22" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="77" t="s">
+      <c r="A37" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="B37" s="78"/>
-      <c r="C37" s="61">
+      <c r="B37" s="69"/>
+      <c r="C37" s="60">
         <v>93.403798109785029</v>
       </c>
-      <c r="D37" s="62">
+      <c r="D37" s="61">
         <v>91.51700700493744</v>
       </c>
-      <c r="E37" s="62">
+      <c r="E37" s="61">
         <v>89.749880462689262</v>
       </c>
-      <c r="F37" s="62">
+      <c r="F37" s="61">
         <v>83.99730958119234</v>
       </c>
-      <c r="G37" s="62">
+      <c r="G37" s="61">
         <v>74.394962965986878</v>
       </c>
-      <c r="H37" s="62">
+      <c r="H37" s="61">
         <v>58.095582470498513</v>
       </c>
-      <c r="I37" s="63">
+      <c r="I37" s="62">
         <v>44.434812706207254</v>
       </c>
       <c r="J37" s="44"/>
@@ -5365,29 +5536,29 @@
         <f t="shared" ref="L37:L39" si="6">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C37:I37)&amp;","</f>
         <v xml:space="preserve">    93.403798109785, 91.5170070049374, 89.7498804626893, 83.9973095811923, 74.3949629659869, 58.0955824704985, 44.4348127062073,</v>
       </c>
-      <c r="M37" s="77" t="s">
+      <c r="M37" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="N37" s="78"/>
-      <c r="O37" s="61">
+      <c r="N37" s="69"/>
+      <c r="O37" s="60">
         <v>3.9553866501853321</v>
       </c>
-      <c r="P37" s="62">
+      <c r="P37" s="61">
         <v>4.517630835861226</v>
       </c>
-      <c r="Q37" s="62">
+      <c r="Q37" s="61">
         <v>5.2125425794506972</v>
       </c>
-      <c r="R37" s="62">
+      <c r="R37" s="61">
         <v>5.6477461387684551</v>
       </c>
-      <c r="S37" s="62">
+      <c r="S37" s="61">
         <v>8.6090564713117175</v>
       </c>
-      <c r="T37" s="62">
+      <c r="T37" s="61">
         <v>11.357157347254571</v>
       </c>
-      <c r="U37" s="63">
+      <c r="U37" s="62">
         <v>9.3757621724255777</v>
       </c>
       <c r="V37" s="1" t="str">
@@ -5396,11 +5567,11 @@
       </c>
     </row>
     <row r="38" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="77" t="s">
+      <c r="A38" s="68" t="s">
         <v>8</v>
       </c>
-      <c r="B38" s="78"/>
-      <c r="C38" s="64">
+      <c r="B38" s="69"/>
+      <c r="C38" s="63">
         <v>92.778947400409621</v>
       </c>
       <c r="D38" s="1">
@@ -5418,7 +5589,7 @@
       <c r="H38" s="1">
         <v>58.300265665116903</v>
       </c>
-      <c r="I38" s="65">
+      <c r="I38" s="64">
         <v>48.584106437626268</v>
       </c>
       <c r="J38" s="44"/>
@@ -5427,11 +5598,11 @@
         <f t="shared" si="6"/>
         <v xml:space="preserve">    92.7789474004096, 91.4503689963737, 89.8794809545421, 84.748756470337, 75.6276087825805, 58.3002656651169, 48.5841064376263,</v>
       </c>
-      <c r="M38" s="77" t="s">
+      <c r="M38" s="68" t="s">
         <v>8</v>
       </c>
-      <c r="N38" s="78"/>
-      <c r="O38" s="64">
+      <c r="N38" s="69"/>
+      <c r="O38" s="63">
         <v>4.3743918396131134</v>
       </c>
       <c r="P38" s="1">
@@ -5449,7 +5620,7 @@
       <c r="T38" s="1">
         <v>11.000258135261941</v>
       </c>
-      <c r="U38" s="65">
+      <c r="U38" s="64">
         <v>9.2918474149187738</v>
       </c>
       <c r="V38" s="1" t="str">
@@ -5458,11 +5629,11 @@
       </c>
     </row>
     <row r="39" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="77" t="s">
-        <v>23</v>
-      </c>
-      <c r="B39" s="78"/>
-      <c r="C39" s="64">
+      <c r="A39" s="68" t="s">
+        <v>21</v>
+      </c>
+      <c r="B39" s="69"/>
+      <c r="C39" s="63">
         <v>92.492055194421354</v>
       </c>
       <c r="D39" s="1">
@@ -5480,7 +5651,7 @@
       <c r="H39" s="1">
         <v>56.229205901331248</v>
       </c>
-      <c r="I39" s="65">
+      <c r="I39" s="64">
         <v>43.695396708102962</v>
       </c>
       <c r="J39" s="44"/>
@@ -5489,11 +5660,11 @@
         <f t="shared" si="6"/>
         <v xml:space="preserve">    92.4920551944214, 91.055738083246, 89.2412648877623, 82.7136018096434, 73.1336770487749, 56.2292059013312, 43.695396708103,</v>
       </c>
-      <c r="M39" s="77" t="s">
-        <v>23</v>
-      </c>
-      <c r="N39" s="78"/>
-      <c r="O39" s="64">
+      <c r="M39" s="68" t="s">
+        <v>21</v>
+      </c>
+      <c r="N39" s="69"/>
+      <c r="O39" s="63">
         <v>4.0986250609792014</v>
       </c>
       <c r="P39" s="1">
@@ -5511,7 +5682,7 @@
       <c r="T39" s="1">
         <v>11.32839542788332</v>
       </c>
-      <c r="U39" s="65">
+      <c r="U39" s="64">
         <v>10.62887090695313</v>
       </c>
       <c r="V39" s="1" t="str">
@@ -5520,113 +5691,113 @@
       </c>
     </row>
     <row r="40" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="77" t="s">
-        <v>24</v>
-      </c>
-      <c r="B40" s="78"/>
-      <c r="C40" s="66">
+      <c r="A40" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="B40" s="69"/>
+      <c r="C40" s="65">
         <v>92.657174075741665</v>
       </c>
-      <c r="D40" s="67">
+      <c r="D40" s="66">
         <v>91.208050814372243</v>
       </c>
-      <c r="E40" s="67">
+      <c r="E40" s="66">
         <v>89.170455678091372</v>
       </c>
-      <c r="F40" s="67">
+      <c r="F40" s="66">
         <v>84.474616062770011</v>
       </c>
-      <c r="G40" s="67">
+      <c r="G40" s="66">
         <v>75.066668593640316</v>
       </c>
-      <c r="H40" s="67">
+      <c r="H40" s="66">
         <v>58.520340993368222</v>
       </c>
-      <c r="I40" s="68">
+      <c r="I40" s="67">
         <v>44.786141592049418</v>
       </c>
-      <c r="J40" s="52"/>
-      <c r="K40" s="52"/>
-      <c r="L40" s="51"/>
-      <c r="M40" s="77" t="s">
-        <v>24</v>
-      </c>
-      <c r="N40" s="78"/>
-      <c r="O40" s="66">
+      <c r="J40" s="51"/>
+      <c r="K40" s="51"/>
+      <c r="L40" s="50"/>
+      <c r="M40" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="N40" s="69"/>
+      <c r="O40" s="65">
         <v>4.2589004392769629</v>
       </c>
-      <c r="P40" s="67">
+      <c r="P40" s="66">
         <v>4.8517186601265534</v>
       </c>
-      <c r="Q40" s="67">
+      <c r="Q40" s="66">
         <v>5.6717673083496472</v>
       </c>
-      <c r="R40" s="67">
+      <c r="R40" s="66">
         <v>5.3079507961921779</v>
       </c>
-      <c r="S40" s="67">
+      <c r="S40" s="66">
         <v>7.7884705615072454</v>
       </c>
-      <c r="T40" s="67">
+      <c r="T40" s="66">
         <v>10.595563377926201</v>
       </c>
-      <c r="U40" s="68">
+      <c r="U40" s="67">
         <v>10.945843294214329</v>
       </c>
       <c r="V40" s="1"/>
     </row>
     <row r="41" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="77" t="s">
-        <v>25</v>
-      </c>
-      <c r="B41" s="79"/>
-      <c r="C41" s="82"/>
-      <c r="D41" s="82"/>
-      <c r="E41" s="82"/>
-      <c r="F41" s="82"/>
-      <c r="G41" s="82"/>
-      <c r="H41" s="82"/>
-      <c r="I41" s="83"/>
+      <c r="A41" s="68" t="s">
+        <v>23</v>
+      </c>
+      <c r="B41" s="72"/>
+      <c r="C41" s="73"/>
+      <c r="D41" s="73"/>
+      <c r="E41" s="73"/>
+      <c r="F41" s="73"/>
+      <c r="G41" s="73"/>
+      <c r="H41" s="73"/>
+      <c r="I41" s="74"/>
       <c r="J41" s="44"/>
       <c r="K41" s="44"/>
       <c r="L41" s="1"/>
-      <c r="M41" s="77" t="s">
-        <v>25</v>
-      </c>
-      <c r="N41" s="79"/>
-      <c r="O41" s="82"/>
-      <c r="P41" s="82"/>
-      <c r="Q41" s="82"/>
-      <c r="R41" s="82"/>
-      <c r="S41" s="82"/>
-      <c r="T41" s="82"/>
-      <c r="U41" s="83"/>
+      <c r="M41" s="68" t="s">
+        <v>23</v>
+      </c>
+      <c r="N41" s="72"/>
+      <c r="O41" s="73"/>
+      <c r="P41" s="73"/>
+      <c r="Q41" s="73"/>
+      <c r="R41" s="73"/>
+      <c r="S41" s="73"/>
+      <c r="T41" s="73"/>
+      <c r="U41" s="74"/>
       <c r="V41" s="1"/>
     </row>
     <row r="42" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="77" t="s">
+      <c r="A42" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="B42" s="78"/>
-      <c r="C42" s="61">
+      <c r="B42" s="69"/>
+      <c r="C42" s="60">
         <v>92.603769819293618</v>
       </c>
-      <c r="D42" s="62">
+      <c r="D42" s="61">
         <v>91.431947068352812</v>
       </c>
-      <c r="E42" s="62">
+      <c r="E42" s="61">
         <v>90.390795042999585</v>
       </c>
-      <c r="F42" s="62">
+      <c r="F42" s="61">
         <v>86.789562828222273</v>
       </c>
-      <c r="G42" s="62">
+      <c r="G42" s="61">
         <v>80.615554033052248</v>
       </c>
-      <c r="H42" s="62">
+      <c r="H42" s="61">
         <v>56.609578553133908</v>
       </c>
-      <c r="I42" s="63">
+      <c r="I42" s="62">
         <v>41.27928062292434</v>
       </c>
       <c r="J42" s="44"/>
@@ -5635,29 +5806,29 @@
         <f t="shared" ref="L42:L44" si="7">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C42:I42)&amp;","</f>
         <v xml:space="preserve">    92.6037698192936, 91.4319470683528, 90.3907950429996, 86.7895628282223, 80.6155540330522, 56.6095785531339, 41.2792806229243,</v>
       </c>
-      <c r="M42" s="77" t="s">
+      <c r="M42" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="N42" s="78"/>
-      <c r="O42" s="61">
+      <c r="N42" s="69"/>
+      <c r="O42" s="60">
         <v>3.708759274801273</v>
       </c>
-      <c r="P42" s="62">
+      <c r="P42" s="61">
         <v>3.9640390541215931</v>
       </c>
-      <c r="Q42" s="62">
+      <c r="Q42" s="61">
         <v>3.7067998106756881</v>
       </c>
-      <c r="R42" s="62">
+      <c r="R42" s="61">
         <v>3.667452632531309</v>
       </c>
-      <c r="S42" s="62">
+      <c r="S42" s="61">
         <v>5.7548227051500218</v>
       </c>
-      <c r="T42" s="62">
+      <c r="T42" s="61">
         <v>8.5366536877555248</v>
       </c>
-      <c r="U42" s="63">
+      <c r="U42" s="62">
         <v>6.3187793027043018</v>
       </c>
       <c r="V42" s="1" t="str">
@@ -5666,11 +5837,11 @@
       </c>
     </row>
     <row r="43" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="84" t="s">
+      <c r="A43" s="70" t="s">
         <v>8</v>
       </c>
-      <c r="B43" s="81"/>
-      <c r="C43" s="64">
+      <c r="B43" s="71"/>
+      <c r="C43" s="63">
         <v>91.377634404932721</v>
       </c>
       <c r="D43" s="1">
@@ -5688,7 +5859,7 @@
       <c r="H43" s="1">
         <v>70.930708745421484</v>
       </c>
-      <c r="I43" s="65">
+      <c r="I43" s="64">
         <v>44.097326232806537</v>
       </c>
       <c r="J43" s="44"/>
@@ -5697,11 +5868,11 @@
         <f t="shared" si="7"/>
         <v xml:space="preserve">    91.3776344049327, 90.4053733332451, 89.3714803083327, 87.6098986263952, 85.5372307015107, 70.9307087454215, 44.0973262328065,</v>
       </c>
-      <c r="M43" s="77" t="s">
+      <c r="M43" s="68" t="s">
         <v>8</v>
       </c>
-      <c r="N43" s="78"/>
-      <c r="O43" s="64">
+      <c r="N43" s="69"/>
+      <c r="O43" s="63">
         <v>3.5684194304484111</v>
       </c>
       <c r="P43" s="1">
@@ -5719,7 +5890,7 @@
       <c r="T43" s="1">
         <v>4.9795199020249923</v>
       </c>
-      <c r="U43" s="65">
+      <c r="U43" s="64">
         <v>2.9223071611371929</v>
       </c>
       <c r="V43" s="1" t="str">
@@ -5728,11 +5899,11 @@
       </c>
     </row>
     <row r="44" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="77" t="s">
-        <v>23</v>
-      </c>
-      <c r="B44" s="78"/>
-      <c r="C44" s="64">
+      <c r="A44" s="68" t="s">
+        <v>21</v>
+      </c>
+      <c r="B44" s="69"/>
+      <c r="C44" s="63">
         <v>92.603715202692385</v>
       </c>
       <c r="D44" s="1">
@@ -5750,7 +5921,7 @@
       <c r="H44" s="1">
         <v>58.188767254712552</v>
       </c>
-      <c r="I44" s="65">
+      <c r="I44" s="64">
         <v>45.468919562576168</v>
       </c>
       <c r="J44" s="44"/>
@@ -5759,11 +5930,11 @@
         <f t="shared" si="7"/>
         <v xml:space="preserve">    92.6037152026924, 91.4849975027203, 90.6301712993249, 85.3420346970645, 78.2086079443082, 58.1887672547126, 45.4689195625762,</v>
       </c>
-      <c r="M44" s="77" t="s">
-        <v>23</v>
-      </c>
-      <c r="N44" s="78"/>
-      <c r="O44" s="64">
+      <c r="M44" s="68" t="s">
+        <v>21</v>
+      </c>
+      <c r="N44" s="69"/>
+      <c r="O44" s="63">
         <v>4.0727132923350373</v>
       </c>
       <c r="P44" s="1">
@@ -5781,7 +5952,7 @@
       <c r="T44" s="1">
         <v>10.3740336621021</v>
       </c>
-      <c r="U44" s="65">
+      <c r="U44" s="64">
         <v>10.707618741543239</v>
       </c>
       <c r="V44" s="1" t="str">
@@ -5790,57 +5961,57 @@
       </c>
     </row>
     <row r="45" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="77" t="s">
-        <v>24</v>
-      </c>
-      <c r="B45" s="78"/>
-      <c r="C45" s="66">
+      <c r="A45" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="B45" s="69"/>
+      <c r="C45" s="65">
         <v>92.692685851985146</v>
       </c>
-      <c r="D45" s="67">
+      <c r="D45" s="66">
         <v>91.028008929063319</v>
       </c>
-      <c r="E45" s="67">
+      <c r="E45" s="66">
         <v>89.101176850288709</v>
       </c>
-      <c r="F45" s="67">
+      <c r="F45" s="66">
         <v>84.121695311135312</v>
       </c>
-      <c r="G45" s="67">
+      <c r="G45" s="66">
         <v>75.514536359946376</v>
       </c>
-      <c r="H45" s="67">
+      <c r="H45" s="66">
         <v>58.551851548300363</v>
       </c>
-      <c r="I45" s="68">
+      <c r="I45" s="67">
         <v>43.528644478603361</v>
       </c>
       <c r="J45" s="44"/>
       <c r="K45" s="44"/>
       <c r="L45" s="1"/>
-      <c r="M45" s="77" t="s">
-        <v>24</v>
-      </c>
-      <c r="N45" s="78"/>
-      <c r="O45" s="66">
+      <c r="M45" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="N45" s="69"/>
+      <c r="O45" s="65">
         <v>4.3508377678439567</v>
       </c>
-      <c r="P45" s="67">
+      <c r="P45" s="66">
         <v>5.1455197984597092</v>
       </c>
-      <c r="Q45" s="67">
+      <c r="Q45" s="66">
         <v>5.0319449257944937</v>
       </c>
-      <c r="R45" s="67">
+      <c r="R45" s="66">
         <v>5.4881092234662896</v>
       </c>
-      <c r="S45" s="67">
+      <c r="S45" s="66">
         <v>8.3963724907401343</v>
       </c>
-      <c r="T45" s="67">
+      <c r="T45" s="66">
         <v>11.26477476806841</v>
       </c>
-      <c r="U45" s="68">
+      <c r="U45" s="67">
         <v>10.478269846537319</v>
       </c>
       <c r="V45" s="1"/>
@@ -5927,16 +6098,36 @@
     </row>
   </sheetData>
   <mergeCells count="56">
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="M44:N44"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="M45:N45"/>
-    <mergeCell ref="A41:I41"/>
-    <mergeCell ref="M41:U41"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="M42:N42"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="M43:N43"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="M25:N25"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="M5:U5"/>
+    <mergeCell ref="M18:U18"/>
+    <mergeCell ref="A13:I13"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="M39:N39"/>
+    <mergeCell ref="M40:N40"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="M37:N37"/>
+    <mergeCell ref="M38:N38"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="M26:N26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="M27:N27"/>
+    <mergeCell ref="A28:I28"/>
+    <mergeCell ref="A16:B16"/>
     <mergeCell ref="A36:I36"/>
     <mergeCell ref="M13:U13"/>
     <mergeCell ref="M36:U36"/>
@@ -5953,40 +6144,30 @@
     <mergeCell ref="M20:N20"/>
     <mergeCell ref="M21:N21"/>
     <mergeCell ref="M22:N22"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="M39:N39"/>
-    <mergeCell ref="M40:N40"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="M37:N37"/>
-    <mergeCell ref="M38:N38"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="M26:N26"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="M27:N27"/>
-    <mergeCell ref="A28:I28"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="M25:N25"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="A5:I5"/>
-    <mergeCell ref="M5:U5"/>
-    <mergeCell ref="M18:U18"/>
-    <mergeCell ref="A13:I13"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="M44:N44"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="M45:N45"/>
+    <mergeCell ref="A41:I41"/>
+    <mergeCell ref="M41:U41"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="M42:N42"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="M43:N43"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="C14:I16 C2:I4 C10:I10 C12:I12">
-    <cfRule type="colorScale" priority="154">
+  <conditionalFormatting sqref="C6:I6">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5997,8 +6178,18 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C14:I16 C2:I4 C12:I12">
-    <cfRule type="colorScale" priority="158">
+  <conditionalFormatting sqref="C7:I7">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6009,8 +6200,18 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C14:I16 C2:I4 C8:I8 C12:I12 C10:I10">
-    <cfRule type="colorScale" priority="151">
+  <conditionalFormatting sqref="C9:I9">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6021,7 +6222,41 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C14:I17 C2:I4 C19:I22 C8:I8 C12:I12 C10:I10">
+  <conditionalFormatting sqref="C11:I11">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C14:I16 C2:I4 C8:I8">
+    <cfRule type="colorScale" priority="159">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C14:I16 C2:I4">
     <cfRule type="colorScale" priority="162">
       <colorScale>
         <cfvo type="min"/>
@@ -6033,8 +6268,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C19:I21">
-    <cfRule type="colorScale" priority="23">
+  <conditionalFormatting sqref="C14:I16 C2:I4">
+    <cfRule type="colorScale" priority="166">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6044,7 +6279,9 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="24">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C14:I17 C2:I4 C19:I22 C8:I8">
+    <cfRule type="colorScale" priority="170">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6054,7 +6291,29 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="25">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C19:I21">
+    <cfRule type="colorScale" priority="31">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="32">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="33">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6066,7 +6325,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J22">
-    <cfRule type="colorScale" priority="10">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6078,7 +6337,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J41:J45">
-    <cfRule type="colorScale" priority="20">
+    <cfRule type="colorScale" priority="28">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6090,7 +6349,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:K22">
-    <cfRule type="colorScale" priority="228">
+    <cfRule type="colorScale" priority="236">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6102,7 +6361,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J5:K5 C3:K4">
-    <cfRule type="colorScale" priority="95">
+    <cfRule type="colorScale" priority="103">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6112,7 +6371,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="96">
+    <cfRule type="colorScale" priority="104">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6122,7 +6381,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="97">
+    <cfRule type="colorScale" priority="105">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6132,7 +6391,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="98">
+    <cfRule type="colorScale" priority="106">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6142,7 +6401,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="99">
+    <cfRule type="colorScale" priority="107">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6152,7 +6411,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="100">
+    <cfRule type="colorScale" priority="108">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6163,8 +6422,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J17:K18 C2:K4 C12:K12 C14:K16 J13:K13 J22:K22 C19:K21 J5:K11">
-    <cfRule type="colorScale" priority="142">
+  <conditionalFormatting sqref="J17:K18 C2:K4 C14:K16 J22:K22 C19:K21 J5:K13">
+    <cfRule type="colorScale" priority="150">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6176,7 +6435,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J41:K45">
-    <cfRule type="colorScale" priority="18">
+    <cfRule type="colorScale" priority="26">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6186,7 +6445,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="21">
+    <cfRule type="colorScale" priority="29">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6198,7 +6457,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K22">
-    <cfRule type="colorScale" priority="9">
+    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6210,7 +6469,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K41:K45">
-    <cfRule type="colorScale" priority="22">
+    <cfRule type="colorScale" priority="30">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6221,7 +6480,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C11:I11">
+  <conditionalFormatting sqref="C10:I10">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -6233,7 +6492,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C11:I11">
+  <conditionalFormatting sqref="C10:I10">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -6245,7 +6504,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C9:I9">
+  <conditionalFormatting sqref="C12:I12">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -6257,7 +6516,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C9:I9">
+  <conditionalFormatting sqref="C12:I12">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -6269,44 +6528,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C7:I7">
-    <cfRule type="colorScale" priority="3">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C7:I7">
+  <conditionalFormatting sqref="C6:I12 C2:I4 C14:I17 C19:I22">
     <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C6:I6">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C6:I6">
-    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>

--- a/results_(stress_test)_summary/summary.xlsx
+++ b/results_(stress_test)_summary/summary.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\RnD_Repo\Research_Engineeirng\feature_fusion_PCCxSigmoid-PLV-\results_(stress_test)_summary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE118874-1CE2-47AC-B526-1CF529D5F8D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3799D395-140B-4C7B-8973-2BD6D0477111}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="639" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="639" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="partialdata_20260429" sheetId="6" r:id="rId1"/>
     <sheet name="fullldata_20260429" sheetId="5" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="7" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -57,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="32">
   <si>
     <t>Accuracy</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -152,6 +153,38 @@
   </si>
   <si>
     <t>PCC &amp; PLI</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PLV &amp; PLI</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PLV * σ(PLI)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PLI * σ(PLV)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PCC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PLV</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PLI</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Basis</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Modifier</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -358,7 +391,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="100">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -523,34 +556,22 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -562,33 +583,57 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -945,10 +990,10 @@
       <c r="V1" s="12"/>
     </row>
     <row r="2" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="76" t="s">
+      <c r="A2" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="77"/>
+      <c r="B2" s="69"/>
       <c r="C2" s="20">
         <v>93.101364775358491</v>
       </c>
@@ -982,10 +1027,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C2:I2)&amp;","</f>
         <v xml:space="preserve">    93.1013647753585, 91.3266637254648, 89.7225610371485, 83.857204647099, 76.2429490451186, 60.4027774173364, 47.7409002961387,</v>
       </c>
-      <c r="M2" s="76" t="s">
+      <c r="M2" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="77"/>
+      <c r="N2" s="69"/>
       <c r="O2" s="31">
         <v>3.4649270444699574</v>
       </c>
@@ -1013,10 +1058,10 @@
       </c>
     </row>
     <row r="3" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="76" t="s">
+      <c r="A3" s="68" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="77"/>
+      <c r="B3" s="69"/>
       <c r="C3" s="31">
         <v>93.273358766079312</v>
       </c>
@@ -1050,10 +1095,10 @@
         <f t="shared" ref="L3:L4" si="0">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C3:I3)&amp;","</f>
         <v xml:space="preserve">    93.2733587660793, 91.6155877934354, 90.6205330495939, 86.5975138193237, 78.2243502683126, 60.8549929786013, 48.7439337710534,</v>
       </c>
-      <c r="M3" s="76" t="s">
+      <c r="M3" s="68" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="77"/>
+      <c r="N3" s="69"/>
       <c r="O3" s="31">
         <v>3.4672469457762647</v>
       </c>
@@ -1081,10 +1126,10 @@
       </c>
     </row>
     <row r="4" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="76" t="s">
+      <c r="A4" s="68" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="77"/>
+      <c r="B4" s="69"/>
       <c r="C4" s="24">
         <v>87.593900000000005</v>
       </c>
@@ -1118,10 +1163,10 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    87.5939, 87.6637168141593, 88.1120943952802, 87.9700256922638, 87.4617081462642, 75.2513631894163, 47.7206838582802,</v>
       </c>
-      <c r="M4" s="76" t="s">
+      <c r="M4" s="68" t="s">
         <v>10</v>
       </c>
-      <c r="N4" s="77"/>
+      <c r="N4" s="69"/>
       <c r="O4" s="49">
         <v>2.4529187882918819</v>
       </c>
@@ -1149,31 +1194,31 @@
       </c>
     </row>
     <row r="5" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="76" t="s">
+      <c r="A5" s="68" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="77"/>
+      <c r="B5" s="74"/>
+      <c r="C5" s="74"/>
+      <c r="D5" s="74"/>
+      <c r="E5" s="74"/>
+      <c r="F5" s="74"/>
+      <c r="G5" s="74"/>
+      <c r="H5" s="74"/>
+      <c r="I5" s="69"/>
       <c r="J5" s="35"/>
       <c r="K5" s="35"/>
       <c r="L5" s="12"/>
-      <c r="M5" s="76" t="s">
+      <c r="M5" s="68" t="s">
         <v>12</v>
       </c>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="78"/>
-      <c r="R5" s="78"/>
-      <c r="S5" s="78"/>
-      <c r="T5" s="78"/>
-      <c r="U5" s="77"/>
+      <c r="N5" s="74"/>
+      <c r="O5" s="74"/>
+      <c r="P5" s="74"/>
+      <c r="Q5" s="74"/>
+      <c r="R5" s="74"/>
+      <c r="S5" s="74"/>
+      <c r="T5" s="74"/>
+      <c r="U5" s="69"/>
       <c r="V5" s="12"/>
     </row>
     <row r="6" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -1321,38 +1366,38 @@
       </c>
     </row>
     <row r="8" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="76" t="s">
+      <c r="A8" s="68" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="78"/>
-      <c r="C8" s="83"/>
-      <c r="D8" s="83"/>
-      <c r="E8" s="83"/>
-      <c r="F8" s="83"/>
-      <c r="G8" s="83"/>
-      <c r="H8" s="83"/>
-      <c r="I8" s="82"/>
+      <c r="B8" s="74"/>
+      <c r="C8" s="77"/>
+      <c r="D8" s="77"/>
+      <c r="E8" s="77"/>
+      <c r="F8" s="77"/>
+      <c r="G8" s="77"/>
+      <c r="H8" s="77"/>
+      <c r="I8" s="73"/>
       <c r="J8" s="35"/>
       <c r="K8" s="35"/>
       <c r="L8" s="12"/>
-      <c r="M8" s="76" t="s">
+      <c r="M8" s="68" t="s">
         <v>20</v>
       </c>
-      <c r="N8" s="78"/>
-      <c r="O8" s="83"/>
-      <c r="P8" s="83"/>
-      <c r="Q8" s="83"/>
-      <c r="R8" s="83"/>
-      <c r="S8" s="83"/>
-      <c r="T8" s="83"/>
-      <c r="U8" s="82"/>
+      <c r="N8" s="74"/>
+      <c r="O8" s="77"/>
+      <c r="P8" s="77"/>
+      <c r="Q8" s="77"/>
+      <c r="R8" s="77"/>
+      <c r="S8" s="77"/>
+      <c r="T8" s="77"/>
+      <c r="U8" s="73"/>
       <c r="V8" s="12"/>
     </row>
     <row r="9" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="76" t="s">
+      <c r="A9" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="77"/>
+      <c r="B9" s="69"/>
       <c r="C9" s="31">
         <v>93.782740335124032</v>
       </c>
@@ -1386,10 +1431,10 @@
         <f t="shared" ref="L9:L12" si="4">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C9:I9)&amp;","</f>
         <v xml:space="preserve">    93.782740335124, 91.9482088945406, 90.212980504445, 84.6303889595354, 75.3710931755465, 59.6272113080563, 47.8441855033348,</v>
       </c>
-      <c r="M9" s="76" t="s">
+      <c r="M9" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="N9" s="77"/>
+      <c r="N9" s="69"/>
       <c r="O9" s="31">
         <v>3.5391983918820551</v>
       </c>
@@ -1417,10 +1462,10 @@
       </c>
     </row>
     <row r="10" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="81" t="s">
+      <c r="A10" s="72" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="82"/>
+      <c r="B10" s="73"/>
       <c r="C10" s="34">
         <v>93.226230330712227</v>
       </c>
@@ -1454,10 +1499,10 @@
         <f t="shared" si="4"/>
         <v xml:space="preserve">    93.2262303307122, 91.8332915221297, 90.3252911645718, 85.3834923600839, 76.5670002912366, 59.4145422249904, 50.5634074112521,</v>
       </c>
-      <c r="M10" s="76" t="s">
+      <c r="M10" s="68" t="s">
         <v>8</v>
       </c>
-      <c r="N10" s="77"/>
+      <c r="N10" s="69"/>
       <c r="O10" s="34">
         <v>3.945711842949601</v>
       </c>
@@ -1485,10 +1530,10 @@
       </c>
     </row>
     <row r="11" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="76" t="s">
+      <c r="A11" s="68" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="77"/>
+      <c r="B11" s="69"/>
       <c r="C11" s="34">
         <v>93.004922187908207</v>
       </c>
@@ -1522,10 +1567,10 @@
         <f t="shared" si="4"/>
         <v xml:space="preserve">    93.0049221879082, 91.5185021785079, 89.7294209580821, 83.3486073985646, 74.0877199053048, 57.9173320415113, 48.0077941850708,</v>
       </c>
-      <c r="M11" s="76" t="s">
+      <c r="M11" s="68" t="s">
         <v>21</v>
       </c>
-      <c r="N11" s="77"/>
+      <c r="N11" s="69"/>
       <c r="O11" s="34">
         <v>3.690401528555848</v>
       </c>
@@ -1553,10 +1598,10 @@
       </c>
     </row>
     <row r="12" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="76" t="s">
+      <c r="A12" s="68" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="77"/>
+      <c r="B12" s="69"/>
       <c r="C12" s="37">
         <v>93.123279613145442</v>
       </c>
@@ -1590,10 +1635,10 @@
         <f t="shared" si="4"/>
         <v xml:space="preserve">    93.1232796131454, 91.674385879924, 89.6986882816172, 84.9570671026566, 75.9390825180149, 59.9950922297482, 48.4403036935152,</v>
       </c>
-      <c r="M12" s="76" t="s">
+      <c r="M12" s="68" t="s">
         <v>22</v>
       </c>
-      <c r="N12" s="77"/>
+      <c r="N12" s="69"/>
       <c r="O12" s="37">
         <v>3.8088682011350912</v>
       </c>
@@ -1621,38 +1666,38 @@
       </c>
     </row>
     <row r="13" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="76" t="s">
+      <c r="A13" s="68" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="78"/>
-      <c r="C13" s="79"/>
-      <c r="D13" s="79"/>
-      <c r="E13" s="79"/>
-      <c r="F13" s="79"/>
-      <c r="G13" s="79"/>
-      <c r="H13" s="79"/>
-      <c r="I13" s="80"/>
+      <c r="B13" s="74"/>
+      <c r="C13" s="75"/>
+      <c r="D13" s="75"/>
+      <c r="E13" s="75"/>
+      <c r="F13" s="75"/>
+      <c r="G13" s="75"/>
+      <c r="H13" s="75"/>
+      <c r="I13" s="76"/>
       <c r="J13" s="35"/>
       <c r="K13" s="35"/>
       <c r="L13" s="12"/>
-      <c r="M13" s="76" t="s">
+      <c r="M13" s="68" t="s">
         <v>23</v>
       </c>
-      <c r="N13" s="78"/>
-      <c r="O13" s="79"/>
-      <c r="P13" s="79"/>
-      <c r="Q13" s="79"/>
-      <c r="R13" s="79"/>
-      <c r="S13" s="79"/>
-      <c r="T13" s="79"/>
-      <c r="U13" s="80"/>
+      <c r="N13" s="74"/>
+      <c r="O13" s="75"/>
+      <c r="P13" s="75"/>
+      <c r="Q13" s="75"/>
+      <c r="R13" s="75"/>
+      <c r="S13" s="75"/>
+      <c r="T13" s="75"/>
+      <c r="U13" s="76"/>
       <c r="V13" s="12"/>
     </row>
     <row r="14" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="76" t="s">
+      <c r="A14" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="77"/>
+      <c r="B14" s="69"/>
       <c r="C14" s="31">
         <v>92.969518190757128</v>
       </c>
@@ -1686,10 +1731,10 @@
         <f t="shared" ref="L14:L17" si="6">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C14:I14)&amp;","</f>
         <v xml:space="preserve">    92.9695181907571, 91.8515240904621, 90.756145526057, 87.2531365611583, 81.1789721364371, 57.3869295293788, 44.8554428094822,</v>
       </c>
-      <c r="M14" s="76" t="s">
+      <c r="M14" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="N14" s="77"/>
+      <c r="N14" s="69"/>
       <c r="O14" s="31">
         <v>3.3991921823554931</v>
       </c>
@@ -1717,10 +1762,10 @@
       </c>
     </row>
     <row r="15" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="81" t="s">
+      <c r="A15" s="72" t="s">
         <v>8</v>
       </c>
-      <c r="B15" s="82"/>
+      <c r="B15" s="73"/>
       <c r="C15" s="34">
         <v>91.898721730580135</v>
       </c>
@@ -1754,10 +1799,10 @@
         <f t="shared" si="6"/>
         <v xml:space="preserve">    91.8987217305801, 90.765995668936, 89.7052685000158, 87.9596853490659, 85.7500007208828, 71.3873880108536, 45.5963431056209,</v>
       </c>
-      <c r="M15" s="76" t="s">
+      <c r="M15" s="68" t="s">
         <v>8</v>
       </c>
-      <c r="N15" s="77"/>
+      <c r="N15" s="69"/>
       <c r="O15" s="34">
         <v>3.190312271555559</v>
       </c>
@@ -1785,10 +1830,10 @@
       </c>
     </row>
     <row r="16" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="76" t="s">
+      <c r="A16" s="68" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="77"/>
+      <c r="B16" s="69"/>
       <c r="C16" s="34">
         <v>93.044276622923505</v>
       </c>
@@ -1822,10 +1867,10 @@
         <f t="shared" si="6"/>
         <v xml:space="preserve">    93.0442766229235, 91.9351551484009, 90.9488922914558, 85.9525053561594, 78.9151838107019, 59.4421001335075, 49.5338281473023,</v>
       </c>
-      <c r="M16" s="76" t="s">
+      <c r="M16" s="68" t="s">
         <v>21</v>
       </c>
-      <c r="N16" s="77"/>
+      <c r="N16" s="69"/>
       <c r="O16" s="34">
         <v>3.72078192123604</v>
       </c>
@@ -1853,10 +1898,10 @@
       </c>
     </row>
     <row r="17" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="76" t="s">
+      <c r="A17" s="68" t="s">
         <v>22</v>
       </c>
-      <c r="B17" s="77"/>
+      <c r="B17" s="69"/>
       <c r="C17" s="37">
         <v>93.174110502686005</v>
       </c>
@@ -1890,10 +1935,10 @@
         <f t="shared" si="6"/>
         <v xml:space="preserve">    93.174110502686, 91.3917248419104, 89.5915391424955, 84.6905970928238, 76.4013471858177, 59.9636675057743, 47.7255772108755,</v>
       </c>
-      <c r="M17" s="76" t="s">
+      <c r="M17" s="68" t="s">
         <v>22</v>
       </c>
-      <c r="N17" s="77"/>
+      <c r="N17" s="69"/>
       <c r="O17" s="37">
         <v>3.8766021792735019</v>
       </c>
@@ -2003,10 +2048,10 @@
       <c r="V19" s="1"/>
     </row>
     <row r="20" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="68" t="s">
+      <c r="A20" s="70" t="s">
         <v>5</v>
       </c>
-      <c r="B20" s="69"/>
+      <c r="B20" s="71"/>
       <c r="C20" s="41">
         <v>92.567111769713335</v>
       </c>
@@ -2034,10 +2079,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C20:I20)&amp;","</f>
         <v xml:space="preserve">    92.5671117697133, 90.8358586083436, 89.2175053395332, 83.2372459642881, 75.380430844191, 58.9943671875974, 43.6225356413822,</v>
       </c>
-      <c r="M20" s="68" t="s">
+      <c r="M20" s="70" t="s">
         <v>5</v>
       </c>
-      <c r="N20" s="69"/>
+      <c r="N20" s="71"/>
       <c r="O20" s="40">
         <v>3.88093621561358</v>
       </c>
@@ -2065,10 +2110,10 @@
       </c>
     </row>
     <row r="21" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="68" t="s">
+      <c r="A21" s="70" t="s">
         <v>6</v>
       </c>
-      <c r="B21" s="69"/>
+      <c r="B21" s="71"/>
       <c r="C21" s="41">
         <v>92.866950218042462</v>
       </c>
@@ -2096,10 +2141,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C21:I21)&amp;","</f>
         <v xml:space="preserve">    92.8669502180425, 91.2426907647456, 90.1370532276984, 86.0801529266134, 77.4102172551968, 59.6761947649801, 46.3954904194042,</v>
       </c>
-      <c r="M21" s="68" t="s">
+      <c r="M21" s="70" t="s">
         <v>6</v>
       </c>
-      <c r="N21" s="69"/>
+      <c r="N21" s="71"/>
       <c r="O21" s="41">
         <v>3.8319643020864191</v>
       </c>
@@ -2127,10 +2172,10 @@
       </c>
     </row>
     <row r="22" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="68" t="s">
+      <c r="A22" s="70" t="s">
         <v>10</v>
       </c>
-      <c r="B22" s="69"/>
+      <c r="B22" s="71"/>
       <c r="C22" s="28">
         <v>87.268396410214976</v>
       </c>
@@ -2158,10 +2203,10 @@
         <f t="shared" ref="L22:L25" si="9">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C22:I22)&amp;","</f>
         <v xml:space="preserve">    87.268396410215, 87.2564283986868, 87.8221063041704, 87.6807264423516, 87.1448793671852, 74.9765678865158, 46.4175473948824,</v>
       </c>
-      <c r="M22" s="68" t="s">
+      <c r="M22" s="70" t="s">
         <v>10</v>
       </c>
-      <c r="N22" s="69"/>
+      <c r="N22" s="71"/>
       <c r="O22" s="28">
         <v>2.610595868561878</v>
       </c>
@@ -2189,31 +2234,31 @@
       </c>
     </row>
     <row r="23" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="68" t="s">
+      <c r="A23" s="70" t="s">
         <v>12</v>
       </c>
-      <c r="B23" s="72"/>
-      <c r="C23" s="72"/>
-      <c r="D23" s="72"/>
-      <c r="E23" s="72"/>
-      <c r="F23" s="72"/>
-      <c r="G23" s="72"/>
-      <c r="H23" s="72"/>
-      <c r="I23" s="69"/>
+      <c r="B23" s="78"/>
+      <c r="C23" s="78"/>
+      <c r="D23" s="78"/>
+      <c r="E23" s="78"/>
+      <c r="F23" s="78"/>
+      <c r="G23" s="78"/>
+      <c r="H23" s="78"/>
+      <c r="I23" s="71"/>
       <c r="J23" s="44"/>
       <c r="K23" s="44"/>
       <c r="L23" s="1"/>
-      <c r="M23" s="68" t="s">
+      <c r="M23" s="70" t="s">
         <v>12</v>
       </c>
-      <c r="N23" s="72"/>
-      <c r="O23" s="72"/>
-      <c r="P23" s="72"/>
-      <c r="Q23" s="72"/>
-      <c r="R23" s="72"/>
-      <c r="S23" s="72"/>
-      <c r="T23" s="72"/>
-      <c r="U23" s="69"/>
+      <c r="N23" s="78"/>
+      <c r="O23" s="78"/>
+      <c r="P23" s="78"/>
+      <c r="Q23" s="78"/>
+      <c r="R23" s="78"/>
+      <c r="S23" s="78"/>
+      <c r="T23" s="78"/>
+      <c r="U23" s="71"/>
       <c r="V23" s="1"/>
     </row>
     <row r="24" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
@@ -2349,38 +2394,38 @@
       </c>
     </row>
     <row r="26" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="68" t="s">
+      <c r="A26" s="70" t="s">
         <v>20</v>
       </c>
-      <c r="B26" s="72"/>
-      <c r="C26" s="75"/>
-      <c r="D26" s="75"/>
-      <c r="E26" s="75"/>
-      <c r="F26" s="75"/>
-      <c r="G26" s="75"/>
-      <c r="H26" s="75"/>
-      <c r="I26" s="71"/>
+      <c r="B26" s="78"/>
+      <c r="C26" s="79"/>
+      <c r="D26" s="79"/>
+      <c r="E26" s="79"/>
+      <c r="F26" s="79"/>
+      <c r="G26" s="79"/>
+      <c r="H26" s="79"/>
+      <c r="I26" s="80"/>
       <c r="J26" s="44"/>
       <c r="K26" s="44"/>
       <c r="L26" s="1"/>
-      <c r="M26" s="68" t="s">
+      <c r="M26" s="70" t="s">
         <v>20</v>
       </c>
-      <c r="N26" s="72"/>
-      <c r="O26" s="75"/>
-      <c r="P26" s="75"/>
-      <c r="Q26" s="75"/>
-      <c r="R26" s="75"/>
-      <c r="S26" s="75"/>
-      <c r="T26" s="75"/>
-      <c r="U26" s="71"/>
+      <c r="N26" s="78"/>
+      <c r="O26" s="79"/>
+      <c r="P26" s="79"/>
+      <c r="Q26" s="79"/>
+      <c r="R26" s="79"/>
+      <c r="S26" s="79"/>
+      <c r="T26" s="79"/>
+      <c r="U26" s="80"/>
       <c r="V26" s="1"/>
     </row>
     <row r="27" spans="1:22" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="68" t="s">
+      <c r="A27" s="70" t="s">
         <v>7</v>
       </c>
-      <c r="B27" s="69"/>
+      <c r="B27" s="71"/>
       <c r="C27" s="40">
         <v>93.403798109785029</v>
       </c>
@@ -2408,10 +2453,10 @@
         <f t="shared" ref="L27:L30" si="10">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C27:I27)&amp;","</f>
         <v xml:space="preserve">    93.403798109785, 91.5170070049374, 89.7498804626893, 83.9973095811923, 74.3949629659869, 58.0955824704985, 44.4348127062073,</v>
       </c>
-      <c r="M27" s="68" t="s">
+      <c r="M27" s="70" t="s">
         <v>7</v>
       </c>
-      <c r="N27" s="69"/>
+      <c r="N27" s="71"/>
       <c r="O27" s="40">
         <v>3.9553866501853321</v>
       </c>
@@ -2439,10 +2484,10 @@
       </c>
     </row>
     <row r="28" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="68" t="s">
+      <c r="A28" s="70" t="s">
         <v>8</v>
       </c>
-      <c r="B28" s="69"/>
+      <c r="B28" s="71"/>
       <c r="C28" s="43">
         <v>92.778947400409621</v>
       </c>
@@ -2470,10 +2515,10 @@
         <f t="shared" si="10"/>
         <v xml:space="preserve">    92.7789474004096, 91.4503689963737, 89.8794809545421, 84.748756470337, 75.6276087825805, 58.3002656651169, 48.5841064376263,</v>
       </c>
-      <c r="M28" s="68" t="s">
+      <c r="M28" s="70" t="s">
         <v>8</v>
       </c>
-      <c r="N28" s="69"/>
+      <c r="N28" s="71"/>
       <c r="O28" s="43">
         <v>4.3743918396131134</v>
       </c>
@@ -2501,10 +2546,10 @@
       </c>
     </row>
     <row r="29" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="68" t="s">
+      <c r="A29" s="70" t="s">
         <v>21</v>
       </c>
-      <c r="B29" s="69"/>
+      <c r="B29" s="71"/>
       <c r="C29" s="43">
         <v>92.492055194421354</v>
       </c>
@@ -2532,10 +2577,10 @@
         <f t="shared" si="10"/>
         <v xml:space="preserve">    92.4920551944214, 91.055738083246, 89.2412648877623, 82.7136018096434, 73.1336770487749, 56.2292059013312, 43.695396708103,</v>
       </c>
-      <c r="M29" s="68" t="s">
+      <c r="M29" s="70" t="s">
         <v>21</v>
       </c>
-      <c r="N29" s="69"/>
+      <c r="N29" s="71"/>
       <c r="O29" s="43">
         <v>4.0986250609792014</v>
       </c>
@@ -2563,10 +2608,10 @@
       </c>
     </row>
     <row r="30" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="68" t="s">
+      <c r="A30" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="B30" s="69"/>
+      <c r="B30" s="71"/>
       <c r="C30" s="46">
         <v>92.657174075741665</v>
       </c>
@@ -2594,10 +2639,10 @@
         <f t="shared" si="10"/>
         <v xml:space="preserve">    92.6571740757417, 91.2080508143722, 89.1704556780914, 84.47461606277, 75.0666685936403, 58.5203409933682, 44.7861415920494,</v>
       </c>
-      <c r="M30" s="68" t="s">
+      <c r="M30" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="N30" s="69"/>
+      <c r="N30" s="71"/>
       <c r="O30" s="46">
         <v>4.2589004392769629</v>
       </c>
@@ -2625,38 +2670,38 @@
       </c>
     </row>
     <row r="31" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="68" t="s">
+      <c r="A31" s="70" t="s">
         <v>23</v>
       </c>
-      <c r="B31" s="72"/>
-      <c r="C31" s="73"/>
-      <c r="D31" s="73"/>
-      <c r="E31" s="73"/>
-      <c r="F31" s="73"/>
-      <c r="G31" s="73"/>
-      <c r="H31" s="73"/>
-      <c r="I31" s="74"/>
+      <c r="B31" s="78"/>
+      <c r="C31" s="81"/>
+      <c r="D31" s="81"/>
+      <c r="E31" s="81"/>
+      <c r="F31" s="81"/>
+      <c r="G31" s="81"/>
+      <c r="H31" s="81"/>
+      <c r="I31" s="82"/>
       <c r="J31" s="44"/>
       <c r="K31" s="44"/>
       <c r="L31" s="1"/>
-      <c r="M31" s="68" t="s">
+      <c r="M31" s="70" t="s">
         <v>23</v>
       </c>
-      <c r="N31" s="72"/>
-      <c r="O31" s="73"/>
-      <c r="P31" s="73"/>
-      <c r="Q31" s="73"/>
-      <c r="R31" s="73"/>
-      <c r="S31" s="73"/>
-      <c r="T31" s="73"/>
-      <c r="U31" s="74"/>
+      <c r="N31" s="78"/>
+      <c r="O31" s="81"/>
+      <c r="P31" s="81"/>
+      <c r="Q31" s="81"/>
+      <c r="R31" s="81"/>
+      <c r="S31" s="81"/>
+      <c r="T31" s="81"/>
+      <c r="U31" s="82"/>
       <c r="V31" s="1"/>
     </row>
     <row r="32" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="68" t="s">
+      <c r="A32" s="70" t="s">
         <v>7</v>
       </c>
-      <c r="B32" s="69"/>
+      <c r="B32" s="71"/>
       <c r="C32" s="40">
         <v>92.603769819293618</v>
       </c>
@@ -2684,10 +2729,10 @@
         <f t="shared" ref="L32:L35" si="11">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C32:I32)&amp;","</f>
         <v xml:space="preserve">    92.6037698192936, 91.4319470683528, 90.3907950429996, 86.7895628282223, 80.6155540330522, 56.6095785531339, 41.2792806229243,</v>
       </c>
-      <c r="M32" s="68" t="s">
+      <c r="M32" s="70" t="s">
         <v>7</v>
       </c>
-      <c r="N32" s="69"/>
+      <c r="N32" s="71"/>
       <c r="O32" s="40">
         <v>3.708759274801273</v>
       </c>
@@ -2715,10 +2760,10 @@
       </c>
     </row>
     <row r="33" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="70" t="s">
+      <c r="A33" s="83" t="s">
         <v>8</v>
       </c>
-      <c r="B33" s="71"/>
+      <c r="B33" s="80"/>
       <c r="C33" s="43">
         <v>91.377634404932721</v>
       </c>
@@ -2746,10 +2791,10 @@
         <f t="shared" si="11"/>
         <v xml:space="preserve">    91.3776344049327, 90.4053733332451, 89.3714803083327, 87.6098986263952, 85.5372307015107, 70.9307087454215, 44.0973262328065,</v>
       </c>
-      <c r="M33" s="68" t="s">
+      <c r="M33" s="70" t="s">
         <v>8</v>
       </c>
-      <c r="N33" s="69"/>
+      <c r="N33" s="71"/>
       <c r="O33" s="43">
         <v>3.5684194304484111</v>
       </c>
@@ -2777,10 +2822,10 @@
       </c>
     </row>
     <row r="34" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="68" t="s">
+      <c r="A34" s="70" t="s">
         <v>21</v>
       </c>
-      <c r="B34" s="69"/>
+      <c r="B34" s="71"/>
       <c r="C34" s="43">
         <v>92.603715202692385</v>
       </c>
@@ -2808,10 +2853,10 @@
         <f t="shared" si="11"/>
         <v xml:space="preserve">    92.6037152026924, 91.4849975027203, 90.6301712993249, 85.3420346970645, 78.2086079443082, 58.1887672547126, 45.4689195625762,</v>
       </c>
-      <c r="M34" s="68" t="s">
+      <c r="M34" s="70" t="s">
         <v>21</v>
       </c>
-      <c r="N34" s="69"/>
+      <c r="N34" s="71"/>
       <c r="O34" s="43">
         <v>4.0727132923350373</v>
       </c>
@@ -2839,10 +2884,10 @@
       </c>
     </row>
     <row r="35" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="68" t="s">
+      <c r="A35" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="B35" s="69"/>
+      <c r="B35" s="71"/>
       <c r="C35" s="46">
         <v>92.692685851985146</v>
       </c>
@@ -2870,10 +2915,10 @@
         <f t="shared" si="11"/>
         <v xml:space="preserve">    92.6926858519851, 91.0280089290633, 89.1011768502887, 84.1216953111353, 75.5145363599464, 58.5518515483004, 43.5286444786034,</v>
       </c>
-      <c r="M35" s="68" t="s">
+      <c r="M35" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="N35" s="69"/>
+      <c r="N35" s="71"/>
       <c r="O35" s="46">
         <v>4.3508377678439567</v>
       </c>
@@ -2982,54 +3027,6 @@
     </row>
   </sheetData>
   <mergeCells count="56">
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="A5:I5"/>
-    <mergeCell ref="M5:U5"/>
-    <mergeCell ref="A8:I8"/>
-    <mergeCell ref="M8:U8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="M9:N9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="A13:I13"/>
-    <mergeCell ref="M13:U13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="M22:N22"/>
-    <mergeCell ref="A23:I23"/>
-    <mergeCell ref="M23:U23"/>
-    <mergeCell ref="A26:I26"/>
-    <mergeCell ref="M26:U26"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="M27:N27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="M29:N29"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="M30:N30"/>
-    <mergeCell ref="A31:I31"/>
-    <mergeCell ref="M31:U31"/>
     <mergeCell ref="A35:B35"/>
     <mergeCell ref="M35:N35"/>
     <mergeCell ref="A32:B32"/>
@@ -3038,6 +3035,54 @@
     <mergeCell ref="M33:N33"/>
     <mergeCell ref="A34:B34"/>
     <mergeCell ref="M34:N34"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="M29:N29"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="M30:N30"/>
+    <mergeCell ref="A31:I31"/>
+    <mergeCell ref="M31:U31"/>
+    <mergeCell ref="A26:I26"/>
+    <mergeCell ref="M26:U26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="M27:N27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="A23:I23"/>
+    <mergeCell ref="M23:U23"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="A13:I13"/>
+    <mergeCell ref="M13:U13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="M5:U5"/>
+    <mergeCell ref="A8:I8"/>
+    <mergeCell ref="M8:U8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="M9:N9"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="M4:N4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C2:I4">
@@ -3367,7 +3412,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61C29D5C-8639-4163-9432-7C70C26E1499}">
-  <dimension ref="A1:V51"/>
+  <dimension ref="A1:V60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="25" style="10" customWidth="1"/>
@@ -3443,10 +3488,10 @@
       <c r="V1" s="12"/>
     </row>
     <row r="2" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="76" t="s">
+      <c r="A2" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="77"/>
+      <c r="B2" s="69"/>
       <c r="C2" s="20">
         <v>93.101364775358491</v>
       </c>
@@ -3480,10 +3525,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C2:I2)&amp;","</f>
         <v xml:space="preserve">    93.1013647753585, 91.3266637254648, 89.7225610371485, 83.857204647099, 76.2429490451186, 60.4027774173364, 47.7409002961387,</v>
       </c>
-      <c r="M2" s="76" t="s">
+      <c r="M2" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="77"/>
+      <c r="N2" s="69"/>
       <c r="O2" s="31">
         <v>3.4649270444699574</v>
       </c>
@@ -3511,10 +3556,10 @@
       </c>
     </row>
     <row r="3" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="76" t="s">
+      <c r="A3" s="68" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="77"/>
+      <c r="B3" s="69"/>
       <c r="C3" s="31">
         <v>93.273358766079312</v>
       </c>
@@ -3545,13 +3590,13 @@
         <v>81.54747164767862</v>
       </c>
       <c r="L3" s="12" t="str">
-        <f t="shared" ref="L3:L16" si="0">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C3:I3)&amp;","</f>
+        <f t="shared" ref="L3:L18" si="0">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C3:I3)&amp;","</f>
         <v xml:space="preserve">    93.2733587660793, 91.6155877934354, 90.6205330495939, 86.5975138193237, 78.2243502683126, 60.8549929786013, 48.7439337710534,</v>
       </c>
-      <c r="M3" s="76" t="s">
+      <c r="M3" s="68" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="77"/>
+      <c r="N3" s="69"/>
       <c r="O3" s="31">
         <v>3.4672469457762647</v>
       </c>
@@ -3574,15 +3619,15 @@
         <v>9.1853207799272329</v>
       </c>
       <c r="V3" s="12" t="str">
-        <f t="shared" ref="V3:V16" si="1">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,O3:U3)&amp;","</f>
+        <f t="shared" ref="V3:V18" si="1">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,O3:U3)&amp;","</f>
         <v xml:space="preserve">    3.46724694577626, 4.10663738581389, 4.44334428313897, 4.85726616902442, 6.73340650119937, 9.30559121407586, 9.18532077992723,</v>
       </c>
     </row>
     <row r="4" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="76" t="s">
+      <c r="A4" s="68" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="77"/>
+      <c r="B4" s="69"/>
       <c r="C4" s="24">
         <v>87.593900000000005</v>
       </c>
@@ -3616,10 +3661,10 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    87.5939, 87.6637168141593, 88.1120943952802, 87.9700256922638, 87.4617081462642, 75.2513631894163, 47.7206838582802,</v>
       </c>
-      <c r="M4" s="76" t="s">
+      <c r="M4" s="68" t="s">
         <v>10</v>
       </c>
-      <c r="N4" s="77"/>
+      <c r="N4" s="69"/>
       <c r="O4" s="49">
         <v>2.4529187882918819</v>
       </c>
@@ -3647,35 +3692,35 @@
       </c>
     </row>
     <row r="5" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="76" t="s">
+      <c r="A5" s="68" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="77"/>
+      <c r="B5" s="74"/>
+      <c r="C5" s="74"/>
+      <c r="D5" s="74"/>
+      <c r="E5" s="74"/>
+      <c r="F5" s="74"/>
+      <c r="G5" s="74"/>
+      <c r="H5" s="74"/>
+      <c r="I5" s="69"/>
       <c r="J5" s="35"/>
       <c r="K5" s="35"/>
       <c r="L5" s="12"/>
-      <c r="M5" s="76" t="s">
+      <c r="M5" s="68" t="s">
         <v>12</v>
       </c>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="78"/>
-      <c r="R5" s="78"/>
-      <c r="S5" s="78"/>
-      <c r="T5" s="78"/>
-      <c r="U5" s="77"/>
+      <c r="N5" s="74"/>
+      <c r="O5" s="74"/>
+      <c r="P5" s="74"/>
+      <c r="Q5" s="74"/>
+      <c r="R5" s="74"/>
+      <c r="S5" s="74"/>
+      <c r="T5" s="74"/>
+      <c r="U5" s="69"/>
       <c r="V5" s="12"/>
     </row>
     <row r="6" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="72" t="s">
         <v>11</v>
       </c>
       <c r="B6" s="8" t="s">
@@ -3714,7 +3759,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    93.4021632251721, 91.8271265322364, 90.5586899540653, 86.0233767881498, 80.0763011214053, 61.7128781390843, 46.4235100072953,</v>
       </c>
-      <c r="M6" s="93" t="s">
+      <c r="M6" s="72" t="s">
         <v>11</v>
       </c>
       <c r="N6" s="8" t="s">
@@ -3747,9 +3792,7 @@
       </c>
     </row>
     <row r="7" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>11</v>
-      </c>
+      <c r="A7" s="84"/>
       <c r="B7" s="8" t="s">
         <v>14</v>
       </c>
@@ -3786,9 +3829,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    92.6912487708948, 92.7069813176008, 91.7345132743363, 88.8675536408908, 87.5647050003316, 75.6237856728864, 48.8313393714478,</v>
       </c>
-      <c r="M7" s="93" t="s">
-        <v>11</v>
-      </c>
+      <c r="M7" s="84"/>
       <c r="N7" s="8" t="s">
         <v>14</v>
       </c>
@@ -3819,31 +3860,29 @@
       </c>
     </row>
     <row r="8" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
-        <v>11</v>
-      </c>
+      <c r="A8" s="84"/>
       <c r="B8" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="84">
+      <c r="C8" s="57">
         <v>93.359910841212596</v>
       </c>
-      <c r="D8" s="85">
+      <c r="D8" s="58">
         <v>93.004951023221068</v>
       </c>
-      <c r="E8" s="85">
+      <c r="E8" s="58">
         <v>91.679628139805132</v>
       </c>
-      <c r="F8" s="85">
+      <c r="F8" s="58">
         <v>85.408749210633317</v>
       </c>
-      <c r="G8" s="85">
+      <c r="G8" s="58">
         <v>76.226619607436049</v>
       </c>
-      <c r="H8" s="85">
+      <c r="H8" s="58">
         <v>61.249065014979941</v>
       </c>
-      <c r="I8" s="86">
+      <c r="I8" s="59">
         <v>49.631651946239451</v>
       </c>
       <c r="J8" s="35" cm="1">
@@ -3854,40 +3893,39 @@
         <f t="array" ref="K8">-SUMPRODUCT((D1:I1-C1:H1)*(C8:H8+D8:I8)/2)</f>
         <v>81.817588459531066</v>
       </c>
-      <c r="L8" s="12"/>
-      <c r="M8" s="93" t="s">
-        <v>11</v>
-      </c>
+      <c r="L8" s="12" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    93.3599108412126, 93.0049510232211, 91.6796281398051, 85.4087492106333, 76.226619607436, 61.2490650149799, 49.6316519462395,</v>
+      </c>
+      <c r="M8" s="84"/>
       <c r="N8" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="O8" s="87">
+      <c r="O8" s="57">
         <v>3.6969489802746338</v>
       </c>
-      <c r="P8" s="88">
+      <c r="P8" s="58">
         <v>3.7743162236554419</v>
       </c>
-      <c r="Q8" s="88">
+      <c r="Q8" s="58">
         <v>4.0183161455895977</v>
       </c>
-      <c r="R8" s="88">
+      <c r="R8" s="58">
         <v>5.5239472036366646</v>
       </c>
-      <c r="S8" s="88">
+      <c r="S8" s="58">
         <v>8.887831326254588</v>
       </c>
-      <c r="T8" s="88">
+      <c r="T8" s="58">
         <v>10.788676865113089</v>
       </c>
-      <c r="U8" s="89">
+      <c r="U8" s="59">
         <v>8.9042998213690989</v>
       </c>
       <c r="V8" s="12"/>
     </row>
     <row r="9" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
-        <v>11</v>
-      </c>
+      <c r="A9" s="84"/>
       <c r="B9" s="8" t="s">
         <v>18</v>
       </c>
@@ -3920,10 +3958,11 @@
         <f t="array" ref="K9">-SUMPRODUCT((D1:I1-C1:H1)*(C9:H9+D9:I9)/2)</f>
         <v>82.757600051326861</v>
       </c>
-      <c r="L9" s="12"/>
-      <c r="M9" s="93" t="s">
-        <v>11</v>
-      </c>
+      <c r="L9" s="12" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    93.4021689922347, 93.2487766618512, 92.6912718391451, 88.4524750790808, 80.8362500252309, 58.5874935480987, 46.7616127013786,</v>
+      </c>
+      <c r="M9" s="84"/>
       <c r="N9" s="8" t="s">
         <v>18</v>
       </c>
@@ -3951,31 +3990,29 @@
       <c r="V9" s="12"/>
     </row>
     <row r="10" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
-        <v>11</v>
-      </c>
+      <c r="A10" s="84"/>
       <c r="B10" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="94">
+      <c r="C10" s="57">
         <v>93.347099311701101</v>
       </c>
-      <c r="D10" s="95">
+      <c r="D10" s="58">
         <v>92.429741318408162</v>
       </c>
-      <c r="E10" s="95">
+      <c r="E10" s="58">
         <v>91.177980201674188</v>
       </c>
-      <c r="F10" s="95">
+      <c r="F10" s="58">
         <v>88.609442988261151</v>
       </c>
-      <c r="G10" s="95">
+      <c r="G10" s="58">
         <v>83.887882536469476</v>
       </c>
-      <c r="H10" s="95">
+      <c r="H10" s="58">
         <v>65.46502997430774</v>
       </c>
-      <c r="I10" s="96">
+      <c r="I10" s="59">
         <v>53.025920062745648</v>
       </c>
       <c r="J10" s="35" cm="1">
@@ -3990,2174 +4027,2683 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    93.3470993117011, 92.4297413184082, 91.1779802016742, 88.6094429882612, 83.8878825364695, 65.4650299743077, 53.0259200627456,</v>
       </c>
-      <c r="M10" s="93" t="s">
-        <v>11</v>
-      </c>
+      <c r="M10" s="84"/>
       <c r="N10" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="O10" s="94">
+      <c r="O10" s="57">
         <v>3.530639787063353</v>
       </c>
-      <c r="P10" s="95">
+      <c r="P10" s="58">
         <v>3.7877954805458178</v>
       </c>
-      <c r="Q10" s="95">
+      <c r="Q10" s="58">
         <v>3.5724123756053681</v>
       </c>
-      <c r="R10" s="95">
+      <c r="R10" s="58">
         <v>3.9540852979376608</v>
       </c>
-      <c r="S10" s="95">
+      <c r="S10" s="58">
         <v>4.7311149340952454</v>
       </c>
-      <c r="T10" s="95">
+      <c r="T10" s="58">
         <v>6.8843348259745856</v>
       </c>
-      <c r="U10" s="96">
+      <c r="U10" s="59">
         <v>6.3274200723455936</v>
       </c>
       <c r="V10" s="12"/>
     </row>
     <row r="11" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="93" t="s">
-        <v>11</v>
-      </c>
+      <c r="A11" s="84"/>
       <c r="B11" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" s="57">
-        <v>90.295968534906564</v>
-      </c>
-      <c r="D11" s="58">
-        <v>90.405113077679459</v>
-      </c>
-      <c r="E11" s="58">
-        <v>90.529243332554771</v>
-      </c>
-      <c r="F11" s="58">
-        <v>90.464208167890718</v>
-      </c>
-      <c r="G11" s="58">
-        <v>89.370346340942973</v>
-      </c>
-      <c r="H11" s="58">
-        <v>80.495811670804514</v>
-      </c>
-      <c r="I11" s="59">
-        <v>54.200509231625418</v>
+        <v>25</v>
+      </c>
+      <c r="C11" s="90">
+        <v>90.975423662834444</v>
+      </c>
+      <c r="D11" s="91">
+        <v>90.202556538839715</v>
+      </c>
+      <c r="E11" s="91">
+        <v>90.170108161258611</v>
+      </c>
+      <c r="F11" s="91">
+        <v>88.70908052837828</v>
+      </c>
+      <c r="G11" s="91">
+        <v>86.950939598670132</v>
+      </c>
+      <c r="H11" s="91">
+        <v>75.792829811099864</v>
+      </c>
+      <c r="I11" s="92">
+        <v>48.150537634408593</v>
       </c>
       <c r="J11" s="35" cm="1">
         <f t="array" ref="J11">-SUMPRODUCT((D1:H1-C1:G1)*(C11:G11+D11:H11)/2)</f>
-        <v>80.788810528926135</v>
+        <v>80.001938958526168</v>
       </c>
       <c r="K11" s="35" cm="1">
         <f t="array" ref="K11">-SUMPRODUCT((D1:I1-C1:H1)*(C11:H11+D11:I11)/2)</f>
-        <v>84.156218551486887</v>
-      </c>
-      <c r="L11" s="12"/>
-      <c r="M11" s="93" t="s">
-        <v>11</v>
-      </c>
+        <v>83.100523144663882</v>
+      </c>
+      <c r="L11" s="12" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    90.9754236628344, 90.2025565388397, 90.1701081612586, 88.7090805283783, 86.9509395986701, 75.7928298110999, 48.1505376344086,</v>
+      </c>
+      <c r="M11" s="84"/>
       <c r="N11" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="O11" s="90">
+        <v>3.3313581707075852</v>
+      </c>
+      <c r="P11" s="91">
+        <v>2.8735231153997312</v>
+      </c>
+      <c r="Q11" s="91">
+        <v>2.9020080993283321</v>
+      </c>
+      <c r="R11" s="91">
+        <v>2.6230573417030318</v>
+      </c>
+      <c r="S11" s="91">
+        <v>3.0561479691174078</v>
+      </c>
+      <c r="T11" s="91">
+        <v>3.639426101786353</v>
+      </c>
+      <c r="U11" s="92">
+        <v>2.9250848924264208</v>
+      </c>
+      <c r="V11" s="12"/>
+    </row>
+    <row r="12" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="84"/>
+      <c r="B12" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="O11" s="57">
-        <v>2.645635465917767</v>
-      </c>
-      <c r="P11" s="58">
-        <v>2.349990742414489</v>
-      </c>
-      <c r="Q11" s="58">
-        <v>2.284121152514234</v>
-      </c>
-      <c r="R11" s="58">
-        <v>2.4722451039664972</v>
-      </c>
-      <c r="S11" s="58">
-        <v>2.569604191233966</v>
-      </c>
-      <c r="T11" s="58">
-        <v>3.931910154117956</v>
-      </c>
-      <c r="U11" s="59">
-        <v>6.3131910290344502</v>
-      </c>
-      <c r="V11" s="12"/>
-    </row>
-    <row r="12" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="93" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" s="94">
-        <v>87.757128810226178</v>
-      </c>
-      <c r="D12" s="95">
-        <v>87.214361715931787</v>
-      </c>
-      <c r="E12" s="95">
-        <v>87.421857743867449</v>
-      </c>
-      <c r="F12" s="95">
-        <v>87.622418879056042</v>
-      </c>
-      <c r="G12" s="95">
-        <v>86.807385877040446</v>
-      </c>
-      <c r="H12" s="95">
-        <v>75.901045856798063</v>
-      </c>
-      <c r="I12" s="96">
-        <v>48.250428925279053</v>
+      <c r="C12" s="57">
+        <v>90.295968534906564</v>
+      </c>
+      <c r="D12" s="58">
+        <v>90.405113077679459</v>
+      </c>
+      <c r="E12" s="58">
+        <v>90.529243332554771</v>
+      </c>
+      <c r="F12" s="58">
+        <v>90.464208167890718</v>
+      </c>
+      <c r="G12" s="58">
+        <v>89.370346340942973</v>
+      </c>
+      <c r="H12" s="58">
+        <v>80.495811670804514</v>
+      </c>
+      <c r="I12" s="59">
+        <v>54.200509231625418</v>
       </c>
       <c r="J12" s="35" cm="1">
         <f t="array" ref="J12">-SUMPRODUCT((D1:H1-C1:G1)*(C12:G12+D12:H12)/2)</f>
-        <v>78.062303235033738</v>
+        <v>80.788810528926135</v>
       </c>
       <c r="K12" s="35" cm="1">
         <f t="array" ref="K12">-SUMPRODUCT((D1:I1-C1:H1)*(C12:H12+D12:I12)/2)</f>
-        <v>81.166090104585663</v>
+        <v>84.156218551486887</v>
       </c>
       <c r="L12" s="12" t="str">
         <f t="shared" si="0"/>
+        <v xml:space="preserve">    90.2959685349066, 90.4051130776795, 90.5292433325548, 90.4642081678907, 89.370346340943, 80.4958116708045, 54.2005092316254,</v>
+      </c>
+      <c r="M12" s="84"/>
+      <c r="N12" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="O12" s="57">
+        <v>2.645635465917767</v>
+      </c>
+      <c r="P12" s="58">
+        <v>2.349990742414489</v>
+      </c>
+      <c r="Q12" s="58">
+        <v>2.284121152514234</v>
+      </c>
+      <c r="R12" s="58">
+        <v>2.4722451039664972</v>
+      </c>
+      <c r="S12" s="58">
+        <v>2.569604191233966</v>
+      </c>
+      <c r="T12" s="58">
+        <v>3.931910154117956</v>
+      </c>
+      <c r="U12" s="59">
+        <v>6.3131910290344502</v>
+      </c>
+      <c r="V12" s="12"/>
+    </row>
+    <row r="13" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="84"/>
+      <c r="B13" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="57">
+        <v>87.757128810226178</v>
+      </c>
+      <c r="D13" s="58">
+        <v>87.214361715931787</v>
+      </c>
+      <c r="E13" s="58">
+        <v>87.421857743867449</v>
+      </c>
+      <c r="F13" s="58">
+        <v>87.622418879056042</v>
+      </c>
+      <c r="G13" s="58">
+        <v>86.807385877040446</v>
+      </c>
+      <c r="H13" s="58">
+        <v>75.901045856798063</v>
+      </c>
+      <c r="I13" s="59">
+        <v>48.250428925279053</v>
+      </c>
+      <c r="J13" s="35" cm="1">
+        <f t="array" ref="J13">-SUMPRODUCT((D1:H1-C1:G1)*(C13:G13+D13:H13)/2)</f>
+        <v>78.062303235033738</v>
+      </c>
+      <c r="K13" s="35" cm="1">
+        <f t="array" ref="K13">-SUMPRODUCT((D1:I1-C1:H1)*(C13:H13+D13:I13)/2)</f>
+        <v>81.166090104585663</v>
+      </c>
+      <c r="L13" s="12" t="str">
+        <f t="shared" si="0"/>
         <v xml:space="preserve">    87.7571288102262, 87.2143617159318, 87.4218577438674, 87.622418879056, 86.8073858770404, 75.9010458567981, 48.2504289252791,</v>
       </c>
-      <c r="M12" s="93" t="s">
-        <v>11</v>
-      </c>
-      <c r="N12" s="8" t="s">
+      <c r="M13" s="84"/>
+      <c r="N13" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="O12" s="94">
+      <c r="O13" s="57">
         <v>2.4219047595763121</v>
       </c>
-      <c r="P12" s="95">
+      <c r="P13" s="58">
         <v>2.3217688638534999</v>
       </c>
-      <c r="Q12" s="95">
+      <c r="Q13" s="58">
         <v>1.9206629777265249</v>
       </c>
-      <c r="R12" s="95">
+      <c r="R13" s="58">
         <v>2.0167242206543352</v>
       </c>
-      <c r="S12" s="95">
+      <c r="S13" s="58">
         <v>1.6755361920192899</v>
       </c>
-      <c r="T12" s="95">
+      <c r="T13" s="58">
         <v>3.611109605289736</v>
       </c>
-      <c r="U12" s="96">
+      <c r="U13" s="59">
         <v>3.8722711387036122</v>
       </c>
-      <c r="V12" s="12"/>
-    </row>
-    <row r="13" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="76" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="78"/>
-      <c r="C13" s="83"/>
-      <c r="D13" s="83"/>
-      <c r="E13" s="83"/>
-      <c r="F13" s="83"/>
-      <c r="G13" s="83"/>
-      <c r="H13" s="83"/>
-      <c r="I13" s="82"/>
-      <c r="J13" s="35"/>
-      <c r="K13" s="35"/>
-      <c r="L13" s="12"/>
-      <c r="M13" s="76" t="s">
-        <v>20</v>
-      </c>
-      <c r="N13" s="78"/>
-      <c r="O13" s="83"/>
-      <c r="P13" s="83"/>
-      <c r="Q13" s="83"/>
-      <c r="R13" s="83"/>
-      <c r="S13" s="83"/>
-      <c r="T13" s="83"/>
-      <c r="U13" s="82"/>
       <c r="V13" s="12"/>
     </row>
     <row r="14" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="76" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" s="77"/>
-      <c r="C14" s="52">
-        <v>93.782740335124032</v>
-      </c>
-      <c r="D14" s="53">
-        <v>91.948208894540599</v>
-      </c>
-      <c r="E14" s="53">
-        <v>90.212980504444957</v>
-      </c>
-      <c r="F14" s="53">
-        <v>84.630388959535409</v>
-      </c>
-      <c r="G14" s="53">
-        <v>75.371093175546491</v>
-      </c>
-      <c r="H14" s="53">
-        <v>59.627211308056303</v>
-      </c>
-      <c r="I14" s="54">
-        <v>47.844185503334799</v>
+      <c r="A14" s="85"/>
+      <c r="B14" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="90">
+        <v>87.38938053097344</v>
+      </c>
+      <c r="D14" s="91">
+        <v>87.136676499508383</v>
+      </c>
+      <c r="E14" s="91">
+        <v>87.169124877089473</v>
+      </c>
+      <c r="F14" s="91">
+        <v>87.617502458210453</v>
+      </c>
+      <c r="G14" s="91">
+        <v>86.525073746312685</v>
+      </c>
+      <c r="H14" s="91">
+        <v>73.91603156890055</v>
+      </c>
+      <c r="I14" s="92">
+        <v>47.131944624665152</v>
       </c>
       <c r="J14" s="35" cm="1">
         <f t="array" ref="J14">-SUMPRODUCT((D1:H1-C1:G1)*(C14:G14+D14:H14)/2)</f>
-        <v>78.220843605913544</v>
+        <v>77.81182911040176</v>
       </c>
       <c r="K14" s="35" cm="1">
         <f t="array" ref="K14">-SUMPRODUCT((D1:I1-C1:H1)*(C14:H14+D14:I14)/2)</f>
-        <v>80.907628526198323</v>
+        <v>80.838028515240907</v>
       </c>
       <c r="L14" s="12" t="str">
         <f t="shared" si="0"/>
+        <v xml:space="preserve">    87.3893805309734, 87.1366764995084, 87.1691248770895, 87.6175024582105, 86.5250737463127, 73.9160315689006, 47.1319446246652,</v>
+      </c>
+      <c r="M14" s="85"/>
+      <c r="N14" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="O14" s="12">
+        <v>2.3114467772059939</v>
+      </c>
+      <c r="P14" s="12">
+        <v>1.808974585726052</v>
+      </c>
+      <c r="Q14" s="12">
+        <v>1.926285810675562</v>
+      </c>
+      <c r="R14" s="12">
+        <v>1.875569382848</v>
+      </c>
+      <c r="S14" s="12">
+        <v>1.6559404586511339</v>
+      </c>
+      <c r="T14" s="12">
+        <v>2.9852787187065402</v>
+      </c>
+      <c r="U14" s="12">
+        <v>2.1122202966826809</v>
+      </c>
+      <c r="V14" s="12"/>
+    </row>
+    <row r="15" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" s="74"/>
+      <c r="C15" s="89"/>
+      <c r="D15" s="89"/>
+      <c r="E15" s="89"/>
+      <c r="F15" s="89"/>
+      <c r="G15" s="89"/>
+      <c r="H15" s="89"/>
+      <c r="I15" s="76"/>
+      <c r="J15" s="35"/>
+      <c r="K15" s="35"/>
+      <c r="L15" s="12"/>
+      <c r="M15" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="N15" s="74"/>
+      <c r="O15" s="77"/>
+      <c r="P15" s="77"/>
+      <c r="Q15" s="77"/>
+      <c r="R15" s="77"/>
+      <c r="S15" s="77"/>
+      <c r="T15" s="77"/>
+      <c r="U15" s="73"/>
+      <c r="V15" s="12"/>
+    </row>
+    <row r="16" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="68" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" s="69"/>
+      <c r="C16" s="52">
+        <v>93.782740335124032</v>
+      </c>
+      <c r="D16" s="53">
+        <v>91.948208894540599</v>
+      </c>
+      <c r="E16" s="53">
+        <v>90.212980504444957</v>
+      </c>
+      <c r="F16" s="53">
+        <v>84.630388959535409</v>
+      </c>
+      <c r="G16" s="53">
+        <v>75.371093175546491</v>
+      </c>
+      <c r="H16" s="53">
+        <v>59.627211308056303</v>
+      </c>
+      <c r="I16" s="54">
+        <v>47.844185503334799</v>
+      </c>
+      <c r="J16" s="35" cm="1">
+        <f t="array" ref="J16">-SUMPRODUCT((D1:H1-C1:G1)*(C16:G16+D16:H16)/2)</f>
+        <v>78.220843605913544</v>
+      </c>
+      <c r="K16" s="35" cm="1">
+        <f t="array" ref="K16">-SUMPRODUCT((D1:I1-C1:H1)*(C16:H16+D16:I16)/2)</f>
+        <v>80.907628526198323</v>
+      </c>
+      <c r="L16" s="12" t="str">
+        <f t="shared" si="0"/>
         <v xml:space="preserve">    93.782740335124, 91.9482088945406, 90.212980504445, 84.6303889595354, 75.3710931755465, 59.6272113080563, 47.8441855033348,</v>
       </c>
-      <c r="M14" s="76" t="s">
+      <c r="M16" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="N14" s="77"/>
-      <c r="O14" s="52">
+      <c r="N16" s="69"/>
+      <c r="O16" s="52">
         <v>3.5391983918820551</v>
       </c>
-      <c r="P14" s="53">
+      <c r="P16" s="53">
         <v>4.1060038651541966</v>
       </c>
-      <c r="Q14" s="53">
+      <c r="Q16" s="53">
         <v>4.774795806468676</v>
       </c>
-      <c r="R14" s="53">
+      <c r="R16" s="53">
         <v>5.3483339064680431</v>
       </c>
-      <c r="S14" s="53">
+      <c r="S16" s="53">
         <v>8.0994903921197494</v>
       </c>
-      <c r="T14" s="53">
+      <c r="T16" s="53">
         <v>10.59987402205407</v>
       </c>
-      <c r="U14" s="54">
+      <c r="U16" s="54">
         <v>8.7604668874903737</v>
       </c>
-      <c r="V14" s="12" t="str">
+      <c r="V16" s="12" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">    3.53919839188206, 4.1060038651542, 4.77479580646868, 5.34833390646804, 8.09949039211975, 10.5998740220541, 8.76046688749037,</v>
       </c>
     </row>
-    <row r="15" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="81" t="s">
+    <row r="17" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="72" t="s">
         <v>8</v>
       </c>
-      <c r="B15" s="82"/>
-      <c r="C15" s="55">
+      <c r="B17" s="73"/>
+      <c r="C17" s="55">
         <v>93.226230330712227</v>
       </c>
-      <c r="D15" s="12">
+      <c r="D17" s="12">
         <v>91.83329152212967</v>
       </c>
-      <c r="E15" s="12">
+      <c r="E17" s="12">
         <v>90.325291164571794</v>
       </c>
-      <c r="F15" s="12">
+      <c r="F17" s="12">
         <v>85.383492360083878</v>
       </c>
-      <c r="G15" s="12">
+      <c r="G17" s="12">
         <v>76.567000291236639</v>
       </c>
-      <c r="H15" s="12">
+      <c r="H17" s="12">
         <v>59.41454222499042</v>
       </c>
-      <c r="I15" s="56">
+      <c r="I17" s="56">
         <v>50.563407411252108</v>
       </c>
-      <c r="J15" s="35" cm="1">
-        <f t="array" ref="J15">-SUMPRODUCT((D1:H1-C1:G1)*(C15:G15+D15:H15)/2)</f>
+      <c r="J17" s="35" cm="1">
+        <f t="array" ref="J17">-SUMPRODUCT((D1:H1-C1:G1)*(C17:G17+D17:H17)/2)</f>
         <v>78.369743178285859</v>
       </c>
-      <c r="K15" s="35" cm="1">
-        <f t="array" ref="K15">-SUMPRODUCT((D1:I1-C1:H1)*(C15:H15+D15:I15)/2)</f>
+      <c r="K17" s="35" cm="1">
+        <f t="array" ref="K17">-SUMPRODUCT((D1:I1-C1:H1)*(C17:H17+D17:I17)/2)</f>
         <v>81.11919191919192</v>
       </c>
-      <c r="L15" s="12" t="str">
+      <c r="L17" s="12" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">    93.2262303307122, 91.8332915221297, 90.3252911645718, 85.3834923600839, 76.5670002912366, 59.4145422249904, 50.5634074112521,</v>
       </c>
-      <c r="M15" s="76" t="s">
+      <c r="M17" s="68" t="s">
         <v>8</v>
       </c>
-      <c r="N15" s="77"/>
-      <c r="O15" s="55">
+      <c r="N17" s="69"/>
+      <c r="O17" s="55">
         <v>3.945711842949601</v>
       </c>
-      <c r="P15" s="12">
+      <c r="P17" s="12">
         <v>4.8525950161134093</v>
       </c>
-      <c r="Q15" s="12">
+      <c r="Q17" s="12">
         <v>4.4346894499148144</v>
       </c>
-      <c r="R15" s="12">
+      <c r="R17" s="12">
         <v>5.4810029574676529</v>
       </c>
-      <c r="S15" s="12">
+      <c r="S17" s="12">
         <v>8.4636725644600066</v>
       </c>
-      <c r="T15" s="12">
+      <c r="T17" s="12">
         <v>10.788297692871961</v>
       </c>
-      <c r="U15" s="56">
+      <c r="U17" s="56">
         <v>8.7433484877826491</v>
       </c>
-      <c r="V15" s="12" t="str">
+      <c r="V17" s="12" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">    3.9457118429496, 4.85259501611341, 4.43468944991481, 5.48100295746765, 8.46367256446001, 10.788297692872, 8.74334848778265,</v>
       </c>
     </row>
-    <row r="16" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="76" t="s">
+    <row r="18" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="68" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="77"/>
-      <c r="C16" s="55">
+      <c r="B18" s="69"/>
+      <c r="C18" s="55">
         <v>93.004922187908207</v>
       </c>
-      <c r="D16" s="12">
+      <c r="D18" s="12">
         <v>91.518502178507859</v>
       </c>
-      <c r="E16" s="12">
+      <c r="E18" s="12">
         <v>89.729420958082102</v>
       </c>
-      <c r="F16" s="12">
+      <c r="F18" s="12">
         <v>83.348607398564567</v>
       </c>
-      <c r="G16" s="12">
+      <c r="G18" s="12">
         <v>74.087719905304837</v>
       </c>
-      <c r="H16" s="12">
+      <c r="H18" s="12">
         <v>57.917332041511322</v>
       </c>
-      <c r="I16" s="56">
+      <c r="I18" s="56">
         <v>48.007794185070807</v>
       </c>
-      <c r="J16" s="35" cm="1">
-        <f t="array" ref="J16">-SUMPRODUCT((D1:H1-C1:G1)*(C16:G16+D16:H16)/2)</f>
+      <c r="J18" s="35" cm="1">
+        <f t="array" ref="J18">-SUMPRODUCT((D1:H1-C1:G1)*(C18:G18+D18:H18)/2)</f>
         <v>77.501290236074709</v>
       </c>
-      <c r="K16" s="35" cm="1">
-        <f t="array" ref="K16">-SUMPRODUCT((D1:I1-C1:H1)*(C16:H16+D16:I16)/2)</f>
+      <c r="K18" s="35" cm="1">
+        <f t="array" ref="K18">-SUMPRODUCT((D1:I1-C1:H1)*(C18:H18+D18:I18)/2)</f>
         <v>80.14941839173926</v>
       </c>
-      <c r="L16" s="12" t="str">
+      <c r="L18" s="12" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">    93.0049221879082, 91.5185021785079, 89.7294209580821, 83.3486073985646, 74.0877199053048, 57.9173320415113, 48.0077941850708,</v>
       </c>
-      <c r="M16" s="76" t="s">
+      <c r="M18" s="68" t="s">
         <v>21</v>
       </c>
-      <c r="N16" s="77"/>
-      <c r="O16" s="55">
+      <c r="N18" s="69"/>
+      <c r="O18" s="55">
         <v>3.690401528555848</v>
       </c>
-      <c r="P16" s="12">
+      <c r="P18" s="12">
         <v>4.2469367469027457</v>
       </c>
-      <c r="Q16" s="12">
+      <c r="Q18" s="12">
         <v>4.4611096369834957</v>
       </c>
-      <c r="R16" s="12">
+      <c r="R18" s="12">
         <v>5.4089286426803449</v>
       </c>
-      <c r="S16" s="12">
+      <c r="S18" s="12">
         <v>9.092124974067179</v>
       </c>
-      <c r="T16" s="12">
+      <c r="T18" s="12">
         <v>10.83557708581068</v>
       </c>
-      <c r="U16" s="56">
+      <c r="U18" s="56">
         <v>9.2904800440053528</v>
       </c>
-      <c r="V16" s="12" t="str">
+      <c r="V18" s="12" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">    3.69040152855585, 4.24693674690275, 4.4611096369835, 5.40892864268034, 9.09212497406718, 10.8355770858107, 9.29048004400535,</v>
       </c>
     </row>
-    <row r="17" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="76" t="s">
+    <row r="19" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="68" t="s">
         <v>22</v>
       </c>
-      <c r="B17" s="77"/>
-      <c r="C17" s="57">
+      <c r="B19" s="69"/>
+      <c r="C19" s="57">
         <v>93.123279613145442</v>
       </c>
-      <c r="D17" s="58">
+      <c r="D19" s="58">
         <v>91.674385879923975</v>
       </c>
-      <c r="E17" s="58">
+      <c r="E19" s="58">
         <v>89.698688281617194</v>
       </c>
-      <c r="F17" s="58">
+      <c r="F19" s="58">
         <v>84.957067102656595</v>
       </c>
-      <c r="G17" s="58">
+      <c r="G19" s="58">
         <v>75.939082518014857</v>
       </c>
-      <c r="H17" s="58">
+      <c r="H19" s="58">
         <v>59.995092229748238</v>
       </c>
-      <c r="I17" s="59">
+      <c r="I19" s="59">
         <v>48.440303693515233</v>
-      </c>
-      <c r="J17" s="35" cm="1">
-        <f t="array" ref="J17">-SUMPRODUCT((D1:H1-C1:G1)*(C17:G17+D17:H17)/2)</f>
-        <v>78.078434213675436</v>
-      </c>
-      <c r="K17" s="35" cm="1">
-        <f t="array" ref="K17">-SUMPRODUCT((D1:I1-C1:H1)*(C17:H17+D17:I17)/2)</f>
-        <v>80.789319111757024</v>
-      </c>
-      <c r="L17" s="12"/>
-      <c r="M17" s="76" t="s">
-        <v>22</v>
-      </c>
-      <c r="N17" s="77"/>
-      <c r="O17" s="57">
-        <v>3.8088682011350912</v>
-      </c>
-      <c r="P17" s="58">
-        <v>4.4783864386850611</v>
-      </c>
-      <c r="Q17" s="58">
-        <v>5.0849840192173117</v>
-      </c>
-      <c r="R17" s="58">
-        <v>5.0366327026230584</v>
-      </c>
-      <c r="S17" s="58">
-        <v>7.6643798786674449</v>
-      </c>
-      <c r="T17" s="58">
-        <v>10.05146904627655</v>
-      </c>
-      <c r="U17" s="59">
-        <v>9.821397671709315</v>
-      </c>
-      <c r="V17" s="12"/>
-    </row>
-    <row r="18" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="76" t="s">
-        <v>23</v>
-      </c>
-      <c r="B18" s="78"/>
-      <c r="C18" s="79"/>
-      <c r="D18" s="79"/>
-      <c r="E18" s="79"/>
-      <c r="F18" s="79"/>
-      <c r="G18" s="79"/>
-      <c r="H18" s="79"/>
-      <c r="I18" s="80"/>
-      <c r="J18" s="35"/>
-      <c r="K18" s="35"/>
-      <c r="L18" s="12"/>
-      <c r="M18" s="76" t="s">
-        <v>23</v>
-      </c>
-      <c r="N18" s="78"/>
-      <c r="O18" s="79"/>
-      <c r="P18" s="79"/>
-      <c r="Q18" s="79"/>
-      <c r="R18" s="79"/>
-      <c r="S18" s="79"/>
-      <c r="T18" s="79"/>
-      <c r="U18" s="80"/>
-      <c r="V18" s="12"/>
-    </row>
-    <row r="19" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="76" t="s">
-        <v>7</v>
-      </c>
-      <c r="B19" s="77"/>
-      <c r="C19" s="52">
-        <v>92.969518190757128</v>
-      </c>
-      <c r="D19" s="53">
-        <v>91.851524090462149</v>
-      </c>
-      <c r="E19" s="53">
-        <v>90.756145526057011</v>
-      </c>
-      <c r="F19" s="53">
-        <v>87.253136561158271</v>
-      </c>
-      <c r="G19" s="53">
-        <v>81.178972136437139</v>
-      </c>
-      <c r="H19" s="53">
-        <v>57.386929529378847</v>
-      </c>
-      <c r="I19" s="54">
-        <v>44.855442809482213</v>
       </c>
       <c r="J19" s="35" cm="1">
         <f t="array" ref="J19">-SUMPRODUCT((D1:H1-C1:G1)*(C19:G19+D19:H19)/2)</f>
-        <v>79.079417714109411</v>
+        <v>78.078434213675436</v>
       </c>
       <c r="K19" s="35" cm="1">
         <f t="array" ref="K19">-SUMPRODUCT((D1:I1-C1:H1)*(C19:H19+D19:I19)/2)</f>
+        <v>80.789319111757024</v>
+      </c>
+      <c r="L19" s="12"/>
+      <c r="M19" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="N19" s="69"/>
+      <c r="O19" s="57">
+        <v>3.8088682011350912</v>
+      </c>
+      <c r="P19" s="58">
+        <v>4.4783864386850611</v>
+      </c>
+      <c r="Q19" s="58">
+        <v>5.0849840192173117</v>
+      </c>
+      <c r="R19" s="58">
+        <v>5.0366327026230584</v>
+      </c>
+      <c r="S19" s="58">
+        <v>7.6643798786674449</v>
+      </c>
+      <c r="T19" s="58">
+        <v>10.05146904627655</v>
+      </c>
+      <c r="U19" s="59">
+        <v>9.821397671709315</v>
+      </c>
+      <c r="V19" s="12"/>
+    </row>
+    <row r="20" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="68" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" s="74"/>
+      <c r="C20" s="75"/>
+      <c r="D20" s="75"/>
+      <c r="E20" s="75"/>
+      <c r="F20" s="75"/>
+      <c r="G20" s="75"/>
+      <c r="H20" s="75"/>
+      <c r="I20" s="76"/>
+      <c r="J20" s="35"/>
+      <c r="K20" s="35"/>
+      <c r="L20" s="12"/>
+      <c r="M20" s="68" t="s">
+        <v>23</v>
+      </c>
+      <c r="N20" s="74"/>
+      <c r="O20" s="75"/>
+      <c r="P20" s="75"/>
+      <c r="Q20" s="75"/>
+      <c r="R20" s="75"/>
+      <c r="S20" s="75"/>
+      <c r="T20" s="75"/>
+      <c r="U20" s="76"/>
+      <c r="V20" s="12"/>
+    </row>
+    <row r="21" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="68" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" s="69"/>
+      <c r="C21" s="52">
+        <v>92.969518190757128</v>
+      </c>
+      <c r="D21" s="53">
+        <v>91.851524090462149</v>
+      </c>
+      <c r="E21" s="53">
+        <v>90.756145526057011</v>
+      </c>
+      <c r="F21" s="53">
+        <v>87.253136561158271</v>
+      </c>
+      <c r="G21" s="53">
+        <v>81.178972136437139</v>
+      </c>
+      <c r="H21" s="53">
+        <v>57.386929529378847</v>
+      </c>
+      <c r="I21" s="54">
+        <v>44.855442809482213</v>
+      </c>
+      <c r="J21" s="35" cm="1">
+        <f t="array" ref="J21">-SUMPRODUCT((D1:H1-C1:G1)*(C21:G21+D21:H21)/2)</f>
+        <v>79.079417714109411</v>
+      </c>
+      <c r="K21" s="35" cm="1">
+        <f t="array" ref="K21">-SUMPRODUCT((D1:I1-C1:H1)*(C21:H21+D21:I21)/2)</f>
         <v>81.635477022580943</v>
       </c>
-      <c r="L19" s="12" t="str">
-        <f t="shared" ref="L19:L21" si="2">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C19:I19)&amp;","</f>
+      <c r="L21" s="12" t="str">
+        <f t="shared" ref="L21:L23" si="2">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C21:I21)&amp;","</f>
         <v xml:space="preserve">    92.9695181907571, 91.8515240904621, 90.756145526057, 87.2531365611583, 81.1789721364371, 57.3869295293788, 44.8554428094822,</v>
       </c>
-      <c r="M19" s="76" t="s">
+      <c r="M21" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="N19" s="77"/>
-      <c r="O19" s="52">
+      <c r="N21" s="69"/>
+      <c r="O21" s="52">
         <v>3.3991921823554931</v>
       </c>
-      <c r="P19" s="53">
+      <c r="P21" s="53">
         <v>3.6561489783789969</v>
       </c>
-      <c r="Q19" s="53">
+      <c r="Q21" s="53">
         <v>3.4316179388806831</v>
       </c>
-      <c r="R19" s="53">
+      <c r="R21" s="53">
         <v>3.3610781227617821</v>
       </c>
-      <c r="S19" s="53">
+      <c r="S21" s="53">
         <v>5.2773835873092807</v>
       </c>
-      <c r="T19" s="53">
+      <c r="T21" s="53">
         <v>8.2027130196510409</v>
       </c>
-      <c r="U19" s="54">
+      <c r="U21" s="54">
         <v>5.203571843512913</v>
       </c>
-      <c r="V19" s="12" t="str">
-        <f t="shared" ref="V19:V21" si="3">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,O19:U19)&amp;","</f>
+      <c r="V21" s="12" t="str">
+        <f t="shared" ref="V21:V23" si="3">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,O21:U21)&amp;","</f>
         <v xml:space="preserve">    3.39919218235549, 3.656148978379, 3.43161793888068, 3.36107812276178, 5.27738358730928, 8.20271301965104, 5.20357184351291,</v>
       </c>
     </row>
-    <row r="20" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="81" t="s">
+    <row r="22" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="72" t="s">
         <v>8</v>
       </c>
-      <c r="B20" s="82"/>
-      <c r="C20" s="55">
+      <c r="B22" s="73"/>
+      <c r="C22" s="55">
         <v>91.898721730580135</v>
       </c>
-      <c r="D20" s="12">
+      <c r="D22" s="12">
         <v>90.765995668936</v>
       </c>
-      <c r="E20" s="12">
+      <c r="E22" s="12">
         <v>89.705268500015848</v>
       </c>
-      <c r="F20" s="12">
+      <c r="F22" s="12">
         <v>87.959685349065893</v>
       </c>
-      <c r="G20" s="12">
+      <c r="G22" s="12">
         <v>85.750000720882824</v>
       </c>
-      <c r="H20" s="12">
+      <c r="H22" s="12">
         <v>71.387388010853613</v>
       </c>
-      <c r="I20" s="56">
+      <c r="I22" s="56">
         <v>45.596343105620853</v>
       </c>
-      <c r="J20" s="35" cm="1">
-        <f t="array" ref="J20">-SUMPRODUCT((D1:H1-C1:G1)*(C20:G20+D20:H20)/2)</f>
+      <c r="J22" s="35" cm="1">
+        <f t="array" ref="J22">-SUMPRODUCT((D1:H1-C1:G1)*(C22:G22+D22:H22)/2)</f>
         <v>79.700846821050931</v>
       </c>
-      <c r="K20" s="35" cm="1">
-        <f t="array" ref="K20">-SUMPRODUCT((D1:I1-C1:H1)*(C20:H20+D20:I20)/2)</f>
+      <c r="K22" s="35" cm="1">
+        <f t="array" ref="K22">-SUMPRODUCT((D1:I1-C1:H1)*(C22:H22+D22:I22)/2)</f>
         <v>82.625440098962798</v>
       </c>
-      <c r="L20" s="12" t="str">
+      <c r="L22" s="12" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">    91.8987217305801, 90.765995668936, 89.7052685000158, 87.9596853490659, 85.7500007208828, 71.3873880108536, 45.5963431056209,</v>
       </c>
-      <c r="M20" s="76" t="s">
+      <c r="M22" s="68" t="s">
         <v>8</v>
       </c>
-      <c r="N20" s="77"/>
-      <c r="O20" s="55">
+      <c r="N22" s="69"/>
+      <c r="O22" s="55">
         <v>3.190312271555559</v>
       </c>
-      <c r="P20" s="12">
+      <c r="P22" s="12">
         <v>2.8828036064622768</v>
       </c>
-      <c r="Q20" s="12">
+      <c r="Q22" s="12">
         <v>2.5884740771146331</v>
       </c>
-      <c r="R20" s="12">
+      <c r="R22" s="12">
         <v>2.6213450470877251</v>
       </c>
-      <c r="S20" s="12">
+      <c r="S22" s="12">
         <v>3.203569989687661</v>
       </c>
-      <c r="T20" s="12">
+      <c r="T22" s="12">
         <v>4.756712112750666</v>
       </c>
-      <c r="U20" s="56">
+      <c r="U22" s="56">
         <v>2.488810891584841</v>
       </c>
-      <c r="V20" s="12" t="str">
+      <c r="V22" s="12" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">    3.19031227155556, 2.88280360646228, 2.58847407711463, 2.62134504708773, 3.20356998968766, 4.75671211275067, 2.48881089158484,</v>
       </c>
     </row>
-    <row r="21" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="76" t="s">
+    <row r="23" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="68" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="77"/>
-      <c r="C21" s="55">
+      <c r="B23" s="69"/>
+      <c r="C23" s="55">
         <v>93.044276622923505</v>
       </c>
-      <c r="D21" s="12">
+      <c r="D23" s="12">
         <v>91.935155148400938</v>
       </c>
-      <c r="E21" s="12">
+      <c r="E23" s="12">
         <v>90.94889229145582</v>
       </c>
-      <c r="F21" s="12">
+      <c r="F23" s="12">
         <v>85.952505356159378</v>
       </c>
-      <c r="G21" s="12">
+      <c r="G23" s="12">
         <v>78.915183810701947</v>
       </c>
-      <c r="H21" s="12">
+      <c r="H23" s="12">
         <v>59.442100133507502</v>
       </c>
-      <c r="I21" s="56">
+      <c r="I23" s="56">
         <v>49.533828147302302</v>
       </c>
-      <c r="J21" s="35" cm="1">
-        <f t="array" ref="J21">-SUMPRODUCT((D1:H1-C1:G1)*(C21:G21+D21:H21)/2)</f>
+      <c r="J23" s="35" cm="1">
+        <f t="array" ref="J23">-SUMPRODUCT((D1:H1-C1:G1)*(C23:G23+D23:H23)/2)</f>
         <v>78.834323321712716</v>
       </c>
-      <c r="K21" s="35" cm="1">
-        <f t="array" ref="K21">-SUMPRODUCT((D1:I1-C1:H1)*(C21:H21+D21:I21)/2)</f>
+      <c r="K23" s="35" cm="1">
+        <f t="array" ref="K23">-SUMPRODUCT((D1:I1-C1:H1)*(C23:H23+D23:I23)/2)</f>
         <v>81.55872152873296</v>
       </c>
-      <c r="L21" s="12" t="str">
+      <c r="L23" s="12" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">    93.0442766229235, 91.9351551484009, 90.9488922914558, 85.9525053561594, 78.9151838107019, 59.4421001335075, 49.5338281473023,</v>
       </c>
-      <c r="M21" s="76" t="s">
+      <c r="M23" s="68" t="s">
         <v>21</v>
       </c>
-      <c r="N21" s="77"/>
-      <c r="O21" s="55">
+      <c r="N23" s="69"/>
+      <c r="O23" s="55">
         <v>3.72078192123604</v>
       </c>
-      <c r="P21" s="12">
+      <c r="P23" s="12">
         <v>4.0467152776216686</v>
       </c>
-      <c r="Q21" s="12">
+      <c r="Q23" s="12">
         <v>4.0235763627769954</v>
       </c>
-      <c r="R21" s="12">
+      <c r="R23" s="12">
         <v>4.4767633212331157</v>
       </c>
-      <c r="S21" s="12">
+      <c r="S23" s="12">
         <v>7.2019016527503927</v>
       </c>
-      <c r="T21" s="12">
+      <c r="T23" s="12">
         <v>10.04668436860082</v>
       </c>
-      <c r="U21" s="56">
+      <c r="U23" s="56">
         <v>9.2355901481835172</v>
       </c>
-      <c r="V21" s="12" t="str">
+      <c r="V23" s="12" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">    3.72078192123604, 4.04671527762167, 4.023576362777, 4.47676332123312, 7.20190165275039, 10.0466843686008, 9.23559014818352,</v>
       </c>
     </row>
-    <row r="22" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="76" t="s">
+    <row r="24" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="68" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="77"/>
-      <c r="C22" s="57">
+      <c r="B24" s="69"/>
+      <c r="C24" s="57">
         <v>93.174110502686005</v>
       </c>
-      <c r="D22" s="58">
+      <c r="D24" s="58">
         <v>91.391724841910417</v>
       </c>
-      <c r="E22" s="58">
+      <c r="E24" s="58">
         <v>89.591539142495463</v>
       </c>
-      <c r="F22" s="58">
+      <c r="F24" s="58">
         <v>84.690597092823751</v>
       </c>
-      <c r="G22" s="58">
+      <c r="G24" s="58">
         <v>76.401347185817656</v>
       </c>
-      <c r="H22" s="58">
+      <c r="H24" s="58">
         <v>59.963667505774268</v>
       </c>
-      <c r="I22" s="59">
+      <c r="I24" s="59">
         <v>47.725577210875521</v>
       </c>
-      <c r="J22" s="35" cm="1">
-        <f t="array" ref="J22">-SUMPRODUCT((D1:H1-C1:G1)*(C22:G22+D22:H22)/2)</f>
+      <c r="J24" s="35" cm="1">
+        <f t="array" ref="J24">-SUMPRODUCT((D1:H1-C1:G1)*(C24:G24+D24:H24)/2)</f>
         <v>77.994698988168864</v>
       </c>
-      <c r="K22" s="35" cm="1">
-        <f t="array" ref="K22">-SUMPRODUCT((D1:I1-C1:H1)*(C22:H22+D22:I22)/2)</f>
+      <c r="K24" s="35" cm="1">
+        <f t="array" ref="K24">-SUMPRODUCT((D1:I1-C1:H1)*(C24:H24+D24:I24)/2)</f>
         <v>80.686930106085114</v>
       </c>
-      <c r="L22" s="12"/>
-      <c r="M22" s="76" t="s">
+      <c r="L24" s="12"/>
+      <c r="M24" s="68" t="s">
         <v>22</v>
       </c>
-      <c r="N22" s="77"/>
-      <c r="O22" s="57">
+      <c r="N24" s="69"/>
+      <c r="O24" s="57">
         <v>3.8766021792735019</v>
       </c>
-      <c r="P22" s="58">
+      <c r="P24" s="58">
         <v>4.8126411406228078</v>
       </c>
-      <c r="Q22" s="58">
+      <c r="Q24" s="58">
         <v>4.6512210016047986</v>
       </c>
-      <c r="R22" s="58">
+      <c r="R24" s="58">
         <v>5.2416066355763284</v>
       </c>
-      <c r="S22" s="58">
+      <c r="S24" s="58">
         <v>8.0769588602235256</v>
       </c>
-      <c r="T22" s="58">
+      <c r="T24" s="58">
         <v>10.657363307561541</v>
       </c>
-      <c r="U22" s="59">
+      <c r="U24" s="59">
         <v>9.200486032966916</v>
       </c>
-      <c r="V22" s="12"/>
-    </row>
-    <row r="23" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="25"/>
-      <c r="B23" s="25"/>
-      <c r="C23" s="25"/>
-      <c r="D23" s="25"/>
-      <c r="E23" s="25"/>
-      <c r="F23" s="25"/>
-      <c r="G23" s="25"/>
-      <c r="H23" s="25"/>
-      <c r="I23" s="25"/>
-      <c r="J23" s="25"/>
-      <c r="K23" s="25"/>
-      <c r="M23" s="25"/>
-      <c r="N23" s="25"/>
-      <c r="O23" s="25"/>
-      <c r="P23" s="25"/>
-      <c r="Q23" s="25"/>
-      <c r="R23" s="25"/>
-      <c r="S23" s="25"/>
-      <c r="T23" s="25"/>
-      <c r="U23" s="25"/>
-    </row>
-    <row r="24" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
+      <c r="V24" s="12"/>
+    </row>
+    <row r="25" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="68" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" s="74"/>
+      <c r="C25" s="75"/>
+      <c r="D25" s="75"/>
+      <c r="E25" s="75"/>
+      <c r="F25" s="75"/>
+      <c r="G25" s="75"/>
+      <c r="H25" s="75"/>
+      <c r="I25" s="76"/>
+      <c r="J25" s="35"/>
+      <c r="K25" s="35"/>
+      <c r="L25" s="12"/>
+      <c r="M25" s="68" t="s">
+        <v>23</v>
+      </c>
+      <c r="N25" s="74"/>
+      <c r="O25" s="75"/>
+      <c r="P25" s="75"/>
+      <c r="Q25" s="75"/>
+      <c r="R25" s="75"/>
+      <c r="S25" s="75"/>
+      <c r="T25" s="75"/>
+      <c r="U25" s="76"/>
+      <c r="V25" s="12"/>
+    </row>
+    <row r="26" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="68" t="s">
+        <v>7</v>
+      </c>
+      <c r="B26" s="69"/>
+      <c r="C26" s="52"/>
+      <c r="D26" s="53"/>
+      <c r="E26" s="53"/>
+      <c r="F26" s="53"/>
+      <c r="G26" s="53"/>
+      <c r="H26" s="53"/>
+      <c r="I26" s="54"/>
+      <c r="J26" s="35" cm="1">
+        <f t="array" ref="J26">-SUMPRODUCT((D1:H1-C1:G1)*(C26:G26+D26:H26)/2)</f>
+        <v>0</v>
+      </c>
+      <c r="K26" s="35" cm="1">
+        <f t="array" ref="K26">-SUMPRODUCT((D1:I1-C1:H1)*(C26:H26+D26:I26)/2)</f>
+        <v>0</v>
+      </c>
+      <c r="L26" s="12" t="str">
+        <f t="shared" ref="L26:L28" si="4">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C26:I26)&amp;","</f>
+        <v xml:space="preserve">    ,</v>
+      </c>
+      <c r="M26" s="68" t="s">
+        <v>7</v>
+      </c>
+      <c r="N26" s="69"/>
+      <c r="O26" s="52"/>
+      <c r="P26" s="53"/>
+      <c r="Q26" s="53"/>
+      <c r="R26" s="53"/>
+      <c r="S26" s="53"/>
+      <c r="T26" s="53"/>
+      <c r="U26" s="54"/>
+      <c r="V26" s="12" t="str">
+        <f t="shared" ref="V26:V28" si="5">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,O26:U26)&amp;","</f>
+        <v xml:space="preserve">    ,</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="72" t="s">
+        <v>8</v>
+      </c>
+      <c r="B27" s="73"/>
+      <c r="C27" s="55"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="12"/>
+      <c r="H27" s="12"/>
+      <c r="I27" s="56"/>
+      <c r="J27" s="35" cm="1">
+        <f t="array" ref="J27">-SUMPRODUCT((D1:H1-C1:G1)*(C27:G27+D27:H27)/2)</f>
+        <v>0</v>
+      </c>
+      <c r="K27" s="35" cm="1">
+        <f t="array" ref="K27">-SUMPRODUCT((D1:I1-C1:H1)*(C27:H27+D27:I27)/2)</f>
+        <v>0</v>
+      </c>
+      <c r="L27" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">    ,</v>
+      </c>
+      <c r="M27" s="68" t="s">
+        <v>8</v>
+      </c>
+      <c r="N27" s="69"/>
+      <c r="O27" s="55"/>
+      <c r="P27" s="12"/>
+      <c r="Q27" s="12"/>
+      <c r="R27" s="12"/>
+      <c r="S27" s="12"/>
+      <c r="T27" s="12"/>
+      <c r="U27" s="56"/>
+      <c r="V27" s="12" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">    ,</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="68" t="s">
+        <v>21</v>
+      </c>
+      <c r="B28" s="69"/>
+      <c r="C28" s="55"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="12"/>
+      <c r="H28" s="12"/>
+      <c r="I28" s="56"/>
+      <c r="J28" s="35" cm="1">
+        <f t="array" ref="J28">-SUMPRODUCT((D1:H1-C1:G1)*(C28:G28+D28:H28)/2)</f>
+        <v>0</v>
+      </c>
+      <c r="K28" s="35" cm="1">
+        <f t="array" ref="K28">-SUMPRODUCT((D1:I1-C1:H1)*(C28:H28+D28:I28)/2)</f>
+        <v>0</v>
+      </c>
+      <c r="L28" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">    ,</v>
+      </c>
+      <c r="M28" s="68" t="s">
+        <v>21</v>
+      </c>
+      <c r="N28" s="69"/>
+      <c r="O28" s="55"/>
+      <c r="P28" s="12"/>
+      <c r="Q28" s="12"/>
+      <c r="R28" s="12"/>
+      <c r="S28" s="12"/>
+      <c r="T28" s="12"/>
+      <c r="U28" s="56"/>
+      <c r="V28" s="12" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">    ,</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="B29" s="69"/>
+      <c r="C29" s="57"/>
+      <c r="D29" s="58"/>
+      <c r="E29" s="58"/>
+      <c r="F29" s="58"/>
+      <c r="G29" s="58"/>
+      <c r="H29" s="58"/>
+      <c r="I29" s="59"/>
+      <c r="J29" s="35" cm="1">
+        <f t="array" ref="J29">-SUMPRODUCT((D1:H1-C1:G1)*(C29:G29+D29:H29)/2)</f>
+        <v>0</v>
+      </c>
+      <c r="K29" s="35" cm="1">
+        <f t="array" ref="K29">-SUMPRODUCT((D1:I1-C1:H1)*(C29:H29+D29:I29)/2)</f>
+        <v>0</v>
+      </c>
+      <c r="L29" s="12"/>
+      <c r="M29" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="N29" s="69"/>
+      <c r="O29" s="57"/>
+      <c r="P29" s="58"/>
+      <c r="Q29" s="58"/>
+      <c r="R29" s="58"/>
+      <c r="S29" s="58"/>
+      <c r="T29" s="58"/>
+      <c r="U29" s="59"/>
+      <c r="V29" s="12"/>
+    </row>
+    <row r="30" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="25"/>
+      <c r="B30" s="25"/>
+      <c r="C30" s="25"/>
+      <c r="D30" s="25"/>
+      <c r="E30" s="25"/>
+      <c r="F30" s="25"/>
+      <c r="G30" s="25"/>
+      <c r="H30" s="25"/>
+      <c r="I30" s="25"/>
+      <c r="J30" s="25"/>
+      <c r="K30" s="25"/>
+      <c r="M30" s="25"/>
+      <c r="N30" s="25"/>
+      <c r="O30" s="25"/>
+      <c r="P30" s="25"/>
+      <c r="Q30" s="25"/>
+      <c r="R30" s="25"/>
+      <c r="S30" s="25"/>
+      <c r="T30" s="25"/>
+      <c r="U30" s="25"/>
+    </row>
+    <row r="31" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B31" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C24" s="15">
+      <c r="C31" s="15">
         <v>1</v>
       </c>
-      <c r="D24" s="15">
+      <c r="D31" s="15">
         <v>0.75</v>
       </c>
-      <c r="E24" s="15">
+      <c r="E31" s="15">
         <v>0.5</v>
       </c>
-      <c r="F24" s="15">
+      <c r="F31" s="15">
         <v>0.3</v>
       </c>
-      <c r="G24" s="15">
+      <c r="G31" s="15">
         <v>0.2</v>
       </c>
-      <c r="H24" s="15">
+      <c r="H31" s="15">
         <v>0.1</v>
       </c>
-      <c r="I24" s="5">
+      <c r="I31" s="5">
         <v>0.05</v>
       </c>
-      <c r="J24" s="19"/>
-      <c r="K24" s="19"/>
-      <c r="L24" s="1"/>
-      <c r="M24" s="4" t="s">
+      <c r="J31" s="19"/>
+      <c r="K31" s="19"/>
+      <c r="L31" s="1"/>
+      <c r="M31" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="N24" s="5" t="s">
+      <c r="N31" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="O24" s="16">
+      <c r="O31" s="16">
         <v>1</v>
       </c>
-      <c r="P24" s="16">
+      <c r="P31" s="16">
         <v>0.75</v>
       </c>
-      <c r="Q24" s="16">
+      <c r="Q31" s="16">
         <v>0.5</v>
       </c>
-      <c r="R24" s="16">
+      <c r="R31" s="16">
         <v>0.3</v>
       </c>
-      <c r="S24" s="16">
+      <c r="S31" s="16">
         <v>0.2</v>
       </c>
-      <c r="T24" s="16">
+      <c r="T31" s="16">
         <v>0.1</v>
       </c>
-      <c r="U24" s="2">
+      <c r="U31" s="2">
         <v>0.05</v>
       </c>
-      <c r="V24" s="1"/>
-    </row>
-    <row r="25" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="68" t="s">
+      <c r="V31" s="1"/>
+    </row>
+    <row r="32" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="70" t="s">
         <v>5</v>
       </c>
-      <c r="B25" s="69"/>
-      <c r="C25" s="41">
+      <c r="B32" s="71"/>
+      <c r="C32" s="41">
         <v>92.567111769713335</v>
       </c>
-      <c r="D25" s="41">
+      <c r="D32" s="41">
         <v>90.835858608343599</v>
       </c>
-      <c r="E25" s="41">
+      <c r="E32" s="41">
         <v>89.217505339533233</v>
       </c>
-      <c r="F25" s="41">
+      <c r="F32" s="41">
         <v>83.237245964288078</v>
       </c>
-      <c r="G25" s="41">
+      <c r="G32" s="41">
         <v>75.380430844191011</v>
       </c>
-      <c r="H25" s="41">
+      <c r="H32" s="41">
         <v>58.994367187597383</v>
       </c>
-      <c r="I25" s="42">
+      <c r="I32" s="42">
         <v>43.622535641382179</v>
-      </c>
-      <c r="J25" s="44"/>
-      <c r="K25" s="44"/>
-      <c r="L25" s="1" t="str">
-        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C25:I25)&amp;","</f>
-        <v xml:space="preserve">    92.5671117697133, 90.8358586083436, 89.2175053395332, 83.2372459642881, 75.380430844191, 58.9943671875974, 43.6225356413822,</v>
-      </c>
-      <c r="M25" s="68" t="s">
-        <v>5</v>
-      </c>
-      <c r="N25" s="69"/>
-      <c r="O25" s="40">
-        <v>3.88093621561358</v>
-      </c>
-      <c r="P25" s="41">
-        <v>4.8164746829677396</v>
-      </c>
-      <c r="Q25" s="41">
-        <v>5.2250608386616522</v>
-      </c>
-      <c r="R25" s="41">
-        <v>5.6675721086724113</v>
-      </c>
-      <c r="S25" s="41">
-        <v>8.3263283482936075</v>
-      </c>
-      <c r="T25" s="41">
-        <v>10.49020927094638</v>
-      </c>
-      <c r="U25" s="42">
-        <v>11.060437347759546</v>
-      </c>
-      <c r="V25" s="1" t="str">
-        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,O25:U25)&amp;","</f>
-        <v xml:space="preserve">    3.88093621561358, 4.81647468296774, 5.22506083866165, 5.66757210867241, 8.32632834829361, 10.4902092709464, 11.0604373477595,</v>
-      </c>
-    </row>
-    <row r="26" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="68" t="s">
-        <v>6</v>
-      </c>
-      <c r="B26" s="69"/>
-      <c r="C26" s="41">
-        <v>92.866950218042462</v>
-      </c>
-      <c r="D26" s="41">
-        <v>91.242690764745561</v>
-      </c>
-      <c r="E26" s="41">
-        <v>90.137053227698445</v>
-      </c>
-      <c r="F26" s="41">
-        <v>86.080152926613408</v>
-      </c>
-      <c r="G26" s="41">
-        <v>77.410217255196784</v>
-      </c>
-      <c r="H26" s="41">
-        <v>59.676194764980139</v>
-      </c>
-      <c r="I26" s="42">
-        <v>46.395490419404197</v>
-      </c>
-      <c r="J26" s="44"/>
-      <c r="K26" s="44"/>
-      <c r="L26" s="1" t="str">
-        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C26:I26)&amp;","</f>
-        <v xml:space="preserve">    92.8669502180425, 91.2426907647456, 90.1370532276984, 86.0801529266134, 77.4102172551968, 59.6761947649801, 46.3954904194042,</v>
-      </c>
-      <c r="M26" s="68" t="s">
-        <v>6</v>
-      </c>
-      <c r="N26" s="69"/>
-      <c r="O26" s="41">
-        <v>3.8319643020864191</v>
-      </c>
-      <c r="P26" s="41">
-        <v>4.3603246705255447</v>
-      </c>
-      <c r="Q26" s="41">
-        <v>4.7987735191879262</v>
-      </c>
-      <c r="R26" s="41">
-        <v>5.1262965367330251</v>
-      </c>
-      <c r="S26" s="41">
-        <v>7.087258799823358</v>
-      </c>
-      <c r="T26" s="41">
-        <v>9.7457736576346736</v>
-      </c>
-      <c r="U26" s="42">
-        <v>10.021578856839133</v>
-      </c>
-      <c r="V26" s="1" t="str">
-        <f t="shared" ref="V26:V39" si="4">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,O26:U26)&amp;","</f>
-        <v xml:space="preserve">    3.83196430208642, 4.36032467052554, 4.79877351918793, 5.12629653673303, 7.08725879982336, 9.74577365763467, 10.0215788568391,</v>
-      </c>
-    </row>
-    <row r="27" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="68" t="s">
-        <v>10</v>
-      </c>
-      <c r="B27" s="69"/>
-      <c r="C27" s="28">
-        <v>87.268396410214976</v>
-      </c>
-      <c r="D27" s="29">
-        <v>87.256428398686779</v>
-      </c>
-      <c r="E27" s="29">
-        <v>87.822106304170404</v>
-      </c>
-      <c r="F27" s="29">
-        <v>87.68072644235157</v>
-      </c>
-      <c r="G27" s="29">
-        <v>87.144879367185226</v>
-      </c>
-      <c r="H27" s="29">
-        <v>74.976567886515753</v>
-      </c>
-      <c r="I27" s="30">
-        <v>46.41754739488244</v>
-      </c>
-      <c r="J27" s="44"/>
-      <c r="K27" s="44"/>
-      <c r="L27" s="1" t="str">
-        <f t="shared" ref="L27:L35" si="5">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C27:I27)&amp;","</f>
-        <v xml:space="preserve">    87.268396410215, 87.2564283986868, 87.8221063041704, 87.6807264423516, 87.1448793671852, 74.9765678865158, 46.4175473948824,</v>
-      </c>
-      <c r="M27" s="68" t="s">
-        <v>10</v>
-      </c>
-      <c r="N27" s="69"/>
-      <c r="O27" s="28">
-        <v>2.610595868561878</v>
-      </c>
-      <c r="P27" s="29">
-        <v>2.3209805270224559</v>
-      </c>
-      <c r="Q27" s="29">
-        <v>2.4426244152699921</v>
-      </c>
-      <c r="R27" s="29">
-        <v>2.2821255442986761</v>
-      </c>
-      <c r="S27" s="29">
-        <v>2.523131741400912</v>
-      </c>
-      <c r="T27" s="29">
-        <v>3.7626100419371111</v>
-      </c>
-      <c r="U27" s="30">
-        <v>4.1161081119796732</v>
-      </c>
-      <c r="V27" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    2.61059586856188, 2.32098052702246, 2.44262441526999, 2.28212554429868, 2.52313174140091, 3.76261004193711, 4.11610811197967,</v>
-      </c>
-    </row>
-    <row r="28" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="68" t="s">
-        <v>12</v>
-      </c>
-      <c r="B28" s="72"/>
-      <c r="C28" s="72"/>
-      <c r="D28" s="72"/>
-      <c r="E28" s="72"/>
-      <c r="F28" s="72"/>
-      <c r="G28" s="72"/>
-      <c r="H28" s="72"/>
-      <c r="I28" s="69"/>
-      <c r="J28" s="44"/>
-      <c r="K28" s="44"/>
-      <c r="L28" s="1"/>
-      <c r="M28" s="68" t="s">
-        <v>12</v>
-      </c>
-      <c r="N28" s="72"/>
-      <c r="O28" s="72"/>
-      <c r="P28" s="72"/>
-      <c r="Q28" s="72"/>
-      <c r="R28" s="72"/>
-      <c r="S28" s="72"/>
-      <c r="T28" s="72"/>
-      <c r="U28" s="69"/>
-      <c r="V28" s="1"/>
-    </row>
-    <row r="29" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="B29" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C29" s="65">
-        <v>92.975694513442221</v>
-      </c>
-      <c r="D29" s="66">
-        <v>91.363613749154311</v>
-      </c>
-      <c r="E29" s="66">
-        <v>90.094017961161143</v>
-      </c>
-      <c r="F29" s="66">
-        <v>85.37773791839254</v>
-      </c>
-      <c r="G29" s="66">
-        <v>79.268159049010507</v>
-      </c>
-      <c r="H29" s="66">
-        <v>60.52121651399365</v>
-      </c>
-      <c r="I29" s="67">
-        <v>42.05444880665619</v>
-      </c>
-      <c r="J29" s="44"/>
-      <c r="K29" s="44"/>
-      <c r="L29" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    92.9756945134422, 91.3636137491543, 90.0940179611611, 85.3777379183925, 79.2681590490105, 60.5212165139937, 42.0544488066562,</v>
-      </c>
-      <c r="M29" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="N29" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="O29" s="65">
-        <v>3.782557259829499</v>
-      </c>
-      <c r="P29" s="66">
-        <v>4.4459073754732694</v>
-      </c>
-      <c r="Q29" s="66">
-        <v>4.6323081197737448</v>
-      </c>
-      <c r="R29" s="66">
-        <v>5.3746795640933653</v>
-      </c>
-      <c r="S29" s="66">
-        <v>5.9912912250355319</v>
-      </c>
-      <c r="T29" s="66">
-        <v>9.0901817740237139</v>
-      </c>
-      <c r="U29" s="67">
-        <v>9.5108664952359483</v>
-      </c>
-      <c r="V29" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    3.7825572598295, 4.44590737547327, 4.63230811977374, 5.37467956409337, 5.99129122503553, 9.09018177402371, 9.51086649523595,</v>
-      </c>
-    </row>
-    <row r="30" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="B30" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C30" s="65">
-        <v>92.311293413260969</v>
-      </c>
-      <c r="D30" s="66">
-        <v>92.333521756806476</v>
-      </c>
-      <c r="E30" s="66">
-        <v>91.381357522919643</v>
-      </c>
-      <c r="F30" s="66">
-        <v>88.560101371956989</v>
-      </c>
-      <c r="G30" s="66">
-        <v>87.278991705998607</v>
-      </c>
-      <c r="H30" s="66">
-        <v>75.38789705567028</v>
-      </c>
-      <c r="I30" s="67">
-        <v>47.478737907175287</v>
-      </c>
-      <c r="J30" s="44"/>
-      <c r="K30" s="44"/>
-      <c r="L30" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    92.311293413261, 92.3335217568065, 91.3813575229196, 88.560101371957, 87.2789917059986, 75.3878970556703, 47.4787379071753,</v>
-      </c>
-      <c r="M30" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="N30" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="O30" s="65">
-        <v>3.45837660705662</v>
-      </c>
-      <c r="P30" s="66">
-        <v>3.6213315124355141</v>
-      </c>
-      <c r="Q30" s="66">
-        <v>3.418827656161032</v>
-      </c>
-      <c r="R30" s="66">
-        <v>3.2543979140806938</v>
-      </c>
-      <c r="S30" s="66">
-        <v>3.202126822778443</v>
-      </c>
-      <c r="T30" s="66">
-        <v>5.2358921781492196</v>
-      </c>
-      <c r="U30" s="67">
-        <v>6.1375770825509051</v>
-      </c>
-      <c r="V30" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    3.45837660705662, 3.62133151243551, 3.41882765616103, 3.25439791408069, 3.20212682277844, 5.23589217814922, 6.13757708255091,</v>
-      </c>
-    </row>
-    <row r="31" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="B31" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C31" s="97">
-        <v>92.98334081387425</v>
-      </c>
-      <c r="D31" s="98">
-        <v>92.665002460688413</v>
-      </c>
-      <c r="E31" s="98">
-        <v>91.240968563949494</v>
-      </c>
-      <c r="F31" s="98">
-        <v>84.837780429069838</v>
-      </c>
-      <c r="G31" s="98">
-        <v>75.450480295384878</v>
-      </c>
-      <c r="H31" s="98">
-        <v>59.708500699124301</v>
-      </c>
-      <c r="I31" s="99">
-        <v>46.827950364949707</v>
-      </c>
-      <c r="J31" s="44"/>
-      <c r="K31" s="44"/>
-      <c r="L31" s="1"/>
-      <c r="M31" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="N31" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="O31" s="90">
-        <v>4.047029068549703</v>
-      </c>
-      <c r="P31" s="91">
-        <v>4.0939802876249018</v>
-      </c>
-      <c r="Q31" s="91">
-        <v>4.4520389395614499</v>
-      </c>
-      <c r="R31" s="91">
-        <v>5.8725133520041934</v>
-      </c>
-      <c r="S31" s="91">
-        <v>9.1198860433459092</v>
-      </c>
-      <c r="T31" s="91">
-        <v>11.4228840807754</v>
-      </c>
-      <c r="U31" s="92">
-        <v>9.7047317426323225</v>
-      </c>
-      <c r="V31" s="1"/>
-    </row>
-    <row r="32" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="B32" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C32" s="65">
-        <v>93.003107171421291</v>
-      </c>
-      <c r="D32" s="66">
-        <v>92.882665900806714</v>
-      </c>
-      <c r="E32" s="66">
-        <v>92.323250249861715</v>
-      </c>
-      <c r="F32" s="66">
-        <v>87.896361279111929</v>
-      </c>
-      <c r="G32" s="66">
-        <v>80.149965599113543</v>
-      </c>
-      <c r="H32" s="66">
-        <v>57.360910597574737</v>
-      </c>
-      <c r="I32" s="67">
-        <v>43.986149507359343</v>
       </c>
       <c r="J32" s="44"/>
       <c r="K32" s="44"/>
-      <c r="L32" s="1"/>
-      <c r="M32" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="N32" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="O32" s="65">
-        <v>3.8815673789284708</v>
-      </c>
-      <c r="P32" s="66">
-        <v>4.3723258101522813</v>
-      </c>
-      <c r="Q32" s="66">
-        <v>4.2934275551121281</v>
-      </c>
-      <c r="R32" s="66">
-        <v>5.2017150988587044</v>
-      </c>
-      <c r="S32" s="66">
-        <v>7.2625504458350916</v>
-      </c>
-      <c r="T32" s="66">
-        <v>11.40658683680142</v>
-      </c>
-      <c r="U32" s="67">
-        <v>9.5393474867950871</v>
-      </c>
-      <c r="V32" s="1"/>
+      <c r="L32" s="1" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C32:I32)&amp;","</f>
+        <v xml:space="preserve">    92.5671117697133, 90.8358586083436, 89.2175053395332, 83.2372459642881, 75.380430844191, 58.9943671875974, 43.6225356413822,</v>
+      </c>
+      <c r="M32" s="70" t="s">
+        <v>5</v>
+      </c>
+      <c r="N32" s="71"/>
+      <c r="O32" s="40">
+        <v>3.88093621561358</v>
+      </c>
+      <c r="P32" s="41">
+        <v>4.8164746829677396</v>
+      </c>
+      <c r="Q32" s="41">
+        <v>5.2250608386616522</v>
+      </c>
+      <c r="R32" s="41">
+        <v>5.6675721086724113</v>
+      </c>
+      <c r="S32" s="41">
+        <v>8.3263283482936075</v>
+      </c>
+      <c r="T32" s="41">
+        <v>10.49020927094638</v>
+      </c>
+      <c r="U32" s="42">
+        <v>11.060437347759546</v>
+      </c>
+      <c r="V32" s="1" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,O32:U32)&amp;","</f>
+        <v xml:space="preserve">    3.88093621561358, 4.81647468296774, 5.22506083866165, 5.66757210867241, 8.32632834829361, 10.4902092709464, 11.0604373477595,</v>
+      </c>
     </row>
     <row r="33" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="B33" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C33" s="97">
-        <v>92.988386774165761</v>
-      </c>
-      <c r="D33" s="98">
-        <v>92.050616029386802</v>
-      </c>
-      <c r="E33" s="98">
-        <v>90.719698676196401</v>
-      </c>
-      <c r="F33" s="98">
-        <v>88.185686945633506</v>
-      </c>
-      <c r="G33" s="98">
-        <v>83.275334389555965</v>
-      </c>
-      <c r="H33" s="98">
-        <v>64.685401955234482</v>
-      </c>
-      <c r="I33" s="99">
-        <v>51.069046974801182</v>
+      <c r="A33" s="70" t="s">
+        <v>6</v>
+      </c>
+      <c r="B33" s="71"/>
+      <c r="C33" s="41">
+        <v>92.866950218042462</v>
+      </c>
+      <c r="D33" s="41">
+        <v>91.242690764745561</v>
+      </c>
+      <c r="E33" s="41">
+        <v>90.137053227698445</v>
+      </c>
+      <c r="F33" s="41">
+        <v>86.080152926613408</v>
+      </c>
+      <c r="G33" s="41">
+        <v>77.410217255196784</v>
+      </c>
+      <c r="H33" s="41">
+        <v>59.676194764980139</v>
+      </c>
+      <c r="I33" s="42">
+        <v>46.395490419404197</v>
       </c>
       <c r="J33" s="44"/>
       <c r="K33" s="44"/>
       <c r="L33" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    92.9883867741658, 92.0506160293868, 90.7196986761964, 88.1856869456335, 83.275334389556, 64.6854019552345, 51.0690469748012,</v>
-      </c>
-      <c r="M33" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="N33" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="O33" s="97">
-        <v>3.845990120862357</v>
-      </c>
-      <c r="P33" s="98">
-        <v>4.1197830115536282</v>
-      </c>
-      <c r="Q33" s="98">
-        <v>3.9254290526154212</v>
-      </c>
-      <c r="R33" s="98">
-        <v>4.2886830099031732</v>
-      </c>
-      <c r="S33" s="98">
-        <v>5.0859486951315533</v>
-      </c>
-      <c r="T33" s="98">
-        <v>7.2871022167686217</v>
-      </c>
-      <c r="U33" s="99">
-        <v>6.9147061894583581</v>
-      </c>
-      <c r="V33" s="1"/>
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C33:I33)&amp;","</f>
+        <v xml:space="preserve">    92.8669502180425, 91.2426907647456, 90.1370532276984, 86.0801529266134, 77.4102172551968, 59.6761947649801, 46.3954904194042,</v>
+      </c>
+      <c r="M33" s="70" t="s">
+        <v>6</v>
+      </c>
+      <c r="N33" s="71"/>
+      <c r="O33" s="41">
+        <v>3.8319643020864191</v>
+      </c>
+      <c r="P33" s="41">
+        <v>4.3603246705255447</v>
+      </c>
+      <c r="Q33" s="41">
+        <v>4.7987735191879262</v>
+      </c>
+      <c r="R33" s="41">
+        <v>5.1262965367330251</v>
+      </c>
+      <c r="S33" s="41">
+        <v>7.087258799823358</v>
+      </c>
+      <c r="T33" s="41">
+        <v>9.7457736576346736</v>
+      </c>
+      <c r="U33" s="42">
+        <v>10.021578856839133</v>
+      </c>
+      <c r="V33" s="1" t="str">
+        <f t="shared" ref="V33:V48" si="6">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,O33:U33)&amp;","</f>
+        <v xml:space="preserve">    3.83196430208642, 4.36032467052554, 4.79877351918793, 5.12629653673303, 7.08725879982336, 9.74577365763467, 10.0215788568391,</v>
+      </c>
     </row>
     <row r="34" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="B34" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="C34" s="65">
-        <v>89.74449346032101</v>
-      </c>
-      <c r="D34" s="66">
-        <v>89.961854893326574</v>
-      </c>
-      <c r="E34" s="66">
-        <v>90.011537582574022</v>
-      </c>
-      <c r="F34" s="66">
-        <v>90.064770133428496</v>
-      </c>
-      <c r="G34" s="66">
-        <v>88.967446677518851</v>
-      </c>
-      <c r="H34" s="66">
-        <v>80.083589667611676</v>
-      </c>
-      <c r="I34" s="67">
-        <v>52.982008110476087</v>
+      <c r="A34" s="70" t="s">
+        <v>10</v>
+      </c>
+      <c r="B34" s="71"/>
+      <c r="C34" s="28">
+        <v>87.268396410214976</v>
+      </c>
+      <c r="D34" s="29">
+        <v>87.256428398686779</v>
+      </c>
+      <c r="E34" s="29">
+        <v>87.822106304170404</v>
+      </c>
+      <c r="F34" s="29">
+        <v>87.68072644235157</v>
+      </c>
+      <c r="G34" s="29">
+        <v>87.144879367185226</v>
+      </c>
+      <c r="H34" s="29">
+        <v>74.976567886515753</v>
+      </c>
+      <c r="I34" s="30">
+        <v>46.41754739488244</v>
       </c>
       <c r="J34" s="44"/>
       <c r="K34" s="44"/>
-      <c r="L34" s="1"/>
-      <c r="M34" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="N34" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="O34" s="65">
-        <v>2.9793986812049931</v>
-      </c>
-      <c r="P34" s="66">
-        <v>2.5386471681353431</v>
-      </c>
-      <c r="Q34" s="66">
-        <v>2.4449126963196481</v>
-      </c>
-      <c r="R34" s="66">
-        <v>2.6222789037595908</v>
-      </c>
-      <c r="S34" s="66">
-        <v>2.7817641077346069</v>
-      </c>
-      <c r="T34" s="66">
-        <v>4.0935792052005926</v>
-      </c>
-      <c r="U34" s="67">
-        <v>6.5884863469929558</v>
-      </c>
-      <c r="V34" s="1"/>
+      <c r="L34" s="1" t="str">
+        <f t="shared" ref="L34:L43" si="7">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C34:I34)&amp;","</f>
+        <v xml:space="preserve">    87.268396410215, 87.2564283986868, 87.8221063041704, 87.6807264423516, 87.1448793671852, 74.9765678865158, 46.4175473948824,</v>
+      </c>
+      <c r="M34" s="70" t="s">
+        <v>10</v>
+      </c>
+      <c r="N34" s="71"/>
+      <c r="O34" s="28">
+        <v>2.610595868561878</v>
+      </c>
+      <c r="P34" s="29">
+        <v>2.3209805270224559</v>
+      </c>
+      <c r="Q34" s="29">
+        <v>2.4426244152699921</v>
+      </c>
+      <c r="R34" s="29">
+        <v>2.2821255442986761</v>
+      </c>
+      <c r="S34" s="29">
+        <v>2.523131741400912</v>
+      </c>
+      <c r="T34" s="29">
+        <v>3.7626100419371111</v>
+      </c>
+      <c r="U34" s="30">
+        <v>4.1161081119796732</v>
+      </c>
+      <c r="V34" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    2.61059586856188, 2.32098052702246, 2.44262441526999, 2.28212554429868, 2.52313174140091, 3.76261004193711, 4.11610811197967,</v>
+      </c>
     </row>
     <row r="35" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="B35" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C35" s="97">
-        <v>87.287634799049286</v>
-      </c>
-      <c r="D35" s="98">
-        <v>86.878696750662726</v>
-      </c>
-      <c r="E35" s="98">
-        <v>87.083363148466532</v>
-      </c>
-      <c r="F35" s="98">
-        <v>87.300294897904948</v>
-      </c>
-      <c r="G35" s="98">
-        <v>86.527431822215689</v>
-      </c>
-      <c r="H35" s="98">
-        <v>75.689128775848914</v>
-      </c>
-      <c r="I35" s="99">
-        <v>46.886907074094779</v>
-      </c>
+      <c r="A35" s="70" t="s">
+        <v>12</v>
+      </c>
+      <c r="B35" s="78"/>
+      <c r="C35" s="78"/>
+      <c r="D35" s="78"/>
+      <c r="E35" s="78"/>
+      <c r="F35" s="78"/>
+      <c r="G35" s="78"/>
+      <c r="H35" s="78"/>
+      <c r="I35" s="71"/>
       <c r="J35" s="44"/>
       <c r="K35" s="44"/>
-      <c r="L35" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    87.2876347990493, 86.8786967506627, 87.0833631484665, 87.3002948979049, 86.5274318222157, 75.6891287758489, 46.8869070740948,</v>
-      </c>
-      <c r="M35" s="14" t="s">
+      <c r="L35" s="1"/>
+      <c r="M35" s="70" t="s">
+        <v>12</v>
+      </c>
+      <c r="N35" s="78"/>
+      <c r="O35" s="78"/>
+      <c r="P35" s="78"/>
+      <c r="Q35" s="78"/>
+      <c r="R35" s="78"/>
+      <c r="S35" s="78"/>
+      <c r="T35" s="78"/>
+      <c r="U35" s="71"/>
+      <c r="V35" s="1"/>
+    </row>
+    <row r="36" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="83" t="s">
         <v>11</v>
       </c>
-      <c r="N35" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="O35" s="97">
-        <v>2.5152339820278629</v>
-      </c>
-      <c r="P35" s="98">
-        <v>2.5980079882709322</v>
-      </c>
-      <c r="Q35" s="98">
-        <v>2.0296317104437578</v>
-      </c>
-      <c r="R35" s="98">
-        <v>2.161003670540631</v>
-      </c>
-      <c r="S35" s="98">
-        <v>1.7804591714461351</v>
-      </c>
-      <c r="T35" s="98">
-        <v>3.6175089321994709</v>
-      </c>
-      <c r="U35" s="99">
-        <v>4.0563769517378363</v>
-      </c>
-      <c r="V35" s="1"/>
-    </row>
-    <row r="36" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="68" t="s">
-        <v>20</v>
-      </c>
-      <c r="B36" s="72"/>
-      <c r="C36" s="75"/>
-      <c r="D36" s="75"/>
-      <c r="E36" s="75"/>
-      <c r="F36" s="75"/>
-      <c r="G36" s="75"/>
-      <c r="H36" s="75"/>
-      <c r="I36" s="71"/>
+      <c r="B36" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C36" s="65">
+        <v>92.975694513442221</v>
+      </c>
+      <c r="D36" s="66">
+        <v>91.363613749154311</v>
+      </c>
+      <c r="E36" s="66">
+        <v>90.094017961161143</v>
+      </c>
+      <c r="F36" s="66">
+        <v>85.37773791839254</v>
+      </c>
+      <c r="G36" s="66">
+        <v>79.268159049010507</v>
+      </c>
+      <c r="H36" s="66">
+        <v>60.52121651399365</v>
+      </c>
+      <c r="I36" s="67">
+        <v>42.05444880665619</v>
+      </c>
       <c r="J36" s="44"/>
       <c r="K36" s="44"/>
-      <c r="L36" s="1"/>
-      <c r="M36" s="68" t="s">
-        <v>20</v>
-      </c>
-      <c r="N36" s="72"/>
-      <c r="O36" s="75"/>
-      <c r="P36" s="75"/>
-      <c r="Q36" s="75"/>
-      <c r="R36" s="75"/>
-      <c r="S36" s="75"/>
-      <c r="T36" s="75"/>
-      <c r="U36" s="71"/>
-      <c r="V36" s="1"/>
-    </row>
-    <row r="37" spans="1:22" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="68" t="s">
-        <v>7</v>
-      </c>
-      <c r="B37" s="69"/>
-      <c r="C37" s="60">
-        <v>93.403798109785029</v>
-      </c>
-      <c r="D37" s="61">
-        <v>91.51700700493744</v>
-      </c>
-      <c r="E37" s="61">
-        <v>89.749880462689262</v>
-      </c>
-      <c r="F37" s="61">
-        <v>83.99730958119234</v>
-      </c>
-      <c r="G37" s="61">
-        <v>74.394962965986878</v>
-      </c>
-      <c r="H37" s="61">
-        <v>58.095582470498513</v>
-      </c>
-      <c r="I37" s="62">
-        <v>44.434812706207254</v>
+      <c r="L36" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">    92.9756945134422, 91.3636137491543, 90.0940179611611, 85.3777379183925, 79.2681590490105, 60.5212165139937, 42.0544488066562,</v>
+      </c>
+      <c r="M36" s="83" t="s">
+        <v>11</v>
+      </c>
+      <c r="N36" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="O36" s="65">
+        <v>3.782557259829499</v>
+      </c>
+      <c r="P36" s="66">
+        <v>4.4459073754732694</v>
+      </c>
+      <c r="Q36" s="66">
+        <v>4.6323081197737448</v>
+      </c>
+      <c r="R36" s="66">
+        <v>5.3746795640933653</v>
+      </c>
+      <c r="S36" s="66">
+        <v>5.9912912250355319</v>
+      </c>
+      <c r="T36" s="66">
+        <v>9.0901817740237139</v>
+      </c>
+      <c r="U36" s="67">
+        <v>9.5108664952359483</v>
+      </c>
+      <c r="V36" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    3.7825572598295, 4.44590737547327, 4.63230811977374, 5.37467956409337, 5.99129122503553, 9.09018177402371, 9.51086649523595,</v>
+      </c>
+    </row>
+    <row r="37" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="86"/>
+      <c r="B37" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C37" s="65">
+        <v>92.311293413260969</v>
+      </c>
+      <c r="D37" s="66">
+        <v>92.333521756806476</v>
+      </c>
+      <c r="E37" s="66">
+        <v>91.381357522919643</v>
+      </c>
+      <c r="F37" s="66">
+        <v>88.560101371956989</v>
+      </c>
+      <c r="G37" s="66">
+        <v>87.278991705998607</v>
+      </c>
+      <c r="H37" s="66">
+        <v>75.38789705567028</v>
+      </c>
+      <c r="I37" s="67">
+        <v>47.478737907175287</v>
       </c>
       <c r="J37" s="44"/>
       <c r="K37" s="44"/>
       <c r="L37" s="1" t="str">
-        <f t="shared" ref="L37:L39" si="6">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C37:I37)&amp;","</f>
-        <v xml:space="preserve">    93.403798109785, 91.5170070049374, 89.7498804626893, 83.9973095811923, 74.3949629659869, 58.0955824704985, 44.4348127062073,</v>
-      </c>
-      <c r="M37" s="68" t="s">
-        <v>7</v>
-      </c>
-      <c r="N37" s="69"/>
-      <c r="O37" s="60">
-        <v>3.9553866501853321</v>
-      </c>
-      <c r="P37" s="61">
-        <v>4.517630835861226</v>
-      </c>
-      <c r="Q37" s="61">
-        <v>5.2125425794506972</v>
-      </c>
-      <c r="R37" s="61">
-        <v>5.6477461387684551</v>
-      </c>
-      <c r="S37" s="61">
-        <v>8.6090564713117175</v>
-      </c>
-      <c r="T37" s="61">
-        <v>11.357157347254571</v>
-      </c>
-      <c r="U37" s="62">
-        <v>9.3757621724255777</v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">    92.311293413261, 92.3335217568065, 91.3813575229196, 88.560101371957, 87.2789917059986, 75.3878970556703, 47.4787379071753,</v>
+      </c>
+      <c r="M37" s="86"/>
+      <c r="N37" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="O37" s="65">
+        <v>3.45837660705662</v>
+      </c>
+      <c r="P37" s="66">
+        <v>3.6213315124355141</v>
+      </c>
+      <c r="Q37" s="66">
+        <v>3.418827656161032</v>
+      </c>
+      <c r="R37" s="66">
+        <v>3.2543979140806938</v>
+      </c>
+      <c r="S37" s="66">
+        <v>3.202126822778443</v>
+      </c>
+      <c r="T37" s="66">
+        <v>5.2358921781492196</v>
+      </c>
+      <c r="U37" s="67">
+        <v>6.1375770825509051</v>
       </c>
       <c r="V37" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    3.95538665018533, 4.51763083586123, 5.2125425794507, 5.64774613876846, 8.60905647131172, 11.3571573472546, 9.37576217242558,</v>
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    3.45837660705662, 3.62133151243551, 3.41882765616103, 3.25439791408069, 3.20212682277844, 5.23589217814922, 6.13757708255091,</v>
       </c>
     </row>
     <row r="38" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="68" t="s">
-        <v>8</v>
-      </c>
-      <c r="B38" s="69"/>
-      <c r="C38" s="63">
-        <v>92.778947400409621</v>
-      </c>
-      <c r="D38" s="1">
-        <v>91.450368996373655</v>
-      </c>
-      <c r="E38" s="1">
-        <v>89.879480954542075</v>
-      </c>
-      <c r="F38" s="1">
-        <v>84.748756470336986</v>
-      </c>
-      <c r="G38" s="1">
-        <v>75.627608782580538</v>
-      </c>
-      <c r="H38" s="1">
-        <v>58.300265665116903</v>
-      </c>
-      <c r="I38" s="64">
-        <v>48.584106437626268</v>
+      <c r="A38" s="86"/>
+      <c r="B38" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C38" s="65">
+        <v>92.98334081387425</v>
+      </c>
+      <c r="D38" s="66">
+        <v>92.665002460688413</v>
+      </c>
+      <c r="E38" s="66">
+        <v>91.240968563949494</v>
+      </c>
+      <c r="F38" s="66">
+        <v>84.837780429069838</v>
+      </c>
+      <c r="G38" s="66">
+        <v>75.450480295384878</v>
+      </c>
+      <c r="H38" s="66">
+        <v>59.708500699124301</v>
+      </c>
+      <c r="I38" s="67">
+        <v>46.827950364949707</v>
       </c>
       <c r="J38" s="44"/>
       <c r="K38" s="44"/>
-      <c r="L38" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">    92.7789474004096, 91.4503689963737, 89.8794809545421, 84.748756470337, 75.6276087825805, 58.3002656651169, 48.5841064376263,</v>
-      </c>
-      <c r="M38" s="68" t="s">
-        <v>8</v>
-      </c>
-      <c r="N38" s="69"/>
-      <c r="O38" s="63">
-        <v>4.3743918396131134</v>
-      </c>
-      <c r="P38" s="1">
-        <v>5.1779143655465321</v>
-      </c>
-      <c r="Q38" s="1">
-        <v>4.8362705721377752</v>
-      </c>
-      <c r="R38" s="1">
-        <v>5.6797782301447892</v>
-      </c>
-      <c r="S38" s="1">
-        <v>9.0190902977959446</v>
-      </c>
-      <c r="T38" s="1">
-        <v>11.000258135261941</v>
-      </c>
-      <c r="U38" s="64">
-        <v>9.2918474149187738</v>
-      </c>
-      <c r="V38" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    4.37439183961311, 5.17791436554653, 4.83627057213778, 5.67977823014479, 9.01909029779594, 11.0002581352619, 9.29184741491877,</v>
-      </c>
+      <c r="L38" s="1"/>
+      <c r="M38" s="86"/>
+      <c r="N38" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O38" s="65">
+        <v>4.047029068549703</v>
+      </c>
+      <c r="P38" s="66">
+        <v>4.0939802876249018</v>
+      </c>
+      <c r="Q38" s="66">
+        <v>4.4520389395614499</v>
+      </c>
+      <c r="R38" s="66">
+        <v>5.8725133520041934</v>
+      </c>
+      <c r="S38" s="66">
+        <v>9.1198860433459092</v>
+      </c>
+      <c r="T38" s="66">
+        <v>11.4228840807754</v>
+      </c>
+      <c r="U38" s="67">
+        <v>9.7047317426323225</v>
+      </c>
+      <c r="V38" s="1"/>
     </row>
     <row r="39" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="68" t="s">
-        <v>21</v>
-      </c>
-      <c r="B39" s="69"/>
-      <c r="C39" s="63">
-        <v>92.492055194421354</v>
-      </c>
-      <c r="D39" s="1">
-        <v>91.055738083245984</v>
-      </c>
-      <c r="E39" s="1">
-        <v>89.241264887762341</v>
-      </c>
-      <c r="F39" s="1">
-        <v>82.713601809643421</v>
-      </c>
-      <c r="G39" s="1">
-        <v>73.133677048774885</v>
-      </c>
-      <c r="H39" s="1">
-        <v>56.229205901331248</v>
-      </c>
-      <c r="I39" s="64">
-        <v>43.695396708102962</v>
+      <c r="A39" s="86"/>
+      <c r="B39" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C39" s="65">
+        <v>93.003107171421291</v>
+      </c>
+      <c r="D39" s="66">
+        <v>92.882665900806714</v>
+      </c>
+      <c r="E39" s="66">
+        <v>92.323250249861715</v>
+      </c>
+      <c r="F39" s="66">
+        <v>87.896361279111929</v>
+      </c>
+      <c r="G39" s="66">
+        <v>80.149965599113543</v>
+      </c>
+      <c r="H39" s="66">
+        <v>57.360910597574737</v>
+      </c>
+      <c r="I39" s="67">
+        <v>43.986149507359343</v>
       </c>
       <c r="J39" s="44"/>
       <c r="K39" s="44"/>
-      <c r="L39" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">    92.4920551944214, 91.055738083246, 89.2412648877623, 82.7136018096434, 73.1336770487749, 56.2292059013312, 43.695396708103,</v>
-      </c>
-      <c r="M39" s="68" t="s">
-        <v>21</v>
-      </c>
-      <c r="N39" s="69"/>
-      <c r="O39" s="63">
-        <v>4.0986250609792014</v>
-      </c>
-      <c r="P39" s="1">
-        <v>4.5926443490712341</v>
-      </c>
-      <c r="Q39" s="1">
-        <v>4.8521598807380544</v>
-      </c>
-      <c r="R39" s="1">
-        <v>5.8188919126166327</v>
-      </c>
-      <c r="S39" s="1">
-        <v>9.5088987825376563</v>
-      </c>
-      <c r="T39" s="1">
-        <v>11.32839542788332</v>
-      </c>
-      <c r="U39" s="64">
-        <v>10.62887090695313</v>
-      </c>
-      <c r="V39" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    4.0986250609792, 4.59264434907123, 4.85215988073805, 5.81889191261663, 9.50889878253766, 11.3283954278833, 10.6288709069531,</v>
-      </c>
+      <c r="L39" s="1"/>
+      <c r="M39" s="86"/>
+      <c r="N39" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="O39" s="65">
+        <v>3.8815673789284708</v>
+      </c>
+      <c r="P39" s="66">
+        <v>4.3723258101522813</v>
+      </c>
+      <c r="Q39" s="66">
+        <v>4.2934275551121281</v>
+      </c>
+      <c r="R39" s="66">
+        <v>5.2017150988587044</v>
+      </c>
+      <c r="S39" s="66">
+        <v>7.2625504458350916</v>
+      </c>
+      <c r="T39" s="66">
+        <v>11.40658683680142</v>
+      </c>
+      <c r="U39" s="67">
+        <v>9.5393474867950871</v>
+      </c>
+      <c r="V39" s="1"/>
     </row>
     <row r="40" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="68" t="s">
-        <v>22</v>
-      </c>
-      <c r="B40" s="69"/>
+      <c r="A40" s="86"/>
+      <c r="B40" s="9" t="s">
+        <v>15</v>
+      </c>
       <c r="C40" s="65">
-        <v>92.657174075741665</v>
+        <v>92.988386774165761</v>
       </c>
       <c r="D40" s="66">
-        <v>91.208050814372243</v>
+        <v>92.050616029386802</v>
       </c>
       <c r="E40" s="66">
-        <v>89.170455678091372</v>
+        <v>90.719698676196401</v>
       </c>
       <c r="F40" s="66">
-        <v>84.474616062770011</v>
+        <v>88.185686945633506</v>
       </c>
       <c r="G40" s="66">
-        <v>75.066668593640316</v>
+        <v>83.275334389555965</v>
       </c>
       <c r="H40" s="66">
-        <v>58.520340993368222</v>
+        <v>64.685401955234482</v>
       </c>
       <c r="I40" s="67">
-        <v>44.786141592049418</v>
-      </c>
-      <c r="J40" s="51"/>
-      <c r="K40" s="51"/>
-      <c r="L40" s="50"/>
-      <c r="M40" s="68" t="s">
-        <v>22</v>
-      </c>
-      <c r="N40" s="69"/>
+        <v>51.069046974801182</v>
+      </c>
+      <c r="J40" s="44"/>
+      <c r="K40" s="44"/>
+      <c r="L40" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">    92.9883867741658, 92.0506160293868, 90.7196986761964, 88.1856869456335, 83.275334389556, 64.6854019552345, 51.0690469748012,</v>
+      </c>
+      <c r="M40" s="86"/>
+      <c r="N40" s="9" t="s">
+        <v>15</v>
+      </c>
       <c r="O40" s="65">
-        <v>4.2589004392769629</v>
+        <v>3.845990120862357</v>
       </c>
       <c r="P40" s="66">
-        <v>4.8517186601265534</v>
+        <v>4.1197830115536282</v>
       </c>
       <c r="Q40" s="66">
-        <v>5.6717673083496472</v>
+        <v>3.9254290526154212</v>
       </c>
       <c r="R40" s="66">
-        <v>5.3079507961921779</v>
+        <v>4.2886830099031732</v>
       </c>
       <c r="S40" s="66">
-        <v>7.7884705615072454</v>
+        <v>5.0859486951315533</v>
       </c>
       <c r="T40" s="66">
-        <v>10.595563377926201</v>
+        <v>7.2871022167686217</v>
       </c>
       <c r="U40" s="67">
-        <v>10.945843294214329</v>
+        <v>6.9147061894583581</v>
       </c>
       <c r="V40" s="1"/>
     </row>
-    <row r="41" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="68" t="s">
-        <v>23</v>
-      </c>
-      <c r="B41" s="72"/>
-      <c r="C41" s="73"/>
-      <c r="D41" s="73"/>
-      <c r="E41" s="73"/>
-      <c r="F41" s="73"/>
-      <c r="G41" s="73"/>
-      <c r="H41" s="73"/>
-      <c r="I41" s="74"/>
+    <row r="41" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="86"/>
+      <c r="B41" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C41" s="93">
+        <v>90.557937802976383</v>
+      </c>
+      <c r="D41" s="94">
+        <v>89.886230037289053</v>
+      </c>
+      <c r="E41" s="94">
+        <v>89.784544221380457</v>
+      </c>
+      <c r="F41" s="94">
+        <v>88.385012329947799</v>
+      </c>
+      <c r="G41" s="94">
+        <v>86.648926570357631</v>
+      </c>
+      <c r="H41" s="94">
+        <v>75.600385397228763</v>
+      </c>
+      <c r="I41" s="95">
+        <v>46.810733956645073</v>
+      </c>
       <c r="J41" s="44"/>
       <c r="K41" s="44"/>
       <c r="L41" s="1"/>
-      <c r="M41" s="68" t="s">
-        <v>23</v>
-      </c>
-      <c r="N41" s="72"/>
-      <c r="O41" s="73"/>
-      <c r="P41" s="73"/>
-      <c r="Q41" s="73"/>
-      <c r="R41" s="73"/>
-      <c r="S41" s="73"/>
-      <c r="T41" s="73"/>
-      <c r="U41" s="74"/>
+      <c r="M41" s="86"/>
+      <c r="N41" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="O41" s="93">
+        <v>3.5359425091643861</v>
+      </c>
+      <c r="P41" s="94">
+        <v>2.9479688908817572</v>
+      </c>
+      <c r="Q41" s="94">
+        <v>3.0863691442002841</v>
+      </c>
+      <c r="R41" s="94">
+        <v>2.7063960445241841</v>
+      </c>
+      <c r="S41" s="94">
+        <v>3.1149226793442399</v>
+      </c>
+      <c r="T41" s="94">
+        <v>3.6181303084227601</v>
+      </c>
+      <c r="U41" s="95">
+        <v>2.9939108090159601</v>
+      </c>
       <c r="V41" s="1"/>
     </row>
-    <row r="42" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="68" t="s">
-        <v>7</v>
-      </c>
-      <c r="B42" s="69"/>
-      <c r="C42" s="60">
-        <v>92.603769819293618</v>
-      </c>
-      <c r="D42" s="61">
-        <v>91.431947068352812</v>
-      </c>
-      <c r="E42" s="61">
-        <v>90.390795042999585</v>
-      </c>
-      <c r="F42" s="61">
-        <v>86.789562828222273</v>
-      </c>
-      <c r="G42" s="61">
-        <v>80.615554033052248</v>
-      </c>
-      <c r="H42" s="61">
-        <v>56.609578553133908</v>
-      </c>
-      <c r="I42" s="62">
-        <v>41.27928062292434</v>
+    <row r="42" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="86"/>
+      <c r="B42" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C42" s="65">
+        <v>89.74449346032101</v>
+      </c>
+      <c r="D42" s="66">
+        <v>89.961854893326574</v>
+      </c>
+      <c r="E42" s="66">
+        <v>90.011537582574022</v>
+      </c>
+      <c r="F42" s="66">
+        <v>90.064770133428496</v>
+      </c>
+      <c r="G42" s="66">
+        <v>88.967446677518851</v>
+      </c>
+      <c r="H42" s="66">
+        <v>80.083589667611676</v>
+      </c>
+      <c r="I42" s="67">
+        <v>52.982008110476087</v>
       </c>
       <c r="J42" s="44"/>
       <c r="K42" s="44"/>
-      <c r="L42" s="1" t="str">
-        <f t="shared" ref="L42:L44" si="7">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C42:I42)&amp;","</f>
-        <v xml:space="preserve">    92.6037698192936, 91.4319470683528, 90.3907950429996, 86.7895628282223, 80.6155540330522, 56.6095785531339, 41.2792806229243,</v>
-      </c>
-      <c r="M42" s="68" t="s">
-        <v>7</v>
-      </c>
-      <c r="N42" s="69"/>
-      <c r="O42" s="60">
-        <v>3.708759274801273</v>
-      </c>
-      <c r="P42" s="61">
-        <v>3.9640390541215931</v>
-      </c>
-      <c r="Q42" s="61">
-        <v>3.7067998106756881</v>
-      </c>
-      <c r="R42" s="61">
-        <v>3.667452632531309</v>
-      </c>
-      <c r="S42" s="61">
-        <v>5.7548227051500218</v>
-      </c>
-      <c r="T42" s="61">
-        <v>8.5366536877555248</v>
-      </c>
-      <c r="U42" s="62">
-        <v>6.3187793027043018</v>
-      </c>
-      <c r="V42" s="1" t="str">
-        <f t="shared" ref="V42:V44" si="8">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,O42:U42)&amp;","</f>
-        <v xml:space="preserve">    3.70875927480127, 3.96403905412159, 3.70679981067569, 3.66745263253131, 5.75482270515002, 8.53665368775552, 6.3187793027043,</v>
-      </c>
-    </row>
-    <row r="43" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="70" t="s">
-        <v>8</v>
-      </c>
-      <c r="B43" s="71"/>
-      <c r="C43" s="63">
-        <v>91.377634404932721</v>
-      </c>
-      <c r="D43" s="1">
-        <v>90.405373333245066</v>
-      </c>
-      <c r="E43" s="1">
-        <v>89.371480308332721</v>
-      </c>
-      <c r="F43" s="1">
-        <v>87.60989862639515</v>
-      </c>
-      <c r="G43" s="1">
-        <v>85.537230701510694</v>
-      </c>
-      <c r="H43" s="1">
-        <v>70.930708745421484</v>
-      </c>
-      <c r="I43" s="64">
-        <v>44.097326232806537</v>
+      <c r="L42" s="1"/>
+      <c r="M42" s="86"/>
+      <c r="N42" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="O42" s="65">
+        <v>2.9793986812049931</v>
+      </c>
+      <c r="P42" s="66">
+        <v>2.5386471681353431</v>
+      </c>
+      <c r="Q42" s="66">
+        <v>2.4449126963196481</v>
+      </c>
+      <c r="R42" s="66">
+        <v>2.6222789037595908</v>
+      </c>
+      <c r="S42" s="66">
+        <v>2.7817641077346069</v>
+      </c>
+      <c r="T42" s="66">
+        <v>4.0935792052005926</v>
+      </c>
+      <c r="U42" s="67">
+        <v>6.5884863469929558</v>
+      </c>
+      <c r="V42" s="1"/>
+    </row>
+    <row r="43" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="86"/>
+      <c r="B43" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C43" s="65">
+        <v>87.287634799049286</v>
+      </c>
+      <c r="D43" s="66">
+        <v>86.878696750662726</v>
+      </c>
+      <c r="E43" s="66">
+        <v>87.083363148466532</v>
+      </c>
+      <c r="F43" s="66">
+        <v>87.300294897904948</v>
+      </c>
+      <c r="G43" s="66">
+        <v>86.527431822215689</v>
+      </c>
+      <c r="H43" s="66">
+        <v>75.689128775848914</v>
+      </c>
+      <c r="I43" s="67">
+        <v>46.886907074094779</v>
       </c>
       <c r="J43" s="44"/>
       <c r="K43" s="44"/>
       <c r="L43" s="1" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">    91.3776344049327, 90.4053733332451, 89.3714803083327, 87.6098986263952, 85.5372307015107, 70.9307087454215, 44.0973262328065,</v>
-      </c>
-      <c r="M43" s="68" t="s">
-        <v>8</v>
-      </c>
-      <c r="N43" s="69"/>
-      <c r="O43" s="63">
-        <v>3.5684194304484111</v>
-      </c>
-      <c r="P43" s="1">
-        <v>3.0347581440341318</v>
-      </c>
-      <c r="Q43" s="1">
-        <v>2.754130276526872</v>
-      </c>
-      <c r="R43" s="1">
-        <v>2.7768782002466339</v>
-      </c>
-      <c r="S43" s="1">
-        <v>3.3184641894178428</v>
-      </c>
-      <c r="T43" s="1">
-        <v>4.9795199020249923</v>
-      </c>
-      <c r="U43" s="64">
-        <v>2.9223071611371929</v>
-      </c>
-      <c r="V43" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">    3.56841943044841, 3.03475814403413, 2.75413027652687, 2.77687820024663, 3.31846418941784, 4.97951990202499, 2.92230716113719,</v>
-      </c>
-    </row>
-    <row r="44" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="68" t="s">
-        <v>21</v>
-      </c>
-      <c r="B44" s="69"/>
-      <c r="C44" s="63">
-        <v>92.603715202692385</v>
-      </c>
-      <c r="D44" s="1">
-        <v>91.484997502720319</v>
-      </c>
-      <c r="E44" s="1">
-        <v>90.630171299324857</v>
-      </c>
-      <c r="F44" s="1">
-        <v>85.342034697064548</v>
-      </c>
-      <c r="G44" s="1">
-        <v>78.208607944308184</v>
-      </c>
-      <c r="H44" s="1">
-        <v>58.188767254712552</v>
-      </c>
-      <c r="I44" s="64">
-        <v>45.468919562576168</v>
+        <v xml:space="preserve">    87.2876347990493, 86.8786967506627, 87.0833631484665, 87.3002948979049, 86.5274318222157, 75.6891287758489, 46.8869070740948,</v>
+      </c>
+      <c r="M43" s="86"/>
+      <c r="N43" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="O43" s="65">
+        <v>2.5152339820278629</v>
+      </c>
+      <c r="P43" s="66">
+        <v>2.5980079882709322</v>
+      </c>
+      <c r="Q43" s="66">
+        <v>2.0296317104437578</v>
+      </c>
+      <c r="R43" s="66">
+        <v>2.161003670540631</v>
+      </c>
+      <c r="S43" s="66">
+        <v>1.7804591714461351</v>
+      </c>
+      <c r="T43" s="66">
+        <v>3.6175089321994709</v>
+      </c>
+      <c r="U43" s="67">
+        <v>4.0563769517378363</v>
+      </c>
+      <c r="V43" s="1"/>
+    </row>
+    <row r="44" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="87"/>
+      <c r="B44" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C44" s="93">
+        <v>86.92964367820916</v>
+      </c>
+      <c r="D44" s="94">
+        <v>86.866051061699935</v>
+      </c>
+      <c r="E44" s="94">
+        <v>86.762869729013673</v>
+      </c>
+      <c r="F44" s="94">
+        <v>87.364519247017455</v>
+      </c>
+      <c r="G44" s="94">
+        <v>86.199216005572438</v>
+      </c>
+      <c r="H44" s="94">
+        <v>73.575313464991169</v>
+      </c>
+      <c r="I44" s="95">
+        <v>45.850722883932022</v>
       </c>
       <c r="J44" s="44"/>
       <c r="K44" s="44"/>
-      <c r="L44" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">    92.6037152026924, 91.4849975027203, 90.6301712993249, 85.3420346970645, 78.2086079443082, 58.1887672547126, 45.4689195625762,</v>
-      </c>
-      <c r="M44" s="68" t="s">
-        <v>21</v>
-      </c>
-      <c r="N44" s="69"/>
-      <c r="O44" s="63">
-        <v>4.0727132923350373</v>
-      </c>
-      <c r="P44" s="1">
-        <v>4.4231285957629458</v>
-      </c>
-      <c r="Q44" s="1">
-        <v>4.3011534303531356</v>
-      </c>
-      <c r="R44" s="1">
-        <v>4.8453894583465429</v>
-      </c>
-      <c r="S44" s="1">
-        <v>7.5589700135942426</v>
-      </c>
-      <c r="T44" s="1">
-        <v>10.3740336621021</v>
-      </c>
-      <c r="U44" s="64">
-        <v>10.707618741543239</v>
-      </c>
-      <c r="V44" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">    4.07271329233504, 4.42312859576295, 4.30115343035314, 4.84538945834654, 7.55897001359424, 10.3740336621021, 10.7076187415432,</v>
-      </c>
-    </row>
-    <row r="45" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="68" t="s">
-        <v>22</v>
-      </c>
-      <c r="B45" s="69"/>
-      <c r="C45" s="65">
-        <v>92.692685851985146</v>
-      </c>
-      <c r="D45" s="66">
-        <v>91.028008929063319</v>
-      </c>
-      <c r="E45" s="66">
-        <v>89.101176850288709</v>
-      </c>
-      <c r="F45" s="66">
-        <v>84.121695311135312</v>
-      </c>
-      <c r="G45" s="66">
-        <v>75.514536359946376</v>
-      </c>
-      <c r="H45" s="66">
-        <v>58.551851548300363</v>
-      </c>
-      <c r="I45" s="67">
-        <v>43.528644478603361</v>
-      </c>
+      <c r="L44" s="1"/>
+      <c r="M44" s="87"/>
+      <c r="N44" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="O44" s="93">
+        <v>2.3788555625895009</v>
+      </c>
+      <c r="P44" s="94">
+        <v>1.890618139395533</v>
+      </c>
+      <c r="Q44" s="94">
+        <v>2.0117430969950041</v>
+      </c>
+      <c r="R44" s="94">
+        <v>1.842672316420805</v>
+      </c>
+      <c r="S44" s="94">
+        <v>1.6901439926207229</v>
+      </c>
+      <c r="T44" s="94">
+        <v>3.097142103089753</v>
+      </c>
+      <c r="U44" s="95">
+        <v>2.401443710230565</v>
+      </c>
+      <c r="V44" s="1"/>
+    </row>
+    <row r="45" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="70" t="s">
+        <v>20</v>
+      </c>
+      <c r="B45" s="78"/>
+      <c r="C45" s="88"/>
+      <c r="D45" s="88"/>
+      <c r="E45" s="88"/>
+      <c r="F45" s="88"/>
+      <c r="G45" s="88"/>
+      <c r="H45" s="88"/>
+      <c r="I45" s="82"/>
       <c r="J45" s="44"/>
       <c r="K45" s="44"/>
       <c r="L45" s="1"/>
-      <c r="M45" s="68" t="s">
+      <c r="M45" s="70" t="s">
+        <v>20</v>
+      </c>
+      <c r="N45" s="78"/>
+      <c r="O45" s="88"/>
+      <c r="P45" s="88"/>
+      <c r="Q45" s="88"/>
+      <c r="R45" s="88"/>
+      <c r="S45" s="88"/>
+      <c r="T45" s="88"/>
+      <c r="U45" s="82"/>
+      <c r="V45" s="1"/>
+    </row>
+    <row r="46" spans="1:22" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="70" t="s">
+        <v>7</v>
+      </c>
+      <c r="B46" s="71"/>
+      <c r="C46" s="60">
+        <v>93.403798109785029</v>
+      </c>
+      <c r="D46" s="61">
+        <v>91.51700700493744</v>
+      </c>
+      <c r="E46" s="61">
+        <v>89.749880462689262</v>
+      </c>
+      <c r="F46" s="61">
+        <v>83.99730958119234</v>
+      </c>
+      <c r="G46" s="61">
+        <v>74.394962965986878</v>
+      </c>
+      <c r="H46" s="61">
+        <v>58.095582470498513</v>
+      </c>
+      <c r="I46" s="62">
+        <v>44.434812706207254</v>
+      </c>
+      <c r="J46" s="44"/>
+      <c r="K46" s="44"/>
+      <c r="L46" s="1" t="str">
+        <f t="shared" ref="L46:L48" si="8">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C46:I46)&amp;","</f>
+        <v xml:space="preserve">    93.403798109785, 91.5170070049374, 89.7498804626893, 83.9973095811923, 74.3949629659869, 58.0955824704985, 44.4348127062073,</v>
+      </c>
+      <c r="M46" s="70" t="s">
+        <v>7</v>
+      </c>
+      <c r="N46" s="71"/>
+      <c r="O46" s="60">
+        <v>3.9553866501853321</v>
+      </c>
+      <c r="P46" s="61">
+        <v>4.517630835861226</v>
+      </c>
+      <c r="Q46" s="61">
+        <v>5.2125425794506972</v>
+      </c>
+      <c r="R46" s="61">
+        <v>5.6477461387684551</v>
+      </c>
+      <c r="S46" s="61">
+        <v>8.6090564713117175</v>
+      </c>
+      <c r="T46" s="61">
+        <v>11.357157347254571</v>
+      </c>
+      <c r="U46" s="62">
+        <v>9.3757621724255777</v>
+      </c>
+      <c r="V46" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    3.95538665018533, 4.51763083586123, 5.2125425794507, 5.64774613876846, 8.60905647131172, 11.3571573472546, 9.37576217242558,</v>
+      </c>
+    </row>
+    <row r="47" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="70" t="s">
+        <v>8</v>
+      </c>
+      <c r="B47" s="71"/>
+      <c r="C47" s="63">
+        <v>92.778947400409621</v>
+      </c>
+      <c r="D47" s="1">
+        <v>91.450368996373655</v>
+      </c>
+      <c r="E47" s="1">
+        <v>89.879480954542075</v>
+      </c>
+      <c r="F47" s="1">
+        <v>84.748756470336986</v>
+      </c>
+      <c r="G47" s="1">
+        <v>75.627608782580538</v>
+      </c>
+      <c r="H47" s="1">
+        <v>58.300265665116903</v>
+      </c>
+      <c r="I47" s="64">
+        <v>48.584106437626268</v>
+      </c>
+      <c r="J47" s="44"/>
+      <c r="K47" s="44"/>
+      <c r="L47" s="1" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    92.7789474004096, 91.4503689963737, 89.8794809545421, 84.748756470337, 75.6276087825805, 58.3002656651169, 48.5841064376263,</v>
+      </c>
+      <c r="M47" s="70" t="s">
+        <v>8</v>
+      </c>
+      <c r="N47" s="71"/>
+      <c r="O47" s="63">
+        <v>4.3743918396131134</v>
+      </c>
+      <c r="P47" s="1">
+        <v>5.1779143655465321</v>
+      </c>
+      <c r="Q47" s="1">
+        <v>4.8362705721377752</v>
+      </c>
+      <c r="R47" s="1">
+        <v>5.6797782301447892</v>
+      </c>
+      <c r="S47" s="1">
+        <v>9.0190902977959446</v>
+      </c>
+      <c r="T47" s="1">
+        <v>11.000258135261941</v>
+      </c>
+      <c r="U47" s="64">
+        <v>9.2918474149187738</v>
+      </c>
+      <c r="V47" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    4.37439183961311, 5.17791436554653, 4.83627057213778, 5.67977823014479, 9.01909029779594, 11.0002581352619, 9.29184741491877,</v>
+      </c>
+    </row>
+    <row r="48" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="70" t="s">
+        <v>21</v>
+      </c>
+      <c r="B48" s="71"/>
+      <c r="C48" s="63">
+        <v>92.492055194421354</v>
+      </c>
+      <c r="D48" s="1">
+        <v>91.055738083245984</v>
+      </c>
+      <c r="E48" s="1">
+        <v>89.241264887762341</v>
+      </c>
+      <c r="F48" s="1">
+        <v>82.713601809643421</v>
+      </c>
+      <c r="G48" s="1">
+        <v>73.133677048774885</v>
+      </c>
+      <c r="H48" s="1">
+        <v>56.229205901331248</v>
+      </c>
+      <c r="I48" s="64">
+        <v>43.695396708102962</v>
+      </c>
+      <c r="J48" s="44"/>
+      <c r="K48" s="44"/>
+      <c r="L48" s="1" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    92.4920551944214, 91.055738083246, 89.2412648877623, 82.7136018096434, 73.1336770487749, 56.2292059013312, 43.695396708103,</v>
+      </c>
+      <c r="M48" s="70" t="s">
+        <v>21</v>
+      </c>
+      <c r="N48" s="71"/>
+      <c r="O48" s="63">
+        <v>4.0986250609792014</v>
+      </c>
+      <c r="P48" s="1">
+        <v>4.5926443490712341</v>
+      </c>
+      <c r="Q48" s="1">
+        <v>4.8521598807380544</v>
+      </c>
+      <c r="R48" s="1">
+        <v>5.8188919126166327</v>
+      </c>
+      <c r="S48" s="1">
+        <v>9.5088987825376563</v>
+      </c>
+      <c r="T48" s="1">
+        <v>11.32839542788332</v>
+      </c>
+      <c r="U48" s="64">
+        <v>10.62887090695313</v>
+      </c>
+      <c r="V48" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    4.0986250609792, 4.59264434907123, 4.85215988073805, 5.81889191261663, 9.50889878253766, 11.3283954278833, 10.6288709069531,</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="N45" s="69"/>
-      <c r="O45" s="65">
+      <c r="B49" s="71"/>
+      <c r="C49" s="65">
+        <v>92.657174075741665</v>
+      </c>
+      <c r="D49" s="66">
+        <v>91.208050814372243</v>
+      </c>
+      <c r="E49" s="66">
+        <v>89.170455678091372</v>
+      </c>
+      <c r="F49" s="66">
+        <v>84.474616062770011</v>
+      </c>
+      <c r="G49" s="66">
+        <v>75.066668593640316</v>
+      </c>
+      <c r="H49" s="66">
+        <v>58.520340993368222</v>
+      </c>
+      <c r="I49" s="67">
+        <v>44.786141592049418</v>
+      </c>
+      <c r="J49" s="51"/>
+      <c r="K49" s="51"/>
+      <c r="L49" s="50"/>
+      <c r="M49" s="70" t="s">
+        <v>22</v>
+      </c>
+      <c r="N49" s="71"/>
+      <c r="O49" s="65">
+        <v>4.2589004392769629</v>
+      </c>
+      <c r="P49" s="66">
+        <v>4.8517186601265534</v>
+      </c>
+      <c r="Q49" s="66">
+        <v>5.6717673083496472</v>
+      </c>
+      <c r="R49" s="66">
+        <v>5.3079507961921779</v>
+      </c>
+      <c r="S49" s="66">
+        <v>7.7884705615072454</v>
+      </c>
+      <c r="T49" s="66">
+        <v>10.595563377926201</v>
+      </c>
+      <c r="U49" s="67">
+        <v>10.945843294214329</v>
+      </c>
+      <c r="V49" s="1"/>
+    </row>
+    <row r="50" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="70" t="s">
+        <v>23</v>
+      </c>
+      <c r="B50" s="78"/>
+      <c r="C50" s="81"/>
+      <c r="D50" s="81"/>
+      <c r="E50" s="81"/>
+      <c r="F50" s="81"/>
+      <c r="G50" s="81"/>
+      <c r="H50" s="81"/>
+      <c r="I50" s="82"/>
+      <c r="J50" s="44"/>
+      <c r="K50" s="44"/>
+      <c r="L50" s="1"/>
+      <c r="M50" s="70" t="s">
+        <v>23</v>
+      </c>
+      <c r="N50" s="78"/>
+      <c r="O50" s="81"/>
+      <c r="P50" s="81"/>
+      <c r="Q50" s="81"/>
+      <c r="R50" s="81"/>
+      <c r="S50" s="81"/>
+      <c r="T50" s="81"/>
+      <c r="U50" s="82"/>
+      <c r="V50" s="1"/>
+    </row>
+    <row r="51" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="70" t="s">
+        <v>7</v>
+      </c>
+      <c r="B51" s="71"/>
+      <c r="C51" s="60">
+        <v>92.603769819293618</v>
+      </c>
+      <c r="D51" s="61">
+        <v>91.431947068352812</v>
+      </c>
+      <c r="E51" s="61">
+        <v>90.390795042999585</v>
+      </c>
+      <c r="F51" s="61">
+        <v>86.789562828222273</v>
+      </c>
+      <c r="G51" s="61">
+        <v>80.615554033052248</v>
+      </c>
+      <c r="H51" s="61">
+        <v>56.609578553133908</v>
+      </c>
+      <c r="I51" s="62">
+        <v>41.27928062292434</v>
+      </c>
+      <c r="J51" s="44"/>
+      <c r="K51" s="44"/>
+      <c r="L51" s="1" t="str">
+        <f t="shared" ref="L51:L53" si="9">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C51:I51)&amp;","</f>
+        <v xml:space="preserve">    92.6037698192936, 91.4319470683528, 90.3907950429996, 86.7895628282223, 80.6155540330522, 56.6095785531339, 41.2792806229243,</v>
+      </c>
+      <c r="M51" s="70" t="s">
+        <v>7</v>
+      </c>
+      <c r="N51" s="71"/>
+      <c r="O51" s="60">
+        <v>3.708759274801273</v>
+      </c>
+      <c r="P51" s="61">
+        <v>3.9640390541215931</v>
+      </c>
+      <c r="Q51" s="61">
+        <v>3.7067998106756881</v>
+      </c>
+      <c r="R51" s="61">
+        <v>3.667452632531309</v>
+      </c>
+      <c r="S51" s="61">
+        <v>5.7548227051500218</v>
+      </c>
+      <c r="T51" s="61">
+        <v>8.5366536877555248</v>
+      </c>
+      <c r="U51" s="62">
+        <v>6.3187793027043018</v>
+      </c>
+      <c r="V51" s="1" t="str">
+        <f t="shared" ref="V51:V53" si="10">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,O51:U51)&amp;","</f>
+        <v xml:space="preserve">    3.70875927480127, 3.96403905412159, 3.70679981067569, 3.66745263253131, 5.75482270515002, 8.53665368775552, 6.3187793027043,</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="83" t="s">
+        <v>8</v>
+      </c>
+      <c r="B52" s="80"/>
+      <c r="C52" s="63">
+        <v>91.377634404932721</v>
+      </c>
+      <c r="D52" s="1">
+        <v>90.405373333245066</v>
+      </c>
+      <c r="E52" s="1">
+        <v>89.371480308332721</v>
+      </c>
+      <c r="F52" s="1">
+        <v>87.60989862639515</v>
+      </c>
+      <c r="G52" s="1">
+        <v>85.537230701510694</v>
+      </c>
+      <c r="H52" s="1">
+        <v>70.930708745421484</v>
+      </c>
+      <c r="I52" s="64">
+        <v>44.097326232806537</v>
+      </c>
+      <c r="J52" s="44"/>
+      <c r="K52" s="44"/>
+      <c r="L52" s="1" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">    91.3776344049327, 90.4053733332451, 89.3714803083327, 87.6098986263952, 85.5372307015107, 70.9307087454215, 44.0973262328065,</v>
+      </c>
+      <c r="M52" s="70" t="s">
+        <v>8</v>
+      </c>
+      <c r="N52" s="71"/>
+      <c r="O52" s="63">
+        <v>3.5684194304484111</v>
+      </c>
+      <c r="P52" s="1">
+        <v>3.0347581440341318</v>
+      </c>
+      <c r="Q52" s="1">
+        <v>2.754130276526872</v>
+      </c>
+      <c r="R52" s="1">
+        <v>2.7768782002466339</v>
+      </c>
+      <c r="S52" s="1">
+        <v>3.3184641894178428</v>
+      </c>
+      <c r="T52" s="1">
+        <v>4.9795199020249923</v>
+      </c>
+      <c r="U52" s="64">
+        <v>2.9223071611371929</v>
+      </c>
+      <c r="V52" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">    3.56841943044841, 3.03475814403413, 2.75413027652687, 2.77687820024663, 3.31846418941784, 4.97951990202499, 2.92230716113719,</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="70" t="s">
+        <v>21</v>
+      </c>
+      <c r="B53" s="71"/>
+      <c r="C53" s="63">
+        <v>92.603715202692385</v>
+      </c>
+      <c r="D53" s="1">
+        <v>91.484997502720319</v>
+      </c>
+      <c r="E53" s="1">
+        <v>90.630171299324857</v>
+      </c>
+      <c r="F53" s="1">
+        <v>85.342034697064548</v>
+      </c>
+      <c r="G53" s="1">
+        <v>78.208607944308184</v>
+      </c>
+      <c r="H53" s="1">
+        <v>58.188767254712552</v>
+      </c>
+      <c r="I53" s="64">
+        <v>45.468919562576168</v>
+      </c>
+      <c r="J53" s="44"/>
+      <c r="K53" s="44"/>
+      <c r="L53" s="1" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">    92.6037152026924, 91.4849975027203, 90.6301712993249, 85.3420346970645, 78.2086079443082, 58.1887672547126, 45.4689195625762,</v>
+      </c>
+      <c r="M53" s="70" t="s">
+        <v>21</v>
+      </c>
+      <c r="N53" s="71"/>
+      <c r="O53" s="63">
+        <v>4.0727132923350373</v>
+      </c>
+      <c r="P53" s="1">
+        <v>4.4231285957629458</v>
+      </c>
+      <c r="Q53" s="1">
+        <v>4.3011534303531356</v>
+      </c>
+      <c r="R53" s="1">
+        <v>4.8453894583465429</v>
+      </c>
+      <c r="S53" s="1">
+        <v>7.5589700135942426</v>
+      </c>
+      <c r="T53" s="1">
+        <v>10.3740336621021</v>
+      </c>
+      <c r="U53" s="64">
+        <v>10.707618741543239</v>
+      </c>
+      <c r="V53" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">    4.07271329233504, 4.42312859576295, 4.30115343035314, 4.84538945834654, 7.55897001359424, 10.3740336621021, 10.7076187415432,</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="70" t="s">
+        <v>22</v>
+      </c>
+      <c r="B54" s="71"/>
+      <c r="C54" s="65">
+        <v>92.692685851985146</v>
+      </c>
+      <c r="D54" s="66">
+        <v>91.028008929063319</v>
+      </c>
+      <c r="E54" s="66">
+        <v>89.101176850288709</v>
+      </c>
+      <c r="F54" s="66">
+        <v>84.121695311135312</v>
+      </c>
+      <c r="G54" s="66">
+        <v>75.514536359946376</v>
+      </c>
+      <c r="H54" s="66">
+        <v>58.551851548300363</v>
+      </c>
+      <c r="I54" s="67">
+        <v>43.528644478603361</v>
+      </c>
+      <c r="J54" s="44"/>
+      <c r="K54" s="44"/>
+      <c r="L54" s="1"/>
+      <c r="M54" s="70" t="s">
+        <v>22</v>
+      </c>
+      <c r="N54" s="71"/>
+      <c r="O54" s="65">
         <v>4.3508377678439567</v>
       </c>
-      <c r="P45" s="66">
+      <c r="P54" s="66">
         <v>5.1455197984597092</v>
       </c>
-      <c r="Q45" s="66">
+      <c r="Q54" s="66">
         <v>5.0319449257944937</v>
       </c>
-      <c r="R45" s="66">
+      <c r="R54" s="66">
         <v>5.4881092234662896</v>
       </c>
-      <c r="S45" s="66">
+      <c r="S54" s="66">
         <v>8.3963724907401343</v>
       </c>
-      <c r="T45" s="66">
+      <c r="T54" s="66">
         <v>11.26477476806841</v>
       </c>
-      <c r="U45" s="67">
+      <c r="U54" s="67">
         <v>10.478269846537319</v>
       </c>
-      <c r="V45" s="1"/>
-    </row>
-    <row r="46" spans="1:22" ht="15" x14ac:dyDescent="0.2">
-      <c r="L46" s="11"/>
-      <c r="M46" s="11"/>
-      <c r="N46" s="11"/>
-      <c r="O46" s="11"/>
-      <c r="P46" s="11"/>
-      <c r="Q46" s="11"/>
-      <c r="R46" s="11"/>
-      <c r="S46" s="11"/>
-      <c r="T46" s="11"/>
-      <c r="U46" s="11"/>
-    </row>
-    <row r="47" spans="1:22" ht="15" x14ac:dyDescent="0.2">
-      <c r="L47" s="11"/>
-      <c r="M47" s="11"/>
-      <c r="N47" s="11"/>
-      <c r="O47" s="11"/>
-      <c r="P47" s="11"/>
-      <c r="Q47" s="11"/>
-      <c r="R47" s="11"/>
-      <c r="S47" s="11"/>
-      <c r="T47" s="11"/>
-      <c r="U47" s="11"/>
-    </row>
-    <row r="48" spans="1:22" ht="15" x14ac:dyDescent="0.2">
-      <c r="J48" s="11"/>
-      <c r="K48" s="11"/>
-      <c r="L48" s="11"/>
-      <c r="M48" s="11"/>
-      <c r="N48" s="11"/>
-      <c r="O48" s="11"/>
-      <c r="P48" s="11"/>
-      <c r="Q48" s="11"/>
-      <c r="R48" s="11"/>
-      <c r="S48" s="11"/>
-      <c r="T48" s="11"/>
-      <c r="U48" s="11"/>
-    </row>
-    <row r="49" spans="10:21" ht="15" x14ac:dyDescent="0.2">
-      <c r="J49" s="11"/>
-      <c r="K49" s="11"/>
-      <c r="L49" s="11"/>
-      <c r="M49" s="11"/>
-      <c r="N49" s="11"/>
-      <c r="O49" s="11"/>
-      <c r="P49" s="11"/>
-      <c r="Q49" s="11"/>
-      <c r="R49" s="11"/>
-      <c r="S49" s="11"/>
-      <c r="T49" s="11"/>
-      <c r="U49" s="11"/>
-    </row>
-    <row r="50" spans="10:21" ht="15" x14ac:dyDescent="0.2">
-      <c r="J50" s="11"/>
-      <c r="K50" s="11"/>
-      <c r="L50" s="11"/>
-      <c r="M50" s="11"/>
-      <c r="N50" s="11"/>
-      <c r="O50" s="11"/>
-      <c r="P50" s="11"/>
-      <c r="Q50" s="11"/>
-      <c r="R50" s="11"/>
-      <c r="S50" s="11"/>
-      <c r="T50" s="11"/>
-      <c r="U50" s="11"/>
-    </row>
-    <row r="51" spans="10:21" ht="15" x14ac:dyDescent="0.2">
-      <c r="J51" s="11"/>
-      <c r="K51" s="11"/>
-      <c r="L51" s="11"/>
-      <c r="M51" s="11"/>
-      <c r="N51" s="11"/>
-      <c r="O51" s="11"/>
-      <c r="P51" s="11"/>
-      <c r="Q51" s="11"/>
-      <c r="R51" s="11"/>
-      <c r="S51" s="11"/>
-      <c r="T51" s="11"/>
-      <c r="U51" s="11"/>
+      <c r="V54" s="1"/>
+    </row>
+    <row r="55" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="70" t="s">
+        <v>24</v>
+      </c>
+      <c r="B55" s="78"/>
+      <c r="C55" s="81"/>
+      <c r="D55" s="81"/>
+      <c r="E55" s="81"/>
+      <c r="F55" s="81"/>
+      <c r="G55" s="81"/>
+      <c r="H55" s="81"/>
+      <c r="I55" s="82"/>
+      <c r="J55" s="44"/>
+      <c r="K55" s="44"/>
+      <c r="L55" s="1"/>
+      <c r="M55" s="70" t="s">
+        <v>23</v>
+      </c>
+      <c r="N55" s="78"/>
+      <c r="O55" s="81"/>
+      <c r="P55" s="81"/>
+      <c r="Q55" s="81"/>
+      <c r="R55" s="81"/>
+      <c r="S55" s="81"/>
+      <c r="T55" s="81"/>
+      <c r="U55" s="82"/>
+      <c r="V55" s="1"/>
+    </row>
+    <row r="56" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="70" t="s">
+        <v>7</v>
+      </c>
+      <c r="B56" s="71"/>
+      <c r="C56" s="60"/>
+      <c r="D56" s="61"/>
+      <c r="E56" s="61"/>
+      <c r="F56" s="61"/>
+      <c r="G56" s="61"/>
+      <c r="H56" s="61"/>
+      <c r="I56" s="62"/>
+      <c r="J56" s="44"/>
+      <c r="K56" s="44"/>
+      <c r="L56" s="1" t="str">
+        <f t="shared" ref="L56:L58" si="11">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C56:I56)&amp;","</f>
+        <v xml:space="preserve">    ,</v>
+      </c>
+      <c r="M56" s="70" t="s">
+        <v>7</v>
+      </c>
+      <c r="N56" s="71"/>
+      <c r="O56" s="60"/>
+      <c r="P56" s="61"/>
+      <c r="Q56" s="61"/>
+      <c r="R56" s="61"/>
+      <c r="S56" s="61"/>
+      <c r="T56" s="61"/>
+      <c r="U56" s="62"/>
+      <c r="V56" s="1" t="str">
+        <f t="shared" ref="V56:V58" si="12">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,O56:U56)&amp;","</f>
+        <v xml:space="preserve">    ,</v>
+      </c>
+    </row>
+    <row r="57" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="83" t="s">
+        <v>8</v>
+      </c>
+      <c r="B57" s="80"/>
+      <c r="C57" s="63"/>
+      <c r="D57" s="1"/>
+      <c r="E57" s="1"/>
+      <c r="F57" s="1"/>
+      <c r="G57" s="1"/>
+      <c r="H57" s="1"/>
+      <c r="I57" s="64"/>
+      <c r="J57" s="44"/>
+      <c r="K57" s="44"/>
+      <c r="L57" s="1" t="str">
+        <f t="shared" si="11"/>
+        <v xml:space="preserve">    ,</v>
+      </c>
+      <c r="M57" s="70" t="s">
+        <v>8</v>
+      </c>
+      <c r="N57" s="71"/>
+      <c r="O57" s="63"/>
+      <c r="P57" s="1"/>
+      <c r="Q57" s="1"/>
+      <c r="R57" s="1"/>
+      <c r="S57" s="1"/>
+      <c r="T57" s="1"/>
+      <c r="U57" s="64"/>
+      <c r="V57" s="1" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">    ,</v>
+      </c>
+    </row>
+    <row r="58" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="70" t="s">
+        <v>21</v>
+      </c>
+      <c r="B58" s="71"/>
+      <c r="C58" s="63"/>
+      <c r="D58" s="1"/>
+      <c r="E58" s="1"/>
+      <c r="F58" s="1"/>
+      <c r="G58" s="1"/>
+      <c r="H58" s="1"/>
+      <c r="I58" s="64"/>
+      <c r="J58" s="44"/>
+      <c r="K58" s="44"/>
+      <c r="L58" s="1" t="str">
+        <f t="shared" si="11"/>
+        <v xml:space="preserve">    ,</v>
+      </c>
+      <c r="M58" s="70" t="s">
+        <v>21</v>
+      </c>
+      <c r="N58" s="71"/>
+      <c r="O58" s="63"/>
+      <c r="P58" s="1"/>
+      <c r="Q58" s="1"/>
+      <c r="R58" s="1"/>
+      <c r="S58" s="1"/>
+      <c r="T58" s="1"/>
+      <c r="U58" s="64"/>
+      <c r="V58" s="1" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">    ,</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="70" t="s">
+        <v>22</v>
+      </c>
+      <c r="B59" s="71"/>
+      <c r="C59" s="65"/>
+      <c r="D59" s="66"/>
+      <c r="E59" s="66"/>
+      <c r="F59" s="66"/>
+      <c r="G59" s="66"/>
+      <c r="H59" s="66"/>
+      <c r="I59" s="67"/>
+      <c r="J59" s="44"/>
+      <c r="K59" s="44"/>
+      <c r="L59" s="1"/>
+      <c r="M59" s="70" t="s">
+        <v>22</v>
+      </c>
+      <c r="N59" s="71"/>
+      <c r="O59" s="65"/>
+      <c r="P59" s="66"/>
+      <c r="Q59" s="66"/>
+      <c r="R59" s="66"/>
+      <c r="S59" s="66"/>
+      <c r="T59" s="66"/>
+      <c r="U59" s="67"/>
+      <c r="V59" s="1"/>
+    </row>
+    <row r="60" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+      <c r="J60" s="11"/>
+      <c r="K60" s="11"/>
+      <c r="L60" s="11"/>
+      <c r="M60" s="11"/>
+      <c r="N60" s="11"/>
+      <c r="O60" s="11"/>
+      <c r="P60" s="11"/>
+      <c r="Q60" s="11"/>
+      <c r="R60" s="11"/>
+      <c r="S60" s="11"/>
+      <c r="T60" s="11"/>
+      <c r="U60" s="11"/>
     </row>
   </sheetData>
-  <mergeCells count="56">
+  <mergeCells count="80">
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="M59:N59"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="M56:N56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="M57:N57"/>
+    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="M58:N58"/>
+    <mergeCell ref="A6:A14"/>
+    <mergeCell ref="M6:M14"/>
+    <mergeCell ref="A36:A44"/>
+    <mergeCell ref="M36:M44"/>
+    <mergeCell ref="A55:I55"/>
+    <mergeCell ref="M55:U55"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="M25:U25"/>
+    <mergeCell ref="M26:N26"/>
+    <mergeCell ref="M27:N27"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="M29:N29"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="M53:N53"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="M54:N54"/>
+    <mergeCell ref="A50:I50"/>
+    <mergeCell ref="M50:U50"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="M51:N51"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="M52:N52"/>
+    <mergeCell ref="A45:I45"/>
+    <mergeCell ref="M15:U15"/>
+    <mergeCell ref="M45:U45"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="M19:N19"/>
+    <mergeCell ref="M35:U35"/>
+    <mergeCell ref="A20:I20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="M23:N23"/>
+    <mergeCell ref="M24:N24"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="M48:N48"/>
+    <mergeCell ref="M49:N49"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="M46:N46"/>
+    <mergeCell ref="M47:N47"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="M33:N33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="M34:N34"/>
+    <mergeCell ref="A35:I35"/>
+    <mergeCell ref="A18:B18"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="M2:N2"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="M25:N25"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="M32:N32"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="M3:N3"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A17:B17"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="M4:N4"/>
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="M5:U5"/>
-    <mergeCell ref="M18:U18"/>
-    <mergeCell ref="A13:I13"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="M39:N39"/>
-    <mergeCell ref="M40:N40"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="M37:N37"/>
-    <mergeCell ref="M38:N38"/>
+    <mergeCell ref="M20:U20"/>
+    <mergeCell ref="A15:I15"/>
+    <mergeCell ref="A25:I25"/>
     <mergeCell ref="A26:B26"/>
-    <mergeCell ref="M26:N26"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="M27:N27"/>
-    <mergeCell ref="A28:I28"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A36:I36"/>
-    <mergeCell ref="M13:U13"/>
-    <mergeCell ref="M36:U36"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="M28:U28"/>
-    <mergeCell ref="A18:I18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="M19:N19"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="M22:N22"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="M44:N44"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="M45:N45"/>
-    <mergeCell ref="A41:I41"/>
-    <mergeCell ref="M41:U41"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="M42:N42"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="M43:N43"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C6:I6">
-    <cfRule type="colorScale" priority="9">
+    <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6167,7 +6713,19 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="10">
+    <cfRule type="colorScale" priority="17">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C6:I14 C2:I4 C16:I19 C21:I24 C26:I29">
+    <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6179,7 +6737,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C7:I7">
-    <cfRule type="colorScale" priority="11">
+    <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6189,7 +6747,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="12">
+    <cfRule type="colorScale" priority="19">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6201,6 +6759,82 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C9:I9">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="21">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C10:I11">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C12:I12">
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="23">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C13:I14">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="min"/>
@@ -6211,64 +6845,8 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="14">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C11:I11">
-    <cfRule type="colorScale" priority="15">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="16">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C14:I16 C2:I4 C8:I8">
-    <cfRule type="colorScale" priority="159">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C14:I16 C2:I4">
-    <cfRule type="colorScale" priority="162">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C14:I16 C2:I4">
+  <conditionalFormatting sqref="C16:I18 C2:I4 C8:I8">
     <cfRule type="colorScale" priority="166">
       <colorScale>
         <cfvo type="min"/>
@@ -6280,8 +6858,18 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C14:I17 C2:I4 C19:I22 C8:I8">
-    <cfRule type="colorScale" priority="170">
+  <conditionalFormatting sqref="C16:I18 C2:I4">
+    <cfRule type="colorScale" priority="169">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="173">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6292,8 +6880,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C19:I21">
-    <cfRule type="colorScale" priority="31">
+  <conditionalFormatting sqref="C16:I19 C2:I4 C21:I24 C8:I8 C26:I29">
+    <cfRule type="colorScale" priority="177">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6303,7 +6891,9 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="32">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C21:I23">
+    <cfRule type="colorScale" priority="38">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6313,6 +6903,138 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="39">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="40">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J29">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J50:J59">
+    <cfRule type="colorScale" priority="35">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:K29">
+    <cfRule type="colorScale" priority="243">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J5:K5 C3:K4">
+    <cfRule type="colorScale" priority="110">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="111">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="112">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="113">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="114">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="115">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J19:K20 C2:K4 C16:K18 C21:K23 J5:K15 J24:K25 J29:K29 C26:K28">
+    <cfRule type="colorScale" priority="157">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J50:K54">
     <cfRule type="colorScale" priority="33">
       <colorScale>
         <cfvo type="min"/>
@@ -6323,8 +7045,18 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="36">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J22">
+  <conditionalFormatting sqref="K2:K29">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -6336,8 +7068,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J41:J45">
-    <cfRule type="colorScale" priority="28">
+  <conditionalFormatting sqref="K50:K59">
+    <cfRule type="colorScale" priority="37">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6348,8 +7080,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:K22">
-    <cfRule type="colorScale" priority="236">
+  <conditionalFormatting sqref="C26:I28">
+    <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6359,9 +7091,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J5:K5 C3:K4">
-    <cfRule type="colorScale" priority="103">
+    <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6371,116 +7101,6 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="104">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="105">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="106">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="107">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="108">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J17:K18 C2:K4 C14:K16 J22:K22 C19:K21 J5:K13">
-    <cfRule type="colorScale" priority="150">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J41:K45">
-    <cfRule type="colorScale" priority="26">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="29">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K22">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K41:K45">
-    <cfRule type="colorScale" priority="30">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C10:I10">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -6492,8 +7112,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C10:I10">
-    <cfRule type="colorScale" priority="8">
+  <conditionalFormatting sqref="J55:K59">
+    <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6503,32 +7123,6 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C12:I12">
-    <cfRule type="colorScale" priority="5">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C12:I12">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C6:I12 C2:I4 C14:I17 C19:I22">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -6543,4 +7137,57 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A38A25A9-7BAB-4662-AC2A-B7F2DABCCE29}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="C1" s="96" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1" s="96"/>
+      <c r="E1" s="96"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="C2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" s="97" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" s="97"/>
+      <c r="B4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" s="97"/>
+      <c r="B5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="C1:E1"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/results_(stress_test)_summary/summary.xlsx
+++ b/results_(stress_test)_summary/summary.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\RnD_Repo\Research_Engineeirng\feature_fusion_PCCxSigmoid-PLV-\results_(stress_test)_summary\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\RnD_Repo\Research_Engineering\feature_fusion_PCCxSigmoid-PLV-\results_(stress_test)_summary\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3799D395-140B-4C7B-8973-2BD6D0477111}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="639" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="639" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="partialdata_20260429" sheetId="6" r:id="rId1"/>
@@ -391,7 +391,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -556,11 +556,17 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -568,10 +574,28 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -583,25 +607,13 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -616,27 +628,9 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -990,10 +984,10 @@
       <c r="V1" s="12"/>
     </row>
     <row r="2" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="68" t="s">
+      <c r="A2" s="84" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="69"/>
+      <c r="B2" s="85"/>
       <c r="C2" s="20">
         <v>93.101364775358491</v>
       </c>
@@ -1027,10 +1021,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C2:I2)&amp;","</f>
         <v xml:space="preserve">    93.1013647753585, 91.3266637254648, 89.7225610371485, 83.857204647099, 76.2429490451186, 60.4027774173364, 47.7409002961387,</v>
       </c>
-      <c r="M2" s="68" t="s">
+      <c r="M2" s="84" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="69"/>
+      <c r="N2" s="85"/>
       <c r="O2" s="31">
         <v>3.4649270444699574</v>
       </c>
@@ -1058,10 +1052,10 @@
       </c>
     </row>
     <row r="3" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="68" t="s">
+      <c r="A3" s="84" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="69"/>
+      <c r="B3" s="85"/>
       <c r="C3" s="31">
         <v>93.273358766079312</v>
       </c>
@@ -1095,10 +1089,10 @@
         <f t="shared" ref="L3:L4" si="0">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C3:I3)&amp;","</f>
         <v xml:space="preserve">    93.2733587660793, 91.6155877934354, 90.6205330495939, 86.5975138193237, 78.2243502683126, 60.8549929786013, 48.7439337710534,</v>
       </c>
-      <c r="M3" s="68" t="s">
+      <c r="M3" s="84" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="69"/>
+      <c r="N3" s="85"/>
       <c r="O3" s="31">
         <v>3.4672469457762647</v>
       </c>
@@ -1126,10 +1120,10 @@
       </c>
     </row>
     <row r="4" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="68" t="s">
+      <c r="A4" s="84" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="69"/>
+      <c r="B4" s="85"/>
       <c r="C4" s="24">
         <v>87.593900000000005</v>
       </c>
@@ -1163,10 +1157,10 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    87.5939, 87.6637168141593, 88.1120943952802, 87.9700256922638, 87.4617081462642, 75.2513631894163, 47.7206838582802,</v>
       </c>
-      <c r="M4" s="68" t="s">
+      <c r="M4" s="84" t="s">
         <v>10</v>
       </c>
-      <c r="N4" s="69"/>
+      <c r="N4" s="85"/>
       <c r="O4" s="49">
         <v>2.4529187882918819</v>
       </c>
@@ -1194,31 +1188,31 @@
       </c>
     </row>
     <row r="5" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="68" t="s">
+      <c r="A5" s="84" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="74"/>
-      <c r="C5" s="74"/>
-      <c r="D5" s="74"/>
-      <c r="E5" s="74"/>
-      <c r="F5" s="74"/>
-      <c r="G5" s="74"/>
-      <c r="H5" s="74"/>
-      <c r="I5" s="69"/>
+      <c r="B5" s="86"/>
+      <c r="C5" s="86"/>
+      <c r="D5" s="86"/>
+      <c r="E5" s="86"/>
+      <c r="F5" s="86"/>
+      <c r="G5" s="86"/>
+      <c r="H5" s="86"/>
+      <c r="I5" s="85"/>
       <c r="J5" s="35"/>
       <c r="K5" s="35"/>
       <c r="L5" s="12"/>
-      <c r="M5" s="68" t="s">
+      <c r="M5" s="84" t="s">
         <v>12</v>
       </c>
-      <c r="N5" s="74"/>
-      <c r="O5" s="74"/>
-      <c r="P5" s="74"/>
-      <c r="Q5" s="74"/>
-      <c r="R5" s="74"/>
-      <c r="S5" s="74"/>
-      <c r="T5" s="74"/>
-      <c r="U5" s="69"/>
+      <c r="N5" s="86"/>
+      <c r="O5" s="86"/>
+      <c r="P5" s="86"/>
+      <c r="Q5" s="86"/>
+      <c r="R5" s="86"/>
+      <c r="S5" s="86"/>
+      <c r="T5" s="86"/>
+      <c r="U5" s="85"/>
       <c r="V5" s="12"/>
     </row>
     <row r="6" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -1366,38 +1360,38 @@
       </c>
     </row>
     <row r="8" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="68" t="s">
+      <c r="A8" s="84" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="74"/>
-      <c r="C8" s="77"/>
-      <c r="D8" s="77"/>
-      <c r="E8" s="77"/>
-      <c r="F8" s="77"/>
-      <c r="G8" s="77"/>
-      <c r="H8" s="77"/>
-      <c r="I8" s="73"/>
+      <c r="B8" s="86"/>
+      <c r="C8" s="91"/>
+      <c r="D8" s="91"/>
+      <c r="E8" s="91"/>
+      <c r="F8" s="91"/>
+      <c r="G8" s="91"/>
+      <c r="H8" s="91"/>
+      <c r="I8" s="90"/>
       <c r="J8" s="35"/>
       <c r="K8" s="35"/>
       <c r="L8" s="12"/>
-      <c r="M8" s="68" t="s">
+      <c r="M8" s="84" t="s">
         <v>20</v>
       </c>
-      <c r="N8" s="74"/>
-      <c r="O8" s="77"/>
-      <c r="P8" s="77"/>
-      <c r="Q8" s="77"/>
-      <c r="R8" s="77"/>
-      <c r="S8" s="77"/>
-      <c r="T8" s="77"/>
-      <c r="U8" s="73"/>
+      <c r="N8" s="86"/>
+      <c r="O8" s="91"/>
+      <c r="P8" s="91"/>
+      <c r="Q8" s="91"/>
+      <c r="R8" s="91"/>
+      <c r="S8" s="91"/>
+      <c r="T8" s="91"/>
+      <c r="U8" s="90"/>
       <c r="V8" s="12"/>
     </row>
     <row r="9" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="68" t="s">
+      <c r="A9" s="84" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="69"/>
+      <c r="B9" s="85"/>
       <c r="C9" s="31">
         <v>93.782740335124032</v>
       </c>
@@ -1431,10 +1425,10 @@
         <f t="shared" ref="L9:L12" si="4">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C9:I9)&amp;","</f>
         <v xml:space="preserve">    93.782740335124, 91.9482088945406, 90.212980504445, 84.6303889595354, 75.3710931755465, 59.6272113080563, 47.8441855033348,</v>
       </c>
-      <c r="M9" s="68" t="s">
+      <c r="M9" s="84" t="s">
         <v>7</v>
       </c>
-      <c r="N9" s="69"/>
+      <c r="N9" s="85"/>
       <c r="O9" s="31">
         <v>3.5391983918820551</v>
       </c>
@@ -1462,10 +1456,10 @@
       </c>
     </row>
     <row r="10" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="72" t="s">
+      <c r="A10" s="89" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="73"/>
+      <c r="B10" s="90"/>
       <c r="C10" s="34">
         <v>93.226230330712227</v>
       </c>
@@ -1499,10 +1493,10 @@
         <f t="shared" si="4"/>
         <v xml:space="preserve">    93.2262303307122, 91.8332915221297, 90.3252911645718, 85.3834923600839, 76.5670002912366, 59.4145422249904, 50.5634074112521,</v>
       </c>
-      <c r="M10" s="68" t="s">
+      <c r="M10" s="84" t="s">
         <v>8</v>
       </c>
-      <c r="N10" s="69"/>
+      <c r="N10" s="85"/>
       <c r="O10" s="34">
         <v>3.945711842949601</v>
       </c>
@@ -1530,10 +1524,10 @@
       </c>
     </row>
     <row r="11" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="68" t="s">
+      <c r="A11" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="69"/>
+      <c r="B11" s="85"/>
       <c r="C11" s="34">
         <v>93.004922187908207</v>
       </c>
@@ -1567,10 +1561,10 @@
         <f t="shared" si="4"/>
         <v xml:space="preserve">    93.0049221879082, 91.5185021785079, 89.7294209580821, 83.3486073985646, 74.0877199053048, 57.9173320415113, 48.0077941850708,</v>
       </c>
-      <c r="M11" s="68" t="s">
+      <c r="M11" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="N11" s="69"/>
+      <c r="N11" s="85"/>
       <c r="O11" s="34">
         <v>3.690401528555848</v>
       </c>
@@ -1598,10 +1592,10 @@
       </c>
     </row>
     <row r="12" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="68" t="s">
+      <c r="A12" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="69"/>
+      <c r="B12" s="85"/>
       <c r="C12" s="37">
         <v>93.123279613145442</v>
       </c>
@@ -1635,10 +1629,10 @@
         <f t="shared" si="4"/>
         <v xml:space="preserve">    93.1232796131454, 91.674385879924, 89.6986882816172, 84.9570671026566, 75.9390825180149, 59.9950922297482, 48.4403036935152,</v>
       </c>
-      <c r="M12" s="68" t="s">
+      <c r="M12" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="N12" s="69"/>
+      <c r="N12" s="85"/>
       <c r="O12" s="37">
         <v>3.8088682011350912</v>
       </c>
@@ -1666,38 +1660,38 @@
       </c>
     </row>
     <row r="13" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="68" t="s">
+      <c r="A13" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="74"/>
-      <c r="C13" s="75"/>
-      <c r="D13" s="75"/>
-      <c r="E13" s="75"/>
-      <c r="F13" s="75"/>
-      <c r="G13" s="75"/>
-      <c r="H13" s="75"/>
-      <c r="I13" s="76"/>
+      <c r="B13" s="86"/>
+      <c r="C13" s="87"/>
+      <c r="D13" s="87"/>
+      <c r="E13" s="87"/>
+      <c r="F13" s="87"/>
+      <c r="G13" s="87"/>
+      <c r="H13" s="87"/>
+      <c r="I13" s="88"/>
       <c r="J13" s="35"/>
       <c r="K13" s="35"/>
       <c r="L13" s="12"/>
-      <c r="M13" s="68" t="s">
+      <c r="M13" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="N13" s="74"/>
-      <c r="O13" s="75"/>
-      <c r="P13" s="75"/>
-      <c r="Q13" s="75"/>
-      <c r="R13" s="75"/>
-      <c r="S13" s="75"/>
-      <c r="T13" s="75"/>
-      <c r="U13" s="76"/>
+      <c r="N13" s="86"/>
+      <c r="O13" s="87"/>
+      <c r="P13" s="87"/>
+      <c r="Q13" s="87"/>
+      <c r="R13" s="87"/>
+      <c r="S13" s="87"/>
+      <c r="T13" s="87"/>
+      <c r="U13" s="88"/>
       <c r="V13" s="12"/>
     </row>
     <row r="14" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="68" t="s">
+      <c r="A14" s="84" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="69"/>
+      <c r="B14" s="85"/>
       <c r="C14" s="31">
         <v>92.969518190757128</v>
       </c>
@@ -1731,10 +1725,10 @@
         <f t="shared" ref="L14:L17" si="6">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C14:I14)&amp;","</f>
         <v xml:space="preserve">    92.9695181907571, 91.8515240904621, 90.756145526057, 87.2531365611583, 81.1789721364371, 57.3869295293788, 44.8554428094822,</v>
       </c>
-      <c r="M14" s="68" t="s">
+      <c r="M14" s="84" t="s">
         <v>7</v>
       </c>
-      <c r="N14" s="69"/>
+      <c r="N14" s="85"/>
       <c r="O14" s="31">
         <v>3.3991921823554931</v>
       </c>
@@ -1762,10 +1756,10 @@
       </c>
     </row>
     <row r="15" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="72" t="s">
+      <c r="A15" s="89" t="s">
         <v>8</v>
       </c>
-      <c r="B15" s="73"/>
+      <c r="B15" s="90"/>
       <c r="C15" s="34">
         <v>91.898721730580135</v>
       </c>
@@ -1799,10 +1793,10 @@
         <f t="shared" si="6"/>
         <v xml:space="preserve">    91.8987217305801, 90.765995668936, 89.7052685000158, 87.9596853490659, 85.7500007208828, 71.3873880108536, 45.5963431056209,</v>
       </c>
-      <c r="M15" s="68" t="s">
+      <c r="M15" s="84" t="s">
         <v>8</v>
       </c>
-      <c r="N15" s="69"/>
+      <c r="N15" s="85"/>
       <c r="O15" s="34">
         <v>3.190312271555559</v>
       </c>
@@ -1830,10 +1824,10 @@
       </c>
     </row>
     <row r="16" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="68" t="s">
+      <c r="A16" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="69"/>
+      <c r="B16" s="85"/>
       <c r="C16" s="34">
         <v>93.044276622923505</v>
       </c>
@@ -1867,10 +1861,10 @@
         <f t="shared" si="6"/>
         <v xml:space="preserve">    93.0442766229235, 91.9351551484009, 90.9488922914558, 85.9525053561594, 78.9151838107019, 59.4421001335075, 49.5338281473023,</v>
       </c>
-      <c r="M16" s="68" t="s">
+      <c r="M16" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="N16" s="69"/>
+      <c r="N16" s="85"/>
       <c r="O16" s="34">
         <v>3.72078192123604</v>
       </c>
@@ -1898,10 +1892,10 @@
       </c>
     </row>
     <row r="17" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="68" t="s">
+      <c r="A17" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="B17" s="69"/>
+      <c r="B17" s="85"/>
       <c r="C17" s="37">
         <v>93.174110502686005</v>
       </c>
@@ -1935,10 +1929,10 @@
         <f t="shared" si="6"/>
         <v xml:space="preserve">    93.174110502686, 91.3917248419104, 89.5915391424955, 84.6905970928238, 76.4013471858177, 59.9636675057743, 47.7255772108755,</v>
       </c>
-      <c r="M17" s="68" t="s">
+      <c r="M17" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="N17" s="69"/>
+      <c r="N17" s="85"/>
       <c r="O17" s="37">
         <v>3.8766021792735019</v>
       </c>
@@ -2048,10 +2042,10 @@
       <c r="V19" s="1"/>
     </row>
     <row r="20" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="70" t="s">
+      <c r="A20" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="B20" s="71"/>
+      <c r="B20" s="77"/>
       <c r="C20" s="41">
         <v>92.567111769713335</v>
       </c>
@@ -2079,10 +2073,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C20:I20)&amp;","</f>
         <v xml:space="preserve">    92.5671117697133, 90.8358586083436, 89.2175053395332, 83.2372459642881, 75.380430844191, 58.9943671875974, 43.6225356413822,</v>
       </c>
-      <c r="M20" s="70" t="s">
+      <c r="M20" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="N20" s="71"/>
+      <c r="N20" s="77"/>
       <c r="O20" s="40">
         <v>3.88093621561358</v>
       </c>
@@ -2110,10 +2104,10 @@
       </c>
     </row>
     <row r="21" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="70" t="s">
+      <c r="A21" s="76" t="s">
         <v>6</v>
       </c>
-      <c r="B21" s="71"/>
+      <c r="B21" s="77"/>
       <c r="C21" s="41">
         <v>92.866950218042462</v>
       </c>
@@ -2141,10 +2135,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C21:I21)&amp;","</f>
         <v xml:space="preserve">    92.8669502180425, 91.2426907647456, 90.1370532276984, 86.0801529266134, 77.4102172551968, 59.6761947649801, 46.3954904194042,</v>
       </c>
-      <c r="M21" s="70" t="s">
+      <c r="M21" s="76" t="s">
         <v>6</v>
       </c>
-      <c r="N21" s="71"/>
+      <c r="N21" s="77"/>
       <c r="O21" s="41">
         <v>3.8319643020864191</v>
       </c>
@@ -2172,10 +2166,10 @@
       </c>
     </row>
     <row r="22" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="70" t="s">
+      <c r="A22" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="B22" s="71"/>
+      <c r="B22" s="77"/>
       <c r="C22" s="28">
         <v>87.268396410214976</v>
       </c>
@@ -2203,10 +2197,10 @@
         <f t="shared" ref="L22:L25" si="9">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C22:I22)&amp;","</f>
         <v xml:space="preserve">    87.268396410215, 87.2564283986868, 87.8221063041704, 87.6807264423516, 87.1448793671852, 74.9765678865158, 46.4175473948824,</v>
       </c>
-      <c r="M22" s="70" t="s">
+      <c r="M22" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="N22" s="71"/>
+      <c r="N22" s="77"/>
       <c r="O22" s="28">
         <v>2.610595868561878</v>
       </c>
@@ -2234,31 +2228,31 @@
       </c>
     </row>
     <row r="23" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="70" t="s">
+      <c r="A23" s="76" t="s">
         <v>12</v>
       </c>
-      <c r="B23" s="78"/>
-      <c r="C23" s="78"/>
-      <c r="D23" s="78"/>
-      <c r="E23" s="78"/>
-      <c r="F23" s="78"/>
-      <c r="G23" s="78"/>
-      <c r="H23" s="78"/>
-      <c r="I23" s="71"/>
+      <c r="B23" s="80"/>
+      <c r="C23" s="80"/>
+      <c r="D23" s="80"/>
+      <c r="E23" s="80"/>
+      <c r="F23" s="80"/>
+      <c r="G23" s="80"/>
+      <c r="H23" s="80"/>
+      <c r="I23" s="77"/>
       <c r="J23" s="44"/>
       <c r="K23" s="44"/>
       <c r="L23" s="1"/>
-      <c r="M23" s="70" t="s">
+      <c r="M23" s="76" t="s">
         <v>12</v>
       </c>
-      <c r="N23" s="78"/>
-      <c r="O23" s="78"/>
-      <c r="P23" s="78"/>
-      <c r="Q23" s="78"/>
-      <c r="R23" s="78"/>
-      <c r="S23" s="78"/>
-      <c r="T23" s="78"/>
-      <c r="U23" s="71"/>
+      <c r="N23" s="80"/>
+      <c r="O23" s="80"/>
+      <c r="P23" s="80"/>
+      <c r="Q23" s="80"/>
+      <c r="R23" s="80"/>
+      <c r="S23" s="80"/>
+      <c r="T23" s="80"/>
+      <c r="U23" s="77"/>
       <c r="V23" s="1"/>
     </row>
     <row r="24" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
@@ -2394,38 +2388,38 @@
       </c>
     </row>
     <row r="26" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="70" t="s">
+      <c r="A26" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="B26" s="78"/>
-      <c r="C26" s="79"/>
-      <c r="D26" s="79"/>
-      <c r="E26" s="79"/>
-      <c r="F26" s="79"/>
-      <c r="G26" s="79"/>
-      <c r="H26" s="79"/>
-      <c r="I26" s="80"/>
+      <c r="B26" s="80"/>
+      <c r="C26" s="83"/>
+      <c r="D26" s="83"/>
+      <c r="E26" s="83"/>
+      <c r="F26" s="83"/>
+      <c r="G26" s="83"/>
+      <c r="H26" s="83"/>
+      <c r="I26" s="79"/>
       <c r="J26" s="44"/>
       <c r="K26" s="44"/>
       <c r="L26" s="1"/>
-      <c r="M26" s="70" t="s">
+      <c r="M26" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="N26" s="78"/>
-      <c r="O26" s="79"/>
-      <c r="P26" s="79"/>
-      <c r="Q26" s="79"/>
-      <c r="R26" s="79"/>
-      <c r="S26" s="79"/>
-      <c r="T26" s="79"/>
-      <c r="U26" s="80"/>
+      <c r="N26" s="80"/>
+      <c r="O26" s="83"/>
+      <c r="P26" s="83"/>
+      <c r="Q26" s="83"/>
+      <c r="R26" s="83"/>
+      <c r="S26" s="83"/>
+      <c r="T26" s="83"/>
+      <c r="U26" s="79"/>
       <c r="V26" s="1"/>
     </row>
     <row r="27" spans="1:22" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="70" t="s">
+      <c r="A27" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="B27" s="71"/>
+      <c r="B27" s="77"/>
       <c r="C27" s="40">
         <v>93.403798109785029</v>
       </c>
@@ -2453,10 +2447,10 @@
         <f t="shared" ref="L27:L30" si="10">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C27:I27)&amp;","</f>
         <v xml:space="preserve">    93.403798109785, 91.5170070049374, 89.7498804626893, 83.9973095811923, 74.3949629659869, 58.0955824704985, 44.4348127062073,</v>
       </c>
-      <c r="M27" s="70" t="s">
+      <c r="M27" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="N27" s="71"/>
+      <c r="N27" s="77"/>
       <c r="O27" s="40">
         <v>3.9553866501853321</v>
       </c>
@@ -2484,10 +2478,10 @@
       </c>
     </row>
     <row r="28" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="70" t="s">
+      <c r="A28" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="B28" s="71"/>
+      <c r="B28" s="77"/>
       <c r="C28" s="43">
         <v>92.778947400409621</v>
       </c>
@@ -2515,10 +2509,10 @@
         <f t="shared" si="10"/>
         <v xml:space="preserve">    92.7789474004096, 91.4503689963737, 89.8794809545421, 84.748756470337, 75.6276087825805, 58.3002656651169, 48.5841064376263,</v>
       </c>
-      <c r="M28" s="70" t="s">
+      <c r="M28" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="N28" s="71"/>
+      <c r="N28" s="77"/>
       <c r="O28" s="43">
         <v>4.3743918396131134</v>
       </c>
@@ -2546,10 +2540,10 @@
       </c>
     </row>
     <row r="29" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="70" t="s">
+      <c r="A29" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="B29" s="71"/>
+      <c r="B29" s="77"/>
       <c r="C29" s="43">
         <v>92.492055194421354</v>
       </c>
@@ -2577,10 +2571,10 @@
         <f t="shared" si="10"/>
         <v xml:space="preserve">    92.4920551944214, 91.055738083246, 89.2412648877623, 82.7136018096434, 73.1336770487749, 56.2292059013312, 43.695396708103,</v>
       </c>
-      <c r="M29" s="70" t="s">
+      <c r="M29" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="N29" s="71"/>
+      <c r="N29" s="77"/>
       <c r="O29" s="43">
         <v>4.0986250609792014</v>
       </c>
@@ -2608,10 +2602,10 @@
       </c>
     </row>
     <row r="30" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="70" t="s">
+      <c r="A30" s="76" t="s">
         <v>22</v>
       </c>
-      <c r="B30" s="71"/>
+      <c r="B30" s="77"/>
       <c r="C30" s="46">
         <v>92.657174075741665</v>
       </c>
@@ -2639,10 +2633,10 @@
         <f t="shared" si="10"/>
         <v xml:space="preserve">    92.6571740757417, 91.2080508143722, 89.1704556780914, 84.47461606277, 75.0666685936403, 58.5203409933682, 44.7861415920494,</v>
       </c>
-      <c r="M30" s="70" t="s">
+      <c r="M30" s="76" t="s">
         <v>22</v>
       </c>
-      <c r="N30" s="71"/>
+      <c r="N30" s="77"/>
       <c r="O30" s="46">
         <v>4.2589004392769629</v>
       </c>
@@ -2670,10 +2664,10 @@
       </c>
     </row>
     <row r="31" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="70" t="s">
+      <c r="A31" s="76" t="s">
         <v>23</v>
       </c>
-      <c r="B31" s="78"/>
+      <c r="B31" s="80"/>
       <c r="C31" s="81"/>
       <c r="D31" s="81"/>
       <c r="E31" s="81"/>
@@ -2684,10 +2678,10 @@
       <c r="J31" s="44"/>
       <c r="K31" s="44"/>
       <c r="L31" s="1"/>
-      <c r="M31" s="70" t="s">
+      <c r="M31" s="76" t="s">
         <v>23</v>
       </c>
-      <c r="N31" s="78"/>
+      <c r="N31" s="80"/>
       <c r="O31" s="81"/>
       <c r="P31" s="81"/>
       <c r="Q31" s="81"/>
@@ -2698,10 +2692,10 @@
       <c r="V31" s="1"/>
     </row>
     <row r="32" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="70" t="s">
+      <c r="A32" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="B32" s="71"/>
+      <c r="B32" s="77"/>
       <c r="C32" s="40">
         <v>92.603769819293618</v>
       </c>
@@ -2729,10 +2723,10 @@
         <f t="shared" ref="L32:L35" si="11">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C32:I32)&amp;","</f>
         <v xml:space="preserve">    92.6037698192936, 91.4319470683528, 90.3907950429996, 86.7895628282223, 80.6155540330522, 56.6095785531339, 41.2792806229243,</v>
       </c>
-      <c r="M32" s="70" t="s">
+      <c r="M32" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="N32" s="71"/>
+      <c r="N32" s="77"/>
       <c r="O32" s="40">
         <v>3.708759274801273</v>
       </c>
@@ -2760,10 +2754,10 @@
       </c>
     </row>
     <row r="33" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="83" t="s">
+      <c r="A33" s="78" t="s">
         <v>8</v>
       </c>
-      <c r="B33" s="80"/>
+      <c r="B33" s="79"/>
       <c r="C33" s="43">
         <v>91.377634404932721</v>
       </c>
@@ -2791,10 +2785,10 @@
         <f t="shared" si="11"/>
         <v xml:space="preserve">    91.3776344049327, 90.4053733332451, 89.3714803083327, 87.6098986263952, 85.5372307015107, 70.9307087454215, 44.0973262328065,</v>
       </c>
-      <c r="M33" s="70" t="s">
+      <c r="M33" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="N33" s="71"/>
+      <c r="N33" s="77"/>
       <c r="O33" s="43">
         <v>3.5684194304484111</v>
       </c>
@@ -2822,10 +2816,10 @@
       </c>
     </row>
     <row r="34" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="70" t="s">
+      <c r="A34" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="B34" s="71"/>
+      <c r="B34" s="77"/>
       <c r="C34" s="43">
         <v>92.603715202692385</v>
       </c>
@@ -2853,10 +2847,10 @@
         <f t="shared" si="11"/>
         <v xml:space="preserve">    92.6037152026924, 91.4849975027203, 90.6301712993249, 85.3420346970645, 78.2086079443082, 58.1887672547126, 45.4689195625762,</v>
       </c>
-      <c r="M34" s="70" t="s">
+      <c r="M34" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="N34" s="71"/>
+      <c r="N34" s="77"/>
       <c r="O34" s="43">
         <v>4.0727132923350373</v>
       </c>
@@ -2884,10 +2878,10 @@
       </c>
     </row>
     <row r="35" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="70" t="s">
+      <c r="A35" s="76" t="s">
         <v>22</v>
       </c>
-      <c r="B35" s="71"/>
+      <c r="B35" s="77"/>
       <c r="C35" s="46">
         <v>92.692685851985146</v>
       </c>
@@ -2915,10 +2909,10 @@
         <f t="shared" si="11"/>
         <v xml:space="preserve">    92.6926858519851, 91.0280089290633, 89.1011768502887, 84.1216953111353, 75.5145363599464, 58.5518515483004, 43.5286444786034,</v>
       </c>
-      <c r="M35" s="70" t="s">
+      <c r="M35" s="76" t="s">
         <v>22</v>
       </c>
-      <c r="N35" s="71"/>
+      <c r="N35" s="77"/>
       <c r="O35" s="46">
         <v>4.3508377678439567</v>
       </c>
@@ -3027,6 +3021,54 @@
     </row>
   </sheetData>
   <mergeCells count="56">
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="M5:U5"/>
+    <mergeCell ref="A8:I8"/>
+    <mergeCell ref="M8:U8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="M9:N9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="A13:I13"/>
+    <mergeCell ref="M13:U13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="A23:I23"/>
+    <mergeCell ref="M23:U23"/>
+    <mergeCell ref="A26:I26"/>
+    <mergeCell ref="M26:U26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="M27:N27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="M29:N29"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="M30:N30"/>
+    <mergeCell ref="A31:I31"/>
+    <mergeCell ref="M31:U31"/>
     <mergeCell ref="A35:B35"/>
     <mergeCell ref="M35:N35"/>
     <mergeCell ref="A32:B32"/>
@@ -3035,54 +3077,6 @@
     <mergeCell ref="M33:N33"/>
     <mergeCell ref="A34:B34"/>
     <mergeCell ref="M34:N34"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="M29:N29"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="M30:N30"/>
-    <mergeCell ref="A31:I31"/>
-    <mergeCell ref="M31:U31"/>
-    <mergeCell ref="A26:I26"/>
-    <mergeCell ref="M26:U26"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="M27:N27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="M22:N22"/>
-    <mergeCell ref="A23:I23"/>
-    <mergeCell ref="M23:U23"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="A13:I13"/>
-    <mergeCell ref="M13:U13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="A5:I5"/>
-    <mergeCell ref="M5:U5"/>
-    <mergeCell ref="A8:I8"/>
-    <mergeCell ref="M8:U8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="M9:N9"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="M4:N4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C2:I4">
@@ -3488,10 +3482,10 @@
       <c r="V1" s="12"/>
     </row>
     <row r="2" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="68" t="s">
+      <c r="A2" s="84" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="69"/>
+      <c r="B2" s="85"/>
       <c r="C2" s="20">
         <v>93.101364775358491</v>
       </c>
@@ -3525,10 +3519,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C2:I2)&amp;","</f>
         <v xml:space="preserve">    93.1013647753585, 91.3266637254648, 89.7225610371485, 83.857204647099, 76.2429490451186, 60.4027774173364, 47.7409002961387,</v>
       </c>
-      <c r="M2" s="68" t="s">
+      <c r="M2" s="84" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="69"/>
+      <c r="N2" s="85"/>
       <c r="O2" s="31">
         <v>3.4649270444699574</v>
       </c>
@@ -3556,10 +3550,10 @@
       </c>
     </row>
     <row r="3" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="68" t="s">
+      <c r="A3" s="84" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="69"/>
+      <c r="B3" s="85"/>
       <c r="C3" s="31">
         <v>93.273358766079312</v>
       </c>
@@ -3593,10 +3587,10 @@
         <f t="shared" ref="L3:L18" si="0">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C3:I3)&amp;","</f>
         <v xml:space="preserve">    93.2733587660793, 91.6155877934354, 90.6205330495939, 86.5975138193237, 78.2243502683126, 60.8549929786013, 48.7439337710534,</v>
       </c>
-      <c r="M3" s="68" t="s">
+      <c r="M3" s="84" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="69"/>
+      <c r="N3" s="85"/>
       <c r="O3" s="31">
         <v>3.4672469457762647</v>
       </c>
@@ -3624,10 +3618,10 @@
       </c>
     </row>
     <row r="4" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="68" t="s">
+      <c r="A4" s="84" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="69"/>
+      <c r="B4" s="85"/>
       <c r="C4" s="24">
         <v>87.593900000000005</v>
       </c>
@@ -3661,10 +3655,10 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    87.5939, 87.6637168141593, 88.1120943952802, 87.9700256922638, 87.4617081462642, 75.2513631894163, 47.7206838582802,</v>
       </c>
-      <c r="M4" s="68" t="s">
+      <c r="M4" s="84" t="s">
         <v>10</v>
       </c>
-      <c r="N4" s="69"/>
+      <c r="N4" s="85"/>
       <c r="O4" s="49">
         <v>2.4529187882918819</v>
       </c>
@@ -3692,35 +3686,35 @@
       </c>
     </row>
     <row r="5" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="68" t="s">
+      <c r="A5" s="84" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="74"/>
-      <c r="C5" s="74"/>
-      <c r="D5" s="74"/>
-      <c r="E5" s="74"/>
-      <c r="F5" s="74"/>
-      <c r="G5" s="74"/>
-      <c r="H5" s="74"/>
-      <c r="I5" s="69"/>
+      <c r="B5" s="86"/>
+      <c r="C5" s="86"/>
+      <c r="D5" s="86"/>
+      <c r="E5" s="86"/>
+      <c r="F5" s="86"/>
+      <c r="G5" s="86"/>
+      <c r="H5" s="86"/>
+      <c r="I5" s="85"/>
       <c r="J5" s="35"/>
       <c r="K5" s="35"/>
       <c r="L5" s="12"/>
-      <c r="M5" s="68" t="s">
+      <c r="M5" s="84" t="s">
         <v>12</v>
       </c>
-      <c r="N5" s="74"/>
-      <c r="O5" s="74"/>
-      <c r="P5" s="74"/>
-      <c r="Q5" s="74"/>
-      <c r="R5" s="74"/>
-      <c r="S5" s="74"/>
-      <c r="T5" s="74"/>
-      <c r="U5" s="69"/>
+      <c r="N5" s="86"/>
+      <c r="O5" s="86"/>
+      <c r="P5" s="86"/>
+      <c r="Q5" s="86"/>
+      <c r="R5" s="86"/>
+      <c r="S5" s="86"/>
+      <c r="T5" s="86"/>
+      <c r="U5" s="85"/>
       <c r="V5" s="12"/>
     </row>
     <row r="6" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="72" t="s">
+      <c r="A6" s="89" t="s">
         <v>11</v>
       </c>
       <c r="B6" s="8" t="s">
@@ -3759,7 +3753,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    93.4021632251721, 91.8271265322364, 90.5586899540653, 86.0233767881498, 80.0763011214053, 61.7128781390843, 46.4235100072953,</v>
       </c>
-      <c r="M6" s="72" t="s">
+      <c r="M6" s="89" t="s">
         <v>11</v>
       </c>
       <c r="N6" s="8" t="s">
@@ -3792,7 +3786,7 @@
       </c>
     </row>
     <row r="7" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="84"/>
+      <c r="A7" s="92"/>
       <c r="B7" s="8" t="s">
         <v>14</v>
       </c>
@@ -3829,7 +3823,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    92.6912487708948, 92.7069813176008, 91.7345132743363, 88.8675536408908, 87.5647050003316, 75.6237856728864, 48.8313393714478,</v>
       </c>
-      <c r="M7" s="84"/>
+      <c r="M7" s="92"/>
       <c r="N7" s="8" t="s">
         <v>14</v>
       </c>
@@ -3860,7 +3854,7 @@
       </c>
     </row>
     <row r="8" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="84"/>
+      <c r="A8" s="92"/>
       <c r="B8" s="8" t="s">
         <v>17</v>
       </c>
@@ -3897,7 +3891,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    93.3599108412126, 93.0049510232211, 91.6796281398051, 85.4087492106333, 76.226619607436, 61.2490650149799, 49.6316519462395,</v>
       </c>
-      <c r="M8" s="84"/>
+      <c r="M8" s="92"/>
       <c r="N8" s="8" t="s">
         <v>17</v>
       </c>
@@ -3925,7 +3919,7 @@
       <c r="V8" s="12"/>
     </row>
     <row r="9" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="84"/>
+      <c r="A9" s="92"/>
       <c r="B9" s="8" t="s">
         <v>18</v>
       </c>
@@ -3962,7 +3956,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    93.4021689922347, 93.2487766618512, 92.6912718391451, 88.4524750790808, 80.8362500252309, 58.5874935480987, 46.7616127013786,</v>
       </c>
-      <c r="M9" s="84"/>
+      <c r="M9" s="92"/>
       <c r="N9" s="8" t="s">
         <v>18</v>
       </c>
@@ -3990,7 +3984,7 @@
       <c r="V9" s="12"/>
     </row>
     <row r="10" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="84"/>
+      <c r="A10" s="92"/>
       <c r="B10" s="8" t="s">
         <v>15</v>
       </c>
@@ -4027,7 +4021,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    93.3470993117011, 92.4297413184082, 91.1779802016742, 88.6094429882612, 83.8878825364695, 65.4650299743077, 53.0259200627456,</v>
       </c>
-      <c r="M10" s="84"/>
+      <c r="M10" s="92"/>
       <c r="N10" s="8" t="s">
         <v>15</v>
       </c>
@@ -4055,29 +4049,29 @@
       <c r="V10" s="12"/>
     </row>
     <row r="11" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="84"/>
+      <c r="A11" s="92"/>
       <c r="B11" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="90">
+      <c r="C11" s="68">
         <v>90.975423662834444</v>
       </c>
-      <c r="D11" s="91">
+      <c r="D11" s="69">
         <v>90.202556538839715</v>
       </c>
-      <c r="E11" s="91">
+      <c r="E11" s="69">
         <v>90.170108161258611</v>
       </c>
-      <c r="F11" s="91">
+      <c r="F11" s="69">
         <v>88.70908052837828</v>
       </c>
-      <c r="G11" s="91">
+      <c r="G11" s="69">
         <v>86.950939598670132</v>
       </c>
-      <c r="H11" s="91">
+      <c r="H11" s="69">
         <v>75.792829811099864</v>
       </c>
-      <c r="I11" s="92">
+      <c r="I11" s="70">
         <v>48.150537634408593</v>
       </c>
       <c r="J11" s="35" cm="1">
@@ -4092,35 +4086,35 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    90.9754236628344, 90.2025565388397, 90.1701081612586, 88.7090805283783, 86.9509395986701, 75.7928298110999, 48.1505376344086,</v>
       </c>
-      <c r="M11" s="84"/>
+      <c r="M11" s="92"/>
       <c r="N11" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="O11" s="90">
+      <c r="O11" s="68">
         <v>3.3313581707075852</v>
       </c>
-      <c r="P11" s="91">
+      <c r="P11" s="69">
         <v>2.8735231153997312</v>
       </c>
-      <c r="Q11" s="91">
+      <c r="Q11" s="69">
         <v>2.9020080993283321</v>
       </c>
-      <c r="R11" s="91">
+      <c r="R11" s="69">
         <v>2.6230573417030318</v>
       </c>
-      <c r="S11" s="91">
+      <c r="S11" s="69">
         <v>3.0561479691174078</v>
       </c>
-      <c r="T11" s="91">
+      <c r="T11" s="69">
         <v>3.639426101786353</v>
       </c>
-      <c r="U11" s="92">
+      <c r="U11" s="70">
         <v>2.9250848924264208</v>
       </c>
       <c r="V11" s="12"/>
     </row>
     <row r="12" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="84"/>
+      <c r="A12" s="92"/>
       <c r="B12" s="8" t="s">
         <v>19</v>
       </c>
@@ -4157,7 +4151,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    90.2959685349066, 90.4051130776795, 90.5292433325548, 90.4642081678907, 89.370346340943, 80.4958116708045, 54.2005092316254,</v>
       </c>
-      <c r="M12" s="84"/>
+      <c r="M12" s="92"/>
       <c r="N12" s="8" t="s">
         <v>19</v>
       </c>
@@ -4185,7 +4179,7 @@
       <c r="V12" s="12"/>
     </row>
     <row r="13" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="84"/>
+      <c r="A13" s="92"/>
       <c r="B13" s="8" t="s">
         <v>16</v>
       </c>
@@ -4222,7 +4216,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    87.7571288102262, 87.2143617159318, 87.4218577438674, 87.622418879056, 86.8073858770404, 75.9010458567981, 48.2504289252791,</v>
       </c>
-      <c r="M13" s="84"/>
+      <c r="M13" s="92"/>
       <c r="N13" s="8" t="s">
         <v>16</v>
       </c>
@@ -4250,29 +4244,29 @@
       <c r="V13" s="12"/>
     </row>
     <row r="14" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="85"/>
+      <c r="A14" s="93"/>
       <c r="B14" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="90">
+      <c r="C14" s="68">
         <v>87.38938053097344</v>
       </c>
-      <c r="D14" s="91">
+      <c r="D14" s="69">
         <v>87.136676499508383</v>
       </c>
-      <c r="E14" s="91">
+      <c r="E14" s="69">
         <v>87.169124877089473</v>
       </c>
-      <c r="F14" s="91">
+      <c r="F14" s="69">
         <v>87.617502458210453</v>
       </c>
-      <c r="G14" s="91">
+      <c r="G14" s="69">
         <v>86.525073746312685</v>
       </c>
-      <c r="H14" s="91">
+      <c r="H14" s="69">
         <v>73.91603156890055</v>
       </c>
-      <c r="I14" s="92">
+      <c r="I14" s="70">
         <v>47.131944624665152</v>
       </c>
       <c r="J14" s="35" cm="1">
@@ -4287,7 +4281,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    87.3893805309734, 87.1366764995084, 87.1691248770895, 87.6175024582105, 86.5250737463127, 73.9160315689006, 47.1319446246652,</v>
       </c>
-      <c r="M14" s="85"/>
+      <c r="M14" s="93"/>
       <c r="N14" s="8" t="s">
         <v>26</v>
       </c>
@@ -4315,38 +4309,38 @@
       <c r="V14" s="12"/>
     </row>
     <row r="15" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="68" t="s">
+      <c r="A15" s="84" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="74"/>
-      <c r="C15" s="89"/>
-      <c r="D15" s="89"/>
-      <c r="E15" s="89"/>
-      <c r="F15" s="89"/>
-      <c r="G15" s="89"/>
-      <c r="H15" s="89"/>
-      <c r="I15" s="76"/>
+      <c r="B15" s="86"/>
+      <c r="C15" s="87"/>
+      <c r="D15" s="87"/>
+      <c r="E15" s="87"/>
+      <c r="F15" s="87"/>
+      <c r="G15" s="87"/>
+      <c r="H15" s="87"/>
+      <c r="I15" s="88"/>
       <c r="J15" s="35"/>
       <c r="K15" s="35"/>
       <c r="L15" s="12"/>
-      <c r="M15" s="68" t="s">
+      <c r="M15" s="84" t="s">
         <v>20</v>
       </c>
-      <c r="N15" s="74"/>
-      <c r="O15" s="77"/>
-      <c r="P15" s="77"/>
-      <c r="Q15" s="77"/>
-      <c r="R15" s="77"/>
-      <c r="S15" s="77"/>
-      <c r="T15" s="77"/>
-      <c r="U15" s="73"/>
+      <c r="N15" s="86"/>
+      <c r="O15" s="91"/>
+      <c r="P15" s="91"/>
+      <c r="Q15" s="91"/>
+      <c r="R15" s="91"/>
+      <c r="S15" s="91"/>
+      <c r="T15" s="91"/>
+      <c r="U15" s="90"/>
       <c r="V15" s="12"/>
     </row>
     <row r="16" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="68" t="s">
+      <c r="A16" s="84" t="s">
         <v>7</v>
       </c>
-      <c r="B16" s="69"/>
+      <c r="B16" s="85"/>
       <c r="C16" s="52">
         <v>93.782740335124032</v>
       </c>
@@ -4380,10 +4374,10 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    93.782740335124, 91.9482088945406, 90.212980504445, 84.6303889595354, 75.3710931755465, 59.6272113080563, 47.8441855033348,</v>
       </c>
-      <c r="M16" s="68" t="s">
+      <c r="M16" s="84" t="s">
         <v>7</v>
       </c>
-      <c r="N16" s="69"/>
+      <c r="N16" s="85"/>
       <c r="O16" s="52">
         <v>3.5391983918820551</v>
       </c>
@@ -4411,10 +4405,10 @@
       </c>
     </row>
     <row r="17" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="72" t="s">
+      <c r="A17" s="89" t="s">
         <v>8</v>
       </c>
-      <c r="B17" s="73"/>
+      <c r="B17" s="90"/>
       <c r="C17" s="55">
         <v>93.226230330712227</v>
       </c>
@@ -4448,10 +4442,10 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    93.2262303307122, 91.8332915221297, 90.3252911645718, 85.3834923600839, 76.5670002912366, 59.4145422249904, 50.5634074112521,</v>
       </c>
-      <c r="M17" s="68" t="s">
+      <c r="M17" s="84" t="s">
         <v>8</v>
       </c>
-      <c r="N17" s="69"/>
+      <c r="N17" s="85"/>
       <c r="O17" s="55">
         <v>3.945711842949601</v>
       </c>
@@ -4479,10 +4473,10 @@
       </c>
     </row>
     <row r="18" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="68" t="s">
+      <c r="A18" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="69"/>
+      <c r="B18" s="85"/>
       <c r="C18" s="55">
         <v>93.004922187908207</v>
       </c>
@@ -4516,10 +4510,10 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    93.0049221879082, 91.5185021785079, 89.7294209580821, 83.3486073985646, 74.0877199053048, 57.9173320415113, 48.0077941850708,</v>
       </c>
-      <c r="M18" s="68" t="s">
+      <c r="M18" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="N18" s="69"/>
+      <c r="N18" s="85"/>
       <c r="O18" s="55">
         <v>3.690401528555848</v>
       </c>
@@ -4547,10 +4541,10 @@
       </c>
     </row>
     <row r="19" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="68" t="s">
+      <c r="A19" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="69"/>
+      <c r="B19" s="85"/>
       <c r="C19" s="57">
         <v>93.123279613145442</v>
       </c>
@@ -4581,10 +4575,10 @@
         <v>80.789319111757024</v>
       </c>
       <c r="L19" s="12"/>
-      <c r="M19" s="68" t="s">
+      <c r="M19" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="N19" s="69"/>
+      <c r="N19" s="85"/>
       <c r="O19" s="57">
         <v>3.8088682011350912</v>
       </c>
@@ -4609,38 +4603,38 @@
       <c r="V19" s="12"/>
     </row>
     <row r="20" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="68" t="s">
+      <c r="A20" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="74"/>
-      <c r="C20" s="75"/>
-      <c r="D20" s="75"/>
-      <c r="E20" s="75"/>
-      <c r="F20" s="75"/>
-      <c r="G20" s="75"/>
-      <c r="H20" s="75"/>
-      <c r="I20" s="76"/>
+      <c r="B20" s="86"/>
+      <c r="C20" s="87"/>
+      <c r="D20" s="87"/>
+      <c r="E20" s="87"/>
+      <c r="F20" s="87"/>
+      <c r="G20" s="87"/>
+      <c r="H20" s="87"/>
+      <c r="I20" s="88"/>
       <c r="J20" s="35"/>
       <c r="K20" s="35"/>
       <c r="L20" s="12"/>
-      <c r="M20" s="68" t="s">
+      <c r="M20" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="N20" s="74"/>
-      <c r="O20" s="75"/>
-      <c r="P20" s="75"/>
-      <c r="Q20" s="75"/>
-      <c r="R20" s="75"/>
-      <c r="S20" s="75"/>
-      <c r="T20" s="75"/>
-      <c r="U20" s="76"/>
+      <c r="N20" s="86"/>
+      <c r="O20" s="87"/>
+      <c r="P20" s="87"/>
+      <c r="Q20" s="87"/>
+      <c r="R20" s="87"/>
+      <c r="S20" s="87"/>
+      <c r="T20" s="87"/>
+      <c r="U20" s="88"/>
       <c r="V20" s="12"/>
     </row>
     <row r="21" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="68" t="s">
+      <c r="A21" s="84" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="69"/>
+      <c r="B21" s="85"/>
       <c r="C21" s="52">
         <v>92.969518190757128</v>
       </c>
@@ -4674,10 +4668,10 @@
         <f t="shared" ref="L21:L23" si="2">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C21:I21)&amp;","</f>
         <v xml:space="preserve">    92.9695181907571, 91.8515240904621, 90.756145526057, 87.2531365611583, 81.1789721364371, 57.3869295293788, 44.8554428094822,</v>
       </c>
-      <c r="M21" s="68" t="s">
+      <c r="M21" s="84" t="s">
         <v>7</v>
       </c>
-      <c r="N21" s="69"/>
+      <c r="N21" s="85"/>
       <c r="O21" s="52">
         <v>3.3991921823554931</v>
       </c>
@@ -4705,10 +4699,10 @@
       </c>
     </row>
     <row r="22" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="72" t="s">
+      <c r="A22" s="89" t="s">
         <v>8</v>
       </c>
-      <c r="B22" s="73"/>
+      <c r="B22" s="90"/>
       <c r="C22" s="55">
         <v>91.898721730580135</v>
       </c>
@@ -4742,10 +4736,10 @@
         <f t="shared" si="2"/>
         <v xml:space="preserve">    91.8987217305801, 90.765995668936, 89.7052685000158, 87.9596853490659, 85.7500007208828, 71.3873880108536, 45.5963431056209,</v>
       </c>
-      <c r="M22" s="68" t="s">
+      <c r="M22" s="84" t="s">
         <v>8</v>
       </c>
-      <c r="N22" s="69"/>
+      <c r="N22" s="85"/>
       <c r="O22" s="55">
         <v>3.190312271555559</v>
       </c>
@@ -4773,10 +4767,10 @@
       </c>
     </row>
     <row r="23" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="68" t="s">
+      <c r="A23" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="B23" s="69"/>
+      <c r="B23" s="85"/>
       <c r="C23" s="55">
         <v>93.044276622923505</v>
       </c>
@@ -4810,10 +4804,10 @@
         <f t="shared" si="2"/>
         <v xml:space="preserve">    93.0442766229235, 91.9351551484009, 90.9488922914558, 85.9525053561594, 78.9151838107019, 59.4421001335075, 49.5338281473023,</v>
       </c>
-      <c r="M23" s="68" t="s">
+      <c r="M23" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="N23" s="69"/>
+      <c r="N23" s="85"/>
       <c r="O23" s="55">
         <v>3.72078192123604</v>
       </c>
@@ -4841,10 +4835,10 @@
       </c>
     </row>
     <row r="24" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="68" t="s">
+      <c r="A24" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="B24" s="69"/>
+      <c r="B24" s="85"/>
       <c r="C24" s="57">
         <v>93.174110502686005</v>
       </c>
@@ -4875,10 +4869,10 @@
         <v>80.686930106085114</v>
       </c>
       <c r="L24" s="12"/>
-      <c r="M24" s="68" t="s">
+      <c r="M24" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="N24" s="69"/>
+      <c r="N24" s="85"/>
       <c r="O24" s="57">
         <v>3.8766021792735019</v>
       </c>
@@ -4903,38 +4897,38 @@
       <c r="V24" s="12"/>
     </row>
     <row r="25" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="68" t="s">
+      <c r="A25" s="84" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="74"/>
-      <c r="C25" s="75"/>
-      <c r="D25" s="75"/>
-      <c r="E25" s="75"/>
-      <c r="F25" s="75"/>
-      <c r="G25" s="75"/>
-      <c r="H25" s="75"/>
-      <c r="I25" s="76"/>
+      <c r="B25" s="86"/>
+      <c r="C25" s="87"/>
+      <c r="D25" s="87"/>
+      <c r="E25" s="87"/>
+      <c r="F25" s="87"/>
+      <c r="G25" s="87"/>
+      <c r="H25" s="87"/>
+      <c r="I25" s="88"/>
       <c r="J25" s="35"/>
       <c r="K25" s="35"/>
       <c r="L25" s="12"/>
-      <c r="M25" s="68" t="s">
+      <c r="M25" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="N25" s="74"/>
-      <c r="O25" s="75"/>
-      <c r="P25" s="75"/>
-      <c r="Q25" s="75"/>
-      <c r="R25" s="75"/>
-      <c r="S25" s="75"/>
-      <c r="T25" s="75"/>
-      <c r="U25" s="76"/>
+      <c r="N25" s="86"/>
+      <c r="O25" s="87"/>
+      <c r="P25" s="87"/>
+      <c r="Q25" s="87"/>
+      <c r="R25" s="87"/>
+      <c r="S25" s="87"/>
+      <c r="T25" s="87"/>
+      <c r="U25" s="88"/>
       <c r="V25" s="12"/>
     </row>
     <row r="26" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="68" t="s">
+      <c r="A26" s="84" t="s">
         <v>7</v>
       </c>
-      <c r="B26" s="69"/>
+      <c r="B26" s="85"/>
       <c r="C26" s="52"/>
       <c r="D26" s="53"/>
       <c r="E26" s="53"/>
@@ -4954,10 +4948,10 @@
         <f t="shared" ref="L26:L28" si="4">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C26:I26)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M26" s="68" t="s">
+      <c r="M26" s="84" t="s">
         <v>7</v>
       </c>
-      <c r="N26" s="69"/>
+      <c r="N26" s="85"/>
       <c r="O26" s="52"/>
       <c r="P26" s="53"/>
       <c r="Q26" s="53"/>
@@ -4971,10 +4965,10 @@
       </c>
     </row>
     <row r="27" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="72" t="s">
+      <c r="A27" s="89" t="s">
         <v>8</v>
       </c>
-      <c r="B27" s="73"/>
+      <c r="B27" s="90"/>
       <c r="C27" s="55"/>
       <c r="D27" s="12"/>
       <c r="E27" s="12"/>
@@ -4994,10 +4988,10 @@
         <f t="shared" si="4"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M27" s="68" t="s">
+      <c r="M27" s="84" t="s">
         <v>8</v>
       </c>
-      <c r="N27" s="69"/>
+      <c r="N27" s="85"/>
       <c r="O27" s="55"/>
       <c r="P27" s="12"/>
       <c r="Q27" s="12"/>
@@ -5011,10 +5005,10 @@
       </c>
     </row>
     <row r="28" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="68" t="s">
+      <c r="A28" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="B28" s="69"/>
+      <c r="B28" s="85"/>
       <c r="C28" s="55"/>
       <c r="D28" s="12"/>
       <c r="E28" s="12"/>
@@ -5034,10 +5028,10 @@
         <f t="shared" si="4"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M28" s="68" t="s">
+      <c r="M28" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="N28" s="69"/>
+      <c r="N28" s="85"/>
       <c r="O28" s="55"/>
       <c r="P28" s="12"/>
       <c r="Q28" s="12"/>
@@ -5051,10 +5045,10 @@
       </c>
     </row>
     <row r="29" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="68" t="s">
+      <c r="A29" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="B29" s="69"/>
+      <c r="B29" s="85"/>
       <c r="C29" s="57"/>
       <c r="D29" s="58"/>
       <c r="E29" s="58"/>
@@ -5071,10 +5065,10 @@
         <v>0</v>
       </c>
       <c r="L29" s="12"/>
-      <c r="M29" s="68" t="s">
+      <c r="M29" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="N29" s="69"/>
+      <c r="N29" s="85"/>
       <c r="O29" s="57"/>
       <c r="P29" s="58"/>
       <c r="Q29" s="58"/>
@@ -5167,10 +5161,10 @@
       <c r="V31" s="1"/>
     </row>
     <row r="32" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="70" t="s">
+      <c r="A32" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="B32" s="71"/>
+      <c r="B32" s="77"/>
       <c r="C32" s="41">
         <v>92.567111769713335</v>
       </c>
@@ -5198,10 +5192,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C32:I32)&amp;","</f>
         <v xml:space="preserve">    92.5671117697133, 90.8358586083436, 89.2175053395332, 83.2372459642881, 75.380430844191, 58.9943671875974, 43.6225356413822,</v>
       </c>
-      <c r="M32" s="70" t="s">
+      <c r="M32" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="N32" s="71"/>
+      <c r="N32" s="77"/>
       <c r="O32" s="40">
         <v>3.88093621561358</v>
       </c>
@@ -5229,10 +5223,10 @@
       </c>
     </row>
     <row r="33" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="70" t="s">
+      <c r="A33" s="76" t="s">
         <v>6</v>
       </c>
-      <c r="B33" s="71"/>
+      <c r="B33" s="77"/>
       <c r="C33" s="41">
         <v>92.866950218042462</v>
       </c>
@@ -5260,10 +5254,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C33:I33)&amp;","</f>
         <v xml:space="preserve">    92.8669502180425, 91.2426907647456, 90.1370532276984, 86.0801529266134, 77.4102172551968, 59.6761947649801, 46.3954904194042,</v>
       </c>
-      <c r="M33" s="70" t="s">
+      <c r="M33" s="76" t="s">
         <v>6</v>
       </c>
-      <c r="N33" s="71"/>
+      <c r="N33" s="77"/>
       <c r="O33" s="41">
         <v>3.8319643020864191</v>
       </c>
@@ -5291,10 +5285,10 @@
       </c>
     </row>
     <row r="34" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="70" t="s">
+      <c r="A34" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="B34" s="71"/>
+      <c r="B34" s="77"/>
       <c r="C34" s="28">
         <v>87.268396410214976</v>
       </c>
@@ -5322,10 +5316,10 @@
         <f t="shared" ref="L34:L43" si="7">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C34:I34)&amp;","</f>
         <v xml:space="preserve">    87.268396410215, 87.2564283986868, 87.8221063041704, 87.6807264423516, 87.1448793671852, 74.9765678865158, 46.4175473948824,</v>
       </c>
-      <c r="M34" s="70" t="s">
+      <c r="M34" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="N34" s="71"/>
+      <c r="N34" s="77"/>
       <c r="O34" s="28">
         <v>2.610595868561878</v>
       </c>
@@ -5353,35 +5347,35 @@
       </c>
     </row>
     <row r="35" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="70" t="s">
+      <c r="A35" s="76" t="s">
         <v>12</v>
       </c>
-      <c r="B35" s="78"/>
-      <c r="C35" s="78"/>
-      <c r="D35" s="78"/>
-      <c r="E35" s="78"/>
-      <c r="F35" s="78"/>
-      <c r="G35" s="78"/>
-      <c r="H35" s="78"/>
-      <c r="I35" s="71"/>
+      <c r="B35" s="80"/>
+      <c r="C35" s="80"/>
+      <c r="D35" s="80"/>
+      <c r="E35" s="80"/>
+      <c r="F35" s="80"/>
+      <c r="G35" s="80"/>
+      <c r="H35" s="80"/>
+      <c r="I35" s="77"/>
       <c r="J35" s="44"/>
       <c r="K35" s="44"/>
       <c r="L35" s="1"/>
-      <c r="M35" s="70" t="s">
+      <c r="M35" s="76" t="s">
         <v>12</v>
       </c>
-      <c r="N35" s="78"/>
-      <c r="O35" s="78"/>
-      <c r="P35" s="78"/>
-      <c r="Q35" s="78"/>
-      <c r="R35" s="78"/>
-      <c r="S35" s="78"/>
-      <c r="T35" s="78"/>
-      <c r="U35" s="71"/>
+      <c r="N35" s="80"/>
+      <c r="O35" s="80"/>
+      <c r="P35" s="80"/>
+      <c r="Q35" s="80"/>
+      <c r="R35" s="80"/>
+      <c r="S35" s="80"/>
+      <c r="T35" s="80"/>
+      <c r="U35" s="77"/>
       <c r="V35" s="1"/>
     </row>
     <row r="36" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="83" t="s">
+      <c r="A36" s="78" t="s">
         <v>11</v>
       </c>
       <c r="B36" s="9" t="s">
@@ -5414,7 +5408,7 @@
         <f t="shared" si="7"/>
         <v xml:space="preserve">    92.9756945134422, 91.3636137491543, 90.0940179611611, 85.3777379183925, 79.2681590490105, 60.5212165139937, 42.0544488066562,</v>
       </c>
-      <c r="M36" s="83" t="s">
+      <c r="M36" s="78" t="s">
         <v>11</v>
       </c>
       <c r="N36" s="9" t="s">
@@ -5447,7 +5441,7 @@
       </c>
     </row>
     <row r="37" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="86"/>
+      <c r="A37" s="94"/>
       <c r="B37" s="9" t="s">
         <v>14</v>
       </c>
@@ -5478,7 +5472,7 @@
         <f t="shared" si="7"/>
         <v xml:space="preserve">    92.311293413261, 92.3335217568065, 91.3813575229196, 88.560101371957, 87.2789917059986, 75.3878970556703, 47.4787379071753,</v>
       </c>
-      <c r="M37" s="86"/>
+      <c r="M37" s="94"/>
       <c r="N37" s="9" t="s">
         <v>14</v>
       </c>
@@ -5509,7 +5503,7 @@
       </c>
     </row>
     <row r="38" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="86"/>
+      <c r="A38" s="94"/>
       <c r="B38" s="9" t="s">
         <v>17</v>
       </c>
@@ -5537,7 +5531,7 @@
       <c r="J38" s="44"/>
       <c r="K38" s="44"/>
       <c r="L38" s="1"/>
-      <c r="M38" s="86"/>
+      <c r="M38" s="94"/>
       <c r="N38" s="9" t="s">
         <v>17</v>
       </c>
@@ -5565,7 +5559,7 @@
       <c r="V38" s="1"/>
     </row>
     <row r="39" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="86"/>
+      <c r="A39" s="94"/>
       <c r="B39" s="9" t="s">
         <v>18</v>
       </c>
@@ -5593,7 +5587,7 @@
       <c r="J39" s="44"/>
       <c r="K39" s="44"/>
       <c r="L39" s="1"/>
-      <c r="M39" s="86"/>
+      <c r="M39" s="94"/>
       <c r="N39" s="9" t="s">
         <v>18</v>
       </c>
@@ -5621,7 +5615,7 @@
       <c r="V39" s="1"/>
     </row>
     <row r="40" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="86"/>
+      <c r="A40" s="94"/>
       <c r="B40" s="9" t="s">
         <v>15</v>
       </c>
@@ -5652,7 +5646,7 @@
         <f t="shared" si="7"/>
         <v xml:space="preserve">    92.9883867741658, 92.0506160293868, 90.7196986761964, 88.1856869456335, 83.275334389556, 64.6854019552345, 51.0690469748012,</v>
       </c>
-      <c r="M40" s="86"/>
+      <c r="M40" s="94"/>
       <c r="N40" s="9" t="s">
         <v>15</v>
       </c>
@@ -5680,63 +5674,63 @@
       <c r="V40" s="1"/>
     </row>
     <row r="41" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="86"/>
+      <c r="A41" s="94"/>
       <c r="B41" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C41" s="93">
+      <c r="C41" s="71">
         <v>90.557937802976383</v>
       </c>
-      <c r="D41" s="94">
+      <c r="D41" s="72">
         <v>89.886230037289053</v>
       </c>
-      <c r="E41" s="94">
+      <c r="E41" s="72">
         <v>89.784544221380457</v>
       </c>
-      <c r="F41" s="94">
+      <c r="F41" s="72">
         <v>88.385012329947799</v>
       </c>
-      <c r="G41" s="94">
+      <c r="G41" s="72">
         <v>86.648926570357631</v>
       </c>
-      <c r="H41" s="94">
+      <c r="H41" s="72">
         <v>75.600385397228763</v>
       </c>
-      <c r="I41" s="95">
+      <c r="I41" s="73">
         <v>46.810733956645073</v>
       </c>
       <c r="J41" s="44"/>
       <c r="K41" s="44"/>
       <c r="L41" s="1"/>
-      <c r="M41" s="86"/>
+      <c r="M41" s="94"/>
       <c r="N41" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="O41" s="93">
+      <c r="O41" s="71">
         <v>3.5359425091643861</v>
       </c>
-      <c r="P41" s="94">
+      <c r="P41" s="72">
         <v>2.9479688908817572</v>
       </c>
-      <c r="Q41" s="94">
+      <c r="Q41" s="72">
         <v>3.0863691442002841</v>
       </c>
-      <c r="R41" s="94">
+      <c r="R41" s="72">
         <v>2.7063960445241841</v>
       </c>
-      <c r="S41" s="94">
+      <c r="S41" s="72">
         <v>3.1149226793442399</v>
       </c>
-      <c r="T41" s="94">
+      <c r="T41" s="72">
         <v>3.6181303084227601</v>
       </c>
-      <c r="U41" s="95">
+      <c r="U41" s="73">
         <v>2.9939108090159601</v>
       </c>
       <c r="V41" s="1"/>
     </row>
     <row r="42" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="86"/>
+      <c r="A42" s="94"/>
       <c r="B42" s="9" t="s">
         <v>19</v>
       </c>
@@ -5764,7 +5758,7 @@
       <c r="J42" s="44"/>
       <c r="K42" s="44"/>
       <c r="L42" s="1"/>
-      <c r="M42" s="86"/>
+      <c r="M42" s="94"/>
       <c r="N42" s="9" t="s">
         <v>19</v>
       </c>
@@ -5792,7 +5786,7 @@
       <c r="V42" s="1"/>
     </row>
     <row r="43" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="86"/>
+      <c r="A43" s="94"/>
       <c r="B43" s="9" t="s">
         <v>16</v>
       </c>
@@ -5823,7 +5817,7 @@
         <f t="shared" si="7"/>
         <v xml:space="preserve">    87.2876347990493, 86.8786967506627, 87.0833631484665, 87.3002948979049, 86.5274318222157, 75.6891287758489, 46.8869070740948,</v>
       </c>
-      <c r="M43" s="86"/>
+      <c r="M43" s="94"/>
       <c r="N43" s="9" t="s">
         <v>16</v>
       </c>
@@ -5851,94 +5845,94 @@
       <c r="V43" s="1"/>
     </row>
     <row r="44" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="87"/>
+      <c r="A44" s="95"/>
       <c r="B44" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C44" s="93">
+      <c r="C44" s="71">
         <v>86.92964367820916</v>
       </c>
-      <c r="D44" s="94">
+      <c r="D44" s="72">
         <v>86.866051061699935</v>
       </c>
-      <c r="E44" s="94">
+      <c r="E44" s="72">
         <v>86.762869729013673</v>
       </c>
-      <c r="F44" s="94">
+      <c r="F44" s="72">
         <v>87.364519247017455</v>
       </c>
-      <c r="G44" s="94">
+      <c r="G44" s="72">
         <v>86.199216005572438</v>
       </c>
-      <c r="H44" s="94">
+      <c r="H44" s="72">
         <v>73.575313464991169</v>
       </c>
-      <c r="I44" s="95">
+      <c r="I44" s="73">
         <v>45.850722883932022</v>
       </c>
       <c r="J44" s="44"/>
       <c r="K44" s="44"/>
       <c r="L44" s="1"/>
-      <c r="M44" s="87"/>
+      <c r="M44" s="95"/>
       <c r="N44" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="O44" s="93">
+      <c r="O44" s="71">
         <v>2.3788555625895009</v>
       </c>
-      <c r="P44" s="94">
+      <c r="P44" s="72">
         <v>1.890618139395533</v>
       </c>
-      <c r="Q44" s="94">
+      <c r="Q44" s="72">
         <v>2.0117430969950041</v>
       </c>
-      <c r="R44" s="94">
+      <c r="R44" s="72">
         <v>1.842672316420805</v>
       </c>
-      <c r="S44" s="94">
+      <c r="S44" s="72">
         <v>1.6901439926207229</v>
       </c>
-      <c r="T44" s="94">
+      <c r="T44" s="72">
         <v>3.097142103089753</v>
       </c>
-      <c r="U44" s="95">
+      <c r="U44" s="73">
         <v>2.401443710230565</v>
       </c>
       <c r="V44" s="1"/>
     </row>
     <row r="45" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="70" t="s">
+      <c r="A45" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="B45" s="78"/>
-      <c r="C45" s="88"/>
-      <c r="D45" s="88"/>
-      <c r="E45" s="88"/>
-      <c r="F45" s="88"/>
-      <c r="G45" s="88"/>
-      <c r="H45" s="88"/>
+      <c r="B45" s="80"/>
+      <c r="C45" s="81"/>
+      <c r="D45" s="81"/>
+      <c r="E45" s="81"/>
+      <c r="F45" s="81"/>
+      <c r="G45" s="81"/>
+      <c r="H45" s="81"/>
       <c r="I45" s="82"/>
       <c r="J45" s="44"/>
       <c r="K45" s="44"/>
       <c r="L45" s="1"/>
-      <c r="M45" s="70" t="s">
+      <c r="M45" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="N45" s="78"/>
-      <c r="O45" s="88"/>
-      <c r="P45" s="88"/>
-      <c r="Q45" s="88"/>
-      <c r="R45" s="88"/>
-      <c r="S45" s="88"/>
-      <c r="T45" s="88"/>
+      <c r="N45" s="80"/>
+      <c r="O45" s="81"/>
+      <c r="P45" s="81"/>
+      <c r="Q45" s="81"/>
+      <c r="R45" s="81"/>
+      <c r="S45" s="81"/>
+      <c r="T45" s="81"/>
       <c r="U45" s="82"/>
       <c r="V45" s="1"/>
     </row>
     <row r="46" spans="1:22" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="70" t="s">
+      <c r="A46" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="B46" s="71"/>
+      <c r="B46" s="77"/>
       <c r="C46" s="60">
         <v>93.403798109785029</v>
       </c>
@@ -5966,10 +5960,10 @@
         <f t="shared" ref="L46:L48" si="8">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C46:I46)&amp;","</f>
         <v xml:space="preserve">    93.403798109785, 91.5170070049374, 89.7498804626893, 83.9973095811923, 74.3949629659869, 58.0955824704985, 44.4348127062073,</v>
       </c>
-      <c r="M46" s="70" t="s">
+      <c r="M46" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="N46" s="71"/>
+      <c r="N46" s="77"/>
       <c r="O46" s="60">
         <v>3.9553866501853321</v>
       </c>
@@ -5997,10 +5991,10 @@
       </c>
     </row>
     <row r="47" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="70" t="s">
+      <c r="A47" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="B47" s="71"/>
+      <c r="B47" s="77"/>
       <c r="C47" s="63">
         <v>92.778947400409621</v>
       </c>
@@ -6028,10 +6022,10 @@
         <f t="shared" si="8"/>
         <v xml:space="preserve">    92.7789474004096, 91.4503689963737, 89.8794809545421, 84.748756470337, 75.6276087825805, 58.3002656651169, 48.5841064376263,</v>
       </c>
-      <c r="M47" s="70" t="s">
+      <c r="M47" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="N47" s="71"/>
+      <c r="N47" s="77"/>
       <c r="O47" s="63">
         <v>4.3743918396131134</v>
       </c>
@@ -6059,10 +6053,10 @@
       </c>
     </row>
     <row r="48" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="70" t="s">
+      <c r="A48" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="B48" s="71"/>
+      <c r="B48" s="77"/>
       <c r="C48" s="63">
         <v>92.492055194421354</v>
       </c>
@@ -6090,10 +6084,10 @@
         <f t="shared" si="8"/>
         <v xml:space="preserve">    92.4920551944214, 91.055738083246, 89.2412648877623, 82.7136018096434, 73.1336770487749, 56.2292059013312, 43.695396708103,</v>
       </c>
-      <c r="M48" s="70" t="s">
+      <c r="M48" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="N48" s="71"/>
+      <c r="N48" s="77"/>
       <c r="O48" s="63">
         <v>4.0986250609792014</v>
       </c>
@@ -6121,10 +6115,10 @@
       </c>
     </row>
     <row r="49" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="70" t="s">
+      <c r="A49" s="76" t="s">
         <v>22</v>
       </c>
-      <c r="B49" s="71"/>
+      <c r="B49" s="77"/>
       <c r="C49" s="65">
         <v>92.657174075741665</v>
       </c>
@@ -6149,10 +6143,10 @@
       <c r="J49" s="51"/>
       <c r="K49" s="51"/>
       <c r="L49" s="50"/>
-      <c r="M49" s="70" t="s">
+      <c r="M49" s="76" t="s">
         <v>22</v>
       </c>
-      <c r="N49" s="71"/>
+      <c r="N49" s="77"/>
       <c r="O49" s="65">
         <v>4.2589004392769629</v>
       </c>
@@ -6177,10 +6171,10 @@
       <c r="V49" s="1"/>
     </row>
     <row r="50" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="70" t="s">
+      <c r="A50" s="76" t="s">
         <v>23</v>
       </c>
-      <c r="B50" s="78"/>
+      <c r="B50" s="80"/>
       <c r="C50" s="81"/>
       <c r="D50" s="81"/>
       <c r="E50" s="81"/>
@@ -6191,10 +6185,10 @@
       <c r="J50" s="44"/>
       <c r="K50" s="44"/>
       <c r="L50" s="1"/>
-      <c r="M50" s="70" t="s">
+      <c r="M50" s="76" t="s">
         <v>23</v>
       </c>
-      <c r="N50" s="78"/>
+      <c r="N50" s="80"/>
       <c r="O50" s="81"/>
       <c r="P50" s="81"/>
       <c r="Q50" s="81"/>
@@ -6205,10 +6199,10 @@
       <c r="V50" s="1"/>
     </row>
     <row r="51" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="70" t="s">
+      <c r="A51" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="B51" s="71"/>
+      <c r="B51" s="77"/>
       <c r="C51" s="60">
         <v>92.603769819293618</v>
       </c>
@@ -6236,10 +6230,10 @@
         <f t="shared" ref="L51:L53" si="9">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C51:I51)&amp;","</f>
         <v xml:space="preserve">    92.6037698192936, 91.4319470683528, 90.3907950429996, 86.7895628282223, 80.6155540330522, 56.6095785531339, 41.2792806229243,</v>
       </c>
-      <c r="M51" s="70" t="s">
+      <c r="M51" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="N51" s="71"/>
+      <c r="N51" s="77"/>
       <c r="O51" s="60">
         <v>3.708759274801273</v>
       </c>
@@ -6267,10 +6261,10 @@
       </c>
     </row>
     <row r="52" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="83" t="s">
+      <c r="A52" s="78" t="s">
         <v>8</v>
       </c>
-      <c r="B52" s="80"/>
+      <c r="B52" s="79"/>
       <c r="C52" s="63">
         <v>91.377634404932721</v>
       </c>
@@ -6298,10 +6292,10 @@
         <f t="shared" si="9"/>
         <v xml:space="preserve">    91.3776344049327, 90.4053733332451, 89.3714803083327, 87.6098986263952, 85.5372307015107, 70.9307087454215, 44.0973262328065,</v>
       </c>
-      <c r="M52" s="70" t="s">
+      <c r="M52" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="N52" s="71"/>
+      <c r="N52" s="77"/>
       <c r="O52" s="63">
         <v>3.5684194304484111</v>
       </c>
@@ -6329,10 +6323,10 @@
       </c>
     </row>
     <row r="53" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="70" t="s">
+      <c r="A53" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="B53" s="71"/>
+      <c r="B53" s="77"/>
       <c r="C53" s="63">
         <v>92.603715202692385</v>
       </c>
@@ -6360,10 +6354,10 @@
         <f t="shared" si="9"/>
         <v xml:space="preserve">    92.6037152026924, 91.4849975027203, 90.6301712993249, 85.3420346970645, 78.2086079443082, 58.1887672547126, 45.4689195625762,</v>
       </c>
-      <c r="M53" s="70" t="s">
+      <c r="M53" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="N53" s="71"/>
+      <c r="N53" s="77"/>
       <c r="O53" s="63">
         <v>4.0727132923350373</v>
       </c>
@@ -6391,10 +6385,10 @@
       </c>
     </row>
     <row r="54" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="70" t="s">
+      <c r="A54" s="76" t="s">
         <v>22</v>
       </c>
-      <c r="B54" s="71"/>
+      <c r="B54" s="77"/>
       <c r="C54" s="65">
         <v>92.692685851985146</v>
       </c>
@@ -6419,10 +6413,10 @@
       <c r="J54" s="44"/>
       <c r="K54" s="44"/>
       <c r="L54" s="1"/>
-      <c r="M54" s="70" t="s">
+      <c r="M54" s="76" t="s">
         <v>22</v>
       </c>
-      <c r="N54" s="71"/>
+      <c r="N54" s="77"/>
       <c r="O54" s="65">
         <v>4.3508377678439567</v>
       </c>
@@ -6447,10 +6441,10 @@
       <c r="V54" s="1"/>
     </row>
     <row r="55" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="70" t="s">
+      <c r="A55" s="76" t="s">
         <v>24</v>
       </c>
-      <c r="B55" s="78"/>
+      <c r="B55" s="80"/>
       <c r="C55" s="81"/>
       <c r="D55" s="81"/>
       <c r="E55" s="81"/>
@@ -6461,10 +6455,10 @@
       <c r="J55" s="44"/>
       <c r="K55" s="44"/>
       <c r="L55" s="1"/>
-      <c r="M55" s="70" t="s">
+      <c r="M55" s="76" t="s">
         <v>23</v>
       </c>
-      <c r="N55" s="78"/>
+      <c r="N55" s="80"/>
       <c r="O55" s="81"/>
       <c r="P55" s="81"/>
       <c r="Q55" s="81"/>
@@ -6475,10 +6469,10 @@
       <c r="V55" s="1"/>
     </row>
     <row r="56" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="70" t="s">
+      <c r="A56" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="B56" s="71"/>
+      <c r="B56" s="77"/>
       <c r="C56" s="60"/>
       <c r="D56" s="61"/>
       <c r="E56" s="61"/>
@@ -6492,10 +6486,10 @@
         <f t="shared" ref="L56:L58" si="11">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C56:I56)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M56" s="70" t="s">
+      <c r="M56" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="N56" s="71"/>
+      <c r="N56" s="77"/>
       <c r="O56" s="60"/>
       <c r="P56" s="61"/>
       <c r="Q56" s="61"/>
@@ -6509,10 +6503,10 @@
       </c>
     </row>
     <row r="57" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="83" t="s">
+      <c r="A57" s="78" t="s">
         <v>8</v>
       </c>
-      <c r="B57" s="80"/>
+      <c r="B57" s="79"/>
       <c r="C57" s="63"/>
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
@@ -6526,10 +6520,10 @@
         <f t="shared" si="11"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M57" s="70" t="s">
+      <c r="M57" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="N57" s="71"/>
+      <c r="N57" s="77"/>
       <c r="O57" s="63"/>
       <c r="P57" s="1"/>
       <c r="Q57" s="1"/>
@@ -6543,10 +6537,10 @@
       </c>
     </row>
     <row r="58" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="70" t="s">
+      <c r="A58" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="B58" s="71"/>
+      <c r="B58" s="77"/>
       <c r="C58" s="63"/>
       <c r="D58" s="1"/>
       <c r="E58" s="1"/>
@@ -6560,10 +6554,10 @@
         <f t="shared" si="11"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M58" s="70" t="s">
+      <c r="M58" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="N58" s="71"/>
+      <c r="N58" s="77"/>
       <c r="O58" s="63"/>
       <c r="P58" s="1"/>
       <c r="Q58" s="1"/>
@@ -6577,10 +6571,10 @@
       </c>
     </row>
     <row r="59" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="70" t="s">
+      <c r="A59" s="76" t="s">
         <v>22</v>
       </c>
-      <c r="B59" s="71"/>
+      <c r="B59" s="77"/>
       <c r="C59" s="65"/>
       <c r="D59" s="66"/>
       <c r="E59" s="66"/>
@@ -6591,10 +6585,10 @@
       <c r="J59" s="44"/>
       <c r="K59" s="44"/>
       <c r="L59" s="1"/>
-      <c r="M59" s="70" t="s">
+      <c r="M59" s="76" t="s">
         <v>22</v>
       </c>
-      <c r="N59" s="71"/>
+      <c r="N59" s="77"/>
       <c r="O59" s="65"/>
       <c r="P59" s="66"/>
       <c r="Q59" s="66"/>
@@ -6620,14 +6614,62 @@
     </row>
   </sheetData>
   <mergeCells count="80">
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="M59:N59"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="M56:N56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="M57:N57"/>
-    <mergeCell ref="A58:B58"/>
-    <mergeCell ref="M58:N58"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="M32:N32"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="M5:U5"/>
+    <mergeCell ref="M20:U20"/>
+    <mergeCell ref="A15:I15"/>
+    <mergeCell ref="A25:I25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="M48:N48"/>
+    <mergeCell ref="M49:N49"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="M46:N46"/>
+    <mergeCell ref="M47:N47"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="M33:N33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="M34:N34"/>
+    <mergeCell ref="A35:I35"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A45:I45"/>
+    <mergeCell ref="M15:U15"/>
+    <mergeCell ref="M45:U45"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="M19:N19"/>
+    <mergeCell ref="M35:U35"/>
+    <mergeCell ref="A20:I20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="M23:N23"/>
+    <mergeCell ref="M24:N24"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="M54:N54"/>
+    <mergeCell ref="A50:I50"/>
+    <mergeCell ref="M50:U50"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="M51:N51"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="M52:N52"/>
     <mergeCell ref="A6:A14"/>
     <mergeCell ref="M6:M14"/>
     <mergeCell ref="A36:A44"/>
@@ -6644,62 +6686,14 @@
     <mergeCell ref="M29:N29"/>
     <mergeCell ref="A53:B53"/>
     <mergeCell ref="M53:N53"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="M54:N54"/>
-    <mergeCell ref="A50:I50"/>
-    <mergeCell ref="M50:U50"/>
-    <mergeCell ref="A51:B51"/>
-    <mergeCell ref="M51:N51"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="M52:N52"/>
-    <mergeCell ref="A45:I45"/>
-    <mergeCell ref="M15:U15"/>
-    <mergeCell ref="M45:U45"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="M19:N19"/>
-    <mergeCell ref="M35:U35"/>
-    <mergeCell ref="A20:I20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="M22:N22"/>
-    <mergeCell ref="M23:N23"/>
-    <mergeCell ref="M24:N24"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="M48:N48"/>
-    <mergeCell ref="M49:N49"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="A46:B46"/>
-    <mergeCell ref="A47:B47"/>
-    <mergeCell ref="M46:N46"/>
-    <mergeCell ref="M47:N47"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="M33:N33"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="M34:N34"/>
-    <mergeCell ref="A35:I35"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="M32:N32"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="A5:I5"/>
-    <mergeCell ref="M5:U5"/>
-    <mergeCell ref="M20:U20"/>
-    <mergeCell ref="A15:I15"/>
-    <mergeCell ref="A25:I25"/>
-    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="M59:N59"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="M56:N56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="M57:N57"/>
+    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="M58:N58"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C6:I6">
@@ -6803,7 +6797,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C12:I12">
-    <cfRule type="colorScale" priority="22">
+    <cfRule type="colorScale" priority="23">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6813,7 +6807,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="23">
+    <cfRule type="colorScale" priority="22">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6914,6 +6908,38 @@
       </colorScale>
     </cfRule>
     <cfRule type="colorScale" priority="40">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C26:I28">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -7035,6 +7061,16 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J50:K54">
+    <cfRule type="colorScale" priority="36">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="33">
       <colorScale>
         <cfvo type="min"/>
@@ -7045,7 +7081,19 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="36">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J55:K59">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -7080,60 +7128,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C26:I28">
-    <cfRule type="colorScale" priority="5">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J55:K59">
-    <cfRule type="colorScale" priority="3">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -7145,11 +7139,11 @@
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="C1" s="96" t="s">
+      <c r="C1" s="75" t="s">
         <v>31</v>
       </c>
-      <c r="D1" s="96"/>
-      <c r="E1" s="96"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="C2" t="s">
@@ -7163,7 +7157,7 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" s="97" t="s">
+      <c r="A3" s="74" t="s">
         <v>30</v>
       </c>
       <c r="B3" t="s">
@@ -7171,13 +7165,13 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" s="97"/>
+      <c r="A4" s="74"/>
       <c r="B4" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" s="97"/>
+      <c r="A5" s="74"/>
       <c r="B5" t="s">
         <v>29</v>
       </c>

--- a/results_(stress_test)_summary/summary.xlsx
+++ b/results_(stress_test)_summary/summary.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\RnD_Repo\Research_Engineering\feature_fusion_PCCxSigmoid-PLV-\results_(stress_test)_summary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3799D395-140B-4C7B-8973-2BD6D0477111}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAAD3D7B-8ED0-45D8-BD1C-3D7869504624}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="639" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="partialdata_20260429" sheetId="6" r:id="rId1"/>
-    <sheet name="fullldata_20260429" sheetId="5" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="7" r:id="rId3"/>
+    <sheet name="partialdata_20260429_spt_idx" sheetId="6" r:id="rId1"/>
+    <sheet name="fullldata_20260524_spt_idx" sheetId="5" r:id="rId2"/>
+    <sheet name="confusion_mtx" sheetId="7" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="36">
   <si>
     <t>Accuracy</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -184,7 +184,23 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Modifier</t>
+    <t>Reliability threshold</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0 (no threshold)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Basis</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AUC</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -391,7 +407,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="127">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -562,12 +578,66 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -580,6 +650,21 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -589,45 +674,55 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -984,10 +1079,10 @@
       <c r="V1" s="12"/>
     </row>
     <row r="2" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="84" t="s">
+      <c r="A2" s="111" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="85"/>
+      <c r="B2" s="112"/>
       <c r="C2" s="20">
         <v>93.101364775358491</v>
       </c>
@@ -1021,10 +1116,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C2:I2)&amp;","</f>
         <v xml:space="preserve">    93.1013647753585, 91.3266637254648, 89.7225610371485, 83.857204647099, 76.2429490451186, 60.4027774173364, 47.7409002961387,</v>
       </c>
-      <c r="M2" s="84" t="s">
+      <c r="M2" s="111" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="85"/>
+      <c r="N2" s="112"/>
       <c r="O2" s="31">
         <v>3.4649270444699574</v>
       </c>
@@ -1052,10 +1147,10 @@
       </c>
     </row>
     <row r="3" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="84" t="s">
+      <c r="A3" s="111" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="85"/>
+      <c r="B3" s="112"/>
       <c r="C3" s="31">
         <v>93.273358766079312</v>
       </c>
@@ -1086,13 +1181,13 @@
         <v>81.54747164767862</v>
       </c>
       <c r="L3" s="12" t="str">
-        <f t="shared" ref="L3:L4" si="0">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C3:I3)&amp;","</f>
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C3:I3)&amp;","</f>
         <v xml:space="preserve">    93.2733587660793, 91.6155877934354, 90.6205330495939, 86.5975138193237, 78.2243502683126, 60.8549929786013, 48.7439337710534,</v>
       </c>
-      <c r="M3" s="84" t="s">
+      <c r="M3" s="111" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="85"/>
+      <c r="N3" s="112"/>
       <c r="O3" s="31">
         <v>3.4672469457762647</v>
       </c>
@@ -1115,15 +1210,15 @@
         <v>9.1853207799272329</v>
       </c>
       <c r="V3" s="12" t="str">
-        <f t="shared" ref="V3:V4" si="1">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,O3:U3)&amp;","</f>
+        <f t="shared" ref="V3:V4" si="0">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,O3:U3)&amp;","</f>
         <v xml:space="preserve">    3.46724694577626, 4.10663738581389, 4.44334428313897, 4.85726616902442, 6.73340650119937, 9.30559121407586, 9.18532077992723,</v>
       </c>
     </row>
     <row r="4" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="84" t="s">
+      <c r="A4" s="111" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="85"/>
+      <c r="B4" s="112"/>
       <c r="C4" s="24">
         <v>87.593900000000005</v>
       </c>
@@ -1154,13 +1249,13 @@
         <v>81.468931946607086</v>
       </c>
       <c r="L4" s="12" t="str">
-        <f t="shared" si="0"/>
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C4:I4)&amp;","</f>
         <v xml:space="preserve">    87.5939, 87.6637168141593, 88.1120943952802, 87.9700256922638, 87.4617081462642, 75.2513631894163, 47.7206838582802,</v>
       </c>
-      <c r="M4" s="84" t="s">
+      <c r="M4" s="111" t="s">
         <v>10</v>
       </c>
-      <c r="N4" s="85"/>
+      <c r="N4" s="112"/>
       <c r="O4" s="49">
         <v>2.4529187882918819</v>
       </c>
@@ -1183,36 +1278,36 @@
         <v>3.7419646549723868</v>
       </c>
       <c r="V4" s="12" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v xml:space="preserve">    2.45291878829188, 2.16276566139488, 2.29733988047472, 2.13416531965459, 2.38348787528267, 3.78798604641006, 3.74196465497239,</v>
       </c>
     </row>
     <row r="5" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="84" t="s">
+      <c r="A5" s="111" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="86"/>
-      <c r="C5" s="86"/>
-      <c r="D5" s="86"/>
-      <c r="E5" s="86"/>
-      <c r="F5" s="86"/>
-      <c r="G5" s="86"/>
-      <c r="H5" s="86"/>
-      <c r="I5" s="85"/>
+      <c r="B5" s="113"/>
+      <c r="C5" s="113"/>
+      <c r="D5" s="113"/>
+      <c r="E5" s="113"/>
+      <c r="F5" s="113"/>
+      <c r="G5" s="113"/>
+      <c r="H5" s="113"/>
+      <c r="I5" s="112"/>
       <c r="J5" s="35"/>
       <c r="K5" s="35"/>
       <c r="L5" s="12"/>
-      <c r="M5" s="84" t="s">
+      <c r="M5" s="111" t="s">
         <v>12</v>
       </c>
-      <c r="N5" s="86"/>
-      <c r="O5" s="86"/>
-      <c r="P5" s="86"/>
-      <c r="Q5" s="86"/>
-      <c r="R5" s="86"/>
-      <c r="S5" s="86"/>
-      <c r="T5" s="86"/>
-      <c r="U5" s="85"/>
+      <c r="N5" s="113"/>
+      <c r="O5" s="113"/>
+      <c r="P5" s="113"/>
+      <c r="Q5" s="113"/>
+      <c r="R5" s="113"/>
+      <c r="S5" s="113"/>
+      <c r="T5" s="113"/>
+      <c r="U5" s="112"/>
       <c r="V5" s="12"/>
     </row>
     <row r="6" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -1252,7 +1347,7 @@
         <v>81.707947516847028</v>
       </c>
       <c r="L6" s="12" t="str">
-        <f t="shared" ref="L6:L7" si="2">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C6:I6)&amp;","</f>
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C6:I6)&amp;","</f>
         <v xml:space="preserve">    93.4021632251721, 91.8271265322364, 90.5586899540653, 86.0233767881498, 80.0763011214053, 61.7128781390843, 46.4235100072953,</v>
       </c>
       <c r="M6" s="7" t="s">
@@ -1283,7 +1378,7 @@
         <v>8.6649338950065129</v>
       </c>
       <c r="V6" s="12" t="str">
-        <f t="shared" ref="V6:V7" si="3">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,O6:U6)&amp;","</f>
+        <f t="shared" ref="V6:V7" si="1">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,O6:U6)&amp;","</f>
         <v xml:space="preserve">    3.39573454381898, 4.07012417155694, 4.25451390939223, 5.05503861074922, 5.59981814470124, 8.78151364991547, 8.66493389500651,</v>
       </c>
     </row>
@@ -1324,7 +1419,7 @@
         <v>84.382587868407157</v>
       </c>
       <c r="L7" s="12" t="str">
-        <f t="shared" si="2"/>
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C7:I7)&amp;","</f>
         <v xml:space="preserve">    92.6912487708948, 92.7069813176008, 91.7345132743363, 88.8675536408908, 87.5647050003316, 75.6237856728864, 48.8313393714478,</v>
       </c>
       <c r="M7" s="7" t="s">
@@ -1355,43 +1450,43 @@
         <v>5.9316401890770027</v>
       </c>
       <c r="V7" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v xml:space="preserve">    3.14920929515277, 3.31820763369914, 3.19816618617616, 3.13212695988859, 3.07506319977273, 5.16611420499541, 5.931640189077,</v>
       </c>
     </row>
     <row r="8" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="84" t="s">
+      <c r="A8" s="111" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="86"/>
-      <c r="C8" s="91"/>
-      <c r="D8" s="91"/>
-      <c r="E8" s="91"/>
-      <c r="F8" s="91"/>
-      <c r="G8" s="91"/>
-      <c r="H8" s="91"/>
-      <c r="I8" s="90"/>
+      <c r="B8" s="113"/>
+      <c r="C8" s="116"/>
+      <c r="D8" s="116"/>
+      <c r="E8" s="116"/>
+      <c r="F8" s="116"/>
+      <c r="G8" s="116"/>
+      <c r="H8" s="116"/>
+      <c r="I8" s="110"/>
       <c r="J8" s="35"/>
       <c r="K8" s="35"/>
       <c r="L8" s="12"/>
-      <c r="M8" s="84" t="s">
+      <c r="M8" s="111" t="s">
         <v>20</v>
       </c>
-      <c r="N8" s="86"/>
-      <c r="O8" s="91"/>
-      <c r="P8" s="91"/>
-      <c r="Q8" s="91"/>
-      <c r="R8" s="91"/>
-      <c r="S8" s="91"/>
-      <c r="T8" s="91"/>
-      <c r="U8" s="90"/>
+      <c r="N8" s="113"/>
+      <c r="O8" s="116"/>
+      <c r="P8" s="116"/>
+      <c r="Q8" s="116"/>
+      <c r="R8" s="116"/>
+      <c r="S8" s="116"/>
+      <c r="T8" s="116"/>
+      <c r="U8" s="110"/>
       <c r="V8" s="12"/>
     </row>
     <row r="9" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="84" t="s">
+      <c r="A9" s="111" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="85"/>
+      <c r="B9" s="112"/>
       <c r="C9" s="31">
         <v>93.782740335124032</v>
       </c>
@@ -1422,13 +1517,13 @@
         <v>80.907628526198323</v>
       </c>
       <c r="L9" s="12" t="str">
-        <f t="shared" ref="L9:L12" si="4">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C9:I9)&amp;","</f>
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C9:I9)&amp;","</f>
         <v xml:space="preserve">    93.782740335124, 91.9482088945406, 90.212980504445, 84.6303889595354, 75.3710931755465, 59.6272113080563, 47.8441855033348,</v>
       </c>
-      <c r="M9" s="84" t="s">
+      <c r="M9" s="111" t="s">
         <v>7</v>
       </c>
-      <c r="N9" s="85"/>
+      <c r="N9" s="112"/>
       <c r="O9" s="31">
         <v>3.5391983918820551</v>
       </c>
@@ -1451,15 +1546,15 @@
         <v>8.7604668874903737</v>
       </c>
       <c r="V9" s="12" t="str">
-        <f t="shared" ref="V9:V12" si="5">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,O9:U9)&amp;","</f>
+        <f t="shared" ref="V9:V12" si="2">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,O9:U9)&amp;","</f>
         <v xml:space="preserve">    3.53919839188206, 4.1060038651542, 4.77479580646868, 5.34833390646804, 8.09949039211975, 10.5998740220541, 8.76046688749037,</v>
       </c>
     </row>
     <row r="10" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="89" t="s">
+      <c r="A10" s="102" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="90"/>
+      <c r="B10" s="110"/>
       <c r="C10" s="34">
         <v>93.226230330712227</v>
       </c>
@@ -1490,13 +1585,13 @@
         <v>81.11919191919192</v>
       </c>
       <c r="L10" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C10:I10)&amp;","</f>
         <v xml:space="preserve">    93.2262303307122, 91.8332915221297, 90.3252911645718, 85.3834923600839, 76.5670002912366, 59.4145422249904, 50.5634074112521,</v>
       </c>
-      <c r="M10" s="84" t="s">
+      <c r="M10" s="111" t="s">
         <v>8</v>
       </c>
-      <c r="N10" s="85"/>
+      <c r="N10" s="112"/>
       <c r="O10" s="34">
         <v>3.945711842949601</v>
       </c>
@@ -1519,15 +1614,15 @@
         <v>8.7433484877826491</v>
       </c>
       <c r="V10" s="12" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v xml:space="preserve">    3.9457118429496, 4.85259501611341, 4.43468944991481, 5.48100295746765, 8.46367256446001, 10.788297692872, 8.74334848778265,</v>
       </c>
     </row>
     <row r="11" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="84" t="s">
+      <c r="A11" s="111" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="85"/>
+      <c r="B11" s="112"/>
       <c r="C11" s="34">
         <v>93.004922187908207</v>
       </c>
@@ -1558,13 +1653,13 @@
         <v>80.14941839173926</v>
       </c>
       <c r="L11" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C11:I11)&amp;","</f>
         <v xml:space="preserve">    93.0049221879082, 91.5185021785079, 89.7294209580821, 83.3486073985646, 74.0877199053048, 57.9173320415113, 48.0077941850708,</v>
       </c>
-      <c r="M11" s="84" t="s">
+      <c r="M11" s="111" t="s">
         <v>21</v>
       </c>
-      <c r="N11" s="85"/>
+      <c r="N11" s="112"/>
       <c r="O11" s="34">
         <v>3.690401528555848</v>
       </c>
@@ -1587,15 +1682,15 @@
         <v>9.2904800440053528</v>
       </c>
       <c r="V11" s="12" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v xml:space="preserve">    3.69040152855585, 4.24693674690275, 4.4611096369835, 5.40892864268034, 9.09212497406718, 10.8355770858107, 9.29048004400535,</v>
       </c>
     </row>
     <row r="12" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="84" t="s">
+      <c r="A12" s="111" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="85"/>
+      <c r="B12" s="112"/>
       <c r="C12" s="37">
         <v>93.123279613145442</v>
       </c>
@@ -1626,13 +1721,13 @@
         <v>80.789319111757024</v>
       </c>
       <c r="L12" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C12:I12)&amp;","</f>
         <v xml:space="preserve">    93.1232796131454, 91.674385879924, 89.6986882816172, 84.9570671026566, 75.9390825180149, 59.9950922297482, 48.4403036935152,</v>
       </c>
-      <c r="M12" s="84" t="s">
+      <c r="M12" s="111" t="s">
         <v>22</v>
       </c>
-      <c r="N12" s="85"/>
+      <c r="N12" s="112"/>
       <c r="O12" s="37">
         <v>3.8088682011350912</v>
       </c>
@@ -1655,43 +1750,43 @@
         <v>9.821397671709315</v>
       </c>
       <c r="V12" s="12" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v xml:space="preserve">    3.80886820113509, 4.47838643868506, 5.08498401921731, 5.03663270262306, 7.66437987866744, 10.0514690462765, 9.82139767170931,</v>
       </c>
     </row>
     <row r="13" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="84" t="s">
+      <c r="A13" s="111" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="86"/>
-      <c r="C13" s="87"/>
-      <c r="D13" s="87"/>
-      <c r="E13" s="87"/>
-      <c r="F13" s="87"/>
-      <c r="G13" s="87"/>
-      <c r="H13" s="87"/>
-      <c r="I13" s="88"/>
+      <c r="B13" s="113"/>
+      <c r="C13" s="114"/>
+      <c r="D13" s="114"/>
+      <c r="E13" s="114"/>
+      <c r="F13" s="114"/>
+      <c r="G13" s="114"/>
+      <c r="H13" s="114"/>
+      <c r="I13" s="115"/>
       <c r="J13" s="35"/>
       <c r="K13" s="35"/>
       <c r="L13" s="12"/>
-      <c r="M13" s="84" t="s">
+      <c r="M13" s="111" t="s">
         <v>23</v>
       </c>
-      <c r="N13" s="86"/>
-      <c r="O13" s="87"/>
-      <c r="P13" s="87"/>
-      <c r="Q13" s="87"/>
-      <c r="R13" s="87"/>
-      <c r="S13" s="87"/>
-      <c r="T13" s="87"/>
-      <c r="U13" s="88"/>
+      <c r="N13" s="113"/>
+      <c r="O13" s="114"/>
+      <c r="P13" s="114"/>
+      <c r="Q13" s="114"/>
+      <c r="R13" s="114"/>
+      <c r="S13" s="114"/>
+      <c r="T13" s="114"/>
+      <c r="U13" s="115"/>
       <c r="V13" s="12"/>
     </row>
     <row r="14" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="84" t="s">
+      <c r="A14" s="111" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="85"/>
+      <c r="B14" s="112"/>
       <c r="C14" s="31">
         <v>92.969518190757128</v>
       </c>
@@ -1722,13 +1817,13 @@
         <v>81.635477022580943</v>
       </c>
       <c r="L14" s="12" t="str">
-        <f t="shared" ref="L14:L17" si="6">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C14:I14)&amp;","</f>
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C14:I14)&amp;","</f>
         <v xml:space="preserve">    92.9695181907571, 91.8515240904621, 90.756145526057, 87.2531365611583, 81.1789721364371, 57.3869295293788, 44.8554428094822,</v>
       </c>
-      <c r="M14" s="84" t="s">
+      <c r="M14" s="111" t="s">
         <v>7</v>
       </c>
-      <c r="N14" s="85"/>
+      <c r="N14" s="112"/>
       <c r="O14" s="31">
         <v>3.3991921823554931</v>
       </c>
@@ -1751,15 +1846,15 @@
         <v>5.203571843512913</v>
       </c>
       <c r="V14" s="12" t="str">
-        <f t="shared" ref="V14:V17" si="7">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,O14:U14)&amp;","</f>
+        <f t="shared" ref="V14:V17" si="3">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,O14:U14)&amp;","</f>
         <v xml:space="preserve">    3.39919218235549, 3.656148978379, 3.43161793888068, 3.36107812276178, 5.27738358730928, 8.20271301965104, 5.20357184351291,</v>
       </c>
     </row>
     <row r="15" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="89" t="s">
+      <c r="A15" s="102" t="s">
         <v>8</v>
       </c>
-      <c r="B15" s="90"/>
+      <c r="B15" s="110"/>
       <c r="C15" s="34">
         <v>91.898721730580135</v>
       </c>
@@ -1790,13 +1885,13 @@
         <v>82.625440098962798</v>
       </c>
       <c r="L15" s="12" t="str">
-        <f t="shared" si="6"/>
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C15:I15)&amp;","</f>
         <v xml:space="preserve">    91.8987217305801, 90.765995668936, 89.7052685000158, 87.9596853490659, 85.7500007208828, 71.3873880108536, 45.5963431056209,</v>
       </c>
-      <c r="M15" s="84" t="s">
+      <c r="M15" s="111" t="s">
         <v>8</v>
       </c>
-      <c r="N15" s="85"/>
+      <c r="N15" s="112"/>
       <c r="O15" s="34">
         <v>3.190312271555559</v>
       </c>
@@ -1819,15 +1914,15 @@
         <v>2.488810891584841</v>
       </c>
       <c r="V15" s="12" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    3.19031227155556, 2.88280360646228, 2.58847407711463, 2.62134504708773, 3.20356998968766, 4.75671211275067, 2.48881089158484,</v>
       </c>
     </row>
     <row r="16" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="84" t="s">
+      <c r="A16" s="111" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="85"/>
+      <c r="B16" s="112"/>
       <c r="C16" s="34">
         <v>93.044276622923505</v>
       </c>
@@ -1858,13 +1953,13 @@
         <v>81.55872152873296</v>
       </c>
       <c r="L16" s="12" t="str">
-        <f t="shared" si="6"/>
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C16:I16)&amp;","</f>
         <v xml:space="preserve">    93.0442766229235, 91.9351551484009, 90.9488922914558, 85.9525053561594, 78.9151838107019, 59.4421001335075, 49.5338281473023,</v>
       </c>
-      <c r="M16" s="84" t="s">
+      <c r="M16" s="111" t="s">
         <v>21</v>
       </c>
-      <c r="N16" s="85"/>
+      <c r="N16" s="112"/>
       <c r="O16" s="34">
         <v>3.72078192123604</v>
       </c>
@@ -1887,15 +1982,15 @@
         <v>9.2355901481835172</v>
       </c>
       <c r="V16" s="12" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    3.72078192123604, 4.04671527762167, 4.023576362777, 4.47676332123312, 7.20190165275039, 10.0466843686008, 9.23559014818352,</v>
       </c>
     </row>
     <row r="17" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="84" t="s">
+      <c r="A17" s="111" t="s">
         <v>22</v>
       </c>
-      <c r="B17" s="85"/>
+      <c r="B17" s="112"/>
       <c r="C17" s="37">
         <v>93.174110502686005</v>
       </c>
@@ -1926,13 +2021,13 @@
         <v>80.686930106085114</v>
       </c>
       <c r="L17" s="12" t="str">
-        <f t="shared" si="6"/>
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C17:I17)&amp;","</f>
         <v xml:space="preserve">    93.174110502686, 91.3917248419104, 89.5915391424955, 84.6905970928238, 76.4013471858177, 59.9636675057743, 47.7255772108755,</v>
       </c>
-      <c r="M17" s="84" t="s">
+      <c r="M17" s="111" t="s">
         <v>22</v>
       </c>
-      <c r="N17" s="85"/>
+      <c r="N17" s="112"/>
       <c r="O17" s="37">
         <v>3.8766021792735019</v>
       </c>
@@ -1955,7 +2050,7 @@
         <v>9.200486032966916</v>
       </c>
       <c r="V17" s="12" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">    3.8766021792735, 4.81264114062281, 4.6512210016048, 5.24160663557633, 8.07695886022353, 10.6573633075615, 9.20048603296692,</v>
       </c>
     </row>
@@ -2042,10 +2137,10 @@
       <c r="V19" s="1"/>
     </row>
     <row r="20" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="76" t="s">
+      <c r="A20" s="98" t="s">
         <v>5</v>
       </c>
-      <c r="B20" s="77"/>
+      <c r="B20" s="99"/>
       <c r="C20" s="41">
         <v>92.567111769713335</v>
       </c>
@@ -2073,10 +2168,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C20:I20)&amp;","</f>
         <v xml:space="preserve">    92.5671117697133, 90.8358586083436, 89.2175053395332, 83.2372459642881, 75.380430844191, 58.9943671875974, 43.6225356413822,</v>
       </c>
-      <c r="M20" s="76" t="s">
+      <c r="M20" s="98" t="s">
         <v>5</v>
       </c>
-      <c r="N20" s="77"/>
+      <c r="N20" s="99"/>
       <c r="O20" s="40">
         <v>3.88093621561358</v>
       </c>
@@ -2104,10 +2199,10 @@
       </c>
     </row>
     <row r="21" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="76" t="s">
+      <c r="A21" s="98" t="s">
         <v>6</v>
       </c>
-      <c r="B21" s="77"/>
+      <c r="B21" s="99"/>
       <c r="C21" s="41">
         <v>92.866950218042462</v>
       </c>
@@ -2135,10 +2230,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C21:I21)&amp;","</f>
         <v xml:space="preserve">    92.8669502180425, 91.2426907647456, 90.1370532276984, 86.0801529266134, 77.4102172551968, 59.6761947649801, 46.3954904194042,</v>
       </c>
-      <c r="M21" s="76" t="s">
+      <c r="M21" s="98" t="s">
         <v>6</v>
       </c>
-      <c r="N21" s="77"/>
+      <c r="N21" s="99"/>
       <c r="O21" s="41">
         <v>3.8319643020864191</v>
       </c>
@@ -2161,15 +2256,15 @@
         <v>10.021578856839133</v>
       </c>
       <c r="V21" s="1" t="str">
-        <f t="shared" ref="V21:V30" si="8">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,O21:U21)&amp;","</f>
+        <f t="shared" ref="V21:V30" si="4">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,O21:U21)&amp;","</f>
         <v xml:space="preserve">    3.83196430208642, 4.36032467052554, 4.79877351918793, 5.12629653673303, 7.08725879982336, 9.74577365763467, 10.0215788568391,</v>
       </c>
     </row>
     <row r="22" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="76" t="s">
+      <c r="A22" s="98" t="s">
         <v>10</v>
       </c>
-      <c r="B22" s="77"/>
+      <c r="B22" s="99"/>
       <c r="C22" s="28">
         <v>87.268396410214976</v>
       </c>
@@ -2194,13 +2289,13 @@
       <c r="J22" s="44"/>
       <c r="K22" s="44"/>
       <c r="L22" s="1" t="str">
-        <f t="shared" ref="L22:L25" si="9">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C22:I22)&amp;","</f>
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C22:I22)&amp;","</f>
         <v xml:space="preserve">    87.268396410215, 87.2564283986868, 87.8221063041704, 87.6807264423516, 87.1448793671852, 74.9765678865158, 46.4175473948824,</v>
       </c>
-      <c r="M22" s="76" t="s">
+      <c r="M22" s="98" t="s">
         <v>10</v>
       </c>
-      <c r="N22" s="77"/>
+      <c r="N22" s="99"/>
       <c r="O22" s="28">
         <v>2.610595868561878</v>
       </c>
@@ -2223,36 +2318,36 @@
         <v>4.1161081119796732</v>
       </c>
       <c r="V22" s="1" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    2.61059586856188, 2.32098052702246, 2.44262441526999, 2.28212554429868, 2.52313174140091, 3.76261004193711, 4.11610811197967,</v>
       </c>
     </row>
     <row r="23" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="76" t="s">
+      <c r="A23" s="98" t="s">
         <v>12</v>
       </c>
-      <c r="B23" s="80"/>
-      <c r="C23" s="80"/>
-      <c r="D23" s="80"/>
-      <c r="E23" s="80"/>
-      <c r="F23" s="80"/>
-      <c r="G23" s="80"/>
-      <c r="H23" s="80"/>
-      <c r="I23" s="77"/>
+      <c r="B23" s="107"/>
+      <c r="C23" s="107"/>
+      <c r="D23" s="107"/>
+      <c r="E23" s="107"/>
+      <c r="F23" s="107"/>
+      <c r="G23" s="107"/>
+      <c r="H23" s="107"/>
+      <c r="I23" s="99"/>
       <c r="J23" s="44"/>
       <c r="K23" s="44"/>
       <c r="L23" s="1"/>
-      <c r="M23" s="76" t="s">
+      <c r="M23" s="98" t="s">
         <v>12</v>
       </c>
-      <c r="N23" s="80"/>
-      <c r="O23" s="80"/>
-      <c r="P23" s="80"/>
-      <c r="Q23" s="80"/>
-      <c r="R23" s="80"/>
-      <c r="S23" s="80"/>
-      <c r="T23" s="80"/>
-      <c r="U23" s="77"/>
+      <c r="N23" s="107"/>
+      <c r="O23" s="107"/>
+      <c r="P23" s="107"/>
+      <c r="Q23" s="107"/>
+      <c r="R23" s="107"/>
+      <c r="S23" s="107"/>
+      <c r="T23" s="107"/>
+      <c r="U23" s="99"/>
       <c r="V23" s="1"/>
     </row>
     <row r="24" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
@@ -2286,7 +2381,7 @@
       <c r="J24" s="44"/>
       <c r="K24" s="44"/>
       <c r="L24" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C24:I24)&amp;","</f>
         <v xml:space="preserve">    92.9756945134422, 91.3636137491543, 90.0940179611611, 85.3777379183925, 79.2681590490105, 60.5212165139937, 42.0544488066562,</v>
       </c>
       <c r="M24" s="14" t="s">
@@ -2317,7 +2412,7 @@
         <v>9.5108664952359483</v>
       </c>
       <c r="V24" s="1" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    3.7825572598295, 4.44590737547327, 4.63230811977374, 5.37467956409337, 5.99129122503553, 9.09018177402371, 9.51086649523595,</v>
       </c>
     </row>
@@ -2352,7 +2447,7 @@
       <c r="J25" s="44"/>
       <c r="K25" s="44"/>
       <c r="L25" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C25:I25)&amp;","</f>
         <v xml:space="preserve">    92.311293413261, 92.3335217568065, 91.3813575229196, 88.560101371957, 87.2789917059986, 75.3878970556703, 47.4787379071753,</v>
       </c>
       <c r="M25" s="14" t="s">
@@ -2383,43 +2478,43 @@
         <v>6.1375770825509051</v>
       </c>
       <c r="V25" s="1" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    3.45837660705662, 3.62133151243551, 3.41882765616103, 3.25439791408069, 3.20212682277844, 5.23589217814922, 6.13757708255091,</v>
       </c>
     </row>
     <row r="26" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="76" t="s">
+      <c r="A26" s="98" t="s">
         <v>20</v>
       </c>
-      <c r="B26" s="80"/>
-      <c r="C26" s="83"/>
-      <c r="D26" s="83"/>
-      <c r="E26" s="83"/>
-      <c r="F26" s="83"/>
-      <c r="G26" s="83"/>
-      <c r="H26" s="83"/>
-      <c r="I26" s="79"/>
+      <c r="B26" s="107"/>
+      <c r="C26" s="117"/>
+      <c r="D26" s="117"/>
+      <c r="E26" s="117"/>
+      <c r="F26" s="117"/>
+      <c r="G26" s="117"/>
+      <c r="H26" s="117"/>
+      <c r="I26" s="101"/>
       <c r="J26" s="44"/>
       <c r="K26" s="44"/>
       <c r="L26" s="1"/>
-      <c r="M26" s="76" t="s">
+      <c r="M26" s="98" t="s">
         <v>20</v>
       </c>
-      <c r="N26" s="80"/>
-      <c r="O26" s="83"/>
-      <c r="P26" s="83"/>
-      <c r="Q26" s="83"/>
-      <c r="R26" s="83"/>
-      <c r="S26" s="83"/>
-      <c r="T26" s="83"/>
-      <c r="U26" s="79"/>
+      <c r="N26" s="107"/>
+      <c r="O26" s="117"/>
+      <c r="P26" s="117"/>
+      <c r="Q26" s="117"/>
+      <c r="R26" s="117"/>
+      <c r="S26" s="117"/>
+      <c r="T26" s="117"/>
+      <c r="U26" s="101"/>
       <c r="V26" s="1"/>
     </row>
     <row r="27" spans="1:22" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="76" t="s">
+      <c r="A27" s="98" t="s">
         <v>7</v>
       </c>
-      <c r="B27" s="77"/>
+      <c r="B27" s="99"/>
       <c r="C27" s="40">
         <v>93.403798109785029</v>
       </c>
@@ -2444,13 +2539,13 @@
       <c r="J27" s="44"/>
       <c r="K27" s="44"/>
       <c r="L27" s="1" t="str">
-        <f t="shared" ref="L27:L30" si="10">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C27:I27)&amp;","</f>
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C27:I27)&amp;","</f>
         <v xml:space="preserve">    93.403798109785, 91.5170070049374, 89.7498804626893, 83.9973095811923, 74.3949629659869, 58.0955824704985, 44.4348127062073,</v>
       </c>
-      <c r="M27" s="76" t="s">
+      <c r="M27" s="98" t="s">
         <v>7</v>
       </c>
-      <c r="N27" s="77"/>
+      <c r="N27" s="99"/>
       <c r="O27" s="40">
         <v>3.9553866501853321</v>
       </c>
@@ -2473,15 +2568,15 @@
         <v>9.3757621724255777</v>
       </c>
       <c r="V27" s="1" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    3.95538665018533, 4.51763083586123, 5.2125425794507, 5.64774613876846, 8.60905647131172, 11.3571573472546, 9.37576217242558,</v>
       </c>
     </row>
     <row r="28" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="76" t="s">
+      <c r="A28" s="98" t="s">
         <v>8</v>
       </c>
-      <c r="B28" s="77"/>
+      <c r="B28" s="99"/>
       <c r="C28" s="43">
         <v>92.778947400409621</v>
       </c>
@@ -2506,13 +2601,13 @@
       <c r="J28" s="44"/>
       <c r="K28" s="44"/>
       <c r="L28" s="1" t="str">
-        <f t="shared" si="10"/>
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C28:I28)&amp;","</f>
         <v xml:space="preserve">    92.7789474004096, 91.4503689963737, 89.8794809545421, 84.748756470337, 75.6276087825805, 58.3002656651169, 48.5841064376263,</v>
       </c>
-      <c r="M28" s="76" t="s">
+      <c r="M28" s="98" t="s">
         <v>8</v>
       </c>
-      <c r="N28" s="77"/>
+      <c r="N28" s="99"/>
       <c r="O28" s="43">
         <v>4.3743918396131134</v>
       </c>
@@ -2535,15 +2630,15 @@
         <v>9.2918474149187738</v>
       </c>
       <c r="V28" s="1" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    4.37439183961311, 5.17791436554653, 4.83627057213778, 5.67977823014479, 9.01909029779594, 11.0002581352619, 9.29184741491877,</v>
       </c>
     </row>
     <row r="29" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="76" t="s">
+      <c r="A29" s="98" t="s">
         <v>21</v>
       </c>
-      <c r="B29" s="77"/>
+      <c r="B29" s="99"/>
       <c r="C29" s="43">
         <v>92.492055194421354</v>
       </c>
@@ -2568,13 +2663,13 @@
       <c r="J29" s="44"/>
       <c r="K29" s="44"/>
       <c r="L29" s="1" t="str">
-        <f t="shared" si="10"/>
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C29:I29)&amp;","</f>
         <v xml:space="preserve">    92.4920551944214, 91.055738083246, 89.2412648877623, 82.7136018096434, 73.1336770487749, 56.2292059013312, 43.695396708103,</v>
       </c>
-      <c r="M29" s="76" t="s">
+      <c r="M29" s="98" t="s">
         <v>21</v>
       </c>
-      <c r="N29" s="77"/>
+      <c r="N29" s="99"/>
       <c r="O29" s="43">
         <v>4.0986250609792014</v>
       </c>
@@ -2597,15 +2692,15 @@
         <v>10.62887090695313</v>
       </c>
       <c r="V29" s="1" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    4.0986250609792, 4.59264434907123, 4.85215988073805, 5.81889191261663, 9.50889878253766, 11.3283954278833, 10.6288709069531,</v>
       </c>
     </row>
     <row r="30" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="76" t="s">
+      <c r="A30" s="98" t="s">
         <v>22</v>
       </c>
-      <c r="B30" s="77"/>
+      <c r="B30" s="99"/>
       <c r="C30" s="46">
         <v>92.657174075741665</v>
       </c>
@@ -2630,13 +2725,13 @@
       <c r="J30" s="51"/>
       <c r="K30" s="51"/>
       <c r="L30" s="1" t="str">
-        <f t="shared" si="10"/>
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C30:I30)&amp;","</f>
         <v xml:space="preserve">    92.6571740757417, 91.2080508143722, 89.1704556780914, 84.47461606277, 75.0666685936403, 58.5203409933682, 44.7861415920494,</v>
       </c>
-      <c r="M30" s="76" t="s">
+      <c r="M30" s="98" t="s">
         <v>22</v>
       </c>
-      <c r="N30" s="77"/>
+      <c r="N30" s="99"/>
       <c r="O30" s="46">
         <v>4.2589004392769629</v>
       </c>
@@ -2659,43 +2754,43 @@
         <v>10.945843294214329</v>
       </c>
       <c r="V30" s="1" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">    4.25890043927696, 4.85171866012655, 5.67176730834965, 5.30795079619218, 7.78847056150725, 10.5955633779262, 10.9458432942143,</v>
       </c>
     </row>
     <row r="31" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="76" t="s">
+      <c r="A31" s="98" t="s">
         <v>23</v>
       </c>
-      <c r="B31" s="80"/>
-      <c r="C31" s="81"/>
-      <c r="D31" s="81"/>
-      <c r="E31" s="81"/>
-      <c r="F31" s="81"/>
-      <c r="G31" s="81"/>
-      <c r="H31" s="81"/>
-      <c r="I31" s="82"/>
+      <c r="B31" s="107"/>
+      <c r="C31" s="108"/>
+      <c r="D31" s="108"/>
+      <c r="E31" s="108"/>
+      <c r="F31" s="108"/>
+      <c r="G31" s="108"/>
+      <c r="H31" s="108"/>
+      <c r="I31" s="109"/>
       <c r="J31" s="44"/>
       <c r="K31" s="44"/>
       <c r="L31" s="1"/>
-      <c r="M31" s="76" t="s">
+      <c r="M31" s="98" t="s">
         <v>23</v>
       </c>
-      <c r="N31" s="80"/>
-      <c r="O31" s="81"/>
-      <c r="P31" s="81"/>
-      <c r="Q31" s="81"/>
-      <c r="R31" s="81"/>
-      <c r="S31" s="81"/>
-      <c r="T31" s="81"/>
-      <c r="U31" s="82"/>
+      <c r="N31" s="107"/>
+      <c r="O31" s="108"/>
+      <c r="P31" s="108"/>
+      <c r="Q31" s="108"/>
+      <c r="R31" s="108"/>
+      <c r="S31" s="108"/>
+      <c r="T31" s="108"/>
+      <c r="U31" s="109"/>
       <c r="V31" s="1"/>
     </row>
     <row r="32" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="76" t="s">
+      <c r="A32" s="98" t="s">
         <v>7</v>
       </c>
-      <c r="B32" s="77"/>
+      <c r="B32" s="99"/>
       <c r="C32" s="40">
         <v>92.603769819293618</v>
       </c>
@@ -2720,13 +2815,13 @@
       <c r="J32" s="44"/>
       <c r="K32" s="44"/>
       <c r="L32" s="1" t="str">
-        <f t="shared" ref="L32:L35" si="11">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C32:I32)&amp;","</f>
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C32:I32)&amp;","</f>
         <v xml:space="preserve">    92.6037698192936, 91.4319470683528, 90.3907950429996, 86.7895628282223, 80.6155540330522, 56.6095785531339, 41.2792806229243,</v>
       </c>
-      <c r="M32" s="76" t="s">
+      <c r="M32" s="98" t="s">
         <v>7</v>
       </c>
-      <c r="N32" s="77"/>
+      <c r="N32" s="99"/>
       <c r="O32" s="40">
         <v>3.708759274801273</v>
       </c>
@@ -2749,15 +2844,15 @@
         <v>6.3187793027043018</v>
       </c>
       <c r="V32" s="1" t="str">
-        <f t="shared" ref="V32:V35" si="12">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,O32:U32)&amp;","</f>
+        <f t="shared" ref="V32:V35" si="5">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,O32:U32)&amp;","</f>
         <v xml:space="preserve">    3.70875927480127, 3.96403905412159, 3.70679981067569, 3.66745263253131, 5.75482270515002, 8.53665368775552, 6.3187793027043,</v>
       </c>
     </row>
     <row r="33" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="78" t="s">
+      <c r="A33" s="100" t="s">
         <v>8</v>
       </c>
-      <c r="B33" s="79"/>
+      <c r="B33" s="101"/>
       <c r="C33" s="43">
         <v>91.377634404932721</v>
       </c>
@@ -2782,13 +2877,13 @@
       <c r="J33" s="44"/>
       <c r="K33" s="44"/>
       <c r="L33" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C33:I33)&amp;","</f>
         <v xml:space="preserve">    91.3776344049327, 90.4053733332451, 89.3714803083327, 87.6098986263952, 85.5372307015107, 70.9307087454215, 44.0973262328065,</v>
       </c>
-      <c r="M33" s="76" t="s">
+      <c r="M33" s="98" t="s">
         <v>8</v>
       </c>
-      <c r="N33" s="77"/>
+      <c r="N33" s="99"/>
       <c r="O33" s="43">
         <v>3.5684194304484111</v>
       </c>
@@ -2811,15 +2906,15 @@
         <v>2.9223071611371929</v>
       </c>
       <c r="V33" s="1" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">    3.56841943044841, 3.03475814403413, 2.75413027652687, 2.77687820024663, 3.31846418941784, 4.97951990202499, 2.92230716113719,</v>
       </c>
     </row>
     <row r="34" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="76" t="s">
+      <c r="A34" s="98" t="s">
         <v>21</v>
       </c>
-      <c r="B34" s="77"/>
+      <c r="B34" s="99"/>
       <c r="C34" s="43">
         <v>92.603715202692385</v>
       </c>
@@ -2844,13 +2939,13 @@
       <c r="J34" s="44"/>
       <c r="K34" s="44"/>
       <c r="L34" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C34:I34)&amp;","</f>
         <v xml:space="preserve">    92.6037152026924, 91.4849975027203, 90.6301712993249, 85.3420346970645, 78.2086079443082, 58.1887672547126, 45.4689195625762,</v>
       </c>
-      <c r="M34" s="76" t="s">
+      <c r="M34" s="98" t="s">
         <v>21</v>
       </c>
-      <c r="N34" s="77"/>
+      <c r="N34" s="99"/>
       <c r="O34" s="43">
         <v>4.0727132923350373</v>
       </c>
@@ -2873,15 +2968,15 @@
         <v>10.707618741543239</v>
       </c>
       <c r="V34" s="1" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">    4.07271329233504, 4.42312859576295, 4.30115343035314, 4.84538945834654, 7.55897001359424, 10.3740336621021, 10.7076187415432,</v>
       </c>
     </row>
     <row r="35" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="76" t="s">
+      <c r="A35" s="98" t="s">
         <v>22</v>
       </c>
-      <c r="B35" s="77"/>
+      <c r="B35" s="99"/>
       <c r="C35" s="46">
         <v>92.692685851985146</v>
       </c>
@@ -2906,13 +3001,13 @@
       <c r="J35" s="44"/>
       <c r="K35" s="44"/>
       <c r="L35" s="1" t="str">
-        <f t="shared" si="11"/>
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C35:I35)&amp;","</f>
         <v xml:space="preserve">    92.6926858519851, 91.0280089290633, 89.1011768502887, 84.1216953111353, 75.5145363599464, 58.5518515483004, 43.5286444786034,</v>
       </c>
-      <c r="M35" s="76" t="s">
+      <c r="M35" s="98" t="s">
         <v>22</v>
       </c>
-      <c r="N35" s="77"/>
+      <c r="N35" s="99"/>
       <c r="O35" s="46">
         <v>4.3508377678439567</v>
       </c>
@@ -2935,7 +3030,7 @@
         <v>10.478269846537319</v>
       </c>
       <c r="V35" s="1" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">    4.35083776784396, 5.14551979845971, 5.03194492579449, 5.48810922346629, 8.39637249074013, 11.2647747680684, 10.4782698465373,</v>
       </c>
     </row>
@@ -3079,8 +3174,8 @@
     <mergeCell ref="M34:N34"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="C2:I4">
-    <cfRule type="colorScale" priority="43">
+  <conditionalFormatting sqref="C2:I4 C6:I7 C9:I12 C14:I17">
+    <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3090,7 +3185,9 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="44">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:I4">
+    <cfRule type="colorScale" priority="46">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3100,7 +3197,17 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="46">
+    <cfRule type="colorScale" priority="47">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="49">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3112,7 +3219,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C6:I6">
-    <cfRule type="colorScale" priority="1">
+    <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3122,7 +3229,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="2">
+    <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3134,7 +3241,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C7:I7">
-    <cfRule type="colorScale" priority="8">
+    <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3144,7 +3251,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="9">
+    <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3156,7 +3263,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C9:I11 C14:I16">
-    <cfRule type="colorScale" priority="22">
+    <cfRule type="colorScale" priority="25">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3168,6 +3275,60 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C9:I11">
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="27">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="28">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C9:I12 C14:I17">
+    <cfRule type="colorScale" priority="29">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C14:I16">
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="23">
       <colorScale>
         <cfvo type="min"/>
@@ -3188,63 +3349,9 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="25">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C9:I12 C14:I17">
-    <cfRule type="colorScale" priority="26">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C14:I16">
-    <cfRule type="colorScale" priority="19">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="20">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="21">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:K4 J5:K17">
-    <cfRule type="colorScale" priority="42">
+    <cfRule type="colorScale" priority="45">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3256,7 +3363,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J17">
-    <cfRule type="colorScale" priority="18">
+    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3268,7 +3375,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J31:J35">
-    <cfRule type="colorScale" priority="30">
+    <cfRule type="colorScale" priority="33">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3280,7 +3387,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:K17">
-    <cfRule type="colorScale" priority="265">
+    <cfRule type="colorScale" priority="268">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3292,36 +3399,6 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J5:K5 C3:K4">
-    <cfRule type="colorScale" priority="36">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="37">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="38">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
     <cfRule type="colorScale" priority="39">
       <colorScale>
         <cfvo type="min"/>
@@ -3352,9 +3429,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J31:K35">
-    <cfRule type="colorScale" priority="29">
+    <cfRule type="colorScale" priority="42">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3364,7 +3439,39 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="31">
+    <cfRule type="colorScale" priority="43">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="44">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J31:K35">
+    <cfRule type="colorScale" priority="32">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="34">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3376,7 +3483,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K17">
-    <cfRule type="colorScale" priority="17">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3388,7 +3495,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K31:K35">
-    <cfRule type="colorScale" priority="32">
+    <cfRule type="colorScale" priority="35">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3482,10 +3589,10 @@
       <c r="V1" s="12"/>
     </row>
     <row r="2" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="84" t="s">
+      <c r="A2" s="111" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="85"/>
+      <c r="B2" s="112"/>
       <c r="C2" s="20">
         <v>93.101364775358491</v>
       </c>
@@ -3519,10 +3626,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C2:I2)&amp;","</f>
         <v xml:space="preserve">    93.1013647753585, 91.3266637254648, 89.7225610371485, 83.857204647099, 76.2429490451186, 60.4027774173364, 47.7409002961387,</v>
       </c>
-      <c r="M2" s="84" t="s">
+      <c r="M2" s="111" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="85"/>
+      <c r="N2" s="112"/>
       <c r="O2" s="31">
         <v>3.4649270444699574</v>
       </c>
@@ -3550,10 +3657,10 @@
       </c>
     </row>
     <row r="3" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="84" t="s">
+      <c r="A3" s="111" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="85"/>
+      <c r="B3" s="112"/>
       <c r="C3" s="31">
         <v>93.273358766079312</v>
       </c>
@@ -3587,10 +3694,10 @@
         <f t="shared" ref="L3:L18" si="0">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C3:I3)&amp;","</f>
         <v xml:space="preserve">    93.2733587660793, 91.6155877934354, 90.6205330495939, 86.5975138193237, 78.2243502683126, 60.8549929786013, 48.7439337710534,</v>
       </c>
-      <c r="M3" s="84" t="s">
+      <c r="M3" s="111" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="85"/>
+      <c r="N3" s="112"/>
       <c r="O3" s="31">
         <v>3.4672469457762647</v>
       </c>
@@ -3618,10 +3725,10 @@
       </c>
     </row>
     <row r="4" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="84" t="s">
+      <c r="A4" s="111" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="85"/>
+      <c r="B4" s="112"/>
       <c r="C4" s="24">
         <v>87.593900000000005</v>
       </c>
@@ -3655,10 +3762,10 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    87.5939, 87.6637168141593, 88.1120943952802, 87.9700256922638, 87.4617081462642, 75.2513631894163, 47.7206838582802,</v>
       </c>
-      <c r="M4" s="84" t="s">
+      <c r="M4" s="111" t="s">
         <v>10</v>
       </c>
-      <c r="N4" s="85"/>
+      <c r="N4" s="112"/>
       <c r="O4" s="49">
         <v>2.4529187882918819</v>
       </c>
@@ -3686,35 +3793,35 @@
       </c>
     </row>
     <row r="5" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="84" t="s">
+      <c r="A5" s="111" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="86"/>
-      <c r="C5" s="86"/>
-      <c r="D5" s="86"/>
-      <c r="E5" s="86"/>
-      <c r="F5" s="86"/>
-      <c r="G5" s="86"/>
-      <c r="H5" s="86"/>
-      <c r="I5" s="85"/>
+      <c r="B5" s="113"/>
+      <c r="C5" s="113"/>
+      <c r="D5" s="113"/>
+      <c r="E5" s="113"/>
+      <c r="F5" s="113"/>
+      <c r="G5" s="113"/>
+      <c r="H5" s="113"/>
+      <c r="I5" s="112"/>
       <c r="J5" s="35"/>
       <c r="K5" s="35"/>
       <c r="L5" s="12"/>
-      <c r="M5" s="84" t="s">
+      <c r="M5" s="111" t="s">
         <v>12</v>
       </c>
-      <c r="N5" s="86"/>
-      <c r="O5" s="86"/>
-      <c r="P5" s="86"/>
-      <c r="Q5" s="86"/>
-      <c r="R5" s="86"/>
-      <c r="S5" s="86"/>
-      <c r="T5" s="86"/>
-      <c r="U5" s="85"/>
+      <c r="N5" s="113"/>
+      <c r="O5" s="113"/>
+      <c r="P5" s="113"/>
+      <c r="Q5" s="113"/>
+      <c r="R5" s="113"/>
+      <c r="S5" s="113"/>
+      <c r="T5" s="113"/>
+      <c r="U5" s="112"/>
       <c r="V5" s="12"/>
     </row>
     <row r="6" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="89" t="s">
+      <c r="A6" s="102" t="s">
         <v>11</v>
       </c>
       <c r="B6" s="8" t="s">
@@ -3753,7 +3860,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    93.4021632251721, 91.8271265322364, 90.5586899540653, 86.0233767881498, 80.0763011214053, 61.7128781390843, 46.4235100072953,</v>
       </c>
-      <c r="M6" s="89" t="s">
+      <c r="M6" s="102" t="s">
         <v>11</v>
       </c>
       <c r="N6" s="8" t="s">
@@ -3786,7 +3893,7 @@
       </c>
     </row>
     <row r="7" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="92"/>
+      <c r="A7" s="103"/>
       <c r="B7" s="8" t="s">
         <v>14</v>
       </c>
@@ -3823,7 +3930,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    92.6912487708948, 92.7069813176008, 91.7345132743363, 88.8675536408908, 87.5647050003316, 75.6237856728864, 48.8313393714478,</v>
       </c>
-      <c r="M7" s="92"/>
+      <c r="M7" s="103"/>
       <c r="N7" s="8" t="s">
         <v>14</v>
       </c>
@@ -3854,7 +3961,7 @@
       </c>
     </row>
     <row r="8" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="92"/>
+      <c r="A8" s="103"/>
       <c r="B8" s="8" t="s">
         <v>17</v>
       </c>
@@ -3891,7 +3998,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    93.3599108412126, 93.0049510232211, 91.6796281398051, 85.4087492106333, 76.226619607436, 61.2490650149799, 49.6316519462395,</v>
       </c>
-      <c r="M8" s="92"/>
+      <c r="M8" s="103"/>
       <c r="N8" s="8" t="s">
         <v>17</v>
       </c>
@@ -3919,7 +4026,7 @@
       <c r="V8" s="12"/>
     </row>
     <row r="9" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="92"/>
+      <c r="A9" s="103"/>
       <c r="B9" s="8" t="s">
         <v>18</v>
       </c>
@@ -3956,7 +4063,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    93.4021689922347, 93.2487766618512, 92.6912718391451, 88.4524750790808, 80.8362500252309, 58.5874935480987, 46.7616127013786,</v>
       </c>
-      <c r="M9" s="92"/>
+      <c r="M9" s="103"/>
       <c r="N9" s="8" t="s">
         <v>18</v>
       </c>
@@ -3984,7 +4091,7 @@
       <c r="V9" s="12"/>
     </row>
     <row r="10" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="92"/>
+      <c r="A10" s="103"/>
       <c r="B10" s="8" t="s">
         <v>15</v>
       </c>
@@ -4021,7 +4128,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    93.3470993117011, 92.4297413184082, 91.1779802016742, 88.6094429882612, 83.8878825364695, 65.4650299743077, 53.0259200627456,</v>
       </c>
-      <c r="M10" s="92"/>
+      <c r="M10" s="103"/>
       <c r="N10" s="8" t="s">
         <v>15</v>
       </c>
@@ -4049,7 +4156,7 @@
       <c r="V10" s="12"/>
     </row>
     <row r="11" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="92"/>
+      <c r="A11" s="103"/>
       <c r="B11" s="8" t="s">
         <v>25</v>
       </c>
@@ -4086,7 +4193,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    90.9754236628344, 90.2025565388397, 90.1701081612586, 88.7090805283783, 86.9509395986701, 75.7928298110999, 48.1505376344086,</v>
       </c>
-      <c r="M11" s="92"/>
+      <c r="M11" s="103"/>
       <c r="N11" s="8" t="s">
         <v>25</v>
       </c>
@@ -4114,7 +4221,7 @@
       <c r="V11" s="12"/>
     </row>
     <row r="12" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="92"/>
+      <c r="A12" s="103"/>
       <c r="B12" s="8" t="s">
         <v>19</v>
       </c>
@@ -4151,7 +4258,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    90.2959685349066, 90.4051130776795, 90.5292433325548, 90.4642081678907, 89.370346340943, 80.4958116708045, 54.2005092316254,</v>
       </c>
-      <c r="M12" s="92"/>
+      <c r="M12" s="103"/>
       <c r="N12" s="8" t="s">
         <v>19</v>
       </c>
@@ -4179,7 +4286,7 @@
       <c r="V12" s="12"/>
     </row>
     <row r="13" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="92"/>
+      <c r="A13" s="103"/>
       <c r="B13" s="8" t="s">
         <v>16</v>
       </c>
@@ -4216,7 +4323,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    87.7571288102262, 87.2143617159318, 87.4218577438674, 87.622418879056, 86.8073858770404, 75.9010458567981, 48.2504289252791,</v>
       </c>
-      <c r="M13" s="92"/>
+      <c r="M13" s="103"/>
       <c r="N13" s="8" t="s">
         <v>16</v>
       </c>
@@ -4244,7 +4351,7 @@
       <c r="V13" s="12"/>
     </row>
     <row r="14" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="93"/>
+      <c r="A14" s="104"/>
       <c r="B14" s="8" t="s">
         <v>26</v>
       </c>
@@ -4281,7 +4388,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    87.3893805309734, 87.1366764995084, 87.1691248770895, 87.6175024582105, 86.5250737463127, 73.9160315689006, 47.1319446246652,</v>
       </c>
-      <c r="M14" s="93"/>
+      <c r="M14" s="104"/>
       <c r="N14" s="8" t="s">
         <v>26</v>
       </c>
@@ -4309,38 +4416,38 @@
       <c r="V14" s="12"/>
     </row>
     <row r="15" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="84" t="s">
+      <c r="A15" s="111" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="86"/>
-      <c r="C15" s="87"/>
-      <c r="D15" s="87"/>
-      <c r="E15" s="87"/>
-      <c r="F15" s="87"/>
-      <c r="G15" s="87"/>
-      <c r="H15" s="87"/>
-      <c r="I15" s="88"/>
+      <c r="B15" s="113"/>
+      <c r="C15" s="114"/>
+      <c r="D15" s="114"/>
+      <c r="E15" s="114"/>
+      <c r="F15" s="114"/>
+      <c r="G15" s="114"/>
+      <c r="H15" s="114"/>
+      <c r="I15" s="115"/>
       <c r="J15" s="35"/>
       <c r="K15" s="35"/>
       <c r="L15" s="12"/>
-      <c r="M15" s="84" t="s">
+      <c r="M15" s="111" t="s">
         <v>20</v>
       </c>
-      <c r="N15" s="86"/>
-      <c r="O15" s="91"/>
-      <c r="P15" s="91"/>
-      <c r="Q15" s="91"/>
-      <c r="R15" s="91"/>
-      <c r="S15" s="91"/>
-      <c r="T15" s="91"/>
-      <c r="U15" s="90"/>
+      <c r="N15" s="113"/>
+      <c r="O15" s="116"/>
+      <c r="P15" s="116"/>
+      <c r="Q15" s="116"/>
+      <c r="R15" s="116"/>
+      <c r="S15" s="116"/>
+      <c r="T15" s="116"/>
+      <c r="U15" s="110"/>
       <c r="V15" s="12"/>
     </row>
     <row r="16" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="84" t="s">
+      <c r="A16" s="111" t="s">
         <v>7</v>
       </c>
-      <c r="B16" s="85"/>
+      <c r="B16" s="112"/>
       <c r="C16" s="52">
         <v>93.782740335124032</v>
       </c>
@@ -4374,10 +4481,10 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    93.782740335124, 91.9482088945406, 90.212980504445, 84.6303889595354, 75.3710931755465, 59.6272113080563, 47.8441855033348,</v>
       </c>
-      <c r="M16" s="84" t="s">
+      <c r="M16" s="111" t="s">
         <v>7</v>
       </c>
-      <c r="N16" s="85"/>
+      <c r="N16" s="112"/>
       <c r="O16" s="52">
         <v>3.5391983918820551</v>
       </c>
@@ -4405,10 +4512,10 @@
       </c>
     </row>
     <row r="17" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="89" t="s">
+      <c r="A17" s="102" t="s">
         <v>8</v>
       </c>
-      <c r="B17" s="90"/>
+      <c r="B17" s="110"/>
       <c r="C17" s="55">
         <v>93.226230330712227</v>
       </c>
@@ -4442,10 +4549,10 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    93.2262303307122, 91.8332915221297, 90.3252911645718, 85.3834923600839, 76.5670002912366, 59.4145422249904, 50.5634074112521,</v>
       </c>
-      <c r="M17" s="84" t="s">
+      <c r="M17" s="111" t="s">
         <v>8</v>
       </c>
-      <c r="N17" s="85"/>
+      <c r="N17" s="112"/>
       <c r="O17" s="55">
         <v>3.945711842949601</v>
       </c>
@@ -4473,10 +4580,10 @@
       </c>
     </row>
     <row r="18" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="84" t="s">
+      <c r="A18" s="111" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="85"/>
+      <c r="B18" s="112"/>
       <c r="C18" s="55">
         <v>93.004922187908207</v>
       </c>
@@ -4510,10 +4617,10 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    93.0049221879082, 91.5185021785079, 89.7294209580821, 83.3486073985646, 74.0877199053048, 57.9173320415113, 48.0077941850708,</v>
       </c>
-      <c r="M18" s="84" t="s">
+      <c r="M18" s="111" t="s">
         <v>21</v>
       </c>
-      <c r="N18" s="85"/>
+      <c r="N18" s="112"/>
       <c r="O18" s="55">
         <v>3.690401528555848</v>
       </c>
@@ -4541,100 +4648,72 @@
       </c>
     </row>
     <row r="19" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="84" t="s">
+      <c r="A19" s="111" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="85"/>
-      <c r="C19" s="57">
-        <v>93.123279613145442</v>
-      </c>
-      <c r="D19" s="58">
-        <v>91.674385879923975</v>
-      </c>
-      <c r="E19" s="58">
-        <v>89.698688281617194</v>
-      </c>
-      <c r="F19" s="58">
-        <v>84.957067102656595</v>
-      </c>
-      <c r="G19" s="58">
-        <v>75.939082518014857</v>
-      </c>
-      <c r="H19" s="58">
-        <v>59.995092229748238</v>
-      </c>
-      <c r="I19" s="59">
-        <v>48.440303693515233</v>
-      </c>
+      <c r="B19" s="112"/>
+      <c r="C19" s="57"/>
+      <c r="D19" s="58"/>
+      <c r="E19" s="58"/>
+      <c r="F19" s="58"/>
+      <c r="G19" s="58"/>
+      <c r="H19" s="58"/>
+      <c r="I19" s="59"/>
       <c r="J19" s="35" cm="1">
         <f t="array" ref="J19">-SUMPRODUCT((D1:H1-C1:G1)*(C19:G19+D19:H19)/2)</f>
-        <v>78.078434213675436</v>
+        <v>0</v>
       </c>
       <c r="K19" s="35" cm="1">
         <f t="array" ref="K19">-SUMPRODUCT((D1:I1-C1:H1)*(C19:H19+D19:I19)/2)</f>
-        <v>80.789319111757024</v>
+        <v>0</v>
       </c>
       <c r="L19" s="12"/>
-      <c r="M19" s="84" t="s">
+      <c r="M19" s="111" t="s">
         <v>22</v>
       </c>
-      <c r="N19" s="85"/>
-      <c r="O19" s="57">
-        <v>3.8088682011350912</v>
-      </c>
-      <c r="P19" s="58">
-        <v>4.4783864386850611</v>
-      </c>
-      <c r="Q19" s="58">
-        <v>5.0849840192173117</v>
-      </c>
-      <c r="R19" s="58">
-        <v>5.0366327026230584</v>
-      </c>
-      <c r="S19" s="58">
-        <v>7.6643798786674449</v>
-      </c>
-      <c r="T19" s="58">
-        <v>10.05146904627655</v>
-      </c>
-      <c r="U19" s="59">
-        <v>9.821397671709315</v>
-      </c>
+      <c r="N19" s="112"/>
+      <c r="O19" s="57"/>
+      <c r="P19" s="58"/>
+      <c r="Q19" s="58"/>
+      <c r="R19" s="58"/>
+      <c r="S19" s="58"/>
+      <c r="T19" s="58"/>
+      <c r="U19" s="59"/>
       <c r="V19" s="12"/>
     </row>
     <row r="20" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="84" t="s">
+      <c r="A20" s="111" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="86"/>
-      <c r="C20" s="87"/>
-      <c r="D20" s="87"/>
-      <c r="E20" s="87"/>
-      <c r="F20" s="87"/>
-      <c r="G20" s="87"/>
-      <c r="H20" s="87"/>
-      <c r="I20" s="88"/>
+      <c r="B20" s="113"/>
+      <c r="C20" s="114"/>
+      <c r="D20" s="114"/>
+      <c r="E20" s="114"/>
+      <c r="F20" s="114"/>
+      <c r="G20" s="114"/>
+      <c r="H20" s="114"/>
+      <c r="I20" s="115"/>
       <c r="J20" s="35"/>
       <c r="K20" s="35"/>
       <c r="L20" s="12"/>
-      <c r="M20" s="84" t="s">
+      <c r="M20" s="111" t="s">
         <v>23</v>
       </c>
-      <c r="N20" s="86"/>
-      <c r="O20" s="87"/>
-      <c r="P20" s="87"/>
-      <c r="Q20" s="87"/>
-      <c r="R20" s="87"/>
-      <c r="S20" s="87"/>
-      <c r="T20" s="87"/>
-      <c r="U20" s="88"/>
+      <c r="N20" s="113"/>
+      <c r="O20" s="114"/>
+      <c r="P20" s="114"/>
+      <c r="Q20" s="114"/>
+      <c r="R20" s="114"/>
+      <c r="S20" s="114"/>
+      <c r="T20" s="114"/>
+      <c r="U20" s="115"/>
       <c r="V20" s="12"/>
     </row>
     <row r="21" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="84" t="s">
+      <c r="A21" s="111" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="85"/>
+      <c r="B21" s="112"/>
       <c r="C21" s="52">
         <v>92.969518190757128</v>
       </c>
@@ -4668,10 +4747,10 @@
         <f t="shared" ref="L21:L23" si="2">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C21:I21)&amp;","</f>
         <v xml:space="preserve">    92.9695181907571, 91.8515240904621, 90.756145526057, 87.2531365611583, 81.1789721364371, 57.3869295293788, 44.8554428094822,</v>
       </c>
-      <c r="M21" s="84" t="s">
+      <c r="M21" s="111" t="s">
         <v>7</v>
       </c>
-      <c r="N21" s="85"/>
+      <c r="N21" s="112"/>
       <c r="O21" s="52">
         <v>3.3991921823554931</v>
       </c>
@@ -4699,10 +4778,10 @@
       </c>
     </row>
     <row r="22" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="89" t="s">
+      <c r="A22" s="102" t="s">
         <v>8</v>
       </c>
-      <c r="B22" s="90"/>
+      <c r="B22" s="110"/>
       <c r="C22" s="55">
         <v>91.898721730580135</v>
       </c>
@@ -4736,10 +4815,10 @@
         <f t="shared" si="2"/>
         <v xml:space="preserve">    91.8987217305801, 90.765995668936, 89.7052685000158, 87.9596853490659, 85.7500007208828, 71.3873880108536, 45.5963431056209,</v>
       </c>
-      <c r="M22" s="84" t="s">
+      <c r="M22" s="111" t="s">
         <v>8</v>
       </c>
-      <c r="N22" s="85"/>
+      <c r="N22" s="112"/>
       <c r="O22" s="55">
         <v>3.190312271555559</v>
       </c>
@@ -4767,10 +4846,10 @@
       </c>
     </row>
     <row r="23" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="84" t="s">
+      <c r="A23" s="111" t="s">
         <v>21</v>
       </c>
-      <c r="B23" s="85"/>
+      <c r="B23" s="112"/>
       <c r="C23" s="55">
         <v>93.044276622923505</v>
       </c>
@@ -4804,10 +4883,10 @@
         <f t="shared" si="2"/>
         <v xml:space="preserve">    93.0442766229235, 91.9351551484009, 90.9488922914558, 85.9525053561594, 78.9151838107019, 59.4421001335075, 49.5338281473023,</v>
       </c>
-      <c r="M23" s="84" t="s">
+      <c r="M23" s="111" t="s">
         <v>21</v>
       </c>
-      <c r="N23" s="85"/>
+      <c r="N23" s="112"/>
       <c r="O23" s="55">
         <v>3.72078192123604</v>
       </c>
@@ -4835,227 +4914,283 @@
       </c>
     </row>
     <row r="24" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="84" t="s">
+      <c r="A24" s="111" t="s">
         <v>22</v>
       </c>
-      <c r="B24" s="85"/>
-      <c r="C24" s="57">
-        <v>93.174110502686005</v>
-      </c>
-      <c r="D24" s="58">
-        <v>91.391724841910417</v>
-      </c>
-      <c r="E24" s="58">
-        <v>89.591539142495463</v>
-      </c>
-      <c r="F24" s="58">
-        <v>84.690597092823751</v>
-      </c>
-      <c r="G24" s="58">
-        <v>76.401347185817656</v>
-      </c>
-      <c r="H24" s="58">
-        <v>59.963667505774268</v>
-      </c>
-      <c r="I24" s="59">
-        <v>47.725577210875521</v>
-      </c>
+      <c r="B24" s="112"/>
+      <c r="C24" s="57"/>
+      <c r="D24" s="58"/>
+      <c r="E24" s="58"/>
+      <c r="F24" s="58"/>
+      <c r="G24" s="58"/>
+      <c r="H24" s="58"/>
+      <c r="I24" s="59"/>
       <c r="J24" s="35" cm="1">
         <f t="array" ref="J24">-SUMPRODUCT((D1:H1-C1:G1)*(C24:G24+D24:H24)/2)</f>
-        <v>77.994698988168864</v>
+        <v>0</v>
       </c>
       <c r="K24" s="35" cm="1">
         <f t="array" ref="K24">-SUMPRODUCT((D1:I1-C1:H1)*(C24:H24+D24:I24)/2)</f>
-        <v>80.686930106085114</v>
+        <v>0</v>
       </c>
       <c r="L24" s="12"/>
-      <c r="M24" s="84" t="s">
+      <c r="M24" s="111" t="s">
         <v>22</v>
       </c>
-      <c r="N24" s="85"/>
-      <c r="O24" s="57">
-        <v>3.8766021792735019</v>
-      </c>
-      <c r="P24" s="58">
-        <v>4.8126411406228078</v>
-      </c>
-      <c r="Q24" s="58">
-        <v>4.6512210016047986</v>
-      </c>
-      <c r="R24" s="58">
-        <v>5.2416066355763284</v>
-      </c>
-      <c r="S24" s="58">
-        <v>8.0769588602235256</v>
-      </c>
-      <c r="T24" s="58">
-        <v>10.657363307561541</v>
-      </c>
-      <c r="U24" s="59">
-        <v>9.200486032966916</v>
-      </c>
+      <c r="N24" s="112"/>
+      <c r="O24" s="57"/>
+      <c r="P24" s="58"/>
+      <c r="Q24" s="58"/>
+      <c r="R24" s="58"/>
+      <c r="S24" s="58"/>
+      <c r="T24" s="58"/>
+      <c r="U24" s="59"/>
       <c r="V24" s="12"/>
     </row>
     <row r="25" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="84" t="s">
+      <c r="A25" s="111" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="86"/>
-      <c r="C25" s="87"/>
-      <c r="D25" s="87"/>
-      <c r="E25" s="87"/>
-      <c r="F25" s="87"/>
-      <c r="G25" s="87"/>
-      <c r="H25" s="87"/>
-      <c r="I25" s="88"/>
+      <c r="B25" s="113"/>
+      <c r="C25" s="114"/>
+      <c r="D25" s="114"/>
+      <c r="E25" s="114"/>
+      <c r="F25" s="114"/>
+      <c r="G25" s="114"/>
+      <c r="H25" s="114"/>
+      <c r="I25" s="115"/>
       <c r="J25" s="35"/>
       <c r="K25" s="35"/>
       <c r="L25" s="12"/>
-      <c r="M25" s="84" t="s">
+      <c r="M25" s="111" t="s">
         <v>23</v>
       </c>
-      <c r="N25" s="86"/>
-      <c r="O25" s="87"/>
-      <c r="P25" s="87"/>
-      <c r="Q25" s="87"/>
-      <c r="R25" s="87"/>
-      <c r="S25" s="87"/>
-      <c r="T25" s="87"/>
-      <c r="U25" s="88"/>
+      <c r="N25" s="113"/>
+      <c r="O25" s="114"/>
+      <c r="P25" s="114"/>
+      <c r="Q25" s="114"/>
+      <c r="R25" s="114"/>
+      <c r="S25" s="114"/>
+      <c r="T25" s="114"/>
+      <c r="U25" s="115"/>
       <c r="V25" s="12"/>
     </row>
     <row r="26" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="84" t="s">
+      <c r="A26" s="111" t="s">
         <v>7</v>
       </c>
-      <c r="B26" s="85"/>
-      <c r="C26" s="52"/>
-      <c r="D26" s="53"/>
-      <c r="E26" s="53"/>
-      <c r="F26" s="53"/>
-      <c r="G26" s="53"/>
-      <c r="H26" s="53"/>
-      <c r="I26" s="54"/>
+      <c r="B26" s="112"/>
+      <c r="C26">
+        <v>92.697160010034693</v>
+      </c>
+      <c r="D26">
+        <v>91.153392330383497</v>
+      </c>
+      <c r="E26">
+        <v>90.795499961072366</v>
+      </c>
+      <c r="F26">
+        <v>88.088668587098482</v>
+      </c>
+      <c r="G26">
+        <v>82.942908964033734</v>
+      </c>
+      <c r="H26">
+        <v>60.844658402466003</v>
+      </c>
+      <c r="I26">
+        <v>46.037096630016983</v>
+      </c>
       <c r="J26" s="35" cm="1">
         <f t="array" ref="J26">-SUMPRODUCT((D1:H1-C1:G1)*(C26:G26+D26:H26)/2)</f>
-        <v>0</v>
+        <v>79.35430467968294</v>
       </c>
       <c r="K26" s="35" cm="1">
         <f t="array" ref="K26">-SUMPRODUCT((D1:I1-C1:H1)*(C26:H26+D26:I26)/2)</f>
-        <v>0</v>
+        <v>82.026348555495019</v>
       </c>
       <c r="L26" s="12" t="str">
         <f t="shared" ref="L26:L28" si="4">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C26:I26)&amp;","</f>
-        <v xml:space="preserve">    ,</v>
-      </c>
-      <c r="M26" s="84" t="s">
+        <v xml:space="preserve">    92.6971600100347, 91.1533923303835, 90.7954999610724, 88.0886685870985, 82.9429089640337, 60.844658402466, 46.037096630017,</v>
+      </c>
+      <c r="M26" s="111" t="s">
         <v>7</v>
       </c>
-      <c r="N26" s="85"/>
-      <c r="O26" s="52"/>
-      <c r="P26" s="53"/>
-      <c r="Q26" s="53"/>
-      <c r="R26" s="53"/>
-      <c r="S26" s="53"/>
-      <c r="T26" s="53"/>
-      <c r="U26" s="54"/>
+      <c r="N26" s="112"/>
+      <c r="O26">
+        <v>3.4672971241319281</v>
+      </c>
+      <c r="P26">
+        <v>3.40096673306943</v>
+      </c>
+      <c r="Q26">
+        <v>3.3416051630714589</v>
+      </c>
+      <c r="R26">
+        <v>3.2995786305620469</v>
+      </c>
+      <c r="S26">
+        <v>4.8784748995715699</v>
+      </c>
+      <c r="T26">
+        <v>8.9421591871466681</v>
+      </c>
+      <c r="U26">
+        <v>6.1984010323546244</v>
+      </c>
       <c r="V26" s="12" t="str">
         <f t="shared" ref="V26:V28" si="5">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,O26:U26)&amp;","</f>
-        <v xml:space="preserve">    ,</v>
+        <v xml:space="preserve">    3.46729712413193, 3.40096673306943, 3.34160516307146, 3.29957863056205, 4.87847489957157, 8.94215918714667, 6.19840103235462,</v>
       </c>
     </row>
     <row r="27" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="89" t="s">
+      <c r="A27" s="102" t="s">
         <v>8</v>
       </c>
-      <c r="B27" s="90"/>
-      <c r="C27" s="55"/>
-      <c r="D27" s="12"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="12"/>
-      <c r="H27" s="12"/>
-      <c r="I27" s="56"/>
+      <c r="B27" s="110"/>
+      <c r="C27">
+        <v>89.330608396266385</v>
+      </c>
+      <c r="D27">
+        <v>87.685349065880033</v>
+      </c>
+      <c r="E27">
+        <v>87.756341606184606</v>
+      </c>
+      <c r="F27">
+        <v>87.372670467160916</v>
+      </c>
+      <c r="G27">
+        <v>85.138095196901915</v>
+      </c>
+      <c r="H27">
+        <v>69.818302926495917</v>
+      </c>
+      <c r="I27">
+        <v>45.745505295605213</v>
+      </c>
       <c r="J27" s="35" cm="1">
         <f t="array" ref="J27">-SUMPRODUCT((D1:H1-C1:G1)*(C27:G27+D27:H27)/2)</f>
-        <v>0</v>
+        <v>77.943465413483963</v>
       </c>
       <c r="K27" s="35" cm="1">
         <f t="array" ref="K27">-SUMPRODUCT((D1:I1-C1:H1)*(C27:H27+D27:I27)/2)</f>
-        <v>0</v>
+        <v>80.832560619036485</v>
       </c>
       <c r="L27" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">    ,</v>
-      </c>
-      <c r="M27" s="84" t="s">
+        <v xml:space="preserve">    89.3306083962664, 87.68534906588, 87.7563416061846, 87.3726704671609, 85.1380951969019, 69.8183029264959, 45.7455052956052,</v>
+      </c>
+      <c r="M27" s="111" t="s">
         <v>8</v>
       </c>
-      <c r="N27" s="85"/>
-      <c r="O27" s="55"/>
-      <c r="P27" s="12"/>
-      <c r="Q27" s="12"/>
-      <c r="R27" s="12"/>
-      <c r="S27" s="12"/>
-      <c r="T27" s="12"/>
-      <c r="U27" s="56"/>
+      <c r="N27" s="112"/>
+      <c r="O27">
+        <v>2.4752750787703639</v>
+      </c>
+      <c r="P27">
+        <v>2.2350946776914431</v>
+      </c>
+      <c r="Q27">
+        <v>2.3634860595969851</v>
+      </c>
+      <c r="R27">
+        <v>2.1818023005855189</v>
+      </c>
+      <c r="S27">
+        <v>2.7371586952142821</v>
+      </c>
+      <c r="T27">
+        <v>3.7643473124505271</v>
+      </c>
+      <c r="U27">
+        <v>2.8630655295390701</v>
+      </c>
       <c r="V27" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">    ,</v>
+        <v xml:space="preserve">    2.47527507877036, 2.23509467769144, 2.36348605959699, 2.18180230058552, 2.73715869521428, 3.76434731245053, 2.86306552953907,</v>
       </c>
     </row>
     <row r="28" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="84" t="s">
+      <c r="A28" s="111" t="s">
         <v>21</v>
       </c>
-      <c r="B28" s="85"/>
-      <c r="C28" s="55"/>
-      <c r="D28" s="12"/>
-      <c r="E28" s="12"/>
-      <c r="F28" s="12"/>
-      <c r="G28" s="12"/>
-      <c r="H28" s="12"/>
-      <c r="I28" s="56"/>
+      <c r="B28" s="112"/>
+      <c r="C28">
+        <v>93.512291052114051</v>
+      </c>
+      <c r="D28">
+        <v>91.988206357033064</v>
+      </c>
+      <c r="E28">
+        <v>90.337341441823312</v>
+      </c>
+      <c r="F28">
+        <v>85.275345519136536</v>
+      </c>
+      <c r="G28">
+        <v>76.743235956481755</v>
+      </c>
+      <c r="H28">
+        <v>58.225117287635129</v>
+      </c>
+      <c r="I28">
+        <v>48.536192642958277</v>
+      </c>
       <c r="J28" s="35" cm="1">
         <f t="array" ref="J28">-SUMPRODUCT((D1:H1-C1:G1)*(C28:G28+D28:H28)/2)</f>
-        <v>0</v>
+        <v>78.388871083083174</v>
       </c>
       <c r="K28" s="35" cm="1">
         <f t="array" ref="K28">-SUMPRODUCT((D1:I1-C1:H1)*(C28:H28+D28:I28)/2)</f>
-        <v>0</v>
+        <v>81.057903831348014</v>
       </c>
       <c r="L28" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">    ,</v>
-      </c>
-      <c r="M28" s="84" t="s">
+        <v xml:space="preserve">    93.5122910521141, 91.9882063570331, 90.3373414418233, 85.2753455191365, 76.7432359564818, 58.2251172876351, 48.5361926429583,</v>
+      </c>
+      <c r="M28" s="111" t="s">
         <v>21</v>
       </c>
-      <c r="N28" s="85"/>
-      <c r="O28" s="55"/>
-      <c r="P28" s="12"/>
-      <c r="Q28" s="12"/>
-      <c r="R28" s="12"/>
-      <c r="S28" s="12"/>
-      <c r="T28" s="12"/>
-      <c r="U28" s="56"/>
+      <c r="N28" s="112"/>
+      <c r="O28">
+        <v>3.4388156450568661</v>
+      </c>
+      <c r="P28">
+        <v>3.8166315583343611</v>
+      </c>
+      <c r="Q28">
+        <v>4.5998469529406458</v>
+      </c>
+      <c r="R28">
+        <v>5.1269711147756771</v>
+      </c>
+      <c r="S28">
+        <v>7.9209324172352309</v>
+      </c>
+      <c r="T28">
+        <v>10.577150969508549</v>
+      </c>
+      <c r="U28">
+        <v>8.32548554358935</v>
+      </c>
       <c r="V28" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">    ,</v>
+        <v xml:space="preserve">    3.43881564505687, 3.81663155833436, 4.59984695294065, 5.12697111477568, 7.92093241723523, 10.5771509695085, 8.32548554358935,</v>
       </c>
     </row>
     <row r="29" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="84" t="s">
+      <c r="A29" s="111" t="s">
         <v>22</v>
       </c>
-      <c r="B29" s="85"/>
-      <c r="C29" s="57"/>
-      <c r="D29" s="58"/>
-      <c r="E29" s="58"/>
-      <c r="F29" s="58"/>
-      <c r="G29" s="58"/>
-      <c r="H29" s="58"/>
-      <c r="I29" s="59"/>
+      <c r="B29" s="112"/>
+      <c r="C29" s="126"/>
+      <c r="D29" s="126"/>
+      <c r="E29" s="126"/>
+      <c r="F29" s="126"/>
+      <c r="G29" s="126"/>
+      <c r="H29" s="126"/>
+      <c r="I29" s="126"/>
       <c r="J29" s="35" cm="1">
         <f t="array" ref="J29">-SUMPRODUCT((D1:H1-C1:G1)*(C29:G29+D29:H29)/2)</f>
         <v>0</v>
@@ -5065,17 +5200,17 @@
         <v>0</v>
       </c>
       <c r="L29" s="12"/>
-      <c r="M29" s="84" t="s">
+      <c r="M29" s="111" t="s">
         <v>22</v>
       </c>
-      <c r="N29" s="85"/>
-      <c r="O29" s="57"/>
-      <c r="P29" s="58"/>
-      <c r="Q29" s="58"/>
-      <c r="R29" s="58"/>
-      <c r="S29" s="58"/>
-      <c r="T29" s="58"/>
-      <c r="U29" s="59"/>
+      <c r="N29" s="112"/>
+      <c r="O29" s="95"/>
+      <c r="P29" s="96"/>
+      <c r="Q29" s="96"/>
+      <c r="R29" s="96"/>
+      <c r="S29" s="96"/>
+      <c r="T29" s="96"/>
+      <c r="U29" s="97"/>
       <c r="V29" s="12"/>
     </row>
     <row r="30" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.25">
@@ -5161,10 +5296,10 @@
       <c r="V31" s="1"/>
     </row>
     <row r="32" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="76" t="s">
+      <c r="A32" s="98" t="s">
         <v>5</v>
       </c>
-      <c r="B32" s="77"/>
+      <c r="B32" s="99"/>
       <c r="C32" s="41">
         <v>92.567111769713335</v>
       </c>
@@ -5192,10 +5327,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C32:I32)&amp;","</f>
         <v xml:space="preserve">    92.5671117697133, 90.8358586083436, 89.2175053395332, 83.2372459642881, 75.380430844191, 58.9943671875974, 43.6225356413822,</v>
       </c>
-      <c r="M32" s="76" t="s">
+      <c r="M32" s="98" t="s">
         <v>5</v>
       </c>
-      <c r="N32" s="77"/>
+      <c r="N32" s="99"/>
       <c r="O32" s="40">
         <v>3.88093621561358</v>
       </c>
@@ -5223,10 +5358,10 @@
       </c>
     </row>
     <row r="33" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="76" t="s">
+      <c r="A33" s="98" t="s">
         <v>6</v>
       </c>
-      <c r="B33" s="77"/>
+      <c r="B33" s="99"/>
       <c r="C33" s="41">
         <v>92.866950218042462</v>
       </c>
@@ -5254,10 +5389,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C33:I33)&amp;","</f>
         <v xml:space="preserve">    92.8669502180425, 91.2426907647456, 90.1370532276984, 86.0801529266134, 77.4102172551968, 59.6761947649801, 46.3954904194042,</v>
       </c>
-      <c r="M33" s="76" t="s">
+      <c r="M33" s="98" t="s">
         <v>6</v>
       </c>
-      <c r="N33" s="77"/>
+      <c r="N33" s="99"/>
       <c r="O33" s="41">
         <v>3.8319643020864191</v>
       </c>
@@ -5285,10 +5420,10 @@
       </c>
     </row>
     <row r="34" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="76" t="s">
+      <c r="A34" s="98" t="s">
         <v>10</v>
       </c>
-      <c r="B34" s="77"/>
+      <c r="B34" s="99"/>
       <c r="C34" s="28">
         <v>87.268396410214976</v>
       </c>
@@ -5316,10 +5451,10 @@
         <f t="shared" ref="L34:L43" si="7">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C34:I34)&amp;","</f>
         <v xml:space="preserve">    87.268396410215, 87.2564283986868, 87.8221063041704, 87.6807264423516, 87.1448793671852, 74.9765678865158, 46.4175473948824,</v>
       </c>
-      <c r="M34" s="76" t="s">
+      <c r="M34" s="98" t="s">
         <v>10</v>
       </c>
-      <c r="N34" s="77"/>
+      <c r="N34" s="99"/>
       <c r="O34" s="28">
         <v>2.610595868561878</v>
       </c>
@@ -5347,35 +5482,35 @@
       </c>
     </row>
     <row r="35" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="76" t="s">
+      <c r="A35" s="98" t="s">
         <v>12</v>
       </c>
-      <c r="B35" s="80"/>
-      <c r="C35" s="80"/>
-      <c r="D35" s="80"/>
-      <c r="E35" s="80"/>
-      <c r="F35" s="80"/>
-      <c r="G35" s="80"/>
-      <c r="H35" s="80"/>
-      <c r="I35" s="77"/>
+      <c r="B35" s="107"/>
+      <c r="C35" s="107"/>
+      <c r="D35" s="107"/>
+      <c r="E35" s="107"/>
+      <c r="F35" s="107"/>
+      <c r="G35" s="107"/>
+      <c r="H35" s="107"/>
+      <c r="I35" s="99"/>
       <c r="J35" s="44"/>
       <c r="K35" s="44"/>
       <c r="L35" s="1"/>
-      <c r="M35" s="76" t="s">
+      <c r="M35" s="98" t="s">
         <v>12</v>
       </c>
-      <c r="N35" s="80"/>
-      <c r="O35" s="80"/>
-      <c r="P35" s="80"/>
-      <c r="Q35" s="80"/>
-      <c r="R35" s="80"/>
-      <c r="S35" s="80"/>
-      <c r="T35" s="80"/>
-      <c r="U35" s="77"/>
+      <c r="N35" s="107"/>
+      <c r="O35" s="107"/>
+      <c r="P35" s="107"/>
+      <c r="Q35" s="107"/>
+      <c r="R35" s="107"/>
+      <c r="S35" s="107"/>
+      <c r="T35" s="107"/>
+      <c r="U35" s="99"/>
       <c r="V35" s="1"/>
     </row>
     <row r="36" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="78" t="s">
+      <c r="A36" s="100" t="s">
         <v>11</v>
       </c>
       <c r="B36" s="9" t="s">
@@ -5408,7 +5543,7 @@
         <f t="shared" si="7"/>
         <v xml:space="preserve">    92.9756945134422, 91.3636137491543, 90.0940179611611, 85.3777379183925, 79.2681590490105, 60.5212165139937, 42.0544488066562,</v>
       </c>
-      <c r="M36" s="78" t="s">
+      <c r="M36" s="100" t="s">
         <v>11</v>
       </c>
       <c r="N36" s="9" t="s">
@@ -5441,7 +5576,7 @@
       </c>
     </row>
     <row r="37" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="94"/>
+      <c r="A37" s="105"/>
       <c r="B37" s="9" t="s">
         <v>14</v>
       </c>
@@ -5472,7 +5607,7 @@
         <f t="shared" si="7"/>
         <v xml:space="preserve">    92.311293413261, 92.3335217568065, 91.3813575229196, 88.560101371957, 87.2789917059986, 75.3878970556703, 47.4787379071753,</v>
       </c>
-      <c r="M37" s="94"/>
+      <c r="M37" s="105"/>
       <c r="N37" s="9" t="s">
         <v>14</v>
       </c>
@@ -5503,7 +5638,7 @@
       </c>
     </row>
     <row r="38" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="94"/>
+      <c r="A38" s="105"/>
       <c r="B38" s="9" t="s">
         <v>17</v>
       </c>
@@ -5531,7 +5666,7 @@
       <c r="J38" s="44"/>
       <c r="K38" s="44"/>
       <c r="L38" s="1"/>
-      <c r="M38" s="94"/>
+      <c r="M38" s="105"/>
       <c r="N38" s="9" t="s">
         <v>17</v>
       </c>
@@ -5559,7 +5694,7 @@
       <c r="V38" s="1"/>
     </row>
     <row r="39" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="94"/>
+      <c r="A39" s="105"/>
       <c r="B39" s="9" t="s">
         <v>18</v>
       </c>
@@ -5587,7 +5722,7 @@
       <c r="J39" s="44"/>
       <c r="K39" s="44"/>
       <c r="L39" s="1"/>
-      <c r="M39" s="94"/>
+      <c r="M39" s="105"/>
       <c r="N39" s="9" t="s">
         <v>18</v>
       </c>
@@ -5615,7 +5750,7 @@
       <c r="V39" s="1"/>
     </row>
     <row r="40" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="94"/>
+      <c r="A40" s="105"/>
       <c r="B40" s="9" t="s">
         <v>15</v>
       </c>
@@ -5646,7 +5781,7 @@
         <f t="shared" si="7"/>
         <v xml:space="preserve">    92.9883867741658, 92.0506160293868, 90.7196986761964, 88.1856869456335, 83.275334389556, 64.6854019552345, 51.0690469748012,</v>
       </c>
-      <c r="M40" s="94"/>
+      <c r="M40" s="105"/>
       <c r="N40" s="9" t="s">
         <v>15</v>
       </c>
@@ -5674,7 +5809,7 @@
       <c r="V40" s="1"/>
     </row>
     <row r="41" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="94"/>
+      <c r="A41" s="105"/>
       <c r="B41" s="9" t="s">
         <v>25</v>
       </c>
@@ -5702,7 +5837,7 @@
       <c r="J41" s="44"/>
       <c r="K41" s="44"/>
       <c r="L41" s="1"/>
-      <c r="M41" s="94"/>
+      <c r="M41" s="105"/>
       <c r="N41" s="9" t="s">
         <v>25</v>
       </c>
@@ -5730,7 +5865,7 @@
       <c r="V41" s="1"/>
     </row>
     <row r="42" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="94"/>
+      <c r="A42" s="105"/>
       <c r="B42" s="9" t="s">
         <v>19</v>
       </c>
@@ -5758,7 +5893,7 @@
       <c r="J42" s="44"/>
       <c r="K42" s="44"/>
       <c r="L42" s="1"/>
-      <c r="M42" s="94"/>
+      <c r="M42" s="105"/>
       <c r="N42" s="9" t="s">
         <v>19</v>
       </c>
@@ -5786,7 +5921,7 @@
       <c r="V42" s="1"/>
     </row>
     <row r="43" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="94"/>
+      <c r="A43" s="105"/>
       <c r="B43" s="9" t="s">
         <v>16</v>
       </c>
@@ -5817,7 +5952,7 @@
         <f t="shared" si="7"/>
         <v xml:space="preserve">    87.2876347990493, 86.8786967506627, 87.0833631484665, 87.3002948979049, 86.5274318222157, 75.6891287758489, 46.8869070740948,</v>
       </c>
-      <c r="M43" s="94"/>
+      <c r="M43" s="105"/>
       <c r="N43" s="9" t="s">
         <v>16</v>
       </c>
@@ -5845,7 +5980,7 @@
       <c r="V43" s="1"/>
     </row>
     <row r="44" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="95"/>
+      <c r="A44" s="106"/>
       <c r="B44" s="9" t="s">
         <v>26</v>
       </c>
@@ -5873,7 +6008,7 @@
       <c r="J44" s="44"/>
       <c r="K44" s="44"/>
       <c r="L44" s="1"/>
-      <c r="M44" s="95"/>
+      <c r="M44" s="106"/>
       <c r="N44" s="9" t="s">
         <v>26</v>
       </c>
@@ -5901,38 +6036,38 @@
       <c r="V44" s="1"/>
     </row>
     <row r="45" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="76" t="s">
+      <c r="A45" s="98" t="s">
         <v>20</v>
       </c>
-      <c r="B45" s="80"/>
-      <c r="C45" s="81"/>
-      <c r="D45" s="81"/>
-      <c r="E45" s="81"/>
-      <c r="F45" s="81"/>
-      <c r="G45" s="81"/>
-      <c r="H45" s="81"/>
-      <c r="I45" s="82"/>
+      <c r="B45" s="107"/>
+      <c r="C45" s="108"/>
+      <c r="D45" s="108"/>
+      <c r="E45" s="108"/>
+      <c r="F45" s="108"/>
+      <c r="G45" s="108"/>
+      <c r="H45" s="108"/>
+      <c r="I45" s="109"/>
       <c r="J45" s="44"/>
       <c r="K45" s="44"/>
       <c r="L45" s="1"/>
-      <c r="M45" s="76" t="s">
+      <c r="M45" s="98" t="s">
         <v>20</v>
       </c>
-      <c r="N45" s="80"/>
-      <c r="O45" s="81"/>
-      <c r="P45" s="81"/>
-      <c r="Q45" s="81"/>
-      <c r="R45" s="81"/>
-      <c r="S45" s="81"/>
-      <c r="T45" s="81"/>
-      <c r="U45" s="82"/>
+      <c r="N45" s="107"/>
+      <c r="O45" s="108"/>
+      <c r="P45" s="108"/>
+      <c r="Q45" s="108"/>
+      <c r="R45" s="108"/>
+      <c r="S45" s="108"/>
+      <c r="T45" s="108"/>
+      <c r="U45" s="109"/>
       <c r="V45" s="1"/>
     </row>
     <row r="46" spans="1:22" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="76" t="s">
+      <c r="A46" s="98" t="s">
         <v>7</v>
       </c>
-      <c r="B46" s="77"/>
+      <c r="B46" s="99"/>
       <c r="C46" s="60">
         <v>93.403798109785029</v>
       </c>
@@ -5960,10 +6095,10 @@
         <f t="shared" ref="L46:L48" si="8">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C46:I46)&amp;","</f>
         <v xml:space="preserve">    93.403798109785, 91.5170070049374, 89.7498804626893, 83.9973095811923, 74.3949629659869, 58.0955824704985, 44.4348127062073,</v>
       </c>
-      <c r="M46" s="76" t="s">
+      <c r="M46" s="98" t="s">
         <v>7</v>
       </c>
-      <c r="N46" s="77"/>
+      <c r="N46" s="99"/>
       <c r="O46" s="60">
         <v>3.9553866501853321</v>
       </c>
@@ -5991,10 +6126,10 @@
       </c>
     </row>
     <row r="47" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="76" t="s">
+      <c r="A47" s="98" t="s">
         <v>8</v>
       </c>
-      <c r="B47" s="77"/>
+      <c r="B47" s="99"/>
       <c r="C47" s="63">
         <v>92.778947400409621</v>
       </c>
@@ -6022,10 +6157,10 @@
         <f t="shared" si="8"/>
         <v xml:space="preserve">    92.7789474004096, 91.4503689963737, 89.8794809545421, 84.748756470337, 75.6276087825805, 58.3002656651169, 48.5841064376263,</v>
       </c>
-      <c r="M47" s="76" t="s">
+      <c r="M47" s="98" t="s">
         <v>8</v>
       </c>
-      <c r="N47" s="77"/>
+      <c r="N47" s="99"/>
       <c r="O47" s="63">
         <v>4.3743918396131134</v>
       </c>
@@ -6053,10 +6188,10 @@
       </c>
     </row>
     <row r="48" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="76" t="s">
+      <c r="A48" s="98" t="s">
         <v>21</v>
       </c>
-      <c r="B48" s="77"/>
+      <c r="B48" s="99"/>
       <c r="C48" s="63">
         <v>92.492055194421354</v>
       </c>
@@ -6084,10 +6219,10 @@
         <f t="shared" si="8"/>
         <v xml:space="preserve">    92.4920551944214, 91.055738083246, 89.2412648877623, 82.7136018096434, 73.1336770487749, 56.2292059013312, 43.695396708103,</v>
       </c>
-      <c r="M48" s="76" t="s">
+      <c r="M48" s="98" t="s">
         <v>21</v>
       </c>
-      <c r="N48" s="77"/>
+      <c r="N48" s="99"/>
       <c r="O48" s="63">
         <v>4.0986250609792014</v>
       </c>
@@ -6115,94 +6250,66 @@
       </c>
     </row>
     <row r="49" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="76" t="s">
+      <c r="A49" s="98" t="s">
         <v>22</v>
       </c>
-      <c r="B49" s="77"/>
-      <c r="C49" s="65">
-        <v>92.657174075741665</v>
-      </c>
-      <c r="D49" s="66">
-        <v>91.208050814372243</v>
-      </c>
-      <c r="E49" s="66">
-        <v>89.170455678091372</v>
-      </c>
-      <c r="F49" s="66">
-        <v>84.474616062770011</v>
-      </c>
-      <c r="G49" s="66">
-        <v>75.066668593640316</v>
-      </c>
-      <c r="H49" s="66">
-        <v>58.520340993368222</v>
-      </c>
-      <c r="I49" s="67">
-        <v>44.786141592049418</v>
-      </c>
+      <c r="B49" s="99"/>
+      <c r="C49" s="65"/>
+      <c r="D49" s="66"/>
+      <c r="E49" s="66"/>
+      <c r="F49" s="66"/>
+      <c r="G49" s="66"/>
+      <c r="H49" s="66"/>
+      <c r="I49" s="67"/>
       <c r="J49" s="51"/>
       <c r="K49" s="51"/>
       <c r="L49" s="50"/>
-      <c r="M49" s="76" t="s">
+      <c r="M49" s="98" t="s">
         <v>22</v>
       </c>
-      <c r="N49" s="77"/>
-      <c r="O49" s="65">
-        <v>4.2589004392769629</v>
-      </c>
-      <c r="P49" s="66">
-        <v>4.8517186601265534</v>
-      </c>
-      <c r="Q49" s="66">
-        <v>5.6717673083496472</v>
-      </c>
-      <c r="R49" s="66">
-        <v>5.3079507961921779</v>
-      </c>
-      <c r="S49" s="66">
-        <v>7.7884705615072454</v>
-      </c>
-      <c r="T49" s="66">
-        <v>10.595563377926201</v>
-      </c>
-      <c r="U49" s="67">
-        <v>10.945843294214329</v>
-      </c>
+      <c r="N49" s="99"/>
+      <c r="O49" s="65"/>
+      <c r="P49" s="66"/>
+      <c r="Q49" s="66"/>
+      <c r="R49" s="66"/>
+      <c r="S49" s="66"/>
+      <c r="T49" s="66"/>
+      <c r="U49" s="67"/>
       <c r="V49" s="1"/>
     </row>
     <row r="50" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="76" t="s">
+      <c r="A50" s="98" t="s">
         <v>23</v>
       </c>
-      <c r="B50" s="80"/>
-      <c r="C50" s="81"/>
-      <c r="D50" s="81"/>
-      <c r="E50" s="81"/>
-      <c r="F50" s="81"/>
-      <c r="G50" s="81"/>
-      <c r="H50" s="81"/>
-      <c r="I50" s="82"/>
+      <c r="B50" s="107"/>
+      <c r="C50" s="108"/>
+      <c r="D50" s="108"/>
+      <c r="E50" s="108"/>
+      <c r="F50" s="108"/>
+      <c r="G50" s="108"/>
+      <c r="H50" s="108"/>
+      <c r="I50" s="109"/>
       <c r="J50" s="44"/>
       <c r="K50" s="44"/>
       <c r="L50" s="1"/>
-      <c r="M50" s="76" t="s">
+      <c r="M50" s="98" t="s">
         <v>23</v>
       </c>
-      <c r="N50" s="80"/>
-      <c r="O50" s="81"/>
-      <c r="P50" s="81"/>
-      <c r="Q50" s="81"/>
-      <c r="R50" s="81"/>
-      <c r="S50" s="81"/>
-      <c r="T50" s="81"/>
-      <c r="U50" s="82"/>
+      <c r="N50" s="107"/>
+      <c r="O50" s="108"/>
+      <c r="P50" s="108"/>
+      <c r="Q50" s="108"/>
+      <c r="R50" s="108"/>
+      <c r="S50" s="108"/>
+      <c r="T50" s="108"/>
+      <c r="U50" s="109"/>
       <c r="V50" s="1"/>
     </row>
     <row r="51" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="76" t="s">
+      <c r="A51" s="98" t="s">
         <v>7</v>
       </c>
-      <c r="B51" s="77"/>
+      <c r="B51" s="99"/>
       <c r="C51" s="60">
         <v>92.603769819293618</v>
       </c>
@@ -6230,10 +6337,10 @@
         <f t="shared" ref="L51:L53" si="9">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C51:I51)&amp;","</f>
         <v xml:space="preserve">    92.6037698192936, 91.4319470683528, 90.3907950429996, 86.7895628282223, 80.6155540330522, 56.6095785531339, 41.2792806229243,</v>
       </c>
-      <c r="M51" s="76" t="s">
+      <c r="M51" s="98" t="s">
         <v>7</v>
       </c>
-      <c r="N51" s="77"/>
+      <c r="N51" s="99"/>
       <c r="O51" s="60">
         <v>3.708759274801273</v>
       </c>
@@ -6261,10 +6368,10 @@
       </c>
     </row>
     <row r="52" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="78" t="s">
+      <c r="A52" s="100" t="s">
         <v>8</v>
       </c>
-      <c r="B52" s="79"/>
+      <c r="B52" s="101"/>
       <c r="C52" s="63">
         <v>91.377634404932721</v>
       </c>
@@ -6292,10 +6399,10 @@
         <f t="shared" si="9"/>
         <v xml:space="preserve">    91.3776344049327, 90.4053733332451, 89.3714803083327, 87.6098986263952, 85.5372307015107, 70.9307087454215, 44.0973262328065,</v>
       </c>
-      <c r="M52" s="76" t="s">
+      <c r="M52" s="98" t="s">
         <v>8</v>
       </c>
-      <c r="N52" s="77"/>
+      <c r="N52" s="99"/>
       <c r="O52" s="63">
         <v>3.5684194304484111</v>
       </c>
@@ -6323,10 +6430,10 @@
       </c>
     </row>
     <row r="53" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="76" t="s">
+      <c r="A53" s="98" t="s">
         <v>21</v>
       </c>
-      <c r="B53" s="77"/>
+      <c r="B53" s="99"/>
       <c r="C53" s="63">
         <v>92.603715202692385</v>
       </c>
@@ -6354,10 +6461,10 @@
         <f t="shared" si="9"/>
         <v xml:space="preserve">    92.6037152026924, 91.4849975027203, 90.6301712993249, 85.3420346970645, 78.2086079443082, 58.1887672547126, 45.4689195625762,</v>
       </c>
-      <c r="M53" s="76" t="s">
+      <c r="M53" s="98" t="s">
         <v>21</v>
       </c>
-      <c r="N53" s="77"/>
+      <c r="N53" s="99"/>
       <c r="O53" s="63">
         <v>4.0727132923350373</v>
       </c>
@@ -6385,217 +6492,273 @@
       </c>
     </row>
     <row r="54" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="76" t="s">
+      <c r="A54" s="98" t="s">
         <v>22</v>
       </c>
-      <c r="B54" s="77"/>
-      <c r="C54" s="65">
-        <v>92.692685851985146</v>
-      </c>
-      <c r="D54" s="66">
-        <v>91.028008929063319</v>
-      </c>
-      <c r="E54" s="66">
-        <v>89.101176850288709</v>
-      </c>
-      <c r="F54" s="66">
-        <v>84.121695311135312</v>
-      </c>
-      <c r="G54" s="66">
-        <v>75.514536359946376</v>
-      </c>
-      <c r="H54" s="66">
-        <v>58.551851548300363</v>
-      </c>
-      <c r="I54" s="67">
-        <v>43.528644478603361</v>
-      </c>
+      <c r="B54" s="99"/>
+      <c r="C54" s="65"/>
+      <c r="D54" s="66"/>
+      <c r="E54" s="66"/>
+      <c r="F54" s="66"/>
+      <c r="G54" s="66"/>
+      <c r="H54" s="66"/>
+      <c r="I54" s="67"/>
       <c r="J54" s="44"/>
       <c r="K54" s="44"/>
       <c r="L54" s="1"/>
-      <c r="M54" s="76" t="s">
+      <c r="M54" s="98" t="s">
         <v>22</v>
       </c>
-      <c r="N54" s="77"/>
-      <c r="O54" s="65">
-        <v>4.3508377678439567</v>
-      </c>
-      <c r="P54" s="66">
-        <v>5.1455197984597092</v>
-      </c>
-      <c r="Q54" s="66">
-        <v>5.0319449257944937</v>
-      </c>
-      <c r="R54" s="66">
-        <v>5.4881092234662896</v>
-      </c>
-      <c r="S54" s="66">
-        <v>8.3963724907401343</v>
-      </c>
-      <c r="T54" s="66">
-        <v>11.26477476806841</v>
-      </c>
-      <c r="U54" s="67">
-        <v>10.478269846537319</v>
-      </c>
+      <c r="N54" s="99"/>
+      <c r="O54" s="65"/>
+      <c r="P54" s="66"/>
+      <c r="Q54" s="66"/>
+      <c r="R54" s="66"/>
+      <c r="S54" s="66"/>
+      <c r="T54" s="66"/>
+      <c r="U54" s="67"/>
       <c r="V54" s="1"/>
     </row>
     <row r="55" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="76" t="s">
+      <c r="A55" s="98" t="s">
         <v>24</v>
       </c>
-      <c r="B55" s="80"/>
-      <c r="C55" s="81"/>
-      <c r="D55" s="81"/>
-      <c r="E55" s="81"/>
-      <c r="F55" s="81"/>
-      <c r="G55" s="81"/>
-      <c r="H55" s="81"/>
-      <c r="I55" s="82"/>
+      <c r="B55" s="107"/>
+      <c r="C55" s="108"/>
+      <c r="D55" s="108"/>
+      <c r="E55" s="108"/>
+      <c r="F55" s="108"/>
+      <c r="G55" s="108"/>
+      <c r="H55" s="108"/>
+      <c r="I55" s="109"/>
       <c r="J55" s="44"/>
       <c r="K55" s="44"/>
       <c r="L55" s="1"/>
-      <c r="M55" s="76" t="s">
+      <c r="M55" s="98" t="s">
         <v>23</v>
       </c>
-      <c r="N55" s="80"/>
-      <c r="O55" s="81"/>
-      <c r="P55" s="81"/>
-      <c r="Q55" s="81"/>
-      <c r="R55" s="81"/>
-      <c r="S55" s="81"/>
-      <c r="T55" s="81"/>
-      <c r="U55" s="82"/>
+      <c r="N55" s="107"/>
+      <c r="O55" s="108"/>
+      <c r="P55" s="108"/>
+      <c r="Q55" s="108"/>
+      <c r="R55" s="108"/>
+      <c r="S55" s="108"/>
+      <c r="T55" s="108"/>
+      <c r="U55" s="109"/>
       <c r="V55" s="1"/>
     </row>
     <row r="56" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="76" t="s">
+      <c r="A56" s="98" t="s">
         <v>7</v>
       </c>
-      <c r="B56" s="77"/>
-      <c r="C56" s="60"/>
-      <c r="D56" s="61"/>
-      <c r="E56" s="61"/>
-      <c r="F56" s="61"/>
-      <c r="G56" s="61"/>
-      <c r="H56" s="61"/>
-      <c r="I56" s="62"/>
+      <c r="B56" s="99"/>
+      <c r="C56">
+        <v>92.331949706603581</v>
+      </c>
+      <c r="D56">
+        <v>90.788055458144598</v>
+      </c>
+      <c r="E56">
+        <v>90.424281694963014</v>
+      </c>
+      <c r="F56">
+        <v>87.657631835350699</v>
+      </c>
+      <c r="G56">
+        <v>82.413088603676925</v>
+      </c>
+      <c r="H56">
+        <v>60.275828584147241</v>
+      </c>
+      <c r="I56">
+        <v>42.838428313025517</v>
+      </c>
       <c r="J56" s="44"/>
       <c r="K56" s="44"/>
       <c r="L56" s="1" t="str">
         <f t="shared" ref="L56:L58" si="11">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C56:I56)&amp;","</f>
-        <v xml:space="preserve">    ,</v>
-      </c>
-      <c r="M56" s="76" t="s">
+        <v xml:space="preserve">    92.3319497066036, 90.7880554581446, 90.424281694963, 87.6576318353507, 82.4130886036769, 60.2758285841472, 42.8384283130255,</v>
+      </c>
+      <c r="M56" s="98" t="s">
         <v>7</v>
       </c>
-      <c r="N56" s="77"/>
-      <c r="O56" s="60"/>
-      <c r="P56" s="61"/>
-      <c r="Q56" s="61"/>
-      <c r="R56" s="61"/>
-      <c r="S56" s="61"/>
-      <c r="T56" s="61"/>
-      <c r="U56" s="62"/>
+      <c r="N56" s="99"/>
+      <c r="O56">
+        <v>3.7810235401562768</v>
+      </c>
+      <c r="P56">
+        <v>3.610745427801767</v>
+      </c>
+      <c r="Q56">
+        <v>3.6319421257152249</v>
+      </c>
+      <c r="R56">
+        <v>3.468713140298441</v>
+      </c>
+      <c r="S56">
+        <v>5.1645865648549893</v>
+      </c>
+      <c r="T56">
+        <v>9.2083309434320899</v>
+      </c>
+      <c r="U56">
+        <v>6.8001571811797312</v>
+      </c>
       <c r="V56" s="1" t="str">
         <f t="shared" ref="V56:V58" si="12">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,O56:U56)&amp;","</f>
-        <v xml:space="preserve">    ,</v>
+        <v xml:space="preserve">    3.78102354015628, 3.61074542780177, 3.63194212571522, 3.46871314029844, 5.16458656485499, 9.20833094343209, 6.80015718117973,</v>
       </c>
     </row>
     <row r="57" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="78" t="s">
+      <c r="A57" s="100" t="s">
         <v>8</v>
       </c>
-      <c r="B57" s="79"/>
-      <c r="C57" s="63"/>
-      <c r="D57" s="1"/>
-      <c r="E57" s="1"/>
-      <c r="F57" s="1"/>
-      <c r="G57" s="1"/>
-      <c r="H57" s="1"/>
-      <c r="I57" s="64"/>
+      <c r="B57" s="101"/>
+      <c r="C57">
+        <v>88.993366976652652</v>
+      </c>
+      <c r="D57">
+        <v>87.428157448676032</v>
+      </c>
+      <c r="E57">
+        <v>87.491367457892537</v>
+      </c>
+      <c r="F57">
+        <v>87.036181848509671</v>
+      </c>
+      <c r="G57">
+        <v>84.734260989341792</v>
+      </c>
+      <c r="H57">
+        <v>69.323558886375409</v>
+      </c>
+      <c r="I57">
+        <v>44.224261286068383</v>
+      </c>
       <c r="J57" s="44"/>
       <c r="K57" s="44"/>
       <c r="L57" s="1" t="str">
         <f t="shared" si="11"/>
-        <v xml:space="preserve">    ,</v>
-      </c>
-      <c r="M57" s="76" t="s">
+        <v xml:space="preserve">    88.9933669766527, 87.428157448676, 87.4913674578925, 87.0361818485097, 84.7342609893418, 69.3235588863754, 44.2242612860684,</v>
+      </c>
+      <c r="M57" s="98" t="s">
         <v>8</v>
       </c>
-      <c r="N57" s="77"/>
-      <c r="O57" s="63"/>
-      <c r="P57" s="1"/>
-      <c r="Q57" s="1"/>
-      <c r="R57" s="1"/>
-      <c r="S57" s="1"/>
-      <c r="T57" s="1"/>
-      <c r="U57" s="64"/>
+      <c r="N57" s="99"/>
+      <c r="O57">
+        <v>2.565679873764509</v>
+      </c>
+      <c r="P57">
+        <v>2.352323010993262</v>
+      </c>
+      <c r="Q57">
+        <v>2.474795319702475</v>
+      </c>
+      <c r="R57">
+        <v>2.2135938860767999</v>
+      </c>
+      <c r="S57">
+        <v>2.905191666743812</v>
+      </c>
+      <c r="T57">
+        <v>4.0884722151131134</v>
+      </c>
+      <c r="U57">
+        <v>3.2519858911505728</v>
+      </c>
       <c r="V57" s="1" t="str">
         <f t="shared" si="12"/>
-        <v xml:space="preserve">    ,</v>
+        <v xml:space="preserve">    2.56567987376451, 2.35232301099326, 2.47479531970248, 2.2135938860768, 2.90519166674381, 4.08847221511311, 3.25198589115057,</v>
       </c>
     </row>
     <row r="58" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="76" t="s">
+      <c r="A58" s="98" t="s">
         <v>21</v>
       </c>
-      <c r="B58" s="77"/>
-      <c r="C58" s="63"/>
-      <c r="D58" s="1"/>
-      <c r="E58" s="1"/>
-      <c r="F58" s="1"/>
-      <c r="G58" s="1"/>
-      <c r="H58" s="1"/>
-      <c r="I58" s="64"/>
+      <c r="B58" s="99"/>
+      <c r="C58">
+        <v>93.055308133932627</v>
+      </c>
+      <c r="D58">
+        <v>91.528943714001898</v>
+      </c>
+      <c r="E58">
+        <v>89.882638987004555</v>
+      </c>
+      <c r="F58">
+        <v>84.674810173177292</v>
+      </c>
+      <c r="G58">
+        <v>75.916110561101704</v>
+      </c>
+      <c r="H58">
+        <v>56.764200964537181</v>
+      </c>
+      <c r="I58">
+        <v>44.299590031737637</v>
+      </c>
       <c r="J58" s="44"/>
       <c r="K58" s="44"/>
       <c r="L58" s="1" t="str">
         <f t="shared" si="11"/>
-        <v xml:space="preserve">    ,</v>
-      </c>
-      <c r="M58" s="76" t="s">
+        <v xml:space="preserve">    93.0553081339326, 91.5289437140019, 89.8826389870046, 84.6748101731773, 75.9161105611017, 56.7642009645372, 44.2995900317376,</v>
+      </c>
+      <c r="M58" s="98" t="s">
         <v>21</v>
       </c>
-      <c r="N58" s="77"/>
-      <c r="O58" s="63"/>
-      <c r="P58" s="1"/>
-      <c r="Q58" s="1"/>
-      <c r="R58" s="1"/>
-      <c r="S58" s="1"/>
-      <c r="T58" s="1"/>
-      <c r="U58" s="64"/>
+      <c r="N58" s="99"/>
+      <c r="O58">
+        <v>3.8419168644869521</v>
+      </c>
+      <c r="P58">
+        <v>4.1300496687589057</v>
+      </c>
+      <c r="Q58">
+        <v>4.9130914433578488</v>
+      </c>
+      <c r="R58">
+        <v>5.461364324318545</v>
+      </c>
+      <c r="S58">
+        <v>8.3897175895135803</v>
+      </c>
+      <c r="T58">
+        <v>11.227211743834159</v>
+      </c>
+      <c r="U58">
+        <v>9.9814657114806593</v>
+      </c>
       <c r="V58" s="1" t="str">
         <f t="shared" si="12"/>
-        <v xml:space="preserve">    ,</v>
+        <v xml:space="preserve">    3.84191686448695, 4.13004966875891, 4.91309144335785, 5.46136432431855, 8.38971758951358, 11.2272117438342, 9.98146571148066,</v>
       </c>
     </row>
     <row r="59" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="76" t="s">
+      <c r="A59" s="98" t="s">
         <v>22</v>
       </c>
-      <c r="B59" s="77"/>
-      <c r="C59" s="65"/>
-      <c r="D59" s="66"/>
-      <c r="E59" s="66"/>
-      <c r="F59" s="66"/>
-      <c r="G59" s="66"/>
-      <c r="H59" s="66"/>
-      <c r="I59" s="67"/>
+      <c r="B59" s="99"/>
+      <c r="C59" s="92"/>
+      <c r="D59" s="93"/>
+      <c r="E59" s="93"/>
+      <c r="F59" s="93"/>
+      <c r="G59" s="93"/>
+      <c r="H59" s="93"/>
+      <c r="I59" s="94"/>
       <c r="J59" s="44"/>
       <c r="K59" s="44"/>
       <c r="L59" s="1"/>
-      <c r="M59" s="76" t="s">
+      <c r="M59" s="98" t="s">
         <v>22</v>
       </c>
-      <c r="N59" s="77"/>
-      <c r="O59" s="65"/>
-      <c r="P59" s="66"/>
-      <c r="Q59" s="66"/>
-      <c r="R59" s="66"/>
-      <c r="S59" s="66"/>
-      <c r="T59" s="66"/>
-      <c r="U59" s="67"/>
+      <c r="N59" s="99"/>
+      <c r="O59" s="92"/>
+      <c r="P59" s="93"/>
+      <c r="Q59" s="93"/>
+      <c r="R59" s="93"/>
+      <c r="S59" s="93"/>
+      <c r="T59" s="93"/>
+      <c r="U59" s="94"/>
       <c r="V59" s="1"/>
     </row>
     <row r="60" spans="1:22" ht="15" x14ac:dyDescent="0.2">
@@ -6696,8 +6859,8 @@
     <mergeCell ref="M58:N58"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="C6:I6">
-    <cfRule type="colorScale" priority="16">
+  <conditionalFormatting sqref="C2:I4 C6:I14 C16:I19 C21:I24 C26:I29">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6707,7 +6870,19 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="17">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C6:I6">
+    <cfRule type="colorScale" priority="19">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="20">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6719,7 +6894,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C6:I14 C2:I4 C16:I19 C21:I24 C26:I29">
-    <cfRule type="colorScale" priority="11">
+    <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6731,73 +6906,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C7:I7">
-    <cfRule type="colorScale" priority="18">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="19">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C9:I9">
-    <cfRule type="colorScale" priority="20">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
     <cfRule type="colorScale" priority="21">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C10:I11">
-    <cfRule type="colorScale" priority="14">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="15">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C12:I12">
-    <cfRule type="colorScale" priority="23">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6818,8 +6927,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C13:I14">
-    <cfRule type="colorScale" priority="12">
+  <conditionalFormatting sqref="C9:I9">
+    <cfRule type="colorScale" priority="24">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6829,7 +6938,73 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="13">
+    <cfRule type="colorScale" priority="23">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C10:I11">
+    <cfRule type="colorScale" priority="17">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C12:I12">
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="25">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C13:I14">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6841,7 +7016,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C16:I18 C2:I4 C8:I8">
-    <cfRule type="colorScale" priority="166">
+    <cfRule type="colorScale" priority="169">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6853,7 +7028,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C16:I18 C2:I4">
-    <cfRule type="colorScale" priority="169">
+    <cfRule type="colorScale" priority="172">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6863,7 +7038,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="173">
+    <cfRule type="colorScale" priority="176">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6875,7 +7050,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C16:I19 C2:I4 C21:I24 C8:I8 C26:I29">
-    <cfRule type="colorScale" priority="177">
+    <cfRule type="colorScale" priority="180">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6887,7 +7062,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C21:I23">
-    <cfRule type="colorScale" priority="38">
+    <cfRule type="colorScale" priority="41">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6897,7 +7072,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="39">
+    <cfRule type="colorScale" priority="42">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6907,7 +7082,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="40">
+    <cfRule type="colorScale" priority="43">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6919,7 +7094,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C26:I28">
-    <cfRule type="colorScale" priority="5">
+    <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6929,7 +7104,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="6">
+    <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6939,7 +7114,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="7">
+    <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6951,7 +7126,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J29">
-    <cfRule type="colorScale" priority="2">
+    <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6963,7 +7138,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J50:J59">
-    <cfRule type="colorScale" priority="35">
+    <cfRule type="colorScale" priority="38">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6975,7 +7150,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:K29">
-    <cfRule type="colorScale" priority="243">
+    <cfRule type="colorScale" priority="246">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6987,36 +7162,6 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J5:K5 C3:K4">
-    <cfRule type="colorScale" priority="110">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="111">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="112">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
     <cfRule type="colorScale" priority="113">
       <colorScale>
         <cfvo type="min"/>
@@ -7047,9 +7192,39 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="116">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="117">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="118">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J19:K20 C2:K4 C16:K18 C21:K23 J5:K15 J24:K25 J29:K29 C26:K28">
-    <cfRule type="colorScale" priority="157">
+    <cfRule type="colorScale" priority="160">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -7071,7 +7246,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="33">
+    <cfRule type="colorScale" priority="39">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -7083,7 +7258,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J55:K59">
-    <cfRule type="colorScale" priority="4">
+    <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -7093,7 +7268,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="3">
+    <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -7105,7 +7280,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K29">
-    <cfRule type="colorScale" priority="1">
+    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -7117,7 +7292,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K50:K59">
-    <cfRule type="colorScale" priority="37">
+    <cfRule type="colorScale" priority="40">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -7135,53 +7310,204 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A38A25A9-7BAB-4662-AC2A-B7F2DABCCE29}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="B1:G12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="7" max="7" width="17.5" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="C1" s="75" t="s">
+    <row r="1" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="B2" s="118" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" s="124"/>
+      <c r="D2" s="121" t="s">
         <v>31</v>
       </c>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="C2" t="s">
+      <c r="E2" s="122"/>
+      <c r="F2" s="122"/>
+      <c r="G2" s="123"/>
+    </row>
+    <row r="3" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="120"/>
+      <c r="C3" s="125"/>
+      <c r="D3" s="83" t="s">
         <v>27</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E3" s="80" t="s">
         <v>28</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F3" s="80" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" s="74" t="s">
+      <c r="G3" s="89" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="90" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="91" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="84">
+        <v>79.040000000000006</v>
+      </c>
+      <c r="E4" s="85">
+        <v>79</v>
+      </c>
+      <c r="F4" s="85">
+        <v>81.27</v>
+      </c>
+      <c r="G4" s="86">
+        <v>77.87</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B5" s="25"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="25"/>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B6" s="25"/>
+      <c r="C6" s="25"/>
+      <c r="D6" s="25"/>
+      <c r="E6" s="25"/>
+      <c r="F6" s="25"/>
+      <c r="G6" s="25"/>
+    </row>
+    <row r="7" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="25"/>
+      <c r="C7" s="25"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="G7" s="25"/>
+    </row>
+    <row r="8" spans="2:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="B8" s="118" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="124"/>
+      <c r="D8" s="121" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" s="122"/>
+      <c r="F8" s="122"/>
+      <c r="G8" s="123"/>
+    </row>
+    <row r="9" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="120"/>
+      <c r="C9" s="125"/>
+      <c r="D9" s="83" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" s="80" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" s="80" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9" s="89" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="B10" s="118" t="s">
         <v>30</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C10" s="76" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" s="74"/>
-      <c r="B4" t="s">
+      <c r="D10" s="74">
+        <v>79.040000000000006</v>
+      </c>
+      <c r="E10" s="75">
+        <v>79</v>
+      </c>
+      <c r="F10" s="75">
+        <v>81.27</v>
+      </c>
+      <c r="G10" s="87">
+        <v>77.87</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="B11" s="119"/>
+      <c r="C11" s="78" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" s="74"/>
-      <c r="B5" t="s">
+      <c r="D11" s="77">
+        <v>80.12</v>
+      </c>
+      <c r="E11" s="25">
+        <v>80.239999999999995</v>
+      </c>
+      <c r="F11" s="25">
+        <v>80</v>
+      </c>
+      <c r="G11" s="79">
+        <v>78.8</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="120"/>
+      <c r="C12" s="89" t="s">
         <v>29</v>
       </c>
+      <c r="D12" s="88">
+        <v>80.78</v>
+      </c>
+      <c r="E12" s="81">
+        <v>78.06</v>
+      </c>
+      <c r="F12" s="81">
+        <v>77.819999999999993</v>
+      </c>
+      <c r="G12" s="82">
+        <v>78.39</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="C1:E1"/>
+  <mergeCells count="5">
+    <mergeCell ref="B10:B12"/>
+    <mergeCell ref="D8:G8"/>
+    <mergeCell ref="D2:G2"/>
+    <mergeCell ref="B2:C3"/>
+    <mergeCell ref="B8:C9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="D4:G4">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D10:G12">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>